--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A69E45F-C359-6142-A3EB-24520F587082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B8DC6A-7377-6048-8D53-180E4675AC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Cookpit" sheetId="1" r:id="rId1"/>
@@ -3026,6 +3026,9 @@
       <c r="B90" t="s">
         <v>10</v>
       </c>
+      <c r="C90" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="E90" s="13">
         <v>46388</v>
       </c>
@@ -3429,6 +3432,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F119" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4221,9 +4225,7 @@
       <c r="B47" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>86</v>
-      </c>
+      <c r="C47" s="2"/>
       <c r="D47" s="4">
         <v>46223</v>
       </c>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B8DC6A-7377-6048-8D53-180E4675AC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D9EE9E-E211-FE42-902A-7F803C864364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="4 - Recursos" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$F$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$F$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Agenda Workshop'!$A$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$Q$55</definedName>
   </definedNames>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="380">
   <si>
     <t>Projeto</t>
   </si>
@@ -1178,6 +1178,9 @@
   </si>
   <si>
     <t>4255 - Ademicon - Projeto 2032</t>
+  </si>
+  <si>
+    <t>3569 - Brasal - Implantação Grow</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1313,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1348,6 +1351,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1652,7 +1658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="64.5" bestFit="1" customWidth="1"/>
@@ -1859,27 +1865,24 @@
     </row>
     <row r="13" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>379</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E13" s="12">
-        <v>46296</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>325</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>83</v>
@@ -1896,53 +1899,55 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="E15" s="12">
         <v>46296</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>376</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>377</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="12"/>
+      <c r="E16" s="12">
+        <v>46296</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>376</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>377</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="12">
-        <v>46296</v>
-      </c>
+      <c r="E17" s="12"/>
     </row>
     <row r="18" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="12">
@@ -1954,10 +1959,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="12">
@@ -1969,10 +1974,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="12">
@@ -1984,10 +1989,10 @@
         <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="12">
@@ -1999,10 +2004,10 @@
         <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="12">
@@ -2014,10 +2019,10 @@
         <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="12">
@@ -2029,32 +2034,32 @@
         <v>14</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="12">
         <v>46296</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="25" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="12">
-        <v>46388</v>
+        <v>46296</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2062,10 +2067,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="12">
@@ -2074,13 +2079,13 @@
     </row>
     <row r="27" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="12">
@@ -2089,40 +2094,40 @@
     </row>
     <row r="28" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>378</v>
+        <v>23</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>377</v>
+        <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="12"/>
+      <c r="E28" s="12">
+        <v>46388</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>24</v>
+        <v>378</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="12">
-        <v>46388</v>
-      </c>
+      <c r="E29" s="12"/>
     </row>
     <row r="30" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="12">
         <v>46388</v>
@@ -2130,12 +2135,14 @@
     </row>
     <row r="31" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="D31" s="2"/>
       <c r="E31" s="12">
         <v>46388</v>
@@ -2143,14 +2150,12 @@
     </row>
     <row r="32" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>94</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="12">
         <v>46388</v>
@@ -2158,13 +2163,13 @@
     </row>
     <row r="33" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="12">
@@ -2173,13 +2178,13 @@
     </row>
     <row r="34" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="12">
@@ -2188,13 +2193,13 @@
     </row>
     <row r="35" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="12">
@@ -2203,31 +2208,28 @@
     </row>
     <row r="36" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="12">
         <v>46388</v>
       </c>
-      <c r="F36" s="15" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="37" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="12">
@@ -2239,17 +2241,20 @@
     </row>
     <row r="38" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="12">
-        <v>46661</v>
+        <v>46388</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2257,9 +2262,11 @@
         <v>34</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="D39" s="2"/>
       <c r="E39" s="12">
         <v>46661</v>
@@ -2270,11 +2277,9 @@
         <v>34</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="12">
         <v>46661</v>
@@ -2285,10 +2290,10 @@
         <v>34</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="12">
@@ -2300,10 +2305,10 @@
         <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="12">
@@ -2315,32 +2320,32 @@
         <v>34</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="12">
         <v>46661</v>
       </c>
-      <c r="F43" s="15" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="44" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D44" s="16"/>
+        <v>158</v>
+      </c>
+      <c r="D44" s="2"/>
       <c r="E44" s="12">
-        <v>46388</v>
+        <v>46661</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2348,7 +2353,7 @@
         <v>36</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>83</v>
@@ -2363,10 +2368,12 @@
         <v>36</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+        <v>15</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D46" s="16"/>
       <c r="E46" s="12">
         <v>46388</v>
       </c>
@@ -2376,11 +2383,9 @@
         <v>36</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>94</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="12">
         <v>46388</v>
@@ -2391,10 +2396,10 @@
         <v>36</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="12">
@@ -2406,10 +2411,10 @@
         <v>36</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="12">
@@ -2421,10 +2426,10 @@
         <v>36</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="12">
@@ -2436,10 +2441,10 @@
         <v>36</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="12">
@@ -2451,9 +2456,11 @@
         <v>36</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="D52" s="2"/>
       <c r="E52" s="12">
         <v>46388</v>
@@ -2464,14 +2471,10 @@
         <v>36</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>372</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
       <c r="E53" s="12">
         <v>46388</v>
       </c>
@@ -2481,12 +2484,14 @@
         <v>36</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D54" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>372</v>
+      </c>
       <c r="E54" s="12">
         <v>46388</v>
       </c>
@@ -2496,10 +2501,10 @@
         <v>36</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="12">
@@ -2511,28 +2516,25 @@
         <v>36</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="12">
         <v>46388</v>
       </c>
-      <c r="F56" s="15" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="57" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="12">
@@ -2544,19 +2546,20 @@
     </row>
     <row r="58" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>164</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="D58" s="2"/>
       <c r="E58" s="12">
         <v>46388</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2564,12 +2567,14 @@
         <v>42</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D59" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="E59" s="12">
         <v>46388</v>
       </c>
@@ -2579,10 +2584,10 @@
         <v>42</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>374</v>
+        <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="12">
@@ -2594,10 +2599,10 @@
         <v>42</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>10</v>
+        <v>374</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="12">
@@ -2609,10 +2614,10 @@
         <v>42</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="12">
@@ -2624,10 +2629,10 @@
         <v>42</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="12">
@@ -2642,25 +2647,22 @@
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="12">
         <v>46388</v>
       </c>
-      <c r="F64" s="15" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="65" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="12">
@@ -2675,16 +2677,17 @@
         <v>42</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>159</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="D66" s="2"/>
       <c r="E66" s="12">
         <v>46388</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2692,19 +2695,16 @@
         <v>42</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>375</v>
+        <v>159</v>
       </c>
       <c r="E67" s="12">
         <v>46388</v>
-      </c>
-      <c r="F67" s="15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2712,12 +2712,19 @@
         <v>42</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>375</v>
+      </c>
       <c r="E68" s="12">
         <v>46388</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2725,7 +2732,7 @@
         <v>42</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2734,15 +2741,14 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>46</v>
-      </c>
-      <c r="B70" t="s">
-        <v>47</v>
-      </c>
-      <c r="C70" t="s">
-        <v>79</v>
-      </c>
+      <c r="A70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
       <c r="E70" s="12">
         <v>46388</v>
       </c>
@@ -2752,10 +2758,10 @@
         <v>46</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C71" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E71" s="12">
         <v>46388</v>
@@ -2766,13 +2772,10 @@
         <v>46</v>
       </c>
       <c r="B72" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C72" t="s">
-        <v>61</v>
-      </c>
-      <c r="D72" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E72" s="12">
         <v>46388</v>
@@ -2783,9 +2786,12 @@
         <v>46</v>
       </c>
       <c r="B73" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C73" t="s">
+        <v>61</v>
+      </c>
+      <c r="D73" t="s">
         <v>64</v>
       </c>
       <c r="E73" s="12">
@@ -2797,10 +2803,10 @@
         <v>46</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="E74" s="12">
         <v>46388</v>
@@ -2811,10 +2817,10 @@
         <v>46</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="E75" s="12">
         <v>46388</v>
@@ -2825,10 +2831,10 @@
         <v>46</v>
       </c>
       <c r="B76" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C76" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E76" s="12">
         <v>46388</v>
@@ -2839,10 +2845,10 @@
         <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C77" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="E77" s="12">
         <v>46388</v>
@@ -2853,10 +2859,10 @@
         <v>46</v>
       </c>
       <c r="B78" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C78" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="E78" s="12">
         <v>46388</v>
@@ -2867,10 +2873,10 @@
         <v>46</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>143</v>
+        <v>61</v>
       </c>
       <c r="E79" s="12">
         <v>46388</v>
@@ -2881,16 +2887,13 @@
         <v>46</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E80" s="12">
         <v>46388</v>
-      </c>
-      <c r="F80" s="15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2898,10 +2901,10 @@
         <v>46</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E81" s="12">
         <v>46388</v>
@@ -2915,10 +2918,10 @@
         <v>46</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E82" s="12">
         <v>46388</v>
@@ -2932,10 +2935,10 @@
         <v>46</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E83" s="12">
         <v>46388</v>
@@ -2946,16 +2949,19 @@
     </row>
     <row r="84" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B84" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>162</v>
-      </c>
-      <c r="E84" s="13">
+        <v>147</v>
+      </c>
+      <c r="E84" s="12">
         <v>46388</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2963,10 +2969,10 @@
         <v>55</v>
       </c>
       <c r="B85" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C85" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E85" s="13">
         <v>46388</v>
@@ -2977,10 +2983,10 @@
         <v>55</v>
       </c>
       <c r="B86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="E86" s="13">
         <v>46388</v>
@@ -2991,7 +2997,10 @@
         <v>55</v>
       </c>
       <c r="B87" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C87" t="s">
+        <v>83</v>
       </c>
       <c r="E87" s="13">
         <v>46388</v>
@@ -3002,7 +3011,7 @@
         <v>55</v>
       </c>
       <c r="B88" t="s">
-        <v>166</v>
+        <v>5</v>
       </c>
       <c r="E88" s="13">
         <v>46388</v>
@@ -3013,7 +3022,7 @@
         <v>55</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="E89" s="13">
         <v>46388</v>
@@ -3024,10 +3033,7 @@
         <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="E90" s="13">
         <v>46388</v>
@@ -3038,16 +3044,13 @@
         <v>55</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
-      </c>
-      <c r="C91" t="s">
-        <v>167</v>
+        <v>10</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="E91" s="13">
         <v>46388</v>
-      </c>
-      <c r="F91" s="15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3058,7 +3061,7 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E92" s="13">
         <v>46388</v>
@@ -3069,16 +3072,19 @@
     </row>
     <row r="93" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B93" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E93" s="13">
-        <v>46631</v>
+        <v>46388</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3086,10 +3092,10 @@
         <v>56</v>
       </c>
       <c r="B94" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="E94" s="13">
         <v>46631</v>
@@ -3100,10 +3106,10 @@
         <v>56</v>
       </c>
       <c r="B95" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>170</v>
+        <v>92</v>
       </c>
       <c r="E95" s="13">
         <v>46631</v>
@@ -3114,10 +3120,10 @@
         <v>56</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>71</v>
+        <v>170</v>
       </c>
       <c r="E96" s="13">
         <v>46631</v>
@@ -3128,10 +3134,10 @@
         <v>56</v>
       </c>
       <c r="B97" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E97" s="13">
         <v>46631</v>
@@ -3142,10 +3148,10 @@
         <v>56</v>
       </c>
       <c r="B98" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="E98" s="13">
         <v>46631</v>
@@ -3156,10 +3162,10 @@
         <v>56</v>
       </c>
       <c r="B99" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="E99" s="13">
         <v>46631</v>
@@ -3170,56 +3176,56 @@
         <v>56</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>122</v>
-      </c>
-      <c r="E100" s="13"/>
+        <v>143</v>
+      </c>
+      <c r="E100" s="13">
+        <v>46631</v>
+      </c>
     </row>
     <row r="101" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>56</v>
       </c>
       <c r="B101" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>131</v>
-      </c>
-      <c r="E101" s="13">
-        <v>46631</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="E101" s="13"/>
     </row>
     <row r="102" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>56</v>
       </c>
       <c r="B102" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C102" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="E102" s="13">
         <v>46631</v>
       </c>
-      <c r="F102" s="15" t="s">
-        <v>370</v>
-      </c>
     </row>
     <row r="103" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C103" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E103" s="13">
         <v>46631</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3227,10 +3233,10 @@
         <v>172</v>
       </c>
       <c r="B104" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>95</v>
+        <v>173</v>
       </c>
       <c r="E104" s="13">
         <v>46631</v>
@@ -3241,10 +3247,10 @@
         <v>172</v>
       </c>
       <c r="B105" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="E105" s="13">
         <v>46631</v>
@@ -3255,10 +3261,10 @@
         <v>172</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E106" s="13">
         <v>46631</v>
@@ -3266,13 +3272,16 @@
     </row>
     <row r="107" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>363</v>
+        <v>172</v>
       </c>
       <c r="B107" t="s">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="C107" t="s">
+        <v>143</v>
       </c>
       <c r="E107" s="13">
-        <v>46296</v>
+        <v>46631</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3280,7 +3289,7 @@
         <v>363</v>
       </c>
       <c r="B108" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E108" s="13">
         <v>46296</v>
@@ -3291,7 +3300,7 @@
         <v>363</v>
       </c>
       <c r="B109" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E109" s="13">
         <v>46296</v>
@@ -3302,10 +3311,7 @@
         <v>363</v>
       </c>
       <c r="B110" t="s">
-        <v>7</v>
-      </c>
-      <c r="C110" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E110" s="13">
         <v>46296</v>
@@ -3316,10 +3322,13 @@
         <v>363</v>
       </c>
       <c r="B111" t="s">
-        <v>41</v>
+        <v>7</v>
+      </c>
+      <c r="C111" t="s">
+        <v>170</v>
       </c>
       <c r="E111" s="13">
-        <v>46569</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3327,7 +3336,7 @@
         <v>363</v>
       </c>
       <c r="B112" t="s">
-        <v>364</v>
+        <v>41</v>
       </c>
       <c r="E112" s="13">
         <v>46569</v>
@@ -3338,7 +3347,7 @@
         <v>363</v>
       </c>
       <c r="B113" t="s">
-        <v>17</v>
+        <v>364</v>
       </c>
       <c r="E113" s="13">
         <v>46569</v>
@@ -3349,10 +3358,7 @@
         <v>363</v>
       </c>
       <c r="B114" t="s">
-        <v>33</v>
-      </c>
-      <c r="C114" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="E114" s="13">
         <v>46569</v>
@@ -3363,10 +3369,10 @@
         <v>363</v>
       </c>
       <c r="B115" t="s">
-        <v>365</v>
+        <v>33</v>
       </c>
       <c r="C115" t="s">
-        <v>366</v>
+        <v>142</v>
       </c>
       <c r="E115" s="13">
         <v>46569</v>
@@ -3374,13 +3380,13 @@
     </row>
     <row r="116" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B116" t="s">
-        <v>35</v>
+        <v>365</v>
       </c>
       <c r="C116" t="s">
-        <v>64</v>
+        <v>366</v>
       </c>
       <c r="E116" s="13">
         <v>46569</v>
@@ -3391,10 +3397,10 @@
         <v>361</v>
       </c>
       <c r="B117" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C117" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="E117" s="13">
         <v>46569</v>
@@ -3405,10 +3411,10 @@
         <v>361</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C118" t="s">
-        <v>362</v>
+        <v>86</v>
       </c>
       <c r="E118" s="13">
         <v>46569</v>
@@ -3419,7 +3425,7 @@
         <v>361</v>
       </c>
       <c r="B119" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C119" t="s">
         <v>362</v>
@@ -3427,12 +3433,24 @@
       <c r="E119" s="13">
         <v>46569</v>
       </c>
-      <c r="F119" s="15" t="s">
-        <v>370</v>
-      </c>
+    </row>
+    <row r="120" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>361</v>
+      </c>
+      <c r="B120" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" t="s">
+        <v>362</v>
+      </c>
+      <c r="E120" s="13">
+        <v>46569</v>
+      </c>
+      <c r="F120" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F119" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D9EE9E-E211-FE42-902A-7F803C864364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABA9643-2C7E-5843-A50E-935CD84D03B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Cookpit" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$F$120</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Agenda Workshop'!$A$1:$E$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$Q$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$Q$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="379">
   <si>
     <t>Projeto</t>
   </si>
@@ -826,9 +826,6 @@
     <t>Graziele Xavier Costa</t>
   </si>
   <si>
-    <t>Henrique Simoes De Souza</t>
-  </si>
-  <si>
     <t>José Tarcisio de Souza Neto</t>
   </si>
   <si>
@@ -1021,9 +1018,6 @@
     <t>guilherme.santo@numenit.com</t>
   </si>
   <si>
-    <t>henrique.souza@numenit.com</t>
-  </si>
-  <si>
     <t>jose.souza@numenit.com</t>
   </si>
   <si>
@@ -1181,6 +1175,9 @@
   </si>
   <si>
     <t>3569 - Brasal - Implantação Grow</t>
+  </si>
+  <si>
+    <t>Guilherme Souza Do Espirito Santo (Consultor Jr.) &lt;guilherme.santo@numenit.com&gt;</t>
   </si>
 </sst>
 </file>
@@ -1677,16 +1674,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1824,7 +1821,7 @@
         <v>46388</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1842,7 +1839,7 @@
         <v>46388</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1860,18 +1857,18 @@
         <v>46388</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>325</v>
+        <v>378</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="12"/>
@@ -1928,10 +1925,10 @@
     </row>
     <row r="17" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>61</v>
@@ -2059,7 +2056,7 @@
         <v>46296</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2109,10 +2106,10 @@
     </row>
     <row r="29" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>61</v>
@@ -2236,7 +2233,7 @@
         <v>46388</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2254,7 +2251,7 @@
         <v>46388</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2345,7 +2342,7 @@
         <v>46661</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2490,7 +2487,7 @@
         <v>152</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E54" s="12">
         <v>46388</v>
@@ -2541,7 +2538,7 @@
         <v>46388</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2559,7 +2556,7 @@
         <v>46388</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2599,7 +2596,7 @@
         <v>42</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>162</v>
@@ -2669,7 +2666,7 @@
         <v>46388</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2687,7 +2684,7 @@
         <v>46388</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2718,13 +2715,13 @@
         <v>152</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E68" s="12">
         <v>46388</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2910,7 +2907,7 @@
         <v>46388</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2927,7 +2924,7 @@
         <v>46388</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2944,7 +2941,7 @@
         <v>46388</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2961,7 +2958,7 @@
         <v>46388</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3067,7 +3064,7 @@
         <v>46388</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3084,7 +3081,7 @@
         <v>46388</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3225,7 +3222,7 @@
         <v>46631</v>
       </c>
       <c r="F103" s="15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3286,7 +3283,7 @@
     </row>
     <row r="108" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B108" t="s">
         <v>35</v>
@@ -3297,7 +3294,7 @@
     </row>
     <row r="109" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B109" t="s">
         <v>5</v>
@@ -3308,7 +3305,7 @@
     </row>
     <row r="110" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -3319,7 +3316,7 @@
     </row>
     <row r="111" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
@@ -3333,7 +3330,7 @@
     </row>
     <row r="112" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B112" t="s">
         <v>41</v>
@@ -3344,10 +3341,10 @@
     </row>
     <row r="113" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B113" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E113" s="13">
         <v>46569</v>
@@ -3355,7 +3352,7 @@
     </row>
     <row r="114" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -3366,7 +3363,7 @@
     </row>
     <row r="115" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B115" t="s">
         <v>33</v>
@@ -3380,13 +3377,13 @@
     </row>
     <row r="116" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" t="s">
         <v>363</v>
       </c>
-      <c r="B116" t="s">
-        <v>365</v>
-      </c>
       <c r="C116" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E116" s="13">
         <v>46569</v>
@@ -3394,7 +3391,7 @@
     </row>
     <row r="117" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B117" t="s">
         <v>35</v>
@@ -3408,7 +3405,7 @@
     </row>
     <row r="118" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B118" t="s">
         <v>5</v>
@@ -3422,13 +3419,13 @@
     </row>
     <row r="119" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B119" t="s">
         <v>6</v>
       </c>
       <c r="C119" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E119" s="13">
         <v>46569</v>
@@ -3436,13 +3433,13 @@
     </row>
     <row r="120" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B120" t="s">
         <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E120" s="13">
         <v>46569</v>
@@ -6139,7 +6136,7 @@
         <v>207</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>14</v>
@@ -6163,7 +6160,7 @@
         <v>207</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>14</v>
@@ -6187,7 +6184,7 @@
         <v>207</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>14</v>
@@ -6211,7 +6208,7 @@
         <v>207</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>14</v>
@@ -6235,7 +6232,7 @@
         <v>207</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>14</v>
@@ -7845,7 +7842,7 @@
         <v>207</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>14</v>
@@ -7869,7 +7866,7 @@
         <v>207</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>14</v>
@@ -7893,7 +7890,7 @@
         <v>207</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>14</v>
@@ -7917,7 +7914,7 @@
         <v>207</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>14</v>
@@ -7941,7 +7938,7 @@
         <v>207</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>14</v>
@@ -8022,7 +8019,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19289A2C-A77A-0743-A158-A32EED5567A2}">
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
@@ -8035,52 +8032,52 @@
         <v>59</v>
       </c>
       <c r="B1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D1" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="J1" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="K1" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="L1" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="G1" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="H1" s="17" t="s">
+      <c r="M1" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="O1" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="N1" s="17" t="s">
+      <c r="P1" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="O1" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="P1" s="17" t="s">
+      <c r="Q1" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="Q1" s="17" t="s">
-        <v>280</v>
-      </c>
       <c r="R1" s="17" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
@@ -8088,10 +8085,10 @@
         <v>239</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
@@ -8099,10 +8096,10 @@
         <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -8110,10 +8107,10 @@
         <v>241</v>
       </c>
       <c r="C4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
@@ -8121,13 +8118,13 @@
         <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
@@ -8135,13 +8132,13 @@
         <v>243</v>
       </c>
       <c r="C6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -8149,13 +8146,13 @@
         <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -8163,10 +8160,10 @@
         <v>245</v>
       </c>
       <c r="C8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
@@ -8174,10 +8171,10 @@
         <v>246</v>
       </c>
       <c r="C9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -8185,16 +8182,16 @@
         <v>247</v>
       </c>
       <c r="C10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -8202,19 +8199,19 @@
         <v>248</v>
       </c>
       <c r="C11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R11" s="14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -8222,13 +8219,13 @@
         <v>249</v>
       </c>
       <c r="C12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -8236,13 +8233,13 @@
         <v>250</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
@@ -8250,24 +8247,24 @@
         <v>251</v>
       </c>
       <c r="C14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>294</v>
+      </c>
+      <c r="C15" t="s">
         <v>295</v>
       </c>
-      <c r="C15" t="s">
-        <v>296</v>
-      </c>
       <c r="E15" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -8275,10 +8272,10 @@
         <v>252</v>
       </c>
       <c r="C16" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
@@ -8286,24 +8283,24 @@
         <v>253</v>
       </c>
       <c r="C17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" t="s">
         <v>299</v>
       </c>
-      <c r="C18" t="s">
-        <v>300</v>
-      </c>
       <c r="D18" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
@@ -8311,10 +8308,10 @@
         <v>254</v>
       </c>
       <c r="C19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
@@ -8322,16 +8319,16 @@
         <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -8339,13 +8336,13 @@
         <v>256</v>
       </c>
       <c r="C21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
@@ -8353,13 +8350,13 @@
         <v>257</v>
       </c>
       <c r="C22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
@@ -8367,10 +8364,10 @@
         <v>258</v>
       </c>
       <c r="C23" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
@@ -8378,10 +8375,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
@@ -8389,416 +8386,404 @@
         <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B26" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C26" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B27" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C27" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B28" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B29" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C29" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B30" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C30" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B31" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>341</v>
+      </c>
+      <c r="B32" t="s">
+        <v>368</v>
+      </c>
+      <c r="C32" t="s">
+        <v>313</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>342</v>
+      </c>
+      <c r="B33" t="s">
+        <v>368</v>
+      </c>
+      <c r="C33" t="s">
+        <v>314</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>343</v>
       </c>
-      <c r="B32" t="s">
-        <v>370</v>
-      </c>
-      <c r="C32" t="s">
-        <v>314</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="B34" t="s">
+        <v>368</v>
+      </c>
+      <c r="C34" t="s">
+        <v>315</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>344</v>
       </c>
-      <c r="B33" t="s">
-        <v>370</v>
-      </c>
-      <c r="C33" t="s">
-        <v>315</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="B35" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" t="s">
+        <v>316</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>345</v>
       </c>
-      <c r="B34" t="s">
-        <v>370</v>
-      </c>
-      <c r="C34" t="s">
-        <v>316</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="B36" t="s">
+        <v>368</v>
+      </c>
+      <c r="C36" t="s">
+        <v>317</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>346</v>
       </c>
-      <c r="B35" t="s">
-        <v>370</v>
-      </c>
-      <c r="C35" t="s">
-        <v>317</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="B37" t="s">
+        <v>368</v>
+      </c>
+      <c r="C37" t="s">
+        <v>318</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>347</v>
       </c>
-      <c r="B36" t="s">
-        <v>370</v>
-      </c>
-      <c r="C36" t="s">
-        <v>318</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="B38" t="s">
+        <v>368</v>
+      </c>
+      <c r="C38" t="s">
+        <v>319</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>348</v>
       </c>
-      <c r="B37" t="s">
-        <v>370</v>
-      </c>
-      <c r="C37" t="s">
-        <v>319</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="B39" t="s">
+        <v>368</v>
+      </c>
+      <c r="C39" t="s">
+        <v>320</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>349</v>
       </c>
-      <c r="B38" t="s">
-        <v>370</v>
-      </c>
-      <c r="C38" t="s">
-        <v>320</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="B40" t="s">
+        <v>368</v>
+      </c>
+      <c r="C40" t="s">
+        <v>321</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>350</v>
       </c>
-      <c r="B39" t="s">
-        <v>370</v>
-      </c>
-      <c r="C39" t="s">
-        <v>321</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="B41" t="s">
+        <v>368</v>
+      </c>
+      <c r="C41" t="s">
+        <v>322</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>351</v>
       </c>
-      <c r="B40" t="s">
-        <v>370</v>
-      </c>
-      <c r="C40" t="s">
-        <v>322</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="B42" t="s">
+        <v>368</v>
+      </c>
+      <c r="C42" t="s">
+        <v>323</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>352</v>
       </c>
-      <c r="B41" t="s">
-        <v>370</v>
-      </c>
-      <c r="C41" t="s">
-        <v>323</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>353</v>
-      </c>
-      <c r="B42" t="s">
-        <v>370</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B43" t="s">
+        <v>368</v>
+      </c>
+      <c r="C43" t="s">
         <v>324</v>
       </c>
-      <c r="D42" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>354</v>
-      </c>
-      <c r="B43" t="s">
-        <v>370</v>
-      </c>
-      <c r="C43" t="s">
-        <v>325</v>
-      </c>
       <c r="G43" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>261</v>
       </c>
-      <c r="C44" s="11" t="s">
-        <v>326</v>
+      <c r="C44" t="s">
+        <v>325</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>262</v>
       </c>
       <c r="C45" t="s">
-        <v>327</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>263</v>
       </c>
       <c r="C46" t="s">
-        <v>328</v>
-      </c>
-      <c r="K46" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>264</v>
       </c>
       <c r="C47" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>265</v>
       </c>
       <c r="C48" t="s">
-        <v>330</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="O48" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="P48" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>266</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" t="s">
         <v>331</v>
       </c>
-      <c r="K49" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="O49" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="P49" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>267</v>
-      </c>
-      <c r="C50" s="11" t="s">
+      <c r="L50" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
         <v>332</v>
-      </c>
-      <c r="L50" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>238</v>
       </c>
       <c r="C51" t="s">
         <v>333</v>
       </c>
-      <c r="L51" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="K51" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="O51" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="C52" t="s">
-        <v>335</v>
-      </c>
-      <c r="K52" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="O52" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>358</v>
+      </c>
+      <c r="B54" t="s">
+        <v>368</v>
+      </c>
+      <c r="C54" t="s">
         <v>357</v>
       </c>
-      <c r="D53" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>356</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>360</v>
-      </c>
-      <c r="B55" t="s">
-        <v>370</v>
-      </c>
-      <c r="C55" t="s">
-        <v>359</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>274</v>
+      <c r="D54" s="10" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C44" r:id="rId1" xr:uid="{F0B81481-DE5B-D14B-B491-0E6E430FDAEA}"/>
-    <hyperlink ref="C50" r:id="rId2" xr:uid="{3648738A-80CA-644C-BD1F-CD606A18929D}"/>
-    <hyperlink ref="C54" r:id="rId3" xr:uid="{0F22155A-3689-764A-BB2F-DB1DF0992B60}"/>
+    <hyperlink ref="C49" r:id="rId1" xr:uid="{3648738A-80CA-644C-BD1F-CD606A18929D}"/>
+    <hyperlink ref="C53" r:id="rId2" xr:uid="{0F22155A-3689-764A-BB2F-DB1DF0992B60}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABA9643-2C7E-5843-A50E-935CD84D03B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7125925C-F1CA-7D47-AF68-3CB4979893AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Cookpit" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="4 - Recursos" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$F$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$F$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Agenda Workshop'!$A$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$Q$54</definedName>
   </definedNames>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="379">
   <si>
     <t>Projeto</t>
   </si>
@@ -1655,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="64.5" bestFit="1" customWidth="1"/>
@@ -3391,27 +3391,22 @@
     </row>
     <row r="117" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B117" t="s">
-        <v>35</v>
-      </c>
-      <c r="C117" t="s">
-        <v>64</v>
-      </c>
-      <c r="E117" s="13">
-        <v>46569</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E117" s="13"/>
     </row>
     <row r="118" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>359</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C118" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="E118" s="13">
         <v>46569</v>
@@ -3422,10 +3417,10 @@
         <v>359</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>360</v>
+        <v>86</v>
       </c>
       <c r="E119" s="13">
         <v>46569</v>
@@ -3436,7 +3431,7 @@
         <v>359</v>
       </c>
       <c r="B120" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C120" t="s">
         <v>360</v>
@@ -3444,10 +3439,24 @@
       <c r="E120" s="13">
         <v>46569</v>
       </c>
-      <c r="F120" s="15"/>
+    </row>
+    <row r="121" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>359</v>
+      </c>
+      <c r="B121" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" t="s">
+        <v>360</v>
+      </c>
+      <c r="E121" s="13">
+        <v>46569</v>
+      </c>
+      <c r="F121" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F121" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7125925C-F1CA-7D47-AF68-3CB4979893AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16046F0-AF51-4B4F-8349-8A59AA41B5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="378">
   <si>
     <t>Projeto</t>
   </si>
@@ -154,9 +154,6 @@
     <t>3464 - Solinfitec - Implantação S4HANA</t>
   </si>
   <si>
-    <t>Consultor AP / AR / TR</t>
-  </si>
-  <si>
     <t>Consultor FI / GL / PS</t>
   </si>
   <si>
@@ -1129,9 +1126,6 @@
     <t>4676 - Itaipu - Implementação SAP Cloud ERP</t>
   </si>
   <si>
-    <t>Consultor PP* / PM / QM</t>
-  </si>
-  <si>
     <t>Consultor SD Jr.</t>
   </si>
   <si>
@@ -1178,6 +1172,9 @@
   </si>
   <si>
     <t>Guilherme Souza Do Espirito Santo (Consultor Jr.) &lt;guilherme.santo@numenit.com&gt;</t>
+  </si>
+  <si>
+    <t>Consultor AP / AR</t>
   </si>
 </sst>
 </file>
@@ -1310,7 +1307,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1350,6 +1347,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1674,16 +1674,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1694,7 +1694,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="12">
@@ -1709,7 +1709,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="12">
@@ -1724,7 +1724,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="12">
@@ -1739,7 +1739,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="12">
@@ -1754,7 +1754,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="12">
@@ -1769,7 +1769,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="12">
@@ -1784,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="12">
@@ -1799,7 +1799,7 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="12">
@@ -1814,14 +1814,14 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="12">
         <v>46388</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1832,14 +1832,14 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="12">
         <v>46388</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1850,25 +1850,25 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="12">
         <v>46388</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="12"/>
@@ -1882,10 +1882,10 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E14" s="12">
         <v>46296</v>
@@ -1899,10 +1899,10 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E15" s="12">
         <v>46296</v>
@@ -1916,7 +1916,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="12">
@@ -1925,13 +1925,13 @@
     </row>
     <row r="17" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="12"/>
@@ -1944,7 +1944,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="12">
@@ -1959,7 +1959,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="12">
@@ -1974,7 +1974,7 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="12">
@@ -1989,7 +1989,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="12">
@@ -2004,7 +2004,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="12">
@@ -2019,7 +2019,7 @@
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="12">
@@ -2034,7 +2034,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="12">
@@ -2049,14 +2049,14 @@
         <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="12">
         <v>46296</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2067,7 +2067,7 @@
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="12">
@@ -2082,7 +2082,7 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="12">
@@ -2097,7 +2097,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="12">
@@ -2106,13 +2106,13 @@
     </row>
     <row r="29" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="12"/>
@@ -2138,7 +2138,7 @@
         <v>27</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="12">
@@ -2166,7 +2166,7 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="12">
@@ -2181,7 +2181,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="12">
@@ -2196,7 +2196,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="12">
@@ -2211,7 +2211,7 @@
         <v>33</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="12">
@@ -2226,14 +2226,14 @@
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="12">
         <v>46388</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2244,14 +2244,14 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="12">
         <v>46388</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2262,7 +2262,7 @@
         <v>35</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="12">
@@ -2290,7 +2290,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="12">
@@ -2305,7 +2305,7 @@
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="12">
@@ -2320,7 +2320,7 @@
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="12">
@@ -2335,14 +2335,14 @@
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="12">
         <v>46661</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2353,7 +2353,7 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="12">
@@ -2368,7 +2368,7 @@
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="12">
@@ -2380,7 +2380,7 @@
         <v>36</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>37</v>
+        <v>377</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2396,7 +2396,7 @@
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="12">
@@ -2408,10 +2408,10 @@
         <v>36</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="12">
@@ -2426,7 +2426,7 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="12">
@@ -2441,7 +2441,7 @@
         <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="12">
@@ -2456,7 +2456,7 @@
         <v>33</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="12">
@@ -2468,7 +2468,7 @@
         <v>36</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -2480,14 +2480,14 @@
       <c r="A54" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>40</v>
+      <c r="B54" s="19" t="s">
+        <v>39</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E54" s="12">
         <v>46388</v>
@@ -2498,10 +2498,10 @@
         <v>36</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="12">
@@ -2516,7 +2516,7 @@
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="12">
@@ -2531,14 +2531,14 @@
         <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="12">
         <v>46388</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2549,28 +2549,28 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="12">
         <v>46388</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E59" s="12">
         <v>46388</v>
@@ -2578,13 +2578,13 @@
     </row>
     <row r="60" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="12">
@@ -2593,13 +2593,13 @@
     </row>
     <row r="61" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="12">
@@ -2608,13 +2608,13 @@
     </row>
     <row r="62" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="12">
@@ -2623,13 +2623,13 @@
     </row>
     <row r="63" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="12">
@@ -2638,13 +2638,13 @@
     </row>
     <row r="64" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="12">
@@ -2653,52 +2653,52 @@
     </row>
     <row r="65" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="12">
         <v>46388</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C66" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="12">
         <v>46388</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E67" s="12">
         <v>46388</v>
@@ -2706,30 +2706,30 @@
     </row>
     <row r="68" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E68" s="12">
         <v>46388</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="70" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>13</v>
@@ -2752,13 +2752,13 @@
     </row>
     <row r="71" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" t="s">
         <v>46</v>
       </c>
-      <c r="B71" t="s">
-        <v>47</v>
-      </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E71" s="12">
         <v>46388</v>
@@ -2766,13 +2766,13 @@
     </row>
     <row r="72" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E72" s="12">
         <v>46388</v>
@@ -2780,16 +2780,16 @@
     </row>
     <row r="73" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C73" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D73" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E73" s="12">
         <v>46388</v>
@@ -2797,13 +2797,13 @@
     </row>
     <row r="74" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E74" s="12">
         <v>46388</v>
@@ -2811,13 +2811,13 @@
     </row>
     <row r="75" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E75" s="12">
         <v>46388</v>
@@ -2825,13 +2825,13 @@
     </row>
     <row r="76" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E76" s="12">
         <v>46388</v>
@@ -2839,13 +2839,13 @@
     </row>
     <row r="77" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E77" s="12">
         <v>46388</v>
@@ -2853,13 +2853,13 @@
     </row>
     <row r="78" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E78" s="12">
         <v>46388</v>
@@ -2867,13 +2867,13 @@
     </row>
     <row r="79" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C79" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E79" s="12">
         <v>46388</v>
@@ -2881,13 +2881,13 @@
     </row>
     <row r="80" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E80" s="12">
         <v>46388</v>
@@ -2895,81 +2895,81 @@
     </row>
     <row r="81" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E81" s="12">
         <v>46388</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E82" s="12">
         <v>46388</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E83" s="12">
         <v>46388</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E84" s="12">
         <v>46388</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B85" t="s">
         <v>35</v>
       </c>
       <c r="C85" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E85" s="13">
         <v>46388</v>
@@ -2977,13 +2977,13 @@
     </row>
     <row r="86" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E86" s="13">
         <v>46388</v>
@@ -2991,13 +2991,13 @@
     </row>
     <row r="87" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B87" t="s">
         <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E87" s="13">
         <v>46388</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="88" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B88" t="s">
         <v>5</v>
@@ -3016,10 +3016,10 @@
     </row>
     <row r="89" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B89" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E89" s="13">
         <v>46388</v>
@@ -3027,7 +3027,7 @@
     </row>
     <row r="90" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -3038,13 +3038,13 @@
     </row>
     <row r="91" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B91" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E91" s="13">
         <v>46388</v>
@@ -3052,47 +3052,47 @@
     </row>
     <row r="92" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E92" s="13">
         <v>46388</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E93" s="13">
         <v>46388</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E94" s="13">
         <v>46631</v>
@@ -3100,13 +3100,13 @@
     </row>
     <row r="95" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B95" t="s">
         <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E95" s="13">
         <v>46631</v>
@@ -3114,13 +3114,13 @@
     </row>
     <row r="96" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B96" t="s">
         <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E96" s="13">
         <v>46631</v>
@@ -3128,13 +3128,13 @@
     </row>
     <row r="97" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B97" t="s">
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E97" s="13">
         <v>46631</v>
@@ -3142,13 +3142,13 @@
     </row>
     <row r="98" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E98" s="13">
         <v>46631</v>
@@ -3156,13 +3156,13 @@
     </row>
     <row r="99" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E99" s="13">
         <v>46631</v>
@@ -3170,13 +3170,13 @@
     </row>
     <row r="100" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E100" s="13">
         <v>46631</v>
@@ -3184,25 +3184,25 @@
     </row>
     <row r="101" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B101" t="s">
         <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E101" s="13"/>
     </row>
     <row r="102" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>55</v>
+      </c>
+      <c r="B102" t="s">
         <v>56</v>
       </c>
-      <c r="B102" t="s">
-        <v>57</v>
-      </c>
       <c r="C102" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E102" s="13">
         <v>46631</v>
@@ -3210,30 +3210,30 @@
     </row>
     <row r="103" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B103" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C103" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E103" s="13">
         <v>46631</v>
       </c>
       <c r="F103" s="15" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B104" t="s">
         <v>35</v>
       </c>
       <c r="C104" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E104" s="13">
         <v>46631</v>
@@ -3241,13 +3241,13 @@
     </row>
     <row r="105" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B105" t="s">
         <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E105" s="13">
         <v>46631</v>
@@ -3255,13 +3255,13 @@
     </row>
     <row r="106" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B106" t="s">
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E106" s="13">
         <v>46631</v>
@@ -3269,13 +3269,13 @@
     </row>
     <row r="107" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B107" t="s">
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E107" s="13">
         <v>46631</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="108" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B108" t="s">
         <v>35</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="109" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B109" t="s">
         <v>5</v>
@@ -3305,7 +3305,7 @@
     </row>
     <row r="110" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -3316,13 +3316,13 @@
     </row>
     <row r="111" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E111" s="13">
         <v>46296</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="112" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B112" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E112" s="13">
         <v>46569</v>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="113" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B113" t="s">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="E113" s="13">
         <v>46569</v>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="114" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -3363,13 +3363,13 @@
     </row>
     <row r="115" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B115" t="s">
         <v>33</v>
       </c>
       <c r="C115" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E115" s="13">
         <v>46569</v>
@@ -3377,13 +3377,13 @@
     </row>
     <row r="116" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>360</v>
+      </c>
+      <c r="B116" t="s">
         <v>361</v>
       </c>
-      <c r="B116" t="s">
-        <v>363</v>
-      </c>
       <c r="C116" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E116" s="13">
         <v>46569</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="117" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B117" t="s">
         <v>10</v>
@@ -3400,13 +3400,13 @@
     </row>
     <row r="118" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B118" t="s">
         <v>35</v>
       </c>
       <c r="C118" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E118" s="13">
         <v>46569</v>
@@ -3414,13 +3414,13 @@
     </row>
     <row r="119" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B119" t="s">
         <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E119" s="13">
         <v>46569</v>
@@ -3428,13 +3428,13 @@
     </row>
     <row r="120" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B120" t="s">
         <v>6</v>
       </c>
       <c r="C120" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E120" s="13">
         <v>46569</v>
@@ -3442,13 +3442,13 @@
     </row>
     <row r="121" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E121" s="13">
         <v>46569</v>
@@ -3479,27 +3479,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D2" s="4">
         <v>46113</v>
@@ -3510,13 +3510,13 @@
     </row>
     <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D3" s="4">
         <v>46113</v>
@@ -3527,13 +3527,13 @@
     </row>
     <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D4" s="4">
         <v>46114</v>
@@ -3544,13 +3544,13 @@
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="4">
         <v>46128</v>
@@ -3561,13 +3561,13 @@
     </row>
     <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" s="4">
         <v>46122</v>
@@ -3578,13 +3578,13 @@
     </row>
     <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" s="4">
         <v>46126</v>
@@ -3595,13 +3595,13 @@
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" s="4">
         <v>46129</v>
@@ -3612,13 +3612,13 @@
     </row>
     <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="4">
         <v>46146</v>
@@ -3629,26 +3629,26 @@
     </row>
     <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="D11" s="4">
         <v>46153</v>
@@ -3659,13 +3659,13 @@
     </row>
     <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D12" s="4">
         <v>46140</v>
@@ -3676,13 +3676,13 @@
     </row>
     <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" s="4">
         <v>46162</v>
@@ -3693,13 +3693,13 @@
     </row>
     <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="D14" s="4">
         <v>46163</v>
@@ -3710,10 +3710,10 @@
     </row>
     <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="4">
@@ -3725,13 +3725,13 @@
     </row>
     <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D16" s="4">
         <v>46160</v>
@@ -3742,13 +3742,13 @@
     </row>
     <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D17" s="4">
         <v>46140</v>
@@ -3759,13 +3759,13 @@
     </row>
     <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D18" s="4">
         <v>46150</v>
@@ -3776,13 +3776,13 @@
     </row>
     <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" s="4">
         <v>46150</v>
@@ -3793,13 +3793,13 @@
     </row>
     <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D20" s="4">
         <v>46147</v>
@@ -3810,13 +3810,13 @@
     </row>
     <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D21" s="4">
         <v>46149</v>
@@ -3827,13 +3827,13 @@
     </row>
     <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D22" s="4">
         <v>46181</v>
@@ -3844,13 +3844,13 @@
     </row>
     <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D23" s="4">
         <v>46170</v>
@@ -3861,13 +3861,13 @@
     </row>
     <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D24" s="4">
         <v>46168</v>
@@ -3878,13 +3878,13 @@
     </row>
     <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D25" s="4">
         <v>46167</v>
@@ -3895,13 +3895,13 @@
     </row>
     <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D26" s="4">
         <v>46174</v>
@@ -3912,13 +3912,13 @@
     </row>
     <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="D27" s="4">
         <v>46175</v>
@@ -3929,13 +3929,13 @@
     </row>
     <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D28" s="4">
         <v>46171</v>
@@ -3946,13 +3946,13 @@
     </row>
     <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="D29" s="4">
         <v>46170</v>
@@ -3963,13 +3963,13 @@
     </row>
     <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D30" s="4">
         <v>46181</v>
@@ -3980,13 +3980,13 @@
     </row>
     <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" s="4">
         <v>46178</v>
@@ -3997,13 +3997,13 @@
     </row>
     <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D32" s="4">
         <v>46170</v>
@@ -4014,13 +4014,13 @@
     </row>
     <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D33" s="4">
         <v>46181</v>
@@ -4031,26 +4031,26 @@
     </row>
     <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D35" s="4">
         <v>46155</v>
@@ -4061,13 +4061,13 @@
     </row>
     <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D36" s="4">
         <v>46167</v>
@@ -4078,13 +4078,13 @@
     </row>
     <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" s="4">
         <v>46167</v>
@@ -4095,13 +4095,13 @@
     </row>
     <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D38" s="4">
         <v>46168</v>
@@ -4112,13 +4112,13 @@
     </row>
     <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D39" s="4">
         <v>46175</v>
@@ -4129,13 +4129,13 @@
     </row>
     <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D40" s="4">
         <v>46188</v>
@@ -4146,13 +4146,13 @@
     </row>
     <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D41" s="4">
         <v>46195</v>
@@ -4163,13 +4163,13 @@
     </row>
     <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D42" s="4">
         <v>46202</v>
@@ -4180,10 +4180,10 @@
     </row>
     <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="4">
@@ -4195,10 +4195,10 @@
     </row>
     <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="4">
@@ -4210,13 +4210,13 @@
     </row>
     <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D45" s="4">
         <v>46223</v>
@@ -4227,13 +4227,13 @@
     </row>
     <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D46" s="4">
         <v>46223</v>
@@ -4244,10 +4244,10 @@
     </row>
     <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="4">
@@ -4259,13 +4259,13 @@
     </row>
     <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D48" s="4">
         <v>46230</v>
@@ -4276,13 +4276,13 @@
     </row>
     <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D49" s="4">
         <v>46232</v>
@@ -4293,13 +4293,13 @@
     </row>
     <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D50" s="4">
         <v>46230</v>
@@ -4310,13 +4310,13 @@
     </row>
     <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D51" s="4">
         <v>46161</v>
@@ -4327,13 +4327,13 @@
     </row>
     <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D52" s="4">
         <v>46162</v>
@@ -4344,13 +4344,13 @@
     </row>
     <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="D53" s="4">
         <v>46162</v>
@@ -4361,13 +4361,13 @@
     </row>
     <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D54" s="4">
         <v>46163</v>
@@ -4378,13 +4378,13 @@
     </row>
     <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D55" s="4">
         <v>46174</v>
@@ -4395,13 +4395,13 @@
     </row>
     <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D56" s="4">
         <v>46174</v>
@@ -4412,13 +4412,13 @@
     </row>
     <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="D57" s="4">
         <v>46174</v>
@@ -4429,13 +4429,13 @@
     </row>
     <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="D58" s="4">
         <v>46181</v>
@@ -4446,13 +4446,13 @@
     </row>
     <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="D59" s="4">
         <v>46181</v>
@@ -4463,13 +4463,13 @@
     </row>
     <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D60" s="4">
         <v>46181</v>
@@ -4480,13 +4480,13 @@
     </row>
     <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D61" s="4">
         <v>46181</v>
@@ -4497,13 +4497,13 @@
     </row>
     <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D62" s="4">
         <v>46182</v>
@@ -4514,13 +4514,13 @@
     </row>
     <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D63" s="4">
         <v>46184</v>
@@ -4531,13 +4531,13 @@
     </row>
     <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D64" s="4">
         <v>46188</v>
@@ -4548,13 +4548,13 @@
     </row>
     <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D65" s="4">
         <v>46188</v>
@@ -4565,13 +4565,13 @@
     </row>
     <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="D66" s="4">
         <v>46198</v>
@@ -4929,36 +4929,36 @@
         <v>0</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F2" s="7">
         <v>46174</v>
@@ -4972,19 +4972,19 @@
     </row>
     <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F3" s="7">
         <v>46175</v>
@@ -4998,19 +4998,19 @@
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F4" s="7">
         <v>46177</v>
@@ -5024,19 +5024,19 @@
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F5" s="7">
         <v>46178</v>
@@ -5050,19 +5050,19 @@
     </row>
     <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="F6" s="7">
         <v>46167</v>
@@ -5076,19 +5076,19 @@
     </row>
     <row r="7" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="F7" s="7">
         <v>46168</v>
@@ -5102,19 +5102,19 @@
     </row>
     <row r="8" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="F8" s="7">
         <v>46169</v>
@@ -5128,19 +5128,19 @@
     </row>
     <row r="9" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="F9" s="7">
         <v>46170</v>
@@ -5154,19 +5154,19 @@
     </row>
     <row r="10" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="F10" s="7">
         <v>46171</v>
@@ -5180,19 +5180,19 @@
     </row>
     <row r="11" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F11" s="7">
         <v>46167</v>
@@ -5206,19 +5206,19 @@
     </row>
     <row r="12" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F12" s="7">
         <v>46168</v>
@@ -5232,19 +5232,19 @@
     </row>
     <row r="13" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F13" s="7">
         <v>46169</v>
@@ -5258,19 +5258,19 @@
     </row>
     <row r="14" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F14" s="7">
         <v>46170</v>
@@ -5284,19 +5284,19 @@
     </row>
     <row r="15" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F15" s="7">
         <v>46171</v>
@@ -5310,19 +5310,19 @@
     </row>
     <row r="16" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="F16" s="7">
         <v>46167</v>
@@ -5336,19 +5336,19 @@
     </row>
     <row r="17" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F17" s="7">
         <v>46168</v>
@@ -5362,19 +5362,19 @@
     </row>
     <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F18" s="7">
         <v>46169</v>
@@ -5388,19 +5388,19 @@
     </row>
     <row r="19" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F19" s="7">
         <v>46169</v>
@@ -5414,19 +5414,19 @@
     </row>
     <row r="20" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F20" s="7">
         <v>46170</v>
@@ -5440,19 +5440,19 @@
     </row>
     <row r="21" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F21" s="7">
         <v>46170</v>
@@ -5466,19 +5466,19 @@
     </row>
     <row r="22" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F22" s="7">
         <v>46160</v>
@@ -5492,19 +5492,19 @@
     </row>
     <row r="23" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F23" s="7">
         <v>46161</v>
@@ -5518,19 +5518,19 @@
     </row>
     <row r="24" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F24" s="7">
         <v>46162</v>
@@ -5544,19 +5544,19 @@
     </row>
     <row r="25" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F25" s="7">
         <v>46163</v>
@@ -5570,19 +5570,19 @@
     </row>
     <row r="26" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F26" s="7">
         <v>46164</v>
@@ -5596,19 +5596,19 @@
     </row>
     <row r="27" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F27" s="7">
         <v>46160</v>
@@ -5622,19 +5622,19 @@
     </row>
     <row r="28" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F28" s="7">
         <v>46161</v>
@@ -5648,19 +5648,19 @@
     </row>
     <row r="29" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F29" s="7">
         <v>46162</v>
@@ -5674,19 +5674,19 @@
     </row>
     <row r="30" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F30" s="7">
         <v>46163</v>
@@ -5700,19 +5700,19 @@
     </row>
     <row r="31" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F31" s="7">
         <v>46164</v>
@@ -5726,19 +5726,19 @@
     </row>
     <row r="32" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F32" s="7">
         <v>46160</v>
@@ -5752,19 +5752,19 @@
     </row>
     <row r="33" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F33" s="7">
         <v>46161</v>
@@ -5778,19 +5778,19 @@
     </row>
     <row r="34" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F34" s="7">
         <v>46162</v>
@@ -5804,19 +5804,19 @@
     </row>
     <row r="35" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F35" s="7">
         <v>46163</v>
@@ -5830,19 +5830,19 @@
     </row>
     <row r="36" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F36" s="7">
         <v>46163</v>
@@ -5856,19 +5856,19 @@
     </row>
     <row r="37" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F37" s="7">
         <v>46164</v>
@@ -5882,19 +5882,19 @@
     </row>
     <row r="38" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F38" s="7">
         <v>46160</v>
@@ -5908,19 +5908,19 @@
     </row>
     <row r="39" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F39" s="7">
         <v>46161</v>
@@ -5934,19 +5934,19 @@
     </row>
     <row r="40" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F40" s="7">
         <v>46162</v>
@@ -5960,19 +5960,19 @@
     </row>
     <row r="41" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F41" s="7">
         <v>46163</v>
@@ -5986,19 +5986,19 @@
     </row>
     <row r="42" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F42" s="7">
         <v>46164</v>
@@ -6012,19 +6012,19 @@
     </row>
     <row r="43" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F43" s="7">
         <v>46153</v>
@@ -6038,19 +6038,19 @@
     </row>
     <row r="44" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F44" s="7">
         <v>46154</v>
@@ -6064,19 +6064,19 @@
     </row>
     <row r="45" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F45" s="7">
         <v>46155</v>
@@ -6090,19 +6090,19 @@
     </row>
     <row r="46" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F46" s="7">
         <v>46156</v>
@@ -6116,19 +6116,19 @@
     </row>
     <row r="47" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F47" s="7">
         <v>46157</v>
@@ -6142,17 +6142,17 @@
     </row>
     <row r="48" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F48" s="7">
         <v>46153</v>
@@ -6166,17 +6166,17 @@
     </row>
     <row r="49" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F49" s="7">
         <v>46154</v>
@@ -6190,17 +6190,17 @@
     </row>
     <row r="50" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F50" s="7">
         <v>46155</v>
@@ -6214,17 +6214,17 @@
     </row>
     <row r="51" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F51" s="7">
         <v>46156</v>
@@ -6238,17 +6238,17 @@
     </row>
     <row r="52" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F52" s="7">
         <v>46157</v>
@@ -6262,19 +6262,19 @@
     </row>
     <row r="53" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F53" s="7">
         <v>46153</v>
@@ -6288,19 +6288,19 @@
     </row>
     <row r="54" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F54" s="7">
         <v>46154</v>
@@ -6314,19 +6314,19 @@
     </row>
     <row r="55" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F55" s="7">
         <v>46155</v>
@@ -6340,19 +6340,19 @@
     </row>
     <row r="56" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F56" s="7">
         <v>46156</v>
@@ -6366,19 +6366,19 @@
     </row>
     <row r="57" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="F57" s="7">
         <v>46157</v>
@@ -6392,19 +6392,19 @@
     </row>
     <row r="58" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C58" s="6" t="s">
+      <c r="D58" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="F58" s="7">
         <v>46153</v>
@@ -6418,19 +6418,19 @@
     </row>
     <row r="59" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="E59" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="F59" s="7">
         <v>46153</v>
@@ -6444,19 +6444,19 @@
     </row>
     <row r="60" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C60" s="6" t="s">
+      <c r="D60" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="F60" s="7">
         <v>46154</v>
@@ -6470,19 +6470,19 @@
     </row>
     <row r="61" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C61" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="F61" s="7">
         <v>46154</v>
@@ -6496,19 +6496,19 @@
     </row>
     <row r="62" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C62" s="6" t="s">
+      <c r="D62" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="F62" s="7">
         <v>46155</v>
@@ -6522,19 +6522,19 @@
     </row>
     <row r="63" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F63" s="7">
         <v>46155</v>
@@ -6548,19 +6548,19 @@
     </row>
     <row r="64" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C64" s="6" t="s">
+      <c r="D64" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E64" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="F64" s="7">
         <v>46156</v>
@@ -6574,19 +6574,19 @@
     </row>
     <row r="65" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F65" s="7">
         <v>46156</v>
@@ -6600,19 +6600,19 @@
     </row>
     <row r="66" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C66" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C66" s="6" t="s">
+      <c r="D66" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="F66" s="7">
         <v>46157</v>
@@ -6626,19 +6626,19 @@
     </row>
     <row r="67" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C67" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E67" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="F67" s="7">
         <v>46157</v>
@@ -6652,19 +6652,19 @@
     </row>
     <row r="68" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D68" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F68" s="7">
         <v>46153</v>
@@ -6678,19 +6678,19 @@
     </row>
     <row r="69" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="F69" s="7">
         <v>46154</v>
@@ -6704,19 +6704,19 @@
     </row>
     <row r="70" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D70" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F70" s="7">
         <v>46155</v>
@@ -6730,19 +6730,19 @@
     </row>
     <row r="71" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D71" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F71" s="7">
         <v>46155</v>
@@ -6756,19 +6756,19 @@
     </row>
     <row r="72" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F72" s="7">
         <v>46155</v>
@@ -6782,19 +6782,19 @@
     </row>
     <row r="73" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D73" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E73" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F73" s="7">
         <v>46155</v>
@@ -6808,19 +6808,19 @@
     </row>
     <row r="74" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D74" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E74" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F74" s="7">
         <v>46156</v>
@@ -6834,19 +6834,19 @@
     </row>
     <row r="75" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D75" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E75" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="F75" s="7">
         <v>46157</v>
@@ -6860,19 +6860,19 @@
     </row>
     <row r="76" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F76" s="7">
         <v>46153</v>
@@ -6886,19 +6886,19 @@
     </row>
     <row r="77" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F77" s="7">
         <v>46154</v>
@@ -6912,19 +6912,19 @@
     </row>
     <row r="78" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F78" s="7">
         <v>46155</v>
@@ -6938,19 +6938,19 @@
     </row>
     <row r="79" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F79" s="7">
         <v>46156</v>
@@ -6964,19 +6964,19 @@
     </row>
     <row r="80" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F80" s="7">
         <v>46157</v>
@@ -6990,19 +6990,19 @@
     </row>
     <row r="81" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F81" s="7">
         <v>46153</v>
@@ -7016,19 +7016,19 @@
     </row>
     <row r="82" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F82" s="7">
         <v>46154</v>
@@ -7042,19 +7042,19 @@
     </row>
     <row r="83" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F83" s="7">
         <v>46155</v>
@@ -7068,19 +7068,19 @@
     </row>
     <row r="84" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F84" s="7">
         <v>46156</v>
@@ -7094,19 +7094,19 @@
     </row>
     <row r="85" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F85" s="7">
         <v>46157</v>
@@ -7120,19 +7120,19 @@
     </row>
     <row r="86" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F86" s="7">
         <v>46146</v>
@@ -7146,19 +7146,19 @@
     </row>
     <row r="87" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F87" s="7">
         <v>46147</v>
@@ -7172,19 +7172,19 @@
     </row>
     <row r="88" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F88" s="7">
         <v>46148</v>
@@ -7198,19 +7198,19 @@
     </row>
     <row r="89" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F89" s="7">
         <v>46149</v>
@@ -7224,19 +7224,19 @@
     </row>
     <row r="90" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F90" s="7">
         <v>46150</v>
@@ -7250,19 +7250,19 @@
     </row>
     <row r="91" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F91" s="7">
         <v>46146</v>
@@ -7276,19 +7276,19 @@
     </row>
     <row r="92" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C92" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E92" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="F92" s="7">
         <v>46146</v>
@@ -7302,19 +7302,19 @@
     </row>
     <row r="93" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F93" s="7">
         <v>46147</v>
@@ -7328,19 +7328,19 @@
     </row>
     <row r="94" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F94" s="7">
         <v>46147</v>
@@ -7354,19 +7354,19 @@
     </row>
     <row r="95" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F95" s="7">
         <v>46148</v>
@@ -7380,19 +7380,19 @@
     </row>
     <row r="96" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C96" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E96" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="F96" s="7">
         <v>46149</v>
@@ -7406,19 +7406,19 @@
     </row>
     <row r="97" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F97" s="7">
         <v>46149</v>
@@ -7432,19 +7432,19 @@
     </row>
     <row r="98" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F98" s="7">
         <v>46150</v>
@@ -7458,19 +7458,19 @@
     </row>
     <row r="99" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F99" s="7">
         <v>46146</v>
@@ -7484,19 +7484,19 @@
     </row>
     <row r="100" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F100" s="7">
         <v>46147</v>
@@ -7510,19 +7510,19 @@
     </row>
     <row r="101" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F101" s="7">
         <v>46148</v>
@@ -7536,19 +7536,19 @@
     </row>
     <row r="102" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F102" s="7">
         <v>46149</v>
@@ -7562,19 +7562,19 @@
     </row>
     <row r="103" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F103" s="7">
         <v>46150</v>
@@ -7588,19 +7588,19 @@
     </row>
     <row r="104" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F104" s="7">
         <v>46146</v>
@@ -7614,19 +7614,19 @@
     </row>
     <row r="105" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F105" s="7">
         <v>46147</v>
@@ -7640,19 +7640,19 @@
     </row>
     <row r="106" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F106" s="7">
         <v>46148</v>
@@ -7666,19 +7666,19 @@
     </row>
     <row r="107" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F107" s="7">
         <v>46149</v>
@@ -7692,19 +7692,19 @@
     </row>
     <row r="108" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F108" s="7">
         <v>46150</v>
@@ -7718,19 +7718,19 @@
     </row>
     <row r="109" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F109" s="7">
         <v>46146</v>
@@ -7744,19 +7744,19 @@
     </row>
     <row r="110" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F110" s="7">
         <v>46147</v>
@@ -7770,19 +7770,19 @@
     </row>
     <row r="111" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F111" s="7">
         <v>46148</v>
@@ -7796,19 +7796,19 @@
     </row>
     <row r="112" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F112" s="7">
         <v>46149</v>
@@ -7822,19 +7822,19 @@
     </row>
     <row r="113" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F113" s="7">
         <v>46150</v>
@@ -7848,17 +7848,17 @@
     </row>
     <row r="114" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F114" s="7">
         <v>46146</v>
@@ -7872,17 +7872,17 @@
     </row>
     <row r="115" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F115" s="7">
         <v>46147</v>
@@ -7896,17 +7896,17 @@
     </row>
     <row r="116" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F116" s="7">
         <v>46148</v>
@@ -7920,17 +7920,17 @@
     </row>
     <row r="117" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F117" s="7">
         <v>46149</v>
@@ -7944,17 +7944,17 @@
     </row>
     <row r="118" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F118" s="7">
         <v>46150</v>
@@ -8038,755 +8038,755 @@
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D1" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="J1" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="K1" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="L1" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="G1" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="H1" s="17" t="s">
+      <c r="M1" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="O1" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="N1" s="17" t="s">
+      <c r="P1" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="O1" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="P1" s="17" t="s">
+      <c r="Q1" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="Q1" s="17" t="s">
-        <v>279</v>
-      </c>
       <c r="R1" s="17" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R11" s="14" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" t="s">
         <v>294</v>
       </c>
-      <c r="C15" t="s">
-        <v>295</v>
-      </c>
       <c r="E15" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>297</v>
+      </c>
+      <c r="C18" t="s">
         <v>298</v>
       </c>
-      <c r="C18" t="s">
-        <v>299</v>
-      </c>
       <c r="D18" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C24" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B26" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C26" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B28" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C28" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B29" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C29" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B30" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B31" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C31" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C32" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B33" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C33" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B34" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C34" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C36" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C37" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B38" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C38" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C39" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C40" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C42" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C43" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C46" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C47" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C48" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O48" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P48" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" t="s">
         <v>332</v>
       </c>
-      <c r="C51" t="s">
-        <v>333</v>
-      </c>
       <c r="K51" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C52" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B54" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C54" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16046F0-AF51-4B4F-8349-8A59AA41B5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753487F7-F197-7D49-874D-A173AD66748F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="380">
   <si>
     <t>Projeto</t>
   </si>
@@ -1175,6 +1175,12 @@
   </si>
   <si>
     <t>Consultor AP / AR</t>
+  </si>
+  <si>
+    <t>Fase</t>
+  </si>
+  <si>
+    <t>Prepare</t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1274,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1302,12 +1308,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1346,10 +1361,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1655,18 +1673,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F121"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="64.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.33203125" customWidth="1"/>
-    <col min="3" max="3" width="99.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="66.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1685,8 +1704,11 @@
       <c r="F1" s="1" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G1" s="19" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1700,8 +1722,11 @@
       <c r="E2" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1715,8 +1740,11 @@
       <c r="E3" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1730,8 +1758,11 @@
       <c r="E4" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1745,8 +1776,11 @@
       <c r="E5" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1760,8 +1794,11 @@
       <c r="E6" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1775,8 +1812,11 @@
       <c r="E7" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1790,8 +1830,11 @@
       <c r="E8" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1805,8 +1848,11 @@
       <c r="E9" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G9" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1823,8 +1869,11 @@
       <c r="F10" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1841,8 +1890,11 @@
       <c r="F11" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -1859,8 +1911,11 @@
       <c r="F12" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>375</v>
       </c>
@@ -1871,10 +1926,17 @@
         <v>376</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="18"/>
-    </row>
-    <row r="14" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E13" s="12">
+        <v>46388</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="G13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1890,8 +1952,11 @@
       <c r="E14" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G14" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1907,8 +1972,11 @@
       <c r="E15" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G15" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1922,8 +1990,11 @@
       <c r="E16" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G16" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>372</v>
       </c>
@@ -1935,8 +2006,11 @@
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G17" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1950,8 +2024,11 @@
       <c r="E18" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G18" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
@@ -1965,8 +2042,11 @@
       <c r="E19" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G19" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
@@ -1980,8 +2060,11 @@
       <c r="E20" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G20" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
@@ -1995,8 +2078,11 @@
       <c r="E21" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G21" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
@@ -2010,8 +2096,11 @@
       <c r="E22" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G22" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
@@ -2025,8 +2114,11 @@
       <c r="E23" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G23" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>14</v>
       </c>
@@ -2040,8 +2132,11 @@
       <c r="E24" s="12">
         <v>46296</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G24" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>14</v>
       </c>
@@ -2058,8 +2153,11 @@
       <c r="F25" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G25" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -2073,8 +2171,11 @@
       <c r="E26" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G26" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -2088,8 +2189,11 @@
       <c r="E27" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G27" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
@@ -2103,8 +2207,11 @@
       <c r="E28" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G28" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>374</v>
       </c>
@@ -2116,8 +2223,11 @@
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G29" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -2129,8 +2239,11 @@
       <c r="E30" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G30" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>26</v>
       </c>
@@ -2144,8 +2257,11 @@
       <c r="E31" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G31" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
@@ -2157,8 +2273,11 @@
       <c r="E32" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G32" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>29</v>
       </c>
@@ -2172,8 +2291,11 @@
       <c r="E33" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G33" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>30</v>
       </c>
@@ -2187,8 +2309,11 @@
       <c r="E34" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G34" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>22</v>
       </c>
@@ -2202,8 +2327,11 @@
       <c r="E35" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G35" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -2217,8 +2345,11 @@
       <c r="E36" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>26</v>
       </c>
@@ -2235,8 +2366,11 @@
       <c r="F37" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G37" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>28</v>
       </c>
@@ -2253,8 +2387,11 @@
       <c r="F38" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G38" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>34</v>
       </c>
@@ -2268,8 +2405,11 @@
       <c r="E39" s="12">
         <v>46661</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G39" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>34</v>
       </c>
@@ -2281,8 +2421,11 @@
       <c r="E40" s="12">
         <v>46661</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G40" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>34</v>
       </c>
@@ -2296,8 +2439,11 @@
       <c r="E41" s="12">
         <v>46661</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G41" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>34</v>
       </c>
@@ -2311,8 +2457,11 @@
       <c r="E42" s="12">
         <v>46661</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G42" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>34</v>
       </c>
@@ -2326,8 +2475,11 @@
       <c r="E43" s="12">
         <v>46661</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G43" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>34</v>
       </c>
@@ -2344,8 +2496,11 @@
       <c r="F44" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G44" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>36</v>
       </c>
@@ -2359,8 +2514,11 @@
       <c r="E45" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G45" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>36</v>
       </c>
@@ -2374,8 +2532,11 @@
       <c r="E46" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G46" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>36</v>
       </c>
@@ -2387,8 +2548,11 @@
       <c r="E47" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G47" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>36</v>
       </c>
@@ -2402,8 +2566,11 @@
       <c r="E48" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G48" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>36</v>
       </c>
@@ -2417,8 +2584,11 @@
       <c r="E49" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G49" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>36</v>
       </c>
@@ -2432,8 +2602,11 @@
       <c r="E50" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G50" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>36</v>
       </c>
@@ -2447,8 +2620,11 @@
       <c r="E51" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G51" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>36</v>
       </c>
@@ -2462,8 +2638,11 @@
       <c r="E52" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G52" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>36</v>
       </c>
@@ -2475,12 +2654,15 @@
       <c r="E53" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G53" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="18" t="s">
         <v>39</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2492,8 +2674,11 @@
       <c r="E54" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G54" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>36</v>
       </c>
@@ -2507,8 +2692,11 @@
       <c r="E55" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G55" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>36</v>
       </c>
@@ -2522,8 +2710,11 @@
       <c r="E56" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G56" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>36</v>
       </c>
@@ -2540,8 +2731,11 @@
       <c r="F57" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G57" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>36</v>
       </c>
@@ -2558,8 +2752,11 @@
       <c r="F58" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G58" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>41</v>
       </c>
@@ -2575,8 +2772,11 @@
       <c r="E59" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G59" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>41</v>
       </c>
@@ -2590,8 +2790,11 @@
       <c r="E60" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G60" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>41</v>
       </c>
@@ -2605,8 +2808,11 @@
       <c r="E61" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G61" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>41</v>
       </c>
@@ -2620,8 +2826,11 @@
       <c r="E62" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G62" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>41</v>
       </c>
@@ -2635,8 +2844,11 @@
       <c r="E63" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G63" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>41</v>
       </c>
@@ -2650,8 +2862,11 @@
       <c r="E64" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G64" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>41</v>
       </c>
@@ -2668,8 +2883,11 @@
       <c r="F65" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G65" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>41</v>
       </c>
@@ -2686,8 +2904,11 @@
       <c r="F66" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G66" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>41</v>
       </c>
@@ -2703,8 +2924,11 @@
       <c r="E67" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G67" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>41</v>
       </c>
@@ -2723,8 +2947,11 @@
       <c r="F68" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G68" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>41</v>
       </c>
@@ -2736,8 +2963,11 @@
       <c r="E69" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G69" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>41</v>
       </c>
@@ -2749,8 +2979,11 @@
       <c r="E70" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G70" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>45</v>
       </c>
@@ -2763,8 +2996,11 @@
       <c r="E71" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G71" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>45</v>
       </c>
@@ -2777,8 +3013,11 @@
       <c r="E72" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G72" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>45</v>
       </c>
@@ -2794,8 +3033,11 @@
       <c r="E73" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G73" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>45</v>
       </c>
@@ -2808,8 +3050,11 @@
       <c r="E74" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G74" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>45</v>
       </c>
@@ -2822,8 +3067,11 @@
       <c r="E75" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G75" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>45</v>
       </c>
@@ -2836,8 +3084,11 @@
       <c r="E76" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G76" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>45</v>
       </c>
@@ -2850,8 +3101,11 @@
       <c r="E77" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G77" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>45</v>
       </c>
@@ -2864,8 +3118,11 @@
       <c r="E78" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G78" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>45</v>
       </c>
@@ -2878,8 +3135,11 @@
       <c r="E79" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G79" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>45</v>
       </c>
@@ -2892,8 +3152,11 @@
       <c r="E80" s="12">
         <v>46388</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G80" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>45</v>
       </c>
@@ -2909,8 +3172,11 @@
       <c r="F81" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G81" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>45</v>
       </c>
@@ -2926,8 +3192,11 @@
       <c r="F82" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G82" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>45</v>
       </c>
@@ -2943,8 +3212,11 @@
       <c r="F83" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G83" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>45</v>
       </c>
@@ -2960,8 +3232,11 @@
       <c r="F84" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G84" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>54</v>
       </c>
@@ -2974,8 +3249,11 @@
       <c r="E85" s="13">
         <v>46388</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G85" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>54</v>
       </c>
@@ -2988,8 +3266,11 @@
       <c r="E86" s="13">
         <v>46388</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G86" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>54</v>
       </c>
@@ -3002,8 +3283,11 @@
       <c r="E87" s="13">
         <v>46388</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G87" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>54</v>
       </c>
@@ -3013,8 +3297,11 @@
       <c r="E88" s="13">
         <v>46388</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G88" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>54</v>
       </c>
@@ -3024,8 +3311,11 @@
       <c r="E89" s="13">
         <v>46388</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G89" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>54</v>
       </c>
@@ -3035,8 +3325,11 @@
       <c r="E90" s="13">
         <v>46388</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G90" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>54</v>
       </c>
@@ -3049,8 +3342,11 @@
       <c r="E91" s="13">
         <v>46388</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G91" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>54</v>
       </c>
@@ -3066,8 +3362,11 @@
       <c r="F92" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G92" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>54</v>
       </c>
@@ -3083,8 +3382,11 @@
       <c r="F93" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G93" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>55</v>
       </c>
@@ -3097,8 +3399,11 @@
       <c r="E94" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G94" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>55</v>
       </c>
@@ -3111,8 +3416,11 @@
       <c r="E95" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G95" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>55</v>
       </c>
@@ -3125,8 +3433,11 @@
       <c r="E96" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G96" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>55</v>
       </c>
@@ -3139,8 +3450,11 @@
       <c r="E97" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G97" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>55</v>
       </c>
@@ -3153,8 +3467,11 @@
       <c r="E98" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G98" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>55</v>
       </c>
@@ -3167,8 +3484,11 @@
       <c r="E99" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G99" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>55</v>
       </c>
@@ -3181,8 +3501,11 @@
       <c r="E100" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G100" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>55</v>
       </c>
@@ -3193,8 +3516,11 @@
         <v>121</v>
       </c>
       <c r="E101" s="13"/>
-    </row>
-    <row r="102" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G101" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>55</v>
       </c>
@@ -3207,8 +3533,11 @@
       <c r="E102" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G102" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>55</v>
       </c>
@@ -3224,8 +3553,11 @@
       <c r="F103" s="15" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G103" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>171</v>
       </c>
@@ -3238,8 +3570,11 @@
       <c r="E104" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G104" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>171</v>
       </c>
@@ -3252,8 +3587,11 @@
       <c r="E105" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G105" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>171</v>
       </c>
@@ -3266,8 +3604,11 @@
       <c r="E106" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G106" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>171</v>
       </c>
@@ -3280,8 +3621,11 @@
       <c r="E107" s="13">
         <v>46631</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G107" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>360</v>
       </c>
@@ -3291,8 +3635,11 @@
       <c r="E108" s="13">
         <v>46296</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G108" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>360</v>
       </c>
@@ -3302,8 +3649,11 @@
       <c r="E109" s="13">
         <v>46296</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G109" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>360</v>
       </c>
@@ -3313,8 +3663,11 @@
       <c r="E110" s="13">
         <v>46296</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G110" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>360</v>
       </c>
@@ -3327,8 +3680,11 @@
       <c r="E111" s="13">
         <v>46296</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G111" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>360</v>
       </c>
@@ -3338,8 +3694,11 @@
       <c r="E112" s="13">
         <v>46569</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G112" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>360</v>
       </c>
@@ -3349,8 +3708,11 @@
       <c r="E113" s="13">
         <v>46569</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G113" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>360</v>
       </c>
@@ -3360,8 +3722,11 @@
       <c r="E114" s="13">
         <v>46569</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G114" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>360</v>
       </c>
@@ -3374,8 +3739,11 @@
       <c r="E115" s="13">
         <v>46569</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G115" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>360</v>
       </c>
@@ -3388,8 +3756,11 @@
       <c r="E116" s="13">
         <v>46569</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G116" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>360</v>
       </c>
@@ -3397,8 +3768,11 @@
         <v>10</v>
       </c>
       <c r="E117" s="13"/>
-    </row>
-    <row r="118" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G117" s="20" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>358</v>
       </c>
@@ -3411,8 +3785,11 @@
       <c r="E118" s="13">
         <v>46569</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G118" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>358</v>
       </c>
@@ -3425,8 +3802,11 @@
       <c r="E119" s="13">
         <v>46569</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G119" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>358</v>
       </c>
@@ -3439,8 +3819,11 @@
       <c r="E120" s="13">
         <v>46569</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G120" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>358</v>
       </c>
@@ -3454,9 +3837,21 @@
         <v>46569</v>
       </c>
       <c r="F121" s="15"/>
+      <c r="G121" s="20" t="s">
+        <v>182</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F121" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F121" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="4676 - Itaipu - Implementação SAP Cloud ERP"/>
+        <filter val="4723 - Sooro Renner Nutricao S/A | Grow"/>
+        <filter val="4791 - TUTI EL ROSADO"/>
+        <filter val="4886 - PRINCIPIA COSMÉTICOS"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753487F7-F197-7D49-874D-A173AD66748F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C0B43B-DA1B-0E4B-B1A0-CD87E8F96B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="371">
   <si>
     <t>Projeto</t>
   </si>
@@ -109,39 +109,18 @@
     <t>Consultor QM</t>
   </si>
   <si>
-    <t>4254 - Ademicon - Projeto 2035</t>
-  </si>
-  <si>
     <t>4254 - Ademicon - Projeto 2032</t>
   </si>
   <si>
-    <t>4254 - Ademicon - Projeto 2034</t>
-  </si>
-  <si>
     <t>Consultor Leasing</t>
   </si>
   <si>
-    <t>4254 - Ademicon - Projeto 2029</t>
-  </si>
-  <si>
     <t>Consultor GL / AA / PS / CO</t>
   </si>
   <si>
-    <t>4254 - Ademicon - Projeto 2030</t>
-  </si>
-  <si>
-    <t>4254 - Ademicon - Projeto 2031</t>
-  </si>
-  <si>
-    <t>4254 - Ademicon - Projeto 2033</t>
-  </si>
-  <si>
     <t>Consultor TRM / Fluxo Caixa</t>
   </si>
   <si>
-    <t>4254 - Ademicon - Projeto 2028</t>
-  </si>
-  <si>
     <t>Consultor Group Report</t>
   </si>
   <si>
@@ -1159,18 +1138,9 @@
     <t>Matheus Golin &lt;matheus.golin@nunenit.com&gt;</t>
   </si>
   <si>
-    <t>4063 - Airfix - Implementação SAP Cloud ERP</t>
-  </si>
-  <si>
     <t>Consultor GL</t>
   </si>
   <si>
-    <t>4255 - Ademicon - Projeto 2032</t>
-  </si>
-  <si>
-    <t>3569 - Brasal - Implantação Grow</t>
-  </si>
-  <si>
     <t>Guilherme Souza Do Espirito Santo (Consultor Jr.) &lt;guilherme.santo@numenit.com&gt;</t>
   </si>
   <si>
@@ -1181,6 +1151,9 @@
   </si>
   <si>
     <t>Prepare</t>
+  </si>
+  <si>
+    <t>5258 - PETMAX</t>
   </si>
 </sst>
 </file>
@@ -1673,11 +1646,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.1640625" customWidth="1"/>
+    <col min="1" max="1" width="58.6640625" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
     <col min="3" max="3" width="66.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.83203125" customWidth="1"/>
@@ -1693,22 +1665,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="G1" s="19" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1716,17 +1688,17 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="12">
         <v>46388</v>
       </c>
       <c r="G2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1734,17 +1706,17 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="12">
         <v>46388</v>
       </c>
       <c r="G3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1752,17 +1724,17 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="12">
         <v>46388</v>
       </c>
       <c r="G4" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1770,17 +1742,17 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="12">
         <v>46388</v>
       </c>
       <c r="G5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1788,17 +1760,17 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="12">
         <v>46388</v>
       </c>
       <c r="G6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1806,17 +1778,17 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="12">
         <v>46388</v>
       </c>
       <c r="G7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1824,17 +1796,17 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="12">
         <v>46388</v>
       </c>
       <c r="G8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1842,17 +1814,17 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="12">
         <v>46388</v>
       </c>
       <c r="G9" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1860,20 +1832,20 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="12">
         <v>46388</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G10" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1881,20 +1853,20 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="12">
         <v>46388</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -1902,41 +1874,41 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="12">
         <v>46388</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G12" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>375</v>
+        <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="12">
         <v>46388</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G13" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1944,19 +1916,19 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E14" s="12">
         <v>46296</v>
       </c>
       <c r="G14" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1964,19 +1936,19 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E15" s="12">
         <v>46296</v>
       </c>
       <c r="G15" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1984,33 +1956,33 @@
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="12">
         <v>46296</v>
       </c>
       <c r="G16" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>372</v>
+        <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="12"/>
       <c r="G17" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -2018,17 +1990,17 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="12">
         <v>46296</v>
       </c>
       <c r="G18" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
@@ -2036,17 +2008,17 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="12">
         <v>46296</v>
       </c>
       <c r="G19" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
@@ -2054,17 +2026,17 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="12">
         <v>46296</v>
       </c>
       <c r="G20" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
@@ -2072,17 +2044,17 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="12">
         <v>46296</v>
       </c>
       <c r="G21" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
@@ -2090,17 +2062,17 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="12">
         <v>46296</v>
       </c>
       <c r="G22" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
@@ -2108,17 +2080,17 @@
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="12">
         <v>46296</v>
       </c>
       <c r="G23" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>14</v>
       </c>
@@ -2126,17 +2098,17 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="12">
         <v>46296</v>
       </c>
       <c r="G24" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>14</v>
       </c>
@@ -2144,20 +2116,20 @@
         <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="12">
         <v>46296</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G25" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -2165,17 +2137,17 @@
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="12">
         <v>46388</v>
       </c>
       <c r="G26" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -2183,56 +2155,56 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="12">
         <v>46388</v>
       </c>
       <c r="G27" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="12">
         <v>46388</v>
       </c>
       <c r="G28" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>374</v>
+        <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="12"/>
       <c r="G29" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -2240,30 +2212,30 @@
         <v>46388</v>
       </c>
       <c r="G30" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="12">
         <v>46388</v>
       </c>
       <c r="G31" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>7</v>
@@ -2274,46 +2246,46 @@
         <v>46388</v>
       </c>
       <c r="G32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="12">
         <v>46388</v>
       </c>
       <c r="G33" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="12">
         <v>46388</v>
       </c>
       <c r="G34" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>22</v>
       </c>
@@ -2321,97 +2293,97 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="12">
         <v>46388</v>
       </c>
       <c r="G35" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="12">
         <v>46388</v>
       </c>
       <c r="G36" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="12">
         <v>46388</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G37" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="12">
         <v>46388</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G38" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="12">
         <v>46661</v>
       </c>
       <c r="G39" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>5</v>
@@ -2422,126 +2394,126 @@
         <v>46661</v>
       </c>
       <c r="G40" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="12">
         <v>46661</v>
       </c>
       <c r="G41" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="12">
         <v>46661</v>
       </c>
       <c r="G42" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="12">
         <v>46661</v>
       </c>
       <c r="G43" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="12">
         <v>46661</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G44" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D45" s="16"/>
       <c r="E45" s="12">
         <v>46388</v>
       </c>
       <c r="G45" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D46" s="16"/>
       <c r="E46" s="12">
         <v>46388</v>
       </c>
       <c r="G46" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2549,105 +2521,105 @@
         <v>46388</v>
       </c>
       <c r="G47" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="12">
         <v>46388</v>
       </c>
       <c r="G48" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="12">
         <v>46388</v>
       </c>
       <c r="G49" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="12">
         <v>46388</v>
       </c>
       <c r="G50" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="12">
         <v>46388</v>
       </c>
       <c r="G51" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="12">
         <v>46388</v>
       </c>
       <c r="G52" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -2655,308 +2627,308 @@
         <v>46388</v>
       </c>
       <c r="G53" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E54" s="12">
         <v>46388</v>
       </c>
       <c r="G54" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="12">
         <v>46388</v>
       </c>
       <c r="G55" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="12">
         <v>46388</v>
       </c>
       <c r="G56" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="12">
         <v>46388</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G57" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="12">
         <v>46388</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G58" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E59" s="12">
         <v>46388</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="12">
         <v>46388</v>
       </c>
       <c r="G60" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="12">
         <v>46388</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="12">
         <v>46388</v>
       </c>
       <c r="G62" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="12">
         <v>46388</v>
       </c>
       <c r="G63" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="12">
         <v>46388</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="12">
         <v>46388</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G65" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="12">
         <v>46388</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G66" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E67" s="12">
         <v>46388</v>
       </c>
       <c r="G67" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E68" s="12">
         <v>46388</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2964,12 +2936,12 @@
         <v>46388</v>
       </c>
       <c r="G69" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>13</v>
@@ -2980,316 +2952,316 @@
         <v>46388</v>
       </c>
       <c r="G70" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E71" s="12">
         <v>46388</v>
       </c>
       <c r="G71" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E72" s="12">
         <v>46388</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C73" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D73" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E73" s="12">
         <v>46388</v>
       </c>
       <c r="G73" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E74" s="12">
         <v>46388</v>
       </c>
       <c r="G74" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B75" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C75" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E75" s="12">
         <v>46388</v>
       </c>
       <c r="G75" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C76" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E76" s="12">
         <v>46388</v>
       </c>
       <c r="G76" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B77" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E77" s="12">
         <v>46388</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" t="s">
         <v>45</v>
       </c>
-      <c r="B78" t="s">
-        <v>52</v>
-      </c>
       <c r="C78" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E78" s="12">
         <v>46388</v>
       </c>
       <c r="G78" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B79" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" t="s">
         <v>53</v>
-      </c>
-      <c r="C79" t="s">
-        <v>60</v>
       </c>
       <c r="E79" s="12">
         <v>46388</v>
       </c>
       <c r="G79" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B80" t="s">
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E80" s="12">
         <v>46388</v>
       </c>
       <c r="G80" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E81" s="12">
         <v>46388</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G81" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E82" s="12">
         <v>46388</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G82" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E83" s="12">
         <v>46388</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G83" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E84" s="12">
         <v>46388</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G84" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B85" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E85" s="13">
         <v>46388</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="E86" s="13">
         <v>46388</v>
       </c>
       <c r="G86" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B87" t="s">
         <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E87" s="13">
         <v>46388</v>
       </c>
       <c r="G87" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B88" t="s">
         <v>5</v>
@@ -3298,26 +3270,26 @@
         <v>46388</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B89" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E89" s="13">
         <v>46388</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -3326,322 +3298,322 @@
         <v>46388</v>
       </c>
       <c r="G90" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B91" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E91" s="13">
         <v>46388</v>
       </c>
       <c r="G91" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E92" s="13">
         <v>46388</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G92" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E93" s="13">
         <v>46388</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E94" s="13">
         <v>46631</v>
       </c>
       <c r="G94" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B95" t="s">
         <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E95" s="13">
         <v>46631</v>
       </c>
       <c r="G95" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B96" t="s">
         <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E96" s="13">
         <v>46631</v>
       </c>
       <c r="G96" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B97" t="s">
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E97" s="13">
         <v>46631</v>
       </c>
       <c r="G97" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E98" s="13">
         <v>46631</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E99" s="13">
         <v>46631</v>
       </c>
       <c r="G99" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E100" s="13">
         <v>46631</v>
       </c>
       <c r="G100" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B101" t="s">
         <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E101" s="13"/>
       <c r="G101" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C102" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E102" s="13">
         <v>46631</v>
       </c>
       <c r="G102" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C103" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E103" s="13">
         <v>46631</v>
       </c>
       <c r="F103" s="15" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G103" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E104" s="13">
         <v>46631</v>
       </c>
       <c r="G104" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B105" t="s">
         <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E105" s="13">
         <v>46631</v>
       </c>
       <c r="G105" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B106" t="s">
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E106" s="13">
         <v>46631</v>
       </c>
       <c r="G106" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B107" t="s">
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E107" s="13">
         <v>46631</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B108" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E108" s="13">
         <v>46296</v>
       </c>
       <c r="G108" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B109" t="s">
         <v>5</v>
@@ -3650,12 +3622,12 @@
         <v>46296</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -3664,43 +3636,43 @@
         <v>46296</v>
       </c>
       <c r="G110" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E111" s="13">
         <v>46296</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B112" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E112" s="13">
         <v>46569</v>
       </c>
       <c r="G112" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B113" t="s">
         <v>19</v>
@@ -3709,12 +3681,12 @@
         <v>46569</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -3723,135 +3695,182 @@
         <v>46569</v>
       </c>
       <c r="G114" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B115" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E115" s="13">
         <v>46569</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B116" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C116" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E116" s="13">
         <v>46569</v>
       </c>
       <c r="G116" s="20" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B117" t="s">
         <v>10</v>
       </c>
       <c r="E117" s="13"/>
       <c r="G117" s="20" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B118" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C118" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E118" s="13">
         <v>46569</v>
       </c>
       <c r="G118" s="20" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B119" t="s">
         <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E119" s="13">
         <v>46569</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B120" t="s">
         <v>6</v>
       </c>
       <c r="C120" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="E120" s="13">
         <v>46569</v>
       </c>
       <c r="G120" s="20" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="E121" s="13">
         <v>46569</v>
       </c>
       <c r="F121" s="15"/>
       <c r="G121" s="20" t="s">
-        <v>182</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>370</v>
+      </c>
+      <c r="B122" t="s">
+        <v>28</v>
+      </c>
+      <c r="E122" s="13">
+        <v>46388</v>
+      </c>
+      <c r="G122" s="20" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>370</v>
+      </c>
+      <c r="B123" t="s">
+        <v>5</v>
+      </c>
+      <c r="E123" s="13">
+        <v>46388</v>
+      </c>
+      <c r="G123" s="20" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>370</v>
+      </c>
+      <c r="B124" t="s">
+        <v>6</v>
+      </c>
+      <c r="E124" s="13">
+        <v>46388</v>
+      </c>
+      <c r="G124" s="20" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>370</v>
+      </c>
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" s="13">
+        <v>46388</v>
+      </c>
+      <c r="G125" s="20" t="s">
+        <v>369</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F121" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="4676 - Itaipu - Implementação SAP Cloud ERP"/>
-        <filter val="4723 - Sooro Renner Nutricao S/A | Grow"/>
-        <filter val="4791 - TUTI EL ROSADO"/>
-        <filter val="4886 - PRINCIPIA COSMÉTICOS"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F121" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3874,27 +3893,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D2" s="4">
         <v>46113</v>
@@ -3905,13 +3924,13 @@
     </row>
     <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D3" s="4">
         <v>46113</v>
@@ -3922,13 +3941,13 @@
     </row>
     <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D4" s="4">
         <v>46114</v>
@@ -3939,13 +3958,13 @@
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D5" s="4">
         <v>46128</v>
@@ -3956,13 +3975,13 @@
     </row>
     <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D6" s="4">
         <v>46122</v>
@@ -3973,13 +3992,13 @@
     </row>
     <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D7" s="4">
         <v>46126</v>
@@ -3990,13 +4009,13 @@
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D8" s="4">
         <v>46129</v>
@@ -4007,13 +4026,13 @@
     </row>
     <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D9" s="4">
         <v>46146</v>
@@ -4024,26 +4043,26 @@
     </row>
     <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D11" s="4">
         <v>46153</v>
@@ -4054,13 +4073,13 @@
     </row>
     <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D12" s="4">
         <v>46140</v>
@@ -4071,13 +4090,13 @@
     </row>
     <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D13" s="4">
         <v>46162</v>
@@ -4088,13 +4107,13 @@
     </row>
     <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="D14" s="4">
         <v>46163</v>
@@ -4105,10 +4124,10 @@
     </row>
     <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="4">
@@ -4120,13 +4139,13 @@
     </row>
     <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D16" s="4">
         <v>46160</v>
@@ -4137,13 +4156,13 @@
     </row>
     <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D17" s="4">
         <v>46140</v>
@@ -4154,13 +4173,13 @@
     </row>
     <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D18" s="4">
         <v>46150</v>
@@ -4171,13 +4190,13 @@
     </row>
     <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D19" s="4">
         <v>46150</v>
@@ -4188,13 +4207,13 @@
     </row>
     <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D20" s="4">
         <v>46147</v>
@@ -4205,13 +4224,13 @@
     </row>
     <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D21" s="4">
         <v>46149</v>
@@ -4222,13 +4241,13 @@
     </row>
     <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D22" s="4">
         <v>46181</v>
@@ -4239,13 +4258,13 @@
     </row>
     <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D23" s="4">
         <v>46170</v>
@@ -4256,13 +4275,13 @@
     </row>
     <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D24" s="4">
         <v>46168</v>
@@ -4273,13 +4292,13 @@
     </row>
     <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D25" s="4">
         <v>46167</v>
@@ -4290,13 +4309,13 @@
     </row>
     <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D26" s="4">
         <v>46174</v>
@@ -4307,13 +4326,13 @@
     </row>
     <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="D27" s="4">
         <v>46175</v>
@@ -4324,13 +4343,13 @@
     </row>
     <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="D28" s="4">
         <v>46171</v>
@@ -4341,13 +4360,13 @@
     </row>
     <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D29" s="4">
         <v>46170</v>
@@ -4358,13 +4377,13 @@
     </row>
     <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D30" s="4">
         <v>46181</v>
@@ -4375,13 +4394,13 @@
     </row>
     <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D31" s="4">
         <v>46178</v>
@@ -4392,13 +4411,13 @@
     </row>
     <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D32" s="4">
         <v>46170</v>
@@ -4409,13 +4428,13 @@
     </row>
     <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D33" s="4">
         <v>46181</v>
@@ -4426,26 +4445,26 @@
     </row>
     <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D35" s="4">
         <v>46155</v>
@@ -4456,13 +4475,13 @@
     </row>
     <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D36" s="4">
         <v>46167</v>
@@ -4473,13 +4492,13 @@
     </row>
     <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D37" s="4">
         <v>46167</v>
@@ -4490,13 +4509,13 @@
     </row>
     <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D38" s="4">
         <v>46168</v>
@@ -4507,13 +4526,13 @@
     </row>
     <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D39" s="4">
         <v>46175</v>
@@ -4524,13 +4543,13 @@
     </row>
     <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D40" s="4">
         <v>46188</v>
@@ -4541,13 +4560,13 @@
     </row>
     <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D41" s="4">
         <v>46195</v>
@@ -4558,13 +4577,13 @@
     </row>
     <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D42" s="4">
         <v>46202</v>
@@ -4575,10 +4594,10 @@
     </row>
     <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="4">
@@ -4590,10 +4609,10 @@
     </row>
     <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="4">
@@ -4605,13 +4624,13 @@
     </row>
     <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D45" s="4">
         <v>46223</v>
@@ -4622,13 +4641,13 @@
     </row>
     <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D46" s="4">
         <v>46223</v>
@@ -4639,10 +4658,10 @@
     </row>
     <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="4">
@@ -4654,13 +4673,13 @@
     </row>
     <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D48" s="4">
         <v>46230</v>
@@ -4671,13 +4690,13 @@
     </row>
     <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="D49" s="4">
         <v>46232</v>
@@ -4688,13 +4707,13 @@
     </row>
     <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D50" s="4">
         <v>46230</v>
@@ -4705,13 +4724,13 @@
     </row>
     <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D51" s="4">
         <v>46161</v>
@@ -4722,13 +4741,13 @@
     </row>
     <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D52" s="4">
         <v>46162</v>
@@ -4739,13 +4758,13 @@
     </row>
     <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D53" s="4">
         <v>46162</v>
@@ -4756,13 +4775,13 @@
     </row>
     <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D54" s="4">
         <v>46163</v>
@@ -4773,13 +4792,13 @@
     </row>
     <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D55" s="4">
         <v>46174</v>
@@ -4790,13 +4809,13 @@
     </row>
     <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D56" s="4">
         <v>46174</v>
@@ -4807,13 +4826,13 @@
     </row>
     <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D57" s="4">
         <v>46174</v>
@@ -4824,13 +4843,13 @@
     </row>
     <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="C58" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D58" s="4">
         <v>46181</v>
@@ -4841,13 +4860,13 @@
     </row>
     <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D59" s="4">
         <v>46181</v>
@@ -4858,13 +4877,13 @@
     </row>
     <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D60" s="4">
         <v>46181</v>
@@ -4875,13 +4894,13 @@
     </row>
     <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D61" s="4">
         <v>46181</v>
@@ -4892,13 +4911,13 @@
     </row>
     <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D62" s="4">
         <v>46182</v>
@@ -4909,13 +4928,13 @@
     </row>
     <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D63" s="4">
         <v>46184</v>
@@ -4926,13 +4945,13 @@
     </row>
     <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D64" s="4">
         <v>46188</v>
@@ -4943,13 +4962,13 @@
     </row>
     <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D65" s="4">
         <v>46188</v>
@@ -4960,13 +4979,13 @@
     </row>
     <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D66" s="4">
         <v>46198</v>
@@ -5324,36 +5343,36 @@
         <v>0</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F2" s="7">
         <v>46174</v>
@@ -5367,19 +5386,19 @@
     </row>
     <row r="3" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F3" s="7">
         <v>46175</v>
@@ -5393,19 +5412,19 @@
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F4" s="7">
         <v>46177</v>
@@ -5419,19 +5438,19 @@
     </row>
     <row r="5" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F5" s="7">
         <v>46178</v>
@@ -5445,19 +5464,19 @@
     </row>
     <row r="6" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F6" s="7">
         <v>46167</v>
@@ -5471,19 +5490,19 @@
     </row>
     <row r="7" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F7" s="7">
         <v>46168</v>
@@ -5497,19 +5516,19 @@
     </row>
     <row r="8" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F8" s="7">
         <v>46169</v>
@@ -5523,19 +5542,19 @@
     </row>
     <row r="9" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F9" s="7">
         <v>46170</v>
@@ -5549,19 +5568,19 @@
     </row>
     <row r="10" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F10" s="7">
         <v>46171</v>
@@ -5575,19 +5594,19 @@
     </row>
     <row r="11" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F11" s="7">
         <v>46167</v>
@@ -5601,19 +5620,19 @@
     </row>
     <row r="12" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F12" s="7">
         <v>46168</v>
@@ -5627,19 +5646,19 @@
     </row>
     <row r="13" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F13" s="7">
         <v>46169</v>
@@ -5653,19 +5672,19 @@
     </row>
     <row r="14" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F14" s="7">
         <v>46170</v>
@@ -5679,19 +5698,19 @@
     </row>
     <row r="15" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F15" s="7">
         <v>46171</v>
@@ -5705,19 +5724,19 @@
     </row>
     <row r="16" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D16" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="F16" s="7">
         <v>46167</v>
@@ -5731,19 +5750,19 @@
     </row>
     <row r="17" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D17" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F17" s="7">
         <v>46168</v>
@@ -5757,19 +5776,19 @@
     </row>
     <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F18" s="7">
         <v>46169</v>
@@ -5783,19 +5802,19 @@
     </row>
     <row r="19" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F19" s="7">
         <v>46169</v>
@@ -5809,19 +5828,19 @@
     </row>
     <row r="20" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F20" s="7">
         <v>46170</v>
@@ -5835,19 +5854,19 @@
     </row>
     <row r="21" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F21" s="7">
         <v>46170</v>
@@ -5861,19 +5880,19 @@
     </row>
     <row r="22" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F22" s="7">
         <v>46160</v>
@@ -5887,19 +5906,19 @@
     </row>
     <row r="23" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F23" s="7">
         <v>46161</v>
@@ -5913,19 +5932,19 @@
     </row>
     <row r="24" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C24" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>188</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="F24" s="7">
         <v>46162</v>
@@ -5939,19 +5958,19 @@
     </row>
     <row r="25" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F25" s="7">
         <v>46163</v>
@@ -5965,19 +5984,19 @@
     </row>
     <row r="26" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F26" s="7">
         <v>46164</v>
@@ -5991,19 +6010,19 @@
     </row>
     <row r="27" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D27" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F27" s="7">
         <v>46160</v>
@@ -6017,19 +6036,19 @@
     </row>
     <row r="28" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F28" s="7">
         <v>46161</v>
@@ -6043,19 +6062,19 @@
     </row>
     <row r="29" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D29" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F29" s="7">
         <v>46162</v>
@@ -6069,19 +6088,19 @@
     </row>
     <row r="30" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D30" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F30" s="7">
         <v>46163</v>
@@ -6095,19 +6114,19 @@
     </row>
     <row r="31" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D31" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F31" s="7">
         <v>46164</v>
@@ -6121,19 +6140,19 @@
     </row>
     <row r="32" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F32" s="7">
         <v>46160</v>
@@ -6147,19 +6166,19 @@
     </row>
     <row r="33" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F33" s="7">
         <v>46161</v>
@@ -6173,19 +6192,19 @@
     </row>
     <row r="34" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F34" s="7">
         <v>46162</v>
@@ -6199,19 +6218,19 @@
     </row>
     <row r="35" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F35" s="7">
         <v>46163</v>
@@ -6225,19 +6244,19 @@
     </row>
     <row r="36" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F36" s="7">
         <v>46163</v>
@@ -6251,19 +6270,19 @@
     </row>
     <row r="37" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F37" s="7">
         <v>46164</v>
@@ -6277,19 +6296,19 @@
     </row>
     <row r="38" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F38" s="7">
         <v>46160</v>
@@ -6303,19 +6322,19 @@
     </row>
     <row r="39" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F39" s="7">
         <v>46161</v>
@@ -6329,19 +6348,19 @@
     </row>
     <row r="40" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F40" s="7">
         <v>46162</v>
@@ -6355,19 +6374,19 @@
     </row>
     <row r="41" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F41" s="7">
         <v>46163</v>
@@ -6381,19 +6400,19 @@
     </row>
     <row r="42" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F42" s="7">
         <v>46164</v>
@@ -6407,19 +6426,19 @@
     </row>
     <row r="43" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F43" s="7">
         <v>46153</v>
@@ -6433,19 +6452,19 @@
     </row>
     <row r="44" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F44" s="7">
         <v>46154</v>
@@ -6459,19 +6478,19 @@
     </row>
     <row r="45" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F45" s="7">
         <v>46155</v>
@@ -6485,19 +6504,19 @@
     </row>
     <row r="46" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F46" s="7">
         <v>46156</v>
@@ -6511,19 +6530,19 @@
     </row>
     <row r="47" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F47" s="7">
         <v>46157</v>
@@ -6537,17 +6556,17 @@
     </row>
     <row r="48" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F48" s="7">
         <v>46153</v>
@@ -6561,17 +6580,17 @@
     </row>
     <row r="49" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F49" s="7">
         <v>46154</v>
@@ -6585,17 +6604,17 @@
     </row>
     <row r="50" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F50" s="7">
         <v>46155</v>
@@ -6609,17 +6628,17 @@
     </row>
     <row r="51" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F51" s="7">
         <v>46156</v>
@@ -6633,17 +6652,17 @@
     </row>
     <row r="52" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F52" s="7">
         <v>46157</v>
@@ -6657,19 +6676,19 @@
     </row>
     <row r="53" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F53" s="7">
         <v>46153</v>
@@ -6683,19 +6702,19 @@
     </row>
     <row r="54" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F54" s="7">
         <v>46154</v>
@@ -6709,19 +6728,19 @@
     </row>
     <row r="55" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F55" s="7">
         <v>46155</v>
@@ -6735,19 +6754,19 @@
     </row>
     <row r="56" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F56" s="7">
         <v>46156</v>
@@ -6761,19 +6780,19 @@
     </row>
     <row r="57" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F57" s="7">
         <v>46157</v>
@@ -6787,19 +6806,19 @@
     </row>
     <row r="58" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F58" s="7">
         <v>46153</v>
@@ -6813,19 +6832,19 @@
     </row>
     <row r="59" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F59" s="7">
         <v>46153</v>
@@ -6839,19 +6858,19 @@
     </row>
     <row r="60" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F60" s="7">
         <v>46154</v>
@@ -6865,19 +6884,19 @@
     </row>
     <row r="61" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="F61" s="7">
         <v>46154</v>
@@ -6891,19 +6910,19 @@
     </row>
     <row r="62" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F62" s="7">
         <v>46155</v>
@@ -6917,19 +6936,19 @@
     </row>
     <row r="63" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="F63" s="7">
         <v>46155</v>
@@ -6943,19 +6962,19 @@
     </row>
     <row r="64" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F64" s="7">
         <v>46156</v>
@@ -6969,19 +6988,19 @@
     </row>
     <row r="65" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F65" s="7">
         <v>46156</v>
@@ -6995,19 +7014,19 @@
     </row>
     <row r="66" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F66" s="7">
         <v>46157</v>
@@ -7021,19 +7040,19 @@
     </row>
     <row r="67" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E67" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="F67" s="7">
         <v>46157</v>
@@ -7047,19 +7066,19 @@
     </row>
     <row r="68" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F68" s="7">
         <v>46153</v>
@@ -7073,19 +7092,19 @@
     </row>
     <row r="69" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="F69" s="7">
         <v>46154</v>
@@ -7099,19 +7118,19 @@
     </row>
     <row r="70" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F70" s="7">
         <v>46155</v>
@@ -7125,19 +7144,19 @@
     </row>
     <row r="71" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F71" s="7">
         <v>46155</v>
@@ -7151,19 +7170,19 @@
     </row>
     <row r="72" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F72" s="7">
         <v>46155</v>
@@ -7177,19 +7196,19 @@
     </row>
     <row r="73" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F73" s="7">
         <v>46155</v>
@@ -7203,19 +7222,19 @@
     </row>
     <row r="74" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F74" s="7">
         <v>46156</v>
@@ -7229,19 +7248,19 @@
     </row>
     <row r="75" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F75" s="7">
         <v>46157</v>
@@ -7255,19 +7274,19 @@
     </row>
     <row r="76" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F76" s="7">
         <v>46153</v>
@@ -7281,19 +7300,19 @@
     </row>
     <row r="77" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F77" s="7">
         <v>46154</v>
@@ -7307,19 +7326,19 @@
     </row>
     <row r="78" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F78" s="7">
         <v>46155</v>
@@ -7333,19 +7352,19 @@
     </row>
     <row r="79" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F79" s="7">
         <v>46156</v>
@@ -7359,19 +7378,19 @@
     </row>
     <row r="80" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F80" s="7">
         <v>46157</v>
@@ -7385,19 +7404,19 @@
     </row>
     <row r="81" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C81" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B81" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D81" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F81" s="7">
         <v>46153</v>
@@ -7411,19 +7430,19 @@
     </row>
     <row r="82" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D82" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F82" s="7">
         <v>46154</v>
@@ -7437,19 +7456,19 @@
     </row>
     <row r="83" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C83" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B83" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D83" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F83" s="7">
         <v>46155</v>
@@ -7463,19 +7482,19 @@
     </row>
     <row r="84" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B84" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D84" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F84" s="7">
         <v>46156</v>
@@ -7489,19 +7508,19 @@
     </row>
     <row r="85" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C85" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D85" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F85" s="7">
         <v>46157</v>
@@ -7515,19 +7534,19 @@
     </row>
     <row r="86" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F86" s="7">
         <v>46146</v>
@@ -7541,19 +7560,19 @@
     </row>
     <row r="87" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F87" s="7">
         <v>46147</v>
@@ -7567,19 +7586,19 @@
     </row>
     <row r="88" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F88" s="7">
         <v>46148</v>
@@ -7593,19 +7612,19 @@
     </row>
     <row r="89" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F89" s="7">
         <v>46149</v>
@@ -7619,19 +7638,19 @@
     </row>
     <row r="90" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F90" s="7">
         <v>46150</v>
@@ -7645,19 +7664,19 @@
     </row>
     <row r="91" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F91" s="7">
         <v>46146</v>
@@ -7671,19 +7690,19 @@
     </row>
     <row r="92" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F92" s="7">
         <v>46146</v>
@@ -7697,19 +7716,19 @@
     </row>
     <row r="93" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F93" s="7">
         <v>46147</v>
@@ -7723,19 +7742,19 @@
     </row>
     <row r="94" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F94" s="7">
         <v>46147</v>
@@ -7749,19 +7768,19 @@
     </row>
     <row r="95" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F95" s="7">
         <v>46148</v>
@@ -7775,19 +7794,19 @@
     </row>
     <row r="96" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F96" s="7">
         <v>46149</v>
@@ -7801,19 +7820,19 @@
     </row>
     <row r="97" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F97" s="7">
         <v>46149</v>
@@ -7827,19 +7846,19 @@
     </row>
     <row r="98" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F98" s="7">
         <v>46150</v>
@@ -7853,19 +7872,19 @@
     </row>
     <row r="99" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F99" s="7">
         <v>46146</v>
@@ -7879,19 +7898,19 @@
     </row>
     <row r="100" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F100" s="7">
         <v>46147</v>
@@ -7905,19 +7924,19 @@
     </row>
     <row r="101" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F101" s="7">
         <v>46148</v>
@@ -7931,19 +7950,19 @@
     </row>
     <row r="102" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F102" s="7">
         <v>46149</v>
@@ -7957,19 +7976,19 @@
     </row>
     <row r="103" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F103" s="7">
         <v>46150</v>
@@ -7983,19 +8002,19 @@
     </row>
     <row r="104" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C104" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B104" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D104" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F104" s="7">
         <v>46146</v>
@@ -8009,19 +8028,19 @@
     </row>
     <row r="105" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C105" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B105" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D105" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F105" s="7">
         <v>46147</v>
@@ -8035,19 +8054,19 @@
     </row>
     <row r="106" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B106" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D106" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F106" s="7">
         <v>46148</v>
@@ -8061,19 +8080,19 @@
     </row>
     <row r="107" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C107" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B107" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D107" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F107" s="7">
         <v>46149</v>
@@ -8087,19 +8106,19 @@
     </row>
     <row r="108" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C108" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B108" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="D108" s="6" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F108" s="7">
         <v>46150</v>
@@ -8113,19 +8132,19 @@
     </row>
     <row r="109" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F109" s="7">
         <v>46146</v>
@@ -8139,19 +8158,19 @@
     </row>
     <row r="110" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F110" s="7">
         <v>46147</v>
@@ -8165,19 +8184,19 @@
     </row>
     <row r="111" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F111" s="7">
         <v>46148</v>
@@ -8191,19 +8210,19 @@
     </row>
     <row r="112" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F112" s="7">
         <v>46149</v>
@@ -8217,19 +8236,19 @@
     </row>
     <row r="113" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F113" s="7">
         <v>46150</v>
@@ -8243,17 +8262,17 @@
     </row>
     <row r="114" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="6" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F114" s="7">
         <v>46146</v>
@@ -8267,17 +8286,17 @@
     </row>
     <row r="115" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F115" s="7">
         <v>46147</v>
@@ -8291,17 +8310,17 @@
     </row>
     <row r="116" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F116" s="7">
         <v>46148</v>
@@ -8315,17 +8334,17 @@
     </row>
     <row r="117" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F117" s="7">
         <v>46149</v>
@@ -8339,17 +8358,17 @@
     </row>
     <row r="118" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F118" s="7">
         <v>46150</v>
@@ -8433,755 +8452,755 @@
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="D1" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="H1" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="I1" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="O1" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="P1" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="L1" s="17" t="s">
+      <c r="Q1" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="M1" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="N1" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="O1" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="P1" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q1" s="17" t="s">
-        <v>278</v>
-      </c>
       <c r="R1" s="17" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="C2" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C3" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C4" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C5" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C7" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C9" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C10" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="P10" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C11" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="R11" s="14" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C12" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="N12" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C13" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C15" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C16" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C17" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C18" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C19" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C20" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="P20" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C21" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C22" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="N22" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C23" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C24" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C25" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B26" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C26" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B27" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C27" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B28" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C28" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C29" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B30" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C30" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B31" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C31" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B32" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C32" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C33" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B34" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C34" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C35" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C36" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="B37" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C37" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C38" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C39" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C40" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C41" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C42" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C43" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C44" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C45" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C46" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C47" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C48" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O48" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="P48" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>258</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="L49" s="10" t="s">
         <v>265</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C50" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C51" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C52" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B54" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C54" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C210DB-B04C-7F41-A8A3-A6E9E8ED9414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3934A69-6FCB-0441-AA86-17238F01E7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Cookpit" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="376">
   <si>
     <t>Projeto</t>
   </si>
@@ -172,16 +172,10 @@
     <t>Consultor CO SR</t>
   </si>
   <si>
-    <t>Consultor PP / QM ESP</t>
-  </si>
-  <si>
     <t>Consultor PM SR</t>
   </si>
   <si>
     <t>Consultor Group Reporting SR</t>
-  </si>
-  <si>
-    <t>Consultor RE SR</t>
   </si>
   <si>
     <t>4723 - Sooro Renner Nutricao S/A | Grow</t>
@@ -1685,19 +1679,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1708,14 +1702,14 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="11">
         <v>46388</v>
       </c>
       <c r="G2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1726,14 +1720,14 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="11">
         <v>46388</v>
       </c>
       <c r="G3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1744,14 +1738,14 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="11">
         <v>46388</v>
       </c>
       <c r="G4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1762,14 +1756,14 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="11">
         <v>46388</v>
       </c>
       <c r="G5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1780,14 +1774,14 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="11">
         <v>46388</v>
       </c>
       <c r="G6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1798,14 +1792,14 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="11">
         <v>46388</v>
       </c>
       <c r="G7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1816,14 +1810,14 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="11">
         <v>46388</v>
       </c>
       <c r="G8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1834,14 +1828,14 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="11">
         <v>46388</v>
       </c>
       <c r="G9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1852,17 +1846,17 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="11">
         <v>46388</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1873,17 +1867,17 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="11">
         <v>46388</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1894,17 +1888,17 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="11">
         <v>46388</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1915,17 +1909,17 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="11">
         <v>46388</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1936,16 +1930,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E14" s="11">
         <v>46296</v>
       </c>
       <c r="G14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1956,16 +1950,16 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E15" s="11">
         <v>46296</v>
       </c>
       <c r="G15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1976,14 +1970,14 @@
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="11">
         <v>46296</v>
       </c>
       <c r="G16" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1991,15 +1985,15 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="11"/>
       <c r="G17" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2010,14 +2004,14 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="11">
         <v>46296</v>
       </c>
       <c r="G18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2028,14 +2022,14 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="11">
         <v>46296</v>
       </c>
       <c r="G19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2046,14 +2040,14 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="11">
         <v>46296</v>
       </c>
       <c r="G20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2064,14 +2058,14 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="11">
         <v>46296</v>
       </c>
       <c r="G21" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2082,14 +2076,14 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="11">
         <v>46296</v>
       </c>
       <c r="G22" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2100,14 +2094,14 @@
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="11">
         <v>46296</v>
       </c>
       <c r="G23" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2118,14 +2112,14 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="11">
         <v>46296</v>
       </c>
       <c r="G24" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2136,17 +2130,17 @@
         <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="11">
         <v>46296</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2157,14 +2151,14 @@
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="11">
         <v>46388</v>
       </c>
       <c r="G26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2175,14 +2169,14 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="11">
         <v>46388</v>
       </c>
       <c r="G27" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2193,14 +2187,14 @@
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="11">
         <v>46388</v>
       </c>
       <c r="G28" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2208,15 +2202,15 @@
         <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="11"/>
       <c r="G29" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2232,7 +2226,7 @@
         <v>46388</v>
       </c>
       <c r="G30" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2243,14 +2237,14 @@
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="11">
         <v>46388</v>
       </c>
       <c r="G31" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2266,7 +2260,7 @@
         <v>46388</v>
       </c>
       <c r="G32" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2277,14 +2271,14 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="11">
         <v>46388</v>
       </c>
       <c r="G33" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2295,14 +2289,14 @@
         <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="11">
         <v>46388</v>
       </c>
       <c r="G34" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2313,14 +2307,14 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="11">
         <v>46388</v>
       </c>
       <c r="G35" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2331,14 +2325,14 @@
         <v>26</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="11">
         <v>46388</v>
       </c>
       <c r="G36" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2349,17 +2343,17 @@
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="11">
         <v>46388</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G37" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2370,17 +2364,17 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="11">
         <v>46388</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2391,14 +2385,14 @@
         <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="11">
         <v>46661</v>
       </c>
       <c r="G39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2414,7 +2408,7 @@
         <v>46661</v>
       </c>
       <c r="G40" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2425,14 +2419,14 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="11">
         <v>46661</v>
       </c>
       <c r="G41" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2443,14 +2437,14 @@
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="11">
         <v>46661</v>
       </c>
       <c r="G42" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2461,14 +2455,14 @@
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="11">
         <v>46661</v>
       </c>
       <c r="G43" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2479,17 +2473,17 @@
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="11">
         <v>46661</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2500,14 +2494,14 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="11">
         <v>46388</v>
       </c>
       <c r="G45" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2518,14 +2512,14 @@
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D46" s="15"/>
       <c r="E46" s="11">
         <v>46388</v>
       </c>
       <c r="G46" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2533,7 +2527,7 @@
         <v>29</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2541,7 +2535,7 @@
         <v>46388</v>
       </c>
       <c r="G47" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2552,14 +2546,14 @@
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="11">
         <v>46388</v>
       </c>
       <c r="G48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2570,14 +2564,14 @@
         <v>30</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="11">
         <v>46388</v>
       </c>
       <c r="G49" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2588,14 +2582,14 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="11">
         <v>46388</v>
       </c>
       <c r="G50" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2606,14 +2600,14 @@
         <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="11">
         <v>46388</v>
       </c>
       <c r="G51" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2624,14 +2618,14 @@
         <v>26</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="11">
         <v>46388</v>
       </c>
       <c r="G52" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2647,7 +2641,7 @@
         <v>46388</v>
       </c>
       <c r="G53" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2658,16 +2652,16 @@
         <v>32</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E54" s="11">
         <v>46388</v>
       </c>
       <c r="G54" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2678,14 +2672,14 @@
         <v>33</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="11">
         <v>46388</v>
       </c>
       <c r="G55" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2696,14 +2690,14 @@
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="11">
         <v>46388</v>
       </c>
       <c r="G56" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2714,17 +2708,17 @@
         <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="11">
         <v>46388</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G57" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2735,17 +2729,17 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="11">
         <v>46388</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G58" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2756,16 +2750,16 @@
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E59" s="11">
         <v>46388</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2776,14 +2770,14 @@
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="11">
         <v>46388</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2791,17 +2785,17 @@
         <v>34</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="11">
         <v>46388</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2812,14 +2806,14 @@
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="11">
         <v>46388</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2830,14 +2824,14 @@
         <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="11">
         <v>46388</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2848,14 +2842,14 @@
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="11">
         <v>46388</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2866,17 +2860,17 @@
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="11">
         <v>46388</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2887,17 +2881,17 @@
         <v>35</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="11">
         <v>46388</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2908,16 +2902,16 @@
         <v>36</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E67" s="11">
         <v>46388</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2928,19 +2922,19 @@
         <v>37</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E68" s="11">
         <v>46388</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2948,7 +2942,7 @@
         <v>34</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2956,7 +2950,7 @@
         <v>46388</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2972,7 +2966,7 @@
         <v>46388</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2983,13 +2977,13 @@
         <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E71" s="11">
         <v>46388</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3000,13 +2994,13 @@
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E72" s="11">
         <v>46388</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3017,16 +3011,16 @@
         <v>41</v>
       </c>
       <c r="C73" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D73" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E73" s="11">
         <v>46388</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3037,13 +3031,13 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E74" s="11">
         <v>46388</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3054,13 +3048,13 @@
         <v>42</v>
       </c>
       <c r="C75" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E75" s="11">
         <v>46388</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3068,16 +3062,16 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="C76" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E76" s="11">
         <v>46388</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3085,16 +3079,16 @@
         <v>38</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C77" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E77" s="11">
         <v>46388</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3102,16 +3096,16 @@
         <v>38</v>
       </c>
       <c r="B78" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C78" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E78" s="11">
         <v>46388</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3119,16 +3113,16 @@
         <v>38</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C79" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E79" s="11">
         <v>46388</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3139,13 +3133,13 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E80" s="11">
         <v>46388</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3156,16 +3150,16 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E81" s="11">
         <v>46388</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3176,16 +3170,16 @@
         <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E82" s="11">
         <v>46388</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3196,16 +3190,16 @@
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E83" s="11">
         <v>46388</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3216,72 +3210,72 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E84" s="11">
         <v>46388</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E85" s="12">
         <v>46388</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E86" s="12">
         <v>46388</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
         <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E87" s="12">
         <v>46388</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
         <v>5</v>
@@ -3290,26 +3284,26 @@
         <v>46388</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E89" s="12">
         <v>46388</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -3318,308 +3312,308 @@
         <v>46388</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E91" s="12">
         <v>46388</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E92" s="12">
         <v>46388</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E93" s="12">
         <v>46388</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E94" s="12">
         <v>46631</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B95" t="s">
         <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E95" s="12">
         <v>46631</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B96" t="s">
         <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E96" s="12">
         <v>46631</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B97" t="s">
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E97" s="12">
         <v>46631</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E98" s="12">
         <v>46631</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E99" s="12">
         <v>46631</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E100" s="12">
         <v>46631</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B101" t="s">
         <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E101" s="12"/>
       <c r="G101" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B102" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C102" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E102" s="12">
         <v>46631</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>46</v>
+      </c>
+      <c r="B103" t="s">
         <v>48</v>
       </c>
-      <c r="B103" t="s">
-        <v>50</v>
-      </c>
       <c r="C103" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E103" s="12">
         <v>46631</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>367</v>
+        <v>172</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B104" t="s">
         <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E104" s="12">
         <v>46631</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B105" t="s">
         <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E105" s="12">
         <v>46631</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B106" t="s">
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E106" s="12">
         <v>46631</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B107" t="s">
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E107" s="12">
         <v>46631</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B108" t="s">
         <v>28</v>
@@ -3628,12 +3622,12 @@
         <v>46296</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B109" t="s">
         <v>5</v>
@@ -3642,12 +3636,12 @@
         <v>46296</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -3656,29 +3650,29 @@
         <v>46296</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E111" s="12">
         <v>46296</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B112" t="s">
         <v>33</v>
@@ -3687,12 +3681,12 @@
         <v>46569</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B113" t="s">
         <v>19</v>
@@ -3701,12 +3695,12 @@
         <v>46569</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -3715,127 +3709,127 @@
         <v>46569</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B115" t="s">
         <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E115" s="12">
         <v>46569</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>349</v>
+      </c>
+      <c r="B116" t="s">
+        <v>350</v>
+      </c>
+      <c r="C116" t="s">
         <v>351</v>
-      </c>
-      <c r="B116" t="s">
-        <v>352</v>
-      </c>
-      <c r="C116" t="s">
-        <v>353</v>
       </c>
       <c r="E116" s="12">
         <v>46569</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B117" t="s">
         <v>10</v>
       </c>
       <c r="E117" s="12"/>
       <c r="G117" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B118" t="s">
         <v>28</v>
       </c>
       <c r="C118" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E118" s="12">
         <v>46569</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B119" t="s">
         <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E119" s="12">
         <v>46569</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B120" t="s">
         <v>6</v>
       </c>
       <c r="C120" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E120" s="12">
         <v>46569</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E121" s="12">
         <v>46569</v>
       </c>
       <c r="F121" s="14"/>
       <c r="G121" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B122" t="s">
         <v>28</v>
@@ -3844,12 +3838,12 @@
         <v>46388</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B123" t="s">
         <v>5</v>
@@ -3858,12 +3852,12 @@
         <v>46388</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
@@ -3872,12 +3866,12 @@
         <v>46388</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
@@ -3886,7 +3880,7 @@
         <v>46388</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -3913,27 +3907,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D2" s="3">
         <v>46113</v>
@@ -3944,13 +3938,13 @@
     </row>
     <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D3" s="3">
         <v>46113</v>
@@ -3961,13 +3955,13 @@
     </row>
     <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D4" s="3">
         <v>46114</v>
@@ -3978,13 +3972,13 @@
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3">
         <v>46128</v>
@@ -3995,13 +3989,13 @@
     </row>
     <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D6" s="3">
         <v>46122</v>
@@ -4012,13 +4006,13 @@
     </row>
     <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3">
         <v>46126</v>
@@ -4029,13 +4023,13 @@
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3">
         <v>46129</v>
@@ -4046,13 +4040,13 @@
     </row>
     <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="D9" s="3">
         <v>46146</v>
@@ -4063,26 +4057,26 @@
     </row>
     <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3">
         <v>46153</v>
@@ -4093,13 +4087,13 @@
     </row>
     <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3">
         <v>46140</v>
@@ -4110,13 +4104,13 @@
     </row>
     <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" s="3">
         <v>46162</v>
@@ -4127,13 +4121,13 @@
     </row>
     <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D14" s="3">
         <v>46163</v>
@@ -4144,10 +4138,10 @@
     </row>
     <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3">
@@ -4159,13 +4153,13 @@
     </row>
     <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" s="3">
         <v>46160</v>
@@ -4176,13 +4170,13 @@
     </row>
     <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D17" s="3">
         <v>46140</v>
@@ -4193,13 +4187,13 @@
     </row>
     <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" s="3">
         <v>46150</v>
@@ -4210,13 +4204,13 @@
     </row>
     <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" s="3">
         <v>46150</v>
@@ -4227,13 +4221,13 @@
     </row>
     <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D20" s="3">
         <v>46147</v>
@@ -4244,13 +4238,13 @@
     </row>
     <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D21" s="3">
         <v>46149</v>
@@ -4261,13 +4255,13 @@
     </row>
     <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D22" s="3">
         <v>46181</v>
@@ -4278,13 +4272,13 @@
     </row>
     <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D23" s="3">
         <v>46170</v>
@@ -4295,13 +4289,13 @@
     </row>
     <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D24" s="3">
         <v>46168</v>
@@ -4312,13 +4306,13 @@
     </row>
     <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D25" s="3">
         <v>46167</v>
@@ -4329,13 +4323,13 @@
     </row>
     <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D26" s="3">
         <v>46174</v>
@@ -4346,13 +4340,13 @@
     </row>
     <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D27" s="3">
         <v>46175</v>
@@ -4363,13 +4357,13 @@
     </row>
     <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D28" s="3">
         <v>46171</v>
@@ -4380,13 +4374,13 @@
     </row>
     <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D29" s="3">
         <v>46170</v>
@@ -4397,13 +4391,13 @@
     </row>
     <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D30" s="3">
         <v>46181</v>
@@ -4414,13 +4408,13 @@
     </row>
     <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D31" s="3">
         <v>46178</v>
@@ -4431,13 +4425,13 @@
     </row>
     <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D32" s="3">
         <v>46170</v>
@@ -4448,13 +4442,13 @@
     </row>
     <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D33" s="3">
         <v>46181</v>
@@ -4465,26 +4459,26 @@
     </row>
     <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D35" s="3">
         <v>46155</v>
@@ -4495,13 +4489,13 @@
     </row>
     <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D36" s="3">
         <v>46167</v>
@@ -4512,13 +4506,13 @@
     </row>
     <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D37" s="3">
         <v>46167</v>
@@ -4529,13 +4523,13 @@
     </row>
     <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="D38" s="3">
         <v>46168</v>
@@ -4546,13 +4540,13 @@
     </row>
     <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D39" s="3">
         <v>46175</v>
@@ -4563,13 +4557,13 @@
     </row>
     <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D40" s="3">
         <v>46188</v>
@@ -4580,13 +4574,13 @@
     </row>
     <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D41" s="3">
         <v>46195</v>
@@ -4597,13 +4591,13 @@
     </row>
     <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D42" s="3">
         <v>46202</v>
@@ -4614,10 +4608,10 @@
     </row>
     <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="3">
@@ -4629,10 +4623,10 @@
     </row>
     <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="3">
@@ -4644,13 +4638,13 @@
     </row>
     <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D45" s="3">
         <v>46223</v>
@@ -4661,13 +4655,13 @@
     </row>
     <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D46" s="3">
         <v>46223</v>
@@ -4678,10 +4672,10 @@
     </row>
     <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="3">
@@ -4693,13 +4687,13 @@
     </row>
     <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D48" s="3">
         <v>46230</v>
@@ -4710,13 +4704,13 @@
     </row>
     <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D49" s="3">
         <v>46232</v>
@@ -4727,13 +4721,13 @@
     </row>
     <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D50" s="3">
         <v>46230</v>
@@ -4744,13 +4738,13 @@
     </row>
     <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D51" s="3">
         <v>46161</v>
@@ -4761,13 +4755,13 @@
     </row>
     <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D52" s="3">
         <v>46162</v>
@@ -4778,13 +4772,13 @@
     </row>
     <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D53" s="3">
         <v>46162</v>
@@ -4795,13 +4789,13 @@
     </row>
     <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="C54" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D54" s="3">
         <v>46163</v>
@@ -4812,13 +4806,13 @@
     </row>
     <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D55" s="3">
         <v>46174</v>
@@ -4829,13 +4823,13 @@
     </row>
     <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D56" s="3">
         <v>46174</v>
@@ -4846,13 +4840,13 @@
     </row>
     <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D57" s="3">
         <v>46174</v>
@@ -4863,13 +4857,13 @@
     </row>
     <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D58" s="3">
         <v>46181</v>
@@ -4880,13 +4874,13 @@
     </row>
     <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D59" s="3">
         <v>46181</v>
@@ -4897,13 +4891,13 @@
     </row>
     <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D60" s="3">
         <v>46181</v>
@@ -4914,13 +4908,13 @@
     </row>
     <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D61" s="3">
         <v>46181</v>
@@ -4931,13 +4925,13 @@
     </row>
     <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D62" s="3">
         <v>46182</v>
@@ -4948,13 +4942,13 @@
     </row>
     <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D63" s="3">
         <v>46184</v>
@@ -4965,13 +4959,13 @@
     </row>
     <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D64" s="3">
         <v>46188</v>
@@ -4982,13 +4976,13 @@
     </row>
     <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D65" s="3">
         <v>46188</v>
@@ -4999,13 +4993,13 @@
     </row>
     <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D66" s="3">
         <v>46198</v>
@@ -5362,30 +5356,30 @@
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="E2" s="6">
         <v>46174</v>
@@ -5399,16 +5393,16 @@
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="E3" s="6">
         <v>46175</v>
@@ -5422,16 +5416,16 @@
     </row>
     <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="E4" s="6">
         <v>46177</v>
@@ -5445,16 +5439,16 @@
     </row>
     <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="E5" s="6">
         <v>46178</v>
@@ -5468,16 +5462,16 @@
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E6" s="6">
         <v>46167</v>
@@ -5491,16 +5485,16 @@
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E7" s="6">
         <v>46168</v>
@@ -5514,16 +5508,16 @@
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E8" s="6">
         <v>46169</v>
@@ -5537,16 +5531,16 @@
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E9" s="6">
         <v>46170</v>
@@ -5560,16 +5554,16 @@
     </row>
     <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E10" s="6">
         <v>46171</v>
@@ -5583,16 +5577,16 @@
     </row>
     <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E11" s="6">
         <v>46167</v>
@@ -5606,16 +5600,16 @@
     </row>
     <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E12" s="6">
         <v>46168</v>
@@ -5629,16 +5623,16 @@
     </row>
     <row r="13" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E13" s="6">
         <v>46169</v>
@@ -5652,16 +5646,16 @@
     </row>
     <row r="14" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E14" s="6">
         <v>46170</v>
@@ -5675,16 +5669,16 @@
     </row>
     <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E15" s="6">
         <v>46171</v>
@@ -5698,16 +5692,16 @@
     </row>
     <row r="16" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E16" s="6">
         <v>46167</v>
@@ -5721,16 +5715,16 @@
     </row>
     <row r="17" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>180</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>182</v>
       </c>
       <c r="E17" s="6">
         <v>46168</v>
@@ -5744,16 +5738,16 @@
     </row>
     <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E18" s="6">
         <v>46169</v>
@@ -5767,16 +5761,16 @@
     </row>
     <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E19" s="6">
         <v>46169</v>
@@ -5790,16 +5784,16 @@
     </row>
     <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="E20" s="6">
         <v>46170</v>
@@ -5813,16 +5807,16 @@
     </row>
     <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="E21" s="6">
         <v>46170</v>
@@ -5836,16 +5830,16 @@
     </row>
     <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E22" s="6">
         <v>46160</v>
@@ -5859,16 +5853,16 @@
     </row>
     <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E23" s="6">
         <v>46161</v>
@@ -5882,16 +5876,16 @@
     </row>
     <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E24" s="6">
         <v>46162</v>
@@ -5905,16 +5899,16 @@
     </row>
     <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E25" s="6">
         <v>46163</v>
@@ -5928,16 +5922,16 @@
     </row>
     <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E26" s="6">
         <v>46164</v>
@@ -5951,16 +5945,16 @@
     </row>
     <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E27" s="6">
         <v>46160</v>
@@ -5974,16 +5968,16 @@
     </row>
     <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E28" s="6">
         <v>46161</v>
@@ -5997,16 +5991,16 @@
     </row>
     <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E29" s="6">
         <v>46162</v>
@@ -6020,16 +6014,16 @@
     </row>
     <row r="30" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E30" s="6">
         <v>46163</v>
@@ -6043,16 +6037,16 @@
     </row>
     <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E31" s="6">
         <v>46164</v>
@@ -6066,16 +6060,16 @@
     </row>
     <row r="32" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E32" s="6">
         <v>46160</v>
@@ -6089,16 +6083,16 @@
     </row>
     <row r="33" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E33" s="6">
         <v>46161</v>
@@ -6112,16 +6106,16 @@
     </row>
     <row r="34" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E34" s="6">
         <v>46162</v>
@@ -6135,16 +6129,16 @@
     </row>
     <row r="35" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E35" s="6">
         <v>46163</v>
@@ -6158,16 +6152,16 @@
     </row>
     <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E36" s="6">
         <v>46163</v>
@@ -6181,16 +6175,16 @@
     </row>
     <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E37" s="6">
         <v>46164</v>
@@ -6204,16 +6198,16 @@
     </row>
     <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E38" s="6">
         <v>46160</v>
@@ -6227,16 +6221,16 @@
     </row>
     <row r="39" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E39" s="6">
         <v>46161</v>
@@ -6250,16 +6244,16 @@
     </row>
     <row r="40" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E40" s="6">
         <v>46162</v>
@@ -6273,16 +6267,16 @@
     </row>
     <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E41" s="6">
         <v>46163</v>
@@ -6296,16 +6290,16 @@
     </row>
     <row r="42" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E42" s="6">
         <v>46164</v>
@@ -6319,16 +6313,16 @@
     </row>
     <row r="43" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E43" s="6">
         <v>46153</v>
@@ -6342,16 +6336,16 @@
     </row>
     <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E44" s="6">
         <v>46154</v>
@@ -6365,16 +6359,16 @@
     </row>
     <row r="45" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E45" s="6">
         <v>46155</v>
@@ -6388,16 +6382,16 @@
     </row>
     <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E46" s="6">
         <v>46156</v>
@@ -6411,16 +6405,16 @@
     </row>
     <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E47" s="6">
         <v>46157</v>
@@ -6434,16 +6428,16 @@
     </row>
     <row r="48" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E48" s="6">
         <v>46153</v>
@@ -6457,16 +6451,16 @@
     </row>
     <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E49" s="6">
         <v>46154</v>
@@ -6480,16 +6474,16 @@
     </row>
     <row r="50" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E50" s="6">
         <v>46155</v>
@@ -6503,16 +6497,16 @@
     </row>
     <row r="51" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E51" s="6">
         <v>46156</v>
@@ -6526,16 +6520,16 @@
     </row>
     <row r="52" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E52" s="6">
         <v>46157</v>
@@ -6549,16 +6543,16 @@
     </row>
     <row r="53" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E53" s="6">
         <v>46153</v>
@@ -6572,16 +6566,16 @@
     </row>
     <row r="54" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E54" s="6">
         <v>46154</v>
@@ -6595,16 +6589,16 @@
     </row>
     <row r="55" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E55" s="6">
         <v>46155</v>
@@ -6618,16 +6612,16 @@
     </row>
     <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E56" s="6">
         <v>46156</v>
@@ -6641,16 +6635,16 @@
     </row>
     <row r="57" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E57" s="6">
         <v>46157</v>
@@ -6664,16 +6658,16 @@
     </row>
     <row r="58" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D58" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="E58" s="6">
         <v>46153</v>
@@ -6687,16 +6681,16 @@
     </row>
     <row r="59" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E59" s="6">
         <v>46153</v>
@@ -6710,16 +6704,16 @@
     </row>
     <row r="60" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="E60" s="6">
         <v>46154</v>
@@ -6733,16 +6727,16 @@
     </row>
     <row r="61" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E61" s="6">
         <v>46154</v>
@@ -6756,16 +6750,16 @@
     </row>
     <row r="62" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="E62" s="6">
         <v>46155</v>
@@ -6779,16 +6773,16 @@
     </row>
     <row r="63" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E63" s="6">
         <v>46155</v>
@@ -6802,16 +6796,16 @@
     </row>
     <row r="64" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D64" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="E64" s="6">
         <v>46156</v>
@@ -6825,16 +6819,16 @@
     </row>
     <row r="65" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E65" s="6">
         <v>46156</v>
@@ -6848,16 +6842,16 @@
     </row>
     <row r="66" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="E66" s="6">
         <v>46157</v>
@@ -6871,16 +6865,16 @@
     </row>
     <row r="67" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E67" s="6">
         <v>46157</v>
@@ -6894,16 +6888,16 @@
     </row>
     <row r="68" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E68" s="6">
         <v>46153</v>
@@ -6917,16 +6911,16 @@
     </row>
     <row r="69" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E69" s="6">
         <v>46154</v>
@@ -6940,16 +6934,16 @@
     </row>
     <row r="70" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E70" s="6">
         <v>46155</v>
@@ -6963,16 +6957,16 @@
     </row>
     <row r="71" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E71" s="6">
         <v>46155</v>
@@ -6986,16 +6980,16 @@
     </row>
     <row r="72" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D72" s="5" t="s">
         <v>209</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="E72" s="6">
         <v>46155</v>
@@ -7009,16 +7003,16 @@
     </row>
     <row r="73" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E73" s="6">
         <v>46155</v>
@@ -7032,16 +7026,16 @@
     </row>
     <row r="74" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E74" s="6">
         <v>46156</v>
@@ -7055,16 +7049,16 @@
     </row>
     <row r="75" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E75" s="6">
         <v>46157</v>
@@ -7078,16 +7072,16 @@
     </row>
     <row r="76" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E76" s="6">
         <v>46153</v>
@@ -7101,16 +7095,16 @@
     </row>
     <row r="77" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E77" s="6">
         <v>46154</v>
@@ -7124,16 +7118,16 @@
     </row>
     <row r="78" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E78" s="6">
         <v>46155</v>
@@ -7147,16 +7141,16 @@
     </row>
     <row r="79" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E79" s="6">
         <v>46156</v>
@@ -7170,16 +7164,16 @@
     </row>
     <row r="80" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E80" s="6">
         <v>46157</v>
@@ -7193,16 +7187,16 @@
     </row>
     <row r="81" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E81" s="6">
         <v>46153</v>
@@ -7216,16 +7210,16 @@
     </row>
     <row r="82" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E82" s="6">
         <v>46154</v>
@@ -7239,16 +7233,16 @@
     </row>
     <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E83" s="6">
         <v>46155</v>
@@ -7262,16 +7256,16 @@
     </row>
     <row r="84" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E84" s="6">
         <v>46156</v>
@@ -7285,16 +7279,16 @@
     </row>
     <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E85" s="6">
         <v>46157</v>
@@ -7308,16 +7302,16 @@
     </row>
     <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E86" s="6">
         <v>46146</v>
@@ -7331,16 +7325,16 @@
     </row>
     <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E87" s="6">
         <v>46147</v>
@@ -7354,16 +7348,16 @@
     </row>
     <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E88" s="6">
         <v>46148</v>
@@ -7377,16 +7371,16 @@
     </row>
     <row r="89" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E89" s="6">
         <v>46149</v>
@@ -7400,16 +7394,16 @@
     </row>
     <row r="90" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E90" s="6">
         <v>46150</v>
@@ -7423,16 +7417,16 @@
     </row>
     <row r="91" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E91" s="6">
         <v>46146</v>
@@ -7446,16 +7440,16 @@
     </row>
     <row r="92" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E92" s="6">
         <v>46146</v>
@@ -7469,16 +7463,16 @@
     </row>
     <row r="93" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E93" s="6">
         <v>46147</v>
@@ -7492,16 +7486,16 @@
     </row>
     <row r="94" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E94" s="6">
         <v>46147</v>
@@ -7515,16 +7509,16 @@
     </row>
     <row r="95" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E95" s="6">
         <v>46148</v>
@@ -7538,16 +7532,16 @@
     </row>
     <row r="96" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E96" s="6">
         <v>46149</v>
@@ -7561,16 +7555,16 @@
     </row>
     <row r="97" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E97" s="6">
         <v>46149</v>
@@ -7584,16 +7578,16 @@
     </row>
     <row r="98" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E98" s="6">
         <v>46150</v>
@@ -7607,16 +7601,16 @@
     </row>
     <row r="99" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E99" s="6">
         <v>46146</v>
@@ -7630,16 +7624,16 @@
     </row>
     <row r="100" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E100" s="6">
         <v>46147</v>
@@ -7653,16 +7647,16 @@
     </row>
     <row r="101" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E101" s="6">
         <v>46148</v>
@@ -7676,16 +7670,16 @@
     </row>
     <row r="102" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E102" s="6">
         <v>46149</v>
@@ -7699,16 +7693,16 @@
     </row>
     <row r="103" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E103" s="6">
         <v>46150</v>
@@ -7722,16 +7716,16 @@
     </row>
     <row r="104" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E104" s="6">
         <v>46146</v>
@@ -7745,16 +7739,16 @@
     </row>
     <row r="105" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E105" s="6">
         <v>46147</v>
@@ -7768,16 +7762,16 @@
     </row>
     <row r="106" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E106" s="6">
         <v>46148</v>
@@ -7791,16 +7785,16 @@
     </row>
     <row r="107" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E107" s="6">
         <v>46149</v>
@@ -7814,16 +7808,16 @@
     </row>
     <row r="108" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E108" s="6">
         <v>46150</v>
@@ -7837,16 +7831,16 @@
     </row>
     <row r="109" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E109" s="6">
         <v>46146</v>
@@ -7860,16 +7854,16 @@
     </row>
     <row r="110" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E110" s="6">
         <v>46147</v>
@@ -7883,16 +7877,16 @@
     </row>
     <row r="111" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E111" s="6">
         <v>46148</v>
@@ -7906,16 +7900,16 @@
     </row>
     <row r="112" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E112" s="6">
         <v>46149</v>
@@ -7929,16 +7923,16 @@
     </row>
     <row r="113" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E113" s="6">
         <v>46150</v>
@@ -7952,16 +7946,16 @@
     </row>
     <row r="114" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E114" s="6">
         <v>46146</v>
@@ -7975,16 +7969,16 @@
     </row>
     <row r="115" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E115" s="6">
         <v>46147</v>
@@ -7998,16 +7992,16 @@
     </row>
     <row r="116" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E116" s="6">
         <v>46148</v>
@@ -8021,16 +8015,16 @@
     </row>
     <row r="117" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E117" s="6">
         <v>46149</v>
@@ -8044,16 +8038,16 @@
     </row>
     <row r="118" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E118" s="6">
         <v>46150</v>
@@ -8067,16 +8061,16 @@
     </row>
     <row r="119" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E119" s="6">
         <v>46181</v>
@@ -8091,16 +8085,16 @@
     </row>
     <row r="120" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E120" s="6">
         <v>46182</v>
@@ -8115,16 +8109,16 @@
     </row>
     <row r="121" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E121" s="6">
         <v>46183</v>
@@ -8139,16 +8133,16 @@
     </row>
     <row r="122" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E122" s="6">
         <v>46184</v>
@@ -8163,16 +8157,16 @@
     </row>
     <row r="123" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E123" s="6">
         <v>46185</v>
@@ -8187,16 +8181,16 @@
     </row>
     <row r="124" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E124" s="6">
         <v>46181</v>
@@ -8211,16 +8205,16 @@
     </row>
     <row r="125" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E125" s="6">
         <v>46182</v>
@@ -8235,16 +8229,16 @@
     </row>
     <row r="126" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E126" s="6">
         <v>46183</v>
@@ -8259,16 +8253,16 @@
     </row>
     <row r="127" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E127" s="6">
         <v>46184</v>
@@ -8283,16 +8277,16 @@
     </row>
     <row r="128" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E128" s="6">
         <v>46188</v>
@@ -8307,16 +8301,16 @@
     </row>
     <row r="129" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E129" s="6">
         <v>46189</v>
@@ -8331,16 +8325,16 @@
     </row>
     <row r="130" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>373</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>375</v>
       </c>
       <c r="E130" s="6">
         <v>46190</v>
@@ -8355,16 +8349,16 @@
     </row>
     <row r="131" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D131" s="5" t="s">
         <v>373</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>375</v>
       </c>
       <c r="E131" s="6">
         <v>46191</v>
@@ -8379,16 +8373,16 @@
     </row>
     <row r="132" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E132" s="6">
         <v>46192</v>
@@ -8421,755 +8415,755 @@
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D1" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="F1" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="H1" s="16" t="s">
+      <c r="L1" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="M1" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="M1" s="16" t="s">
+      <c r="N1" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="P1" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="O1" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>269</v>
-      </c>
       <c r="R1" s="16" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C17" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C18" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C23" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C25" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B26" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C26" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B27" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C27" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B28" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C28" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B29" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C29" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B30" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C30" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B31" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C31" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C32" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B33" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C33" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C34" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C35" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C36" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C37" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B38" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C38" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B39" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C39" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B40" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C40" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C41" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B42" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C42" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B43" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C43" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C44" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C45" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C46" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C47" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C48" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C50" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C51" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>341</v>
+      </c>
+      <c r="C52" t="s">
         <v>343</v>
       </c>
-      <c r="C52" t="s">
-        <v>345</v>
-      </c>
       <c r="D52" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>342</v>
+      </c>
+      <c r="C53" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>346</v>
-      </c>
       <c r="E53" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B54" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C54" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3934A69-6FCB-0441-AA86-17238F01E7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62275DD-A34B-EE43-8DA0-443BC86D01C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -172,9 +172,6 @@
     <t>Consultor CO SR</t>
   </si>
   <si>
-    <t>Consultor PM SR</t>
-  </si>
-  <si>
     <t>Consultor Group Reporting SR</t>
   </si>
   <si>
@@ -1169,6 +1166,9 @@
   </si>
   <si>
     <t>Atividade de Realize: Estrutura de custo</t>
+  </si>
+  <si>
+    <t>Consultor PM</t>
   </si>
 </sst>
 </file>
@@ -1679,19 +1679,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="G1" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1702,14 +1702,14 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="11">
         <v>46388</v>
       </c>
       <c r="G2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1720,14 +1720,14 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="11">
         <v>46388</v>
       </c>
       <c r="G3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1738,14 +1738,14 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="11">
         <v>46388</v>
       </c>
       <c r="G4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1756,14 +1756,14 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="11">
         <v>46388</v>
       </c>
       <c r="G5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1774,14 +1774,14 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="11">
         <v>46388</v>
       </c>
       <c r="G6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1792,14 +1792,14 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="11">
         <v>46388</v>
       </c>
       <c r="G7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1810,14 +1810,14 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="11">
         <v>46388</v>
       </c>
       <c r="G8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1828,14 +1828,14 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="11">
         <v>46388</v>
       </c>
       <c r="G9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1846,17 +1846,17 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="11">
         <v>46388</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1867,17 +1867,17 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="11">
         <v>46388</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1888,17 +1888,17 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="11">
         <v>46388</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1909,17 +1909,17 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="11">
         <v>46388</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1930,16 +1930,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E14" s="11">
         <v>46296</v>
       </c>
       <c r="G14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1950,16 +1950,16 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E15" s="11">
         <v>46296</v>
       </c>
       <c r="G15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1970,14 +1970,14 @@
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="11">
         <v>46296</v>
       </c>
       <c r="G16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1985,15 +1985,15 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="11"/>
       <c r="G17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2004,14 +2004,14 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="11">
         <v>46296</v>
       </c>
       <c r="G18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2022,14 +2022,14 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="11">
         <v>46296</v>
       </c>
       <c r="G19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2040,14 +2040,14 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="11">
         <v>46296</v>
       </c>
       <c r="G20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2058,14 +2058,14 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="11">
         <v>46296</v>
       </c>
       <c r="G21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2076,14 +2076,14 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="11">
         <v>46296</v>
       </c>
       <c r="G22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2094,14 +2094,14 @@
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="11">
         <v>46296</v>
       </c>
       <c r="G23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2112,14 +2112,14 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="11">
         <v>46296</v>
       </c>
       <c r="G24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2130,17 +2130,17 @@
         <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="11">
         <v>46296</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2151,14 +2151,14 @@
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="11">
         <v>46388</v>
       </c>
       <c r="G26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2169,14 +2169,14 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="11">
         <v>46388</v>
       </c>
       <c r="G27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2187,14 +2187,14 @@
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="11">
         <v>46388</v>
       </c>
       <c r="G28" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2202,15 +2202,15 @@
         <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="11"/>
       <c r="G29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2226,7 +2226,7 @@
         <v>46388</v>
       </c>
       <c r="G30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2237,14 +2237,14 @@
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="11">
         <v>46388</v>
       </c>
       <c r="G31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2260,7 +2260,7 @@
         <v>46388</v>
       </c>
       <c r="G32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2271,14 +2271,14 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="11">
         <v>46388</v>
       </c>
       <c r="G33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2289,14 +2289,14 @@
         <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="11">
         <v>46388</v>
       </c>
       <c r="G34" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2307,14 +2307,14 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="11">
         <v>46388</v>
       </c>
       <c r="G35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2325,14 +2325,14 @@
         <v>26</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="11">
         <v>46388</v>
       </c>
       <c r="G36" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2343,17 +2343,17 @@
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="11">
         <v>46388</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G37" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2364,17 +2364,17 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="11">
         <v>46388</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G38" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2385,14 +2385,14 @@
         <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="11">
         <v>46661</v>
       </c>
       <c r="G39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2408,7 +2408,7 @@
         <v>46661</v>
       </c>
       <c r="G40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2419,14 +2419,14 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="11">
         <v>46661</v>
       </c>
       <c r="G41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2437,14 +2437,14 @@
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="11">
         <v>46661</v>
       </c>
       <c r="G42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2455,14 +2455,14 @@
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="11">
         <v>46661</v>
       </c>
       <c r="G43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2473,17 +2473,17 @@
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="11">
         <v>46661</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2494,14 +2494,14 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="11">
         <v>46388</v>
       </c>
       <c r="G45" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2512,14 +2512,14 @@
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D46" s="15"/>
       <c r="E46" s="11">
         <v>46388</v>
       </c>
       <c r="G46" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2527,7 +2527,7 @@
         <v>29</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2535,7 +2535,7 @@
         <v>46388</v>
       </c>
       <c r="G47" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2546,14 +2546,14 @@
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="11">
         <v>46388</v>
       </c>
       <c r="G48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2564,14 +2564,14 @@
         <v>30</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="11">
         <v>46388</v>
       </c>
       <c r="G49" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2582,14 +2582,14 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="11">
         <v>46388</v>
       </c>
       <c r="G50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2600,14 +2600,14 @@
         <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="11">
         <v>46388</v>
       </c>
       <c r="G51" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2618,14 +2618,14 @@
         <v>26</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="11">
         <v>46388</v>
       </c>
       <c r="G52" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2641,7 +2641,7 @@
         <v>46388</v>
       </c>
       <c r="G53" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2652,16 +2652,16 @@
         <v>32</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E54" s="11">
         <v>46388</v>
       </c>
       <c r="G54" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2672,14 +2672,14 @@
         <v>33</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="11">
         <v>46388</v>
       </c>
       <c r="G55" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2690,14 +2690,14 @@
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="11">
         <v>46388</v>
       </c>
       <c r="G56" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2708,17 +2708,17 @@
         <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="11">
         <v>46388</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G57" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2729,17 +2729,17 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="11">
         <v>46388</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G58" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2750,16 +2750,16 @@
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E59" s="11">
         <v>46388</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2770,14 +2770,14 @@
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="11">
         <v>46388</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2785,17 +2785,17 @@
         <v>34</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="11">
         <v>46388</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2806,14 +2806,14 @@
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="11">
         <v>46388</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2824,14 +2824,14 @@
         <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="11">
         <v>46388</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2842,14 +2842,14 @@
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="11">
         <v>46388</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2860,17 +2860,17 @@
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="11">
         <v>46388</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2881,17 +2881,17 @@
         <v>35</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="11">
         <v>46388</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2902,16 +2902,16 @@
         <v>36</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E67" s="11">
         <v>46388</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2922,19 +2922,19 @@
         <v>37</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E68" s="11">
         <v>46388</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2942,7 +2942,7 @@
         <v>34</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2950,7 +2950,7 @@
         <v>46388</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2966,7 +2966,7 @@
         <v>46388</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2977,13 +2977,13 @@
         <v>39</v>
       </c>
       <c r="C71" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E71" s="11">
         <v>46388</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2994,13 +2994,13 @@
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E72" s="11">
         <v>46388</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3011,16 +3011,16 @@
         <v>41</v>
       </c>
       <c r="C73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D73" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E73" s="11">
         <v>46388</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3031,13 +3031,13 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E74" s="11">
         <v>46388</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3048,13 +3048,13 @@
         <v>42</v>
       </c>
       <c r="C75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E75" s="11">
         <v>46388</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3062,16 +3062,16 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C76" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E76" s="11">
         <v>46388</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3079,16 +3079,16 @@
         <v>38</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>375</v>
       </c>
       <c r="C77" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E77" s="11">
         <v>46388</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3096,16 +3096,16 @@
         <v>38</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C78" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E78" s="11">
         <v>46388</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3116,13 +3116,13 @@
         <v>31</v>
       </c>
       <c r="C79" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E79" s="11">
         <v>46388</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3133,13 +3133,13 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E80" s="11">
         <v>46388</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3150,16 +3150,16 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E81" s="11">
         <v>46388</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3170,16 +3170,16 @@
         <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E82" s="11">
         <v>46388</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3190,16 +3190,16 @@
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E83" s="11">
         <v>46388</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3210,72 +3210,72 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E84" s="11">
         <v>46388</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B85" t="s">
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E85" s="12">
         <v>46388</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E86" s="12">
         <v>46388</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B87" t="s">
         <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E87" s="12">
         <v>46388</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B88" t="s">
         <v>5</v>
@@ -3284,26 +3284,26 @@
         <v>46388</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E89" s="12">
         <v>46388</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -3312,308 +3312,308 @@
         <v>46388</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B91" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E91" s="12">
         <v>46388</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E92" s="12">
         <v>46388</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E93" s="12">
         <v>46388</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E94" s="12">
         <v>46631</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
         <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E95" s="12">
         <v>46631</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
         <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E96" s="12">
         <v>46631</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E97" s="12">
         <v>46631</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E98" s="12">
         <v>46631</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E99" s="12">
         <v>46631</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E100" s="12">
         <v>46631</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
         <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E101" s="12"/>
       <c r="G101" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>45</v>
+      </c>
+      <c r="B102" t="s">
         <v>46</v>
       </c>
-      <c r="B102" t="s">
-        <v>47</v>
-      </c>
       <c r="C102" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E102" s="12">
         <v>46631</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C103" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E103" s="12">
         <v>46631</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B104" t="s">
         <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E104" s="12">
         <v>46631</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B105" t="s">
         <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E105" s="12">
         <v>46631</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B106" t="s">
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E106" s="12">
         <v>46631</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B107" t="s">
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E107" s="12">
         <v>46631</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B108" t="s">
         <v>28</v>
@@ -3622,12 +3622,12 @@
         <v>46296</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B109" t="s">
         <v>5</v>
@@ -3636,12 +3636,12 @@
         <v>46296</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -3650,29 +3650,29 @@
         <v>46296</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E111" s="12">
         <v>46296</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B112" t="s">
         <v>33</v>
@@ -3681,12 +3681,12 @@
         <v>46569</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B113" t="s">
         <v>19</v>
@@ -3695,12 +3695,12 @@
         <v>46569</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -3709,127 +3709,127 @@
         <v>46569</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B115" t="s">
         <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E115" s="12">
         <v>46569</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>348</v>
+      </c>
+      <c r="B116" t="s">
         <v>349</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>350</v>
-      </c>
-      <c r="C116" t="s">
-        <v>351</v>
       </c>
       <c r="E116" s="12">
         <v>46569</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B117" t="s">
         <v>10</v>
       </c>
       <c r="E117" s="12"/>
       <c r="G117" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B118" t="s">
         <v>28</v>
       </c>
       <c r="C118" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E118" s="12">
         <v>46569</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B119" t="s">
         <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E119" s="12">
         <v>46569</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B120" t="s">
         <v>6</v>
       </c>
       <c r="C120" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E120" s="12">
         <v>46569</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E121" s="12">
         <v>46569</v>
       </c>
       <c r="F121" s="14"/>
       <c r="G121" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B122" t="s">
         <v>28</v>
@@ -3838,12 +3838,12 @@
         <v>46388</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B123" t="s">
         <v>5</v>
@@ -3852,12 +3852,12 @@
         <v>46388</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
@@ -3866,12 +3866,12 @@
         <v>46388</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
@@ -3880,7 +3880,7 @@
         <v>46388</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -3907,27 +3907,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="D2" s="3">
         <v>46113</v>
@@ -3938,13 +3938,13 @@
     </row>
     <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="D3" s="3">
         <v>46113</v>
@@ -3955,13 +3955,13 @@
     </row>
     <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D4" s="3">
         <v>46114</v>
@@ -3972,13 +3972,13 @@
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="3">
         <v>46128</v>
@@ -3989,13 +3989,13 @@
     </row>
     <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" s="3">
         <v>46122</v>
@@ -4006,13 +4006,13 @@
     </row>
     <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D7" s="3">
         <v>46126</v>
@@ -4023,13 +4023,13 @@
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3">
         <v>46129</v>
@@ -4040,13 +4040,13 @@
     </row>
     <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" s="3">
         <v>46146</v>
@@ -4057,26 +4057,26 @@
     </row>
     <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="D11" s="3">
         <v>46153</v>
@@ -4087,13 +4087,13 @@
     </row>
     <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D12" s="3">
         <v>46140</v>
@@ -4104,13 +4104,13 @@
     </row>
     <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="3">
         <v>46162</v>
@@ -4121,13 +4121,13 @@
     </row>
     <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="D14" s="3">
         <v>46163</v>
@@ -4138,10 +4138,10 @@
     </row>
     <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3">
@@ -4153,13 +4153,13 @@
     </row>
     <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="D16" s="3">
         <v>46160</v>
@@ -4170,13 +4170,13 @@
     </row>
     <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D17" s="3">
         <v>46140</v>
@@ -4187,13 +4187,13 @@
     </row>
     <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D18" s="3">
         <v>46150</v>
@@ -4204,13 +4204,13 @@
     </row>
     <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="3">
         <v>46150</v>
@@ -4221,13 +4221,13 @@
     </row>
     <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" s="3">
         <v>46147</v>
@@ -4238,13 +4238,13 @@
     </row>
     <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="3">
         <v>46149</v>
@@ -4255,13 +4255,13 @@
     </row>
     <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D22" s="3">
         <v>46181</v>
@@ -4272,13 +4272,13 @@
     </row>
     <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D23" s="3">
         <v>46170</v>
@@ -4289,13 +4289,13 @@
     </row>
     <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D24" s="3">
         <v>46168</v>
@@ -4306,13 +4306,13 @@
     </row>
     <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D25" s="3">
         <v>46167</v>
@@ -4323,13 +4323,13 @@
     </row>
     <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" s="3">
         <v>46174</v>
@@ -4340,13 +4340,13 @@
     </row>
     <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="D27" s="3">
         <v>46175</v>
@@ -4357,13 +4357,13 @@
     </row>
     <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28" s="3">
         <v>46171</v>
@@ -4374,13 +4374,13 @@
     </row>
     <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="D29" s="3">
         <v>46170</v>
@@ -4391,13 +4391,13 @@
     </row>
     <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D30" s="3">
         <v>46181</v>
@@ -4408,13 +4408,13 @@
     </row>
     <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D31" s="3">
         <v>46178</v>
@@ -4425,13 +4425,13 @@
     </row>
     <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D32" s="3">
         <v>46170</v>
@@ -4442,13 +4442,13 @@
     </row>
     <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D33" s="3">
         <v>46181</v>
@@ -4459,26 +4459,26 @@
     </row>
     <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D35" s="3">
         <v>46155</v>
@@ -4489,13 +4489,13 @@
     </row>
     <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D36" s="3">
         <v>46167</v>
@@ -4506,13 +4506,13 @@
     </row>
     <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D37" s="3">
         <v>46167</v>
@@ -4523,13 +4523,13 @@
     </row>
     <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D38" s="3">
         <v>46168</v>
@@ -4540,13 +4540,13 @@
     </row>
     <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D39" s="3">
         <v>46175</v>
@@ -4557,13 +4557,13 @@
     </row>
     <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D40" s="3">
         <v>46188</v>
@@ -4574,13 +4574,13 @@
     </row>
     <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D41" s="3">
         <v>46195</v>
@@ -4591,13 +4591,13 @@
     </row>
     <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D42" s="3">
         <v>46202</v>
@@ -4608,10 +4608,10 @@
     </row>
     <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="3">
@@ -4623,10 +4623,10 @@
     </row>
     <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="3">
@@ -4638,13 +4638,13 @@
     </row>
     <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D45" s="3">
         <v>46223</v>
@@ -4655,13 +4655,13 @@
     </row>
     <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D46" s="3">
         <v>46223</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="3">
@@ -4687,13 +4687,13 @@
     </row>
     <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D48" s="3">
         <v>46230</v>
@@ -4704,13 +4704,13 @@
     </row>
     <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D49" s="3">
         <v>46232</v>
@@ -4721,13 +4721,13 @@
     </row>
     <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D50" s="3">
         <v>46230</v>
@@ -4738,13 +4738,13 @@
     </row>
     <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D51" s="3">
         <v>46161</v>
@@ -4755,13 +4755,13 @@
     </row>
     <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D52" s="3">
         <v>46162</v>
@@ -4772,13 +4772,13 @@
     </row>
     <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="D53" s="3">
         <v>46162</v>
@@ -4789,13 +4789,13 @@
     </row>
     <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D54" s="3">
         <v>46163</v>
@@ -4806,13 +4806,13 @@
     </row>
     <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D55" s="3">
         <v>46174</v>
@@ -4823,13 +4823,13 @@
     </row>
     <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D56" s="3">
         <v>46174</v>
@@ -4840,13 +4840,13 @@
     </row>
     <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="D57" s="3">
         <v>46174</v>
@@ -4857,13 +4857,13 @@
     </row>
     <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="D58" s="3">
         <v>46181</v>
@@ -4874,13 +4874,13 @@
     </row>
     <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="D59" s="3">
         <v>46181</v>
@@ -4891,13 +4891,13 @@
     </row>
     <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D60" s="3">
         <v>46181</v>
@@ -4908,13 +4908,13 @@
     </row>
     <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D61" s="3">
         <v>46181</v>
@@ -4925,13 +4925,13 @@
     </row>
     <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D62" s="3">
         <v>46182</v>
@@ -4942,13 +4942,13 @@
     </row>
     <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D63" s="3">
         <v>46184</v>
@@ -4959,13 +4959,13 @@
     </row>
     <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D64" s="3">
         <v>46188</v>
@@ -4976,13 +4976,13 @@
     </row>
     <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D65" s="3">
         <v>46188</v>
@@ -4993,13 +4993,13 @@
     </row>
     <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="D66" s="3">
         <v>46198</v>
@@ -5356,30 +5356,30 @@
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E2" s="6">
         <v>46174</v>
@@ -5393,16 +5393,16 @@
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E3" s="6">
         <v>46175</v>
@@ -5416,16 +5416,16 @@
     </row>
     <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E4" s="6">
         <v>46177</v>
@@ -5439,16 +5439,16 @@
     </row>
     <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E5" s="6">
         <v>46178</v>
@@ -5462,16 +5462,16 @@
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E6" s="6">
         <v>46167</v>
@@ -5485,16 +5485,16 @@
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E7" s="6">
         <v>46168</v>
@@ -5508,16 +5508,16 @@
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E8" s="6">
         <v>46169</v>
@@ -5531,16 +5531,16 @@
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E9" s="6">
         <v>46170</v>
@@ -5554,16 +5554,16 @@
     </row>
     <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E10" s="6">
         <v>46171</v>
@@ -5577,16 +5577,16 @@
     </row>
     <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E11" s="6">
         <v>46167</v>
@@ -5600,16 +5600,16 @@
     </row>
     <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E12" s="6">
         <v>46168</v>
@@ -5623,16 +5623,16 @@
     </row>
     <row r="13" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E13" s="6">
         <v>46169</v>
@@ -5646,16 +5646,16 @@
     </row>
     <row r="14" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E14" s="6">
         <v>46170</v>
@@ -5669,16 +5669,16 @@
     </row>
     <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E15" s="6">
         <v>46171</v>
@@ -5692,16 +5692,16 @@
     </row>
     <row r="16" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="E16" s="6">
         <v>46167</v>
@@ -5715,16 +5715,16 @@
     </row>
     <row r="17" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E17" s="6">
         <v>46168</v>
@@ -5738,16 +5738,16 @@
     </row>
     <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E18" s="6">
         <v>46169</v>
@@ -5761,16 +5761,16 @@
     </row>
     <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E19" s="6">
         <v>46169</v>
@@ -5784,16 +5784,16 @@
     </row>
     <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E20" s="6">
         <v>46170</v>
@@ -5807,16 +5807,16 @@
     </row>
     <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E21" s="6">
         <v>46170</v>
@@ -5830,16 +5830,16 @@
     </row>
     <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E22" s="6">
         <v>46160</v>
@@ -5853,16 +5853,16 @@
     </row>
     <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E23" s="6">
         <v>46161</v>
@@ -5876,16 +5876,16 @@
     </row>
     <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E24" s="6">
         <v>46162</v>
@@ -5899,16 +5899,16 @@
     </row>
     <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E25" s="6">
         <v>46163</v>
@@ -5922,16 +5922,16 @@
     </row>
     <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E26" s="6">
         <v>46164</v>
@@ -5945,16 +5945,16 @@
     </row>
     <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E27" s="6">
         <v>46160</v>
@@ -5968,16 +5968,16 @@
     </row>
     <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E28" s="6">
         <v>46161</v>
@@ -5991,16 +5991,16 @@
     </row>
     <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E29" s="6">
         <v>46162</v>
@@ -6014,16 +6014,16 @@
     </row>
     <row r="30" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E30" s="6">
         <v>46163</v>
@@ -6037,16 +6037,16 @@
     </row>
     <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E31" s="6">
         <v>46164</v>
@@ -6060,16 +6060,16 @@
     </row>
     <row r="32" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E32" s="6">
         <v>46160</v>
@@ -6083,16 +6083,16 @@
     </row>
     <row r="33" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E33" s="6">
         <v>46161</v>
@@ -6106,16 +6106,16 @@
     </row>
     <row r="34" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E34" s="6">
         <v>46162</v>
@@ -6129,16 +6129,16 @@
     </row>
     <row r="35" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E35" s="6">
         <v>46163</v>
@@ -6152,16 +6152,16 @@
     </row>
     <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E36" s="6">
         <v>46163</v>
@@ -6175,16 +6175,16 @@
     </row>
     <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E37" s="6">
         <v>46164</v>
@@ -6198,16 +6198,16 @@
     </row>
     <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E38" s="6">
         <v>46160</v>
@@ -6221,16 +6221,16 @@
     </row>
     <row r="39" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E39" s="6">
         <v>46161</v>
@@ -6244,16 +6244,16 @@
     </row>
     <row r="40" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E40" s="6">
         <v>46162</v>
@@ -6267,16 +6267,16 @@
     </row>
     <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E41" s="6">
         <v>46163</v>
@@ -6290,16 +6290,16 @@
     </row>
     <row r="42" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E42" s="6">
         <v>46164</v>
@@ -6313,16 +6313,16 @@
     </row>
     <row r="43" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E43" s="6">
         <v>46153</v>
@@ -6336,16 +6336,16 @@
     </row>
     <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E44" s="6">
         <v>46154</v>
@@ -6359,16 +6359,16 @@
     </row>
     <row r="45" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E45" s="6">
         <v>46155</v>
@@ -6382,16 +6382,16 @@
     </row>
     <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E46" s="6">
         <v>46156</v>
@@ -6405,16 +6405,16 @@
     </row>
     <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E47" s="6">
         <v>46157</v>
@@ -6428,16 +6428,16 @@
     </row>
     <row r="48" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E48" s="6">
         <v>46153</v>
@@ -6451,16 +6451,16 @@
     </row>
     <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E49" s="6">
         <v>46154</v>
@@ -6474,16 +6474,16 @@
     </row>
     <row r="50" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E50" s="6">
         <v>46155</v>
@@ -6497,16 +6497,16 @@
     </row>
     <row r="51" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E51" s="6">
         <v>46156</v>
@@ -6520,16 +6520,16 @@
     </row>
     <row r="52" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E52" s="6">
         <v>46157</v>
@@ -6543,16 +6543,16 @@
     </row>
     <row r="53" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E53" s="6">
         <v>46153</v>
@@ -6566,16 +6566,16 @@
     </row>
     <row r="54" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E54" s="6">
         <v>46154</v>
@@ -6589,16 +6589,16 @@
     </row>
     <row r="55" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E55" s="6">
         <v>46155</v>
@@ -6612,16 +6612,16 @@
     </row>
     <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E56" s="6">
         <v>46156</v>
@@ -6635,16 +6635,16 @@
     </row>
     <row r="57" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E57" s="6">
         <v>46157</v>
@@ -6658,16 +6658,16 @@
     </row>
     <row r="58" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="E58" s="6">
         <v>46153</v>
@@ -6681,16 +6681,16 @@
     </row>
     <row r="59" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="E59" s="6">
         <v>46153</v>
@@ -6704,16 +6704,16 @@
     </row>
     <row r="60" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="E60" s="6">
         <v>46154</v>
@@ -6727,16 +6727,16 @@
     </row>
     <row r="61" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="E61" s="6">
         <v>46154</v>
@@ -6750,16 +6750,16 @@
     </row>
     <row r="62" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="E62" s="6">
         <v>46155</v>
@@ -6773,16 +6773,16 @@
     </row>
     <row r="63" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E63" s="6">
         <v>46155</v>
@@ -6796,16 +6796,16 @@
     </row>
     <row r="64" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="E64" s="6">
         <v>46156</v>
@@ -6819,16 +6819,16 @@
     </row>
     <row r="65" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E65" s="6">
         <v>46156</v>
@@ -6842,16 +6842,16 @@
     </row>
     <row r="66" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="E66" s="6">
         <v>46157</v>
@@ -6865,16 +6865,16 @@
     </row>
     <row r="67" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C67" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="E67" s="6">
         <v>46157</v>
@@ -6888,16 +6888,16 @@
     </row>
     <row r="68" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E68" s="6">
         <v>46153</v>
@@ -6911,16 +6911,16 @@
     </row>
     <row r="69" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E69" s="6">
         <v>46154</v>
@@ -6934,16 +6934,16 @@
     </row>
     <row r="70" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E70" s="6">
         <v>46155</v>
@@ -6957,16 +6957,16 @@
     </row>
     <row r="71" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E71" s="6">
         <v>46155</v>
@@ -6980,16 +6980,16 @@
     </row>
     <row r="72" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E72" s="6">
         <v>46155</v>
@@ -7003,16 +7003,16 @@
     </row>
     <row r="73" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E73" s="6">
         <v>46155</v>
@@ -7026,16 +7026,16 @@
     </row>
     <row r="74" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E74" s="6">
         <v>46156</v>
@@ -7049,16 +7049,16 @@
     </row>
     <row r="75" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E75" s="6">
         <v>46157</v>
@@ -7072,16 +7072,16 @@
     </row>
     <row r="76" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E76" s="6">
         <v>46153</v>
@@ -7095,16 +7095,16 @@
     </row>
     <row r="77" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E77" s="6">
         <v>46154</v>
@@ -7118,16 +7118,16 @@
     </row>
     <row r="78" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E78" s="6">
         <v>46155</v>
@@ -7141,16 +7141,16 @@
     </row>
     <row r="79" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E79" s="6">
         <v>46156</v>
@@ -7164,16 +7164,16 @@
     </row>
     <row r="80" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E80" s="6">
         <v>46157</v>
@@ -7187,16 +7187,16 @@
     </row>
     <row r="81" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E81" s="6">
         <v>46153</v>
@@ -7210,16 +7210,16 @@
     </row>
     <row r="82" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E82" s="6">
         <v>46154</v>
@@ -7233,16 +7233,16 @@
     </row>
     <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E83" s="6">
         <v>46155</v>
@@ -7256,16 +7256,16 @@
     </row>
     <row r="84" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E84" s="6">
         <v>46156</v>
@@ -7279,16 +7279,16 @@
     </row>
     <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E85" s="6">
         <v>46157</v>
@@ -7302,16 +7302,16 @@
     </row>
     <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E86" s="6">
         <v>46146</v>
@@ -7325,16 +7325,16 @@
     </row>
     <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E87" s="6">
         <v>46147</v>
@@ -7348,16 +7348,16 @@
     </row>
     <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E88" s="6">
         <v>46148</v>
@@ -7371,16 +7371,16 @@
     </row>
     <row r="89" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E89" s="6">
         <v>46149</v>
@@ -7394,16 +7394,16 @@
     </row>
     <row r="90" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E90" s="6">
         <v>46150</v>
@@ -7417,16 +7417,16 @@
     </row>
     <row r="91" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E91" s="6">
         <v>46146</v>
@@ -7440,16 +7440,16 @@
     </row>
     <row r="92" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C92" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D92" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="E92" s="6">
         <v>46146</v>
@@ -7463,16 +7463,16 @@
     </row>
     <row r="93" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E93" s="6">
         <v>46147</v>
@@ -7486,16 +7486,16 @@
     </row>
     <row r="94" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E94" s="6">
         <v>46147</v>
@@ -7509,16 +7509,16 @@
     </row>
     <row r="95" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E95" s="6">
         <v>46148</v>
@@ -7532,16 +7532,16 @@
     </row>
     <row r="96" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C96" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D96" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="E96" s="6">
         <v>46149</v>
@@ -7555,16 +7555,16 @@
     </row>
     <row r="97" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E97" s="6">
         <v>46149</v>
@@ -7578,16 +7578,16 @@
     </row>
     <row r="98" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E98" s="6">
         <v>46150</v>
@@ -7601,16 +7601,16 @@
     </row>
     <row r="99" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E99" s="6">
         <v>46146</v>
@@ -7624,16 +7624,16 @@
     </row>
     <row r="100" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E100" s="6">
         <v>46147</v>
@@ -7647,16 +7647,16 @@
     </row>
     <row r="101" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E101" s="6">
         <v>46148</v>
@@ -7670,16 +7670,16 @@
     </row>
     <row r="102" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E102" s="6">
         <v>46149</v>
@@ -7693,16 +7693,16 @@
     </row>
     <row r="103" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E103" s="6">
         <v>46150</v>
@@ -7716,16 +7716,16 @@
     </row>
     <row r="104" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E104" s="6">
         <v>46146</v>
@@ -7739,16 +7739,16 @@
     </row>
     <row r="105" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E105" s="6">
         <v>46147</v>
@@ -7762,16 +7762,16 @@
     </row>
     <row r="106" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E106" s="6">
         <v>46148</v>
@@ -7785,16 +7785,16 @@
     </row>
     <row r="107" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E107" s="6">
         <v>46149</v>
@@ -7808,16 +7808,16 @@
     </row>
     <row r="108" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E108" s="6">
         <v>46150</v>
@@ -7831,16 +7831,16 @@
     </row>
     <row r="109" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E109" s="6">
         <v>46146</v>
@@ -7854,16 +7854,16 @@
     </row>
     <row r="110" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E110" s="6">
         <v>46147</v>
@@ -7877,16 +7877,16 @@
     </row>
     <row r="111" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E111" s="6">
         <v>46148</v>
@@ -7900,16 +7900,16 @@
     </row>
     <row r="112" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E112" s="6">
         <v>46149</v>
@@ -7923,16 +7923,16 @@
     </row>
     <row r="113" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E113" s="6">
         <v>46150</v>
@@ -7946,16 +7946,16 @@
     </row>
     <row r="114" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E114" s="6">
         <v>46146</v>
@@ -7969,16 +7969,16 @@
     </row>
     <row r="115" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E115" s="6">
         <v>46147</v>
@@ -7992,16 +7992,16 @@
     </row>
     <row r="116" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E116" s="6">
         <v>46148</v>
@@ -8015,16 +8015,16 @@
     </row>
     <row r="117" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E117" s="6">
         <v>46149</v>
@@ -8038,16 +8038,16 @@
     </row>
     <row r="118" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E118" s="6">
         <v>46150</v>
@@ -8061,16 +8061,16 @@
     </row>
     <row r="119" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E119" s="6">
         <v>46181</v>
@@ -8085,16 +8085,16 @@
     </row>
     <row r="120" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E120" s="6">
         <v>46182</v>
@@ -8109,16 +8109,16 @@
     </row>
     <row r="121" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E121" s="6">
         <v>46183</v>
@@ -8133,16 +8133,16 @@
     </row>
     <row r="122" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E122" s="6">
         <v>46184</v>
@@ -8157,16 +8157,16 @@
     </row>
     <row r="123" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E123" s="6">
         <v>46185</v>
@@ -8181,16 +8181,16 @@
     </row>
     <row r="124" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E124" s="6">
         <v>46181</v>
@@ -8205,16 +8205,16 @@
     </row>
     <row r="125" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E125" s="6">
         <v>46182</v>
@@ -8229,16 +8229,16 @@
     </row>
     <row r="126" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E126" s="6">
         <v>46183</v>
@@ -8253,16 +8253,16 @@
     </row>
     <row r="127" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E127" s="6">
         <v>46184</v>
@@ -8277,16 +8277,16 @@
     </row>
     <row r="128" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D128" s="5" t="s">
         <v>371</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>372</v>
       </c>
       <c r="E128" s="6">
         <v>46188</v>
@@ -8301,16 +8301,16 @@
     </row>
     <row r="129" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E129" s="6">
         <v>46189</v>
@@ -8325,16 +8325,16 @@
     </row>
     <row r="130" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E130" s="6">
         <v>46190</v>
@@ -8349,16 +8349,16 @@
     </row>
     <row r="131" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E131" s="6">
         <v>46191</v>
@@ -8373,16 +8373,16 @@
     </row>
     <row r="132" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E132" s="6">
         <v>46192</v>
@@ -8415,755 +8415,755 @@
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="R1" s="16" t="s">
         <v>353</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C11" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C15" t="s">
         <v>282</v>
       </c>
-      <c r="C15" t="s">
-        <v>283</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>285</v>
+      </c>
+      <c r="C18" t="s">
         <v>286</v>
       </c>
-      <c r="C18" t="s">
-        <v>287</v>
-      </c>
       <c r="D18" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C23" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B26" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B27" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C27" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B28" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B29" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C30" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B31" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B32" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B33" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C33" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C34" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C35" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C37" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C38" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C40" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C43" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C44" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C46" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C47" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C48" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C50" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>319</v>
+      </c>
+      <c r="C51" t="s">
         <v>320</v>
       </c>
-      <c r="C51" t="s">
-        <v>321</v>
-      </c>
       <c r="K51" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C52" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C54" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62275DD-A34B-EE43-8DA0-443BC86D01C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0241B1E8-5C99-FB4C-ABB6-3AFE08A9BE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="373">
   <si>
     <t>Projeto</t>
   </si>
@@ -160,16 +160,7 @@
     <t>4299 - ERO - SAP CLOUD ERP GROW</t>
   </si>
   <si>
-    <t>Consultor MM SR</t>
-  </si>
-  <si>
-    <t>Consultor SD SR</t>
-  </si>
-  <si>
     <t>Consultor FI PL</t>
-  </si>
-  <si>
-    <t>Consultor CO SR</t>
   </si>
   <si>
     <t>Consultor Group Reporting SR</t>
@@ -1679,19 +1670,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1702,14 +1693,14 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="11">
         <v>46388</v>
       </c>
       <c r="G2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1720,14 +1711,14 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="11">
         <v>46388</v>
       </c>
       <c r="G3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1738,14 +1729,14 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="11">
         <v>46388</v>
       </c>
       <c r="G4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1756,14 +1747,14 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="11">
         <v>46388</v>
       </c>
       <c r="G5" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1774,14 +1765,14 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="11">
         <v>46388</v>
       </c>
       <c r="G6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1792,14 +1783,14 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="11">
         <v>46388</v>
       </c>
       <c r="G7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1810,14 +1801,14 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="11">
         <v>46388</v>
       </c>
       <c r="G8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1828,14 +1819,14 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="11">
         <v>46388</v>
       </c>
       <c r="G9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1846,17 +1837,17 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="11">
         <v>46388</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1867,17 +1858,17 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="11">
         <v>46388</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1888,17 +1879,17 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="11">
         <v>46388</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1909,17 +1900,17 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="11">
         <v>46388</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G13" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1930,16 +1921,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E14" s="11">
         <v>46296</v>
       </c>
       <c r="G14" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1950,16 +1941,16 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E15" s="11">
         <v>46296</v>
       </c>
       <c r="G15" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1970,14 +1961,14 @@
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="11">
         <v>46296</v>
       </c>
       <c r="G16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1985,15 +1976,15 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="11"/>
       <c r="G17" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2004,14 +1995,14 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="11">
         <v>46296</v>
       </c>
       <c r="G18" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2022,14 +2013,14 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="11">
         <v>46296</v>
       </c>
       <c r="G19" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2040,14 +2031,14 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="11">
         <v>46296</v>
       </c>
       <c r="G20" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2058,14 +2049,14 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="11">
         <v>46296</v>
       </c>
       <c r="G21" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2076,14 +2067,14 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="11">
         <v>46296</v>
       </c>
       <c r="G22" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2094,14 +2085,14 @@
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="11">
         <v>46296</v>
       </c>
       <c r="G23" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2112,14 +2103,14 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="11">
         <v>46296</v>
       </c>
       <c r="G24" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2130,17 +2121,17 @@
         <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="11">
         <v>46296</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G25" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2151,14 +2142,14 @@
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="11">
         <v>46388</v>
       </c>
       <c r="G26" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2169,14 +2160,14 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="11">
         <v>46388</v>
       </c>
       <c r="G27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2187,14 +2178,14 @@
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="11">
         <v>46388</v>
       </c>
       <c r="G28" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2202,15 +2193,15 @@
         <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="11"/>
       <c r="G29" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2226,7 +2217,7 @@
         <v>46388</v>
       </c>
       <c r="G30" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2237,14 +2228,14 @@
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="11">
         <v>46388</v>
       </c>
       <c r="G31" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2260,7 +2251,7 @@
         <v>46388</v>
       </c>
       <c r="G32" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2271,14 +2262,14 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="11">
         <v>46388</v>
       </c>
       <c r="G33" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2289,14 +2280,14 @@
         <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="11">
         <v>46388</v>
       </c>
       <c r="G34" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2307,14 +2298,14 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="11">
         <v>46388</v>
       </c>
       <c r="G35" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2325,14 +2316,14 @@
         <v>26</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="11">
         <v>46388</v>
       </c>
       <c r="G36" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2343,17 +2334,17 @@
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="11">
         <v>46388</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G37" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2364,17 +2355,17 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="11">
         <v>46388</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G38" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2385,14 +2376,14 @@
         <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="11">
         <v>46661</v>
       </c>
       <c r="G39" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2408,7 +2399,7 @@
         <v>46661</v>
       </c>
       <c r="G40" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2419,14 +2410,14 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="11">
         <v>46661</v>
       </c>
       <c r="G41" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2437,14 +2428,14 @@
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="11">
         <v>46661</v>
       </c>
       <c r="G42" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2455,14 +2446,14 @@
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="11">
         <v>46661</v>
       </c>
       <c r="G43" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2473,17 +2464,17 @@
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="11">
         <v>46661</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G44" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2494,14 +2485,14 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="11">
         <v>46388</v>
       </c>
       <c r="G45" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2512,14 +2503,14 @@
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D46" s="15"/>
       <c r="E46" s="11">
         <v>46388</v>
       </c>
       <c r="G46" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2527,7 +2518,7 @@
         <v>29</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2535,7 +2526,7 @@
         <v>46388</v>
       </c>
       <c r="G47" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2546,14 +2537,14 @@
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="11">
         <v>46388</v>
       </c>
       <c r="G48" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2564,14 +2555,14 @@
         <v>30</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="11">
         <v>46388</v>
       </c>
       <c r="G49" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2582,14 +2573,14 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="11">
         <v>46388</v>
       </c>
       <c r="G50" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2600,14 +2591,14 @@
         <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="11">
         <v>46388</v>
       </c>
       <c r="G51" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2618,14 +2609,14 @@
         <v>26</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="11">
         <v>46388</v>
       </c>
       <c r="G52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2641,7 +2632,7 @@
         <v>46388</v>
       </c>
       <c r="G53" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2652,16 +2643,16 @@
         <v>32</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E54" s="11">
         <v>46388</v>
       </c>
       <c r="G54" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2672,14 +2663,14 @@
         <v>33</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="11">
         <v>46388</v>
       </c>
       <c r="G55" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2690,14 +2681,14 @@
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="11">
         <v>46388</v>
       </c>
       <c r="G56" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2708,17 +2699,17 @@
         <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="11">
         <v>46388</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G57" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2729,17 +2720,17 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="11">
         <v>46388</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G58" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2750,16 +2741,16 @@
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E59" s="11">
         <v>46388</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2770,14 +2761,14 @@
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="11">
         <v>46388</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2785,17 +2776,17 @@
         <v>34</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="11">
         <v>46388</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2806,14 +2797,14 @@
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="11">
         <v>46388</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2824,14 +2815,14 @@
         <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="11">
         <v>46388</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2842,14 +2833,14 @@
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="11">
         <v>46388</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2860,17 +2851,17 @@
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="11">
         <v>46388</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2881,17 +2872,17 @@
         <v>35</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="11">
         <v>46388</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2902,16 +2893,16 @@
         <v>36</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E67" s="11">
         <v>46388</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2922,19 +2913,19 @@
         <v>37</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E68" s="11">
         <v>46388</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2942,7 +2933,7 @@
         <v>34</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2950,7 +2941,7 @@
         <v>46388</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2966,7 +2957,7 @@
         <v>46388</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2974,16 +2965,16 @@
         <v>38</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E71" s="11">
         <v>46388</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2991,16 +2982,16 @@
         <v>38</v>
       </c>
       <c r="B72" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C72" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E72" s="11">
         <v>46388</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3008,19 +2999,19 @@
         <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C73" t="s">
+        <v>47</v>
+      </c>
+      <c r="D73" t="s">
         <v>50</v>
-      </c>
-      <c r="D73" t="s">
-        <v>53</v>
       </c>
       <c r="E73" s="11">
         <v>46388</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3031,13 +3022,13 @@
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E74" s="11">
         <v>46388</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3045,16 +3036,16 @@
         <v>38</v>
       </c>
       <c r="B75" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="C75" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E75" s="11">
         <v>46388</v>
       </c>
       <c r="G75" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3062,16 +3053,16 @@
         <v>38</v>
       </c>
       <c r="B76" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E76" s="11">
         <v>46388</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3079,16 +3070,16 @@
         <v>38</v>
       </c>
       <c r="B77" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C77" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E77" s="11">
         <v>46388</v>
       </c>
       <c r="G77" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3096,16 +3087,16 @@
         <v>38</v>
       </c>
       <c r="B78" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C78" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E78" s="11">
         <v>46388</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3116,13 +3107,13 @@
         <v>31</v>
       </c>
       <c r="C79" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E79" s="11">
         <v>46388</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3133,13 +3124,13 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E80" s="11">
         <v>46388</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3150,16 +3141,16 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E81" s="11">
         <v>46388</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3170,16 +3161,16 @@
         <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E82" s="11">
         <v>46388</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3190,16 +3181,16 @@
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E83" s="11">
         <v>46388</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3210,72 +3201,72 @@
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E84" s="11">
         <v>46388</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B85" t="s">
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E85" s="12">
         <v>46388</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E86" s="12">
         <v>46388</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B87" t="s">
         <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E87" s="12">
         <v>46388</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B88" t="s">
         <v>5</v>
@@ -3284,26 +3275,26 @@
         <v>46388</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E89" s="12">
         <v>46388</v>
       </c>
       <c r="G89" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -3312,308 +3303,308 @@
         <v>46388</v>
       </c>
       <c r="G90" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B91" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E91" s="12">
         <v>46388</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E92" s="12">
         <v>46388</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E93" s="12">
         <v>46388</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E94" s="12">
         <v>46631</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
         <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E95" s="12">
         <v>46631</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B96" t="s">
         <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E96" s="12">
         <v>46631</v>
       </c>
       <c r="G96" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E97" s="12">
         <v>46631</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E98" s="12">
         <v>46631</v>
       </c>
       <c r="G98" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E99" s="12">
         <v>46631</v>
       </c>
       <c r="G99" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E100" s="12">
         <v>46631</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B101" t="s">
         <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E101" s="12"/>
       <c r="G101" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B102" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C102" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E102" s="12">
         <v>46631</v>
       </c>
       <c r="G102" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B103" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C103" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E103" s="12">
         <v>46631</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G103" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B104" t="s">
         <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E104" s="12">
         <v>46631</v>
       </c>
       <c r="G104" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B105" t="s">
         <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E105" s="12">
         <v>46631</v>
       </c>
       <c r="G105" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B106" t="s">
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E106" s="12">
         <v>46631</v>
       </c>
       <c r="G106" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B107" t="s">
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E107" s="12">
         <v>46631</v>
       </c>
       <c r="G107" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B108" t="s">
         <v>28</v>
@@ -3622,12 +3613,12 @@
         <v>46296</v>
       </c>
       <c r="G108" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B109" t="s">
         <v>5</v>
@@ -3636,12 +3627,12 @@
         <v>46296</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -3650,29 +3641,29 @@
         <v>46296</v>
       </c>
       <c r="G110" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E111" s="12">
         <v>46296</v>
       </c>
       <c r="G111" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s">
         <v>33</v>
@@ -3681,12 +3672,12 @@
         <v>46569</v>
       </c>
       <c r="G112" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B113" t="s">
         <v>19</v>
@@ -3695,12 +3686,12 @@
         <v>46569</v>
       </c>
       <c r="G113" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -3709,127 +3700,127 @@
         <v>46569</v>
       </c>
       <c r="G114" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B115" t="s">
         <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E115" s="12">
         <v>46569</v>
       </c>
       <c r="G115" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B116" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C116" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E116" s="12">
         <v>46569</v>
       </c>
       <c r="G116" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B117" t="s">
         <v>10</v>
       </c>
       <c r="E117" s="12"/>
       <c r="G117" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B118" t="s">
         <v>28</v>
       </c>
       <c r="C118" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E118" s="12">
         <v>46569</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B119" t="s">
         <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E119" s="12">
         <v>46569</v>
       </c>
       <c r="G119" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B120" t="s">
         <v>6</v>
       </c>
       <c r="C120" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E120" s="12">
         <v>46569</v>
       </c>
       <c r="G120" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E121" s="12">
         <v>46569</v>
       </c>
       <c r="F121" s="14"/>
       <c r="G121" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B122" t="s">
         <v>28</v>
@@ -3838,12 +3829,12 @@
         <v>46388</v>
       </c>
       <c r="G122" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B123" t="s">
         <v>5</v>
@@ -3852,12 +3843,12 @@
         <v>46388</v>
       </c>
       <c r="G123" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
@@ -3866,12 +3857,12 @@
         <v>46388</v>
       </c>
       <c r="G124" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
@@ -3880,7 +3871,7 @@
         <v>46388</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -3907,27 +3898,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D2" s="3">
         <v>46113</v>
@@ -3938,13 +3929,13 @@
     </row>
     <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D3" s="3">
         <v>46113</v>
@@ -3955,13 +3946,13 @@
     </row>
     <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D4" s="3">
         <v>46114</v>
@@ -3972,13 +3963,13 @@
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D5" s="3">
         <v>46128</v>
@@ -3989,13 +3980,13 @@
     </row>
     <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D6" s="3">
         <v>46122</v>
@@ -4006,13 +3997,13 @@
     </row>
     <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D7" s="3">
         <v>46126</v>
@@ -4023,13 +4014,13 @@
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3">
         <v>46129</v>
@@ -4040,13 +4031,13 @@
     </row>
     <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3">
         <v>46146</v>
@@ -4057,26 +4048,26 @@
     </row>
     <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D11" s="3">
         <v>46153</v>
@@ -4087,13 +4078,13 @@
     </row>
     <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3">
         <v>46140</v>
@@ -4104,13 +4095,13 @@
     </row>
     <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D13" s="3">
         <v>46162</v>
@@ -4121,13 +4112,13 @@
     </row>
     <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D14" s="3">
         <v>46163</v>
@@ -4138,10 +4129,10 @@
     </row>
     <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3">
@@ -4153,13 +4144,13 @@
     </row>
     <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D16" s="3">
         <v>46160</v>
@@ -4170,13 +4161,13 @@
     </row>
     <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D17" s="3">
         <v>46140</v>
@@ -4187,13 +4178,13 @@
     </row>
     <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18" s="3">
         <v>46150</v>
@@ -4204,13 +4195,13 @@
     </row>
     <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D19" s="3">
         <v>46150</v>
@@ -4221,13 +4212,13 @@
     </row>
     <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D20" s="3">
         <v>46147</v>
@@ -4238,13 +4229,13 @@
     </row>
     <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D21" s="3">
         <v>46149</v>
@@ -4255,13 +4246,13 @@
     </row>
     <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D22" s="3">
         <v>46181</v>
@@ -4272,13 +4263,13 @@
     </row>
     <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="D23" s="3">
         <v>46170</v>
@@ -4289,13 +4280,13 @@
     </row>
     <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D24" s="3">
         <v>46168</v>
@@ -4306,13 +4297,13 @@
     </row>
     <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D25" s="3">
         <v>46167</v>
@@ -4323,13 +4314,13 @@
     </row>
     <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D26" s="3">
         <v>46174</v>
@@ -4340,13 +4331,13 @@
     </row>
     <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D27" s="3">
         <v>46175</v>
@@ -4357,13 +4348,13 @@
     </row>
     <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D28" s="3">
         <v>46171</v>
@@ -4374,13 +4365,13 @@
     </row>
     <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D29" s="3">
         <v>46170</v>
@@ -4391,13 +4382,13 @@
     </row>
     <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D30" s="3">
         <v>46181</v>
@@ -4408,13 +4399,13 @@
     </row>
     <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D31" s="3">
         <v>46178</v>
@@ -4425,13 +4416,13 @@
     </row>
     <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D32" s="3">
         <v>46170</v>
@@ -4442,13 +4433,13 @@
     </row>
     <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D33" s="3">
         <v>46181</v>
@@ -4459,26 +4450,26 @@
     </row>
     <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D35" s="3">
         <v>46155</v>
@@ -4489,13 +4480,13 @@
     </row>
     <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D36" s="3">
         <v>46167</v>
@@ -4506,13 +4497,13 @@
     </row>
     <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D37" s="3">
         <v>46167</v>
@@ -4523,13 +4514,13 @@
     </row>
     <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D38" s="3">
         <v>46168</v>
@@ -4540,13 +4531,13 @@
     </row>
     <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D39" s="3">
         <v>46175</v>
@@ -4557,13 +4548,13 @@
     </row>
     <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="C40" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D40" s="3">
         <v>46188</v>
@@ -4574,13 +4565,13 @@
     </row>
     <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D41" s="3">
         <v>46195</v>
@@ -4591,13 +4582,13 @@
     </row>
     <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D42" s="3">
         <v>46202</v>
@@ -4608,10 +4599,10 @@
     </row>
     <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="3">
@@ -4623,10 +4614,10 @@
     </row>
     <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="3">
@@ -4638,13 +4629,13 @@
     </row>
     <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D45" s="3">
         <v>46223</v>
@@ -4655,13 +4646,13 @@
     </row>
     <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D46" s="3">
         <v>46223</v>
@@ -4672,10 +4663,10 @@
     </row>
     <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="3">
@@ -4687,13 +4678,13 @@
     </row>
     <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D48" s="3">
         <v>46230</v>
@@ -4704,13 +4695,13 @@
     </row>
     <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D49" s="3">
         <v>46232</v>
@@ -4721,13 +4712,13 @@
     </row>
     <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D50" s="3">
         <v>46230</v>
@@ -4738,13 +4729,13 @@
     </row>
     <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D51" s="3">
         <v>46161</v>
@@ -4755,13 +4746,13 @@
     </row>
     <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D52" s="3">
         <v>46162</v>
@@ -4772,13 +4763,13 @@
     </row>
     <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D53" s="3">
         <v>46162</v>
@@ -4789,13 +4780,13 @@
     </row>
     <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D54" s="3">
         <v>46163</v>
@@ -4806,13 +4797,13 @@
     </row>
     <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="C55" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D55" s="3">
         <v>46174</v>
@@ -4823,13 +4814,13 @@
     </row>
     <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D56" s="3">
         <v>46174</v>
@@ -4840,13 +4831,13 @@
     </row>
     <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D57" s="3">
         <v>46174</v>
@@ -4857,13 +4848,13 @@
     </row>
     <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D58" s="3">
         <v>46181</v>
@@ -4874,13 +4865,13 @@
     </row>
     <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D59" s="3">
         <v>46181</v>
@@ -4891,13 +4882,13 @@
     </row>
     <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D60" s="3">
         <v>46181</v>
@@ -4908,13 +4899,13 @@
     </row>
     <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D61" s="3">
         <v>46181</v>
@@ -4925,13 +4916,13 @@
     </row>
     <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D62" s="3">
         <v>46182</v>
@@ -4942,13 +4933,13 @@
     </row>
     <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D63" s="3">
         <v>46184</v>
@@ -4959,13 +4950,13 @@
     </row>
     <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D64" s="3">
         <v>46188</v>
@@ -4976,13 +4967,13 @@
     </row>
     <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D65" s="3">
         <v>46188</v>
@@ -4993,13 +4984,13 @@
     </row>
     <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D66" s="3">
         <v>46198</v>
@@ -5356,30 +5347,30 @@
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E2" s="6">
         <v>46174</v>
@@ -5393,16 +5384,16 @@
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E3" s="6">
         <v>46175</v>
@@ -5416,16 +5407,16 @@
     </row>
     <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E4" s="6">
         <v>46177</v>
@@ -5439,16 +5430,16 @@
     </row>
     <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E5" s="6">
         <v>46178</v>
@@ -5462,16 +5453,16 @@
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E6" s="6">
         <v>46167</v>
@@ -5485,16 +5476,16 @@
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E7" s="6">
         <v>46168</v>
@@ -5508,16 +5499,16 @@
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E8" s="6">
         <v>46169</v>
@@ -5531,16 +5522,16 @@
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E9" s="6">
         <v>46170</v>
@@ -5554,16 +5545,16 @@
     </row>
     <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E10" s="6">
         <v>46171</v>
@@ -5577,16 +5568,16 @@
     </row>
     <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E11" s="6">
         <v>46167</v>
@@ -5600,16 +5591,16 @@
     </row>
     <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E12" s="6">
         <v>46168</v>
@@ -5623,16 +5614,16 @@
     </row>
     <row r="13" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E13" s="6">
         <v>46169</v>
@@ -5646,16 +5637,16 @@
     </row>
     <row r="14" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E14" s="6">
         <v>46170</v>
@@ -5669,16 +5660,16 @@
     </row>
     <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E15" s="6">
         <v>46171</v>
@@ -5692,16 +5683,16 @@
     </row>
     <row r="16" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E16" s="6">
         <v>46167</v>
@@ -5715,16 +5706,16 @@
     </row>
     <row r="17" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E17" s="6">
         <v>46168</v>
@@ -5738,16 +5729,16 @@
     </row>
     <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>180</v>
       </c>
       <c r="E18" s="6">
         <v>46169</v>
@@ -5761,16 +5752,16 @@
     </row>
     <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E19" s="6">
         <v>46169</v>
@@ -5784,16 +5775,16 @@
     </row>
     <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E20" s="6">
         <v>46170</v>
@@ -5807,16 +5798,16 @@
     </row>
     <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E21" s="6">
         <v>46170</v>
@@ -5830,16 +5821,16 @@
     </row>
     <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E22" s="6">
         <v>46160</v>
@@ -5853,16 +5844,16 @@
     </row>
     <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E23" s="6">
         <v>46161</v>
@@ -5876,16 +5867,16 @@
     </row>
     <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E24" s="6">
         <v>46162</v>
@@ -5899,16 +5890,16 @@
     </row>
     <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E25" s="6">
         <v>46163</v>
@@ -5922,16 +5913,16 @@
     </row>
     <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E26" s="6">
         <v>46164</v>
@@ -5945,16 +5936,16 @@
     </row>
     <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E27" s="6">
         <v>46160</v>
@@ -5968,16 +5959,16 @@
     </row>
     <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E28" s="6">
         <v>46161</v>
@@ -5991,16 +5982,16 @@
     </row>
     <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E29" s="6">
         <v>46162</v>
@@ -6014,16 +6005,16 @@
     </row>
     <row r="30" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E30" s="6">
         <v>46163</v>
@@ -6037,16 +6028,16 @@
     </row>
     <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E31" s="6">
         <v>46164</v>
@@ -6060,16 +6051,16 @@
     </row>
     <row r="32" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E32" s="6">
         <v>46160</v>
@@ -6083,16 +6074,16 @@
     </row>
     <row r="33" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E33" s="6">
         <v>46161</v>
@@ -6106,16 +6097,16 @@
     </row>
     <row r="34" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E34" s="6">
         <v>46162</v>
@@ -6129,16 +6120,16 @@
     </row>
     <row r="35" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E35" s="6">
         <v>46163</v>
@@ -6152,16 +6143,16 @@
     </row>
     <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E36" s="6">
         <v>46163</v>
@@ -6175,16 +6166,16 @@
     </row>
     <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="E37" s="6">
         <v>46164</v>
@@ -6198,16 +6189,16 @@
     </row>
     <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E38" s="6">
         <v>46160</v>
@@ -6221,16 +6212,16 @@
     </row>
     <row r="39" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E39" s="6">
         <v>46161</v>
@@ -6244,16 +6235,16 @@
     </row>
     <row r="40" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E40" s="6">
         <v>46162</v>
@@ -6267,16 +6258,16 @@
     </row>
     <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E41" s="6">
         <v>46163</v>
@@ -6290,16 +6281,16 @@
     </row>
     <row r="42" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E42" s="6">
         <v>46164</v>
@@ -6313,16 +6304,16 @@
     </row>
     <row r="43" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E43" s="6">
         <v>46153</v>
@@ -6336,16 +6327,16 @@
     </row>
     <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E44" s="6">
         <v>46154</v>
@@ -6359,16 +6350,16 @@
     </row>
     <row r="45" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E45" s="6">
         <v>46155</v>
@@ -6382,16 +6373,16 @@
     </row>
     <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E46" s="6">
         <v>46156</v>
@@ -6405,16 +6396,16 @@
     </row>
     <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E47" s="6">
         <v>46157</v>
@@ -6428,16 +6419,16 @@
     </row>
     <row r="48" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E48" s="6">
         <v>46153</v>
@@ -6451,16 +6442,16 @@
     </row>
     <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E49" s="6">
         <v>46154</v>
@@ -6474,16 +6465,16 @@
     </row>
     <row r="50" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E50" s="6">
         <v>46155</v>
@@ -6497,16 +6488,16 @@
     </row>
     <row r="51" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E51" s="6">
         <v>46156</v>
@@ -6520,16 +6511,16 @@
     </row>
     <row r="52" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E52" s="6">
         <v>46157</v>
@@ -6543,16 +6534,16 @@
     </row>
     <row r="53" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E53" s="6">
         <v>46153</v>
@@ -6566,16 +6557,16 @@
     </row>
     <row r="54" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E54" s="6">
         <v>46154</v>
@@ -6589,16 +6580,16 @@
     </row>
     <row r="55" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E55" s="6">
         <v>46155</v>
@@ -6612,16 +6603,16 @@
     </row>
     <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E56" s="6">
         <v>46156</v>
@@ -6635,16 +6626,16 @@
     </row>
     <row r="57" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E57" s="6">
         <v>46157</v>
@@ -6658,16 +6649,16 @@
     </row>
     <row r="58" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E58" s="6">
         <v>46153</v>
@@ -6681,16 +6672,16 @@
     </row>
     <row r="59" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="D59" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E59" s="6">
         <v>46153</v>
@@ -6704,16 +6695,16 @@
     </row>
     <row r="60" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E60" s="6">
         <v>46154</v>
@@ -6727,16 +6718,16 @@
     </row>
     <row r="61" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E61" s="6">
         <v>46154</v>
@@ -6750,16 +6741,16 @@
     </row>
     <row r="62" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E62" s="6">
         <v>46155</v>
@@ -6773,16 +6764,16 @@
     </row>
     <row r="63" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E63" s="6">
         <v>46155</v>
@@ -6796,16 +6787,16 @@
     </row>
     <row r="64" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E64" s="6">
         <v>46156</v>
@@ -6819,16 +6810,16 @@
     </row>
     <row r="65" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E65" s="6">
         <v>46156</v>
@@ -6842,16 +6833,16 @@
     </row>
     <row r="66" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E66" s="6">
         <v>46157</v>
@@ -6865,16 +6856,16 @@
     </row>
     <row r="67" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E67" s="6">
         <v>46157</v>
@@ -6888,16 +6879,16 @@
     </row>
     <row r="68" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E68" s="6">
         <v>46153</v>
@@ -6911,16 +6902,16 @@
     </row>
     <row r="69" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E69" s="6">
         <v>46154</v>
@@ -6934,16 +6925,16 @@
     </row>
     <row r="70" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E70" s="6">
         <v>46155</v>
@@ -6957,16 +6948,16 @@
     </row>
     <row r="71" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E71" s="6">
         <v>46155</v>
@@ -6980,16 +6971,16 @@
     </row>
     <row r="72" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E72" s="6">
         <v>46155</v>
@@ -7003,16 +6994,16 @@
     </row>
     <row r="73" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E73" s="6">
         <v>46155</v>
@@ -7026,16 +7017,16 @@
     </row>
     <row r="74" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E74" s="6">
         <v>46156</v>
@@ -7049,16 +7040,16 @@
     </row>
     <row r="75" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E75" s="6">
         <v>46157</v>
@@ -7072,16 +7063,16 @@
     </row>
     <row r="76" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E76" s="6">
         <v>46153</v>
@@ -7095,16 +7086,16 @@
     </row>
     <row r="77" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E77" s="6">
         <v>46154</v>
@@ -7118,16 +7109,16 @@
     </row>
     <row r="78" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E78" s="6">
         <v>46155</v>
@@ -7141,16 +7132,16 @@
     </row>
     <row r="79" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E79" s="6">
         <v>46156</v>
@@ -7164,16 +7155,16 @@
     </row>
     <row r="80" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E80" s="6">
         <v>46157</v>
@@ -7187,16 +7178,16 @@
     </row>
     <row r="81" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E81" s="6">
         <v>46153</v>
@@ -7210,16 +7201,16 @@
     </row>
     <row r="82" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E82" s="6">
         <v>46154</v>
@@ -7233,16 +7224,16 @@
     </row>
     <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E83" s="6">
         <v>46155</v>
@@ -7256,16 +7247,16 @@
     </row>
     <row r="84" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E84" s="6">
         <v>46156</v>
@@ -7279,16 +7270,16 @@
     </row>
     <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E85" s="6">
         <v>46157</v>
@@ -7302,16 +7293,16 @@
     </row>
     <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E86" s="6">
         <v>46146</v>
@@ -7325,16 +7316,16 @@
     </row>
     <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E87" s="6">
         <v>46147</v>
@@ -7348,16 +7339,16 @@
     </row>
     <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E88" s="6">
         <v>46148</v>
@@ -7371,16 +7362,16 @@
     </row>
     <row r="89" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E89" s="6">
         <v>46149</v>
@@ -7394,16 +7385,16 @@
     </row>
     <row r="90" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E90" s="6">
         <v>46150</v>
@@ -7417,16 +7408,16 @@
     </row>
     <row r="91" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E91" s="6">
         <v>46146</v>
@@ -7440,16 +7431,16 @@
     </row>
     <row r="92" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E92" s="6">
         <v>46146</v>
@@ -7463,16 +7454,16 @@
     </row>
     <row r="93" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E93" s="6">
         <v>46147</v>
@@ -7486,16 +7477,16 @@
     </row>
     <row r="94" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E94" s="6">
         <v>46147</v>
@@ -7509,16 +7500,16 @@
     </row>
     <row r="95" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E95" s="6">
         <v>46148</v>
@@ -7532,16 +7523,16 @@
     </row>
     <row r="96" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E96" s="6">
         <v>46149</v>
@@ -7555,16 +7546,16 @@
     </row>
     <row r="97" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E97" s="6">
         <v>46149</v>
@@ -7578,16 +7569,16 @@
     </row>
     <row r="98" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E98" s="6">
         <v>46150</v>
@@ -7601,16 +7592,16 @@
     </row>
     <row r="99" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E99" s="6">
         <v>46146</v>
@@ -7624,16 +7615,16 @@
     </row>
     <row r="100" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E100" s="6">
         <v>46147</v>
@@ -7647,16 +7638,16 @@
     </row>
     <row r="101" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E101" s="6">
         <v>46148</v>
@@ -7670,16 +7661,16 @@
     </row>
     <row r="102" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E102" s="6">
         <v>46149</v>
@@ -7693,16 +7684,16 @@
     </row>
     <row r="103" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E103" s="6">
         <v>46150</v>
@@ -7716,16 +7707,16 @@
     </row>
     <row r="104" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E104" s="6">
         <v>46146</v>
@@ -7739,16 +7730,16 @@
     </row>
     <row r="105" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E105" s="6">
         <v>46147</v>
@@ -7762,16 +7753,16 @@
     </row>
     <row r="106" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E106" s="6">
         <v>46148</v>
@@ -7785,16 +7776,16 @@
     </row>
     <row r="107" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E107" s="6">
         <v>46149</v>
@@ -7808,16 +7799,16 @@
     </row>
     <row r="108" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E108" s="6">
         <v>46150</v>
@@ -7831,16 +7822,16 @@
     </row>
     <row r="109" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E109" s="6">
         <v>46146</v>
@@ -7854,16 +7845,16 @@
     </row>
     <row r="110" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E110" s="6">
         <v>46147</v>
@@ -7877,16 +7868,16 @@
     </row>
     <row r="111" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E111" s="6">
         <v>46148</v>
@@ -7900,16 +7891,16 @@
     </row>
     <row r="112" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E112" s="6">
         <v>46149</v>
@@ -7923,16 +7914,16 @@
     </row>
     <row r="113" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E113" s="6">
         <v>46150</v>
@@ -7946,16 +7937,16 @@
     </row>
     <row r="114" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E114" s="6">
         <v>46146</v>
@@ -7969,16 +7960,16 @@
     </row>
     <row r="115" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E115" s="6">
         <v>46147</v>
@@ -7992,16 +7983,16 @@
     </row>
     <row r="116" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E116" s="6">
         <v>46148</v>
@@ -8015,16 +8006,16 @@
     </row>
     <row r="117" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E117" s="6">
         <v>46149</v>
@@ -8038,16 +8029,16 @@
     </row>
     <row r="118" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E118" s="6">
         <v>46150</v>
@@ -8061,16 +8052,16 @@
     </row>
     <row r="119" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E119" s="6">
         <v>46181</v>
@@ -8085,16 +8076,16 @@
     </row>
     <row r="120" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E120" s="6">
         <v>46182</v>
@@ -8109,16 +8100,16 @@
     </row>
     <row r="121" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E121" s="6">
         <v>46183</v>
@@ -8133,16 +8124,16 @@
     </row>
     <row r="122" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E122" s="6">
         <v>46184</v>
@@ -8157,16 +8148,16 @@
     </row>
     <row r="123" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E123" s="6">
         <v>46185</v>
@@ -8181,16 +8172,16 @@
     </row>
     <row r="124" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E124" s="6">
         <v>46181</v>
@@ -8205,16 +8196,16 @@
     </row>
     <row r="125" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E125" s="6">
         <v>46182</v>
@@ -8229,16 +8220,16 @@
     </row>
     <row r="126" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E126" s="6">
         <v>46183</v>
@@ -8253,16 +8244,16 @@
     </row>
     <row r="127" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E127" s="6">
         <v>46184</v>
@@ -8277,16 +8268,16 @@
     </row>
     <row r="128" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E128" s="6">
         <v>46188</v>
@@ -8301,16 +8292,16 @@
     </row>
     <row r="129" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E129" s="6">
         <v>46189</v>
@@ -8325,16 +8316,16 @@
     </row>
     <row r="130" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E130" s="6">
         <v>46190</v>
@@ -8349,16 +8340,16 @@
     </row>
     <row r="131" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C131" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="B131" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>373</v>
-      </c>
       <c r="D131" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E131" s="6">
         <v>46191</v>
@@ -8373,16 +8364,16 @@
     </row>
     <row r="132" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E132" s="6">
         <v>46192</v>
@@ -8415,755 +8406,755 @@
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D1" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="E1" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="H1" s="16" t="s">
+      <c r="L1" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="N1" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="L1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="P1" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q1" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="N1" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>266</v>
-      </c>
       <c r="R1" s="16" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C12" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C13" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C15" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C16" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C18" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C19" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C20" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C21" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C22" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C23" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C24" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C25" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B26" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C26" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B27" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C27" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B28" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C28" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B29" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C29" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B30" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C30" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B31" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C31" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B32" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C32" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C34" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B36" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C36" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C37" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C38" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B39" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C39" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C40" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B41" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C41" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B42" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C42" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C43" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C44" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C45" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C46" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C47" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C48" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C50" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C51" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C52" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B54" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C54" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0241B1E8-5C99-FB4C-ABB6-3AFE08A9BE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B321F63B-2B5A-A64B-ABCD-4CE03C07C9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="4 - Recursos" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$F$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$F$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Agenda Workshop'!$A$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$Q$54</definedName>
   </definedNames>
@@ -1301,7 +1301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1339,13 +1339,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1681,7 +1678,7 @@
       <c r="F1" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="17" t="s">
         <v>360</v>
       </c>
     </row>
@@ -2185,7 +2182,7 @@
         <v>46388</v>
       </c>
       <c r="G28" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2201,7 +2198,7 @@
       <c r="D29" s="2"/>
       <c r="E29" s="11"/>
       <c r="G29" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2217,7 +2214,7 @@
         <v>46388</v>
       </c>
       <c r="G30" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2235,7 +2232,7 @@
         <v>46388</v>
       </c>
       <c r="G31" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2251,7 +2248,7 @@
         <v>46388</v>
       </c>
       <c r="G32" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2269,7 +2266,7 @@
         <v>46388</v>
       </c>
       <c r="G33" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2287,7 +2284,7 @@
         <v>46388</v>
       </c>
       <c r="G34" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2305,7 +2302,7 @@
         <v>46388</v>
       </c>
       <c r="G35" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2323,7 +2320,7 @@
         <v>46388</v>
       </c>
       <c r="G36" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2344,7 +2341,7 @@
         <v>351</v>
       </c>
       <c r="G37" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2365,7 +2362,7 @@
         <v>351</v>
       </c>
       <c r="G38" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2639,7 +2636,7 @@
       <c r="A54" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -2749,8 +2746,8 @@
       <c r="E59" s="11">
         <v>46388</v>
       </c>
-      <c r="G59" s="19" t="s">
-        <v>361</v>
+      <c r="G59" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2767,8 +2764,8 @@
       <c r="E60" s="11">
         <v>46388</v>
       </c>
-      <c r="G60" s="19" t="s">
-        <v>361</v>
+      <c r="G60" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2785,8 +2782,8 @@
       <c r="E61" s="11">
         <v>46388</v>
       </c>
-      <c r="G61" s="19" t="s">
-        <v>361</v>
+      <c r="G61" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2803,8 +2800,8 @@
       <c r="E62" s="11">
         <v>46388</v>
       </c>
-      <c r="G62" s="19" t="s">
-        <v>361</v>
+      <c r="G62" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2821,8 +2818,8 @@
       <c r="E63" s="11">
         <v>46388</v>
       </c>
-      <c r="G63" s="19" t="s">
-        <v>361</v>
+      <c r="G63" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2839,8 +2836,8 @@
       <c r="E64" s="11">
         <v>46388</v>
       </c>
-      <c r="G64" s="19" t="s">
-        <v>361</v>
+      <c r="G64" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2860,8 +2857,8 @@
       <c r="F65" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G65" s="19" t="s">
-        <v>361</v>
+      <c r="G65" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2881,8 +2878,8 @@
       <c r="F66" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G66" s="19" t="s">
-        <v>361</v>
+      <c r="G66" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2901,8 +2898,8 @@
       <c r="E67" s="11">
         <v>46388</v>
       </c>
-      <c r="G67" s="19" t="s">
-        <v>361</v>
+      <c r="G67" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2924,8 +2921,8 @@
       <c r="F68" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G68" s="19" t="s">
-        <v>361</v>
+      <c r="G68" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2940,8 +2937,8 @@
       <c r="E69" s="11">
         <v>46388</v>
       </c>
-      <c r="G69" s="19" t="s">
-        <v>361</v>
+      <c r="G69" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2956,8 +2953,8 @@
       <c r="E70" s="11">
         <v>46388</v>
       </c>
-      <c r="G70" s="19" t="s">
-        <v>361</v>
+      <c r="G70" s="18" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2973,7 +2970,7 @@
       <c r="E71" s="11">
         <v>46388</v>
       </c>
-      <c r="G71" s="19" t="s">
+      <c r="G71" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -2990,7 +2987,7 @@
       <c r="E72" s="11">
         <v>46388</v>
       </c>
-      <c r="G72" s="19" t="s">
+      <c r="G72" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3010,7 +3007,7 @@
       <c r="E73" s="11">
         <v>46388</v>
       </c>
-      <c r="G73" s="19" t="s">
+      <c r="G73" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3027,7 +3024,7 @@
       <c r="E74" s="11">
         <v>46388</v>
       </c>
-      <c r="G74" s="19" t="s">
+      <c r="G74" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3044,7 +3041,7 @@
       <c r="E75" s="11">
         <v>46388</v>
       </c>
-      <c r="G75" s="19" t="s">
+      <c r="G75" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3061,7 +3058,7 @@
       <c r="E76" s="11">
         <v>46388</v>
       </c>
-      <c r="G76" s="19" t="s">
+      <c r="G76" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3078,7 +3075,7 @@
       <c r="E77" s="11">
         <v>46388</v>
       </c>
-      <c r="G77" s="19" t="s">
+      <c r="G77" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3095,7 +3092,7 @@
       <c r="E78" s="11">
         <v>46388</v>
       </c>
-      <c r="G78" s="19" t="s">
+      <c r="G78" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3112,7 +3109,7 @@
       <c r="E79" s="11">
         <v>46388</v>
       </c>
-      <c r="G79" s="19" t="s">
+      <c r="G79" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3129,7 +3126,7 @@
       <c r="E80" s="11">
         <v>46388</v>
       </c>
-      <c r="G80" s="19" t="s">
+      <c r="G80" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3149,7 +3146,7 @@
       <c r="F81" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G81" s="19" t="s">
+      <c r="G81" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3169,7 +3166,7 @@
       <c r="F82" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G82" s="19" t="s">
+      <c r="G82" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3189,7 +3186,7 @@
       <c r="F83" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G83" s="19" t="s">
+      <c r="G83" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3209,7 +3206,7 @@
       <c r="F84" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G84" s="19" t="s">
+      <c r="G84" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3226,7 +3223,7 @@
       <c r="E85" s="12">
         <v>46388</v>
       </c>
-      <c r="G85" s="19" t="s">
+      <c r="G85" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3243,7 +3240,7 @@
       <c r="E86" s="12">
         <v>46388</v>
       </c>
-      <c r="G86" s="19" t="s">
+      <c r="G86" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3260,7 +3257,7 @@
       <c r="E87" s="12">
         <v>46388</v>
       </c>
-      <c r="G87" s="19" t="s">
+      <c r="G87" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3274,7 +3271,7 @@
       <c r="E88" s="12">
         <v>46388</v>
       </c>
-      <c r="G88" s="19" t="s">
+      <c r="G88" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3288,7 +3285,7 @@
       <c r="E89" s="12">
         <v>46388</v>
       </c>
-      <c r="G89" s="19" t="s">
+      <c r="G89" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3302,7 +3299,7 @@
       <c r="E90" s="12">
         <v>46388</v>
       </c>
-      <c r="G90" s="19" t="s">
+      <c r="G90" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3319,7 +3316,7 @@
       <c r="E91" s="12">
         <v>46388</v>
       </c>
-      <c r="G91" s="19" t="s">
+      <c r="G91" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3339,7 +3336,7 @@
       <c r="F92" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G92" s="19" t="s">
+      <c r="G92" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3359,7 +3356,7 @@
       <c r="F93" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G93" s="19" t="s">
+      <c r="G93" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3376,7 +3373,7 @@
       <c r="E94" s="12">
         <v>46631</v>
       </c>
-      <c r="G94" s="19" t="s">
+      <c r="G94" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3393,7 +3390,7 @@
       <c r="E95" s="12">
         <v>46631</v>
       </c>
-      <c r="G95" s="19" t="s">
+      <c r="G95" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3410,7 +3407,7 @@
       <c r="E96" s="12">
         <v>46631</v>
       </c>
-      <c r="G96" s="19" t="s">
+      <c r="G96" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3427,7 +3424,7 @@
       <c r="E97" s="12">
         <v>46631</v>
       </c>
-      <c r="G97" s="19" t="s">
+      <c r="G97" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3444,7 +3441,7 @@
       <c r="E98" s="12">
         <v>46631</v>
       </c>
-      <c r="G98" s="19" t="s">
+      <c r="G98" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3461,7 +3458,7 @@
       <c r="E99" s="12">
         <v>46631</v>
       </c>
-      <c r="G99" s="19" t="s">
+      <c r="G99" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3478,7 +3475,7 @@
       <c r="E100" s="12">
         <v>46631</v>
       </c>
-      <c r="G100" s="19" t="s">
+      <c r="G100" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3493,7 +3490,7 @@
         <v>108</v>
       </c>
       <c r="E101" s="12"/>
-      <c r="G101" s="19" t="s">
+      <c r="G101" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3510,7 +3507,7 @@
       <c r="E102" s="12">
         <v>46631</v>
       </c>
-      <c r="G102" s="19" t="s">
+      <c r="G102" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3530,7 +3527,7 @@
       <c r="F103" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="G103" s="19" t="s">
+      <c r="G103" s="18" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3547,7 +3544,7 @@
       <c r="E104" s="12">
         <v>46631</v>
       </c>
-      <c r="G104" s="19" t="s">
+      <c r="G104" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3564,7 +3561,7 @@
       <c r="E105" s="12">
         <v>46631</v>
       </c>
-      <c r="G105" s="19" t="s">
+      <c r="G105" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3581,7 +3578,7 @@
       <c r="E106" s="12">
         <v>46631</v>
       </c>
-      <c r="G106" s="19" t="s">
+      <c r="G106" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3598,7 +3595,7 @@
       <c r="E107" s="12">
         <v>46631</v>
       </c>
-      <c r="G107" s="19" t="s">
+      <c r="G107" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3612,7 +3609,7 @@
       <c r="E108" s="12">
         <v>46296</v>
       </c>
-      <c r="G108" s="19" t="s">
+      <c r="G108" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3626,7 +3623,7 @@
       <c r="E109" s="12">
         <v>46296</v>
       </c>
-      <c r="G109" s="19" t="s">
+      <c r="G109" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3640,7 +3637,7 @@
       <c r="E110" s="12">
         <v>46296</v>
       </c>
-      <c r="G110" s="19" t="s">
+      <c r="G110" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3657,7 +3654,7 @@
       <c r="E111" s="12">
         <v>46296</v>
       </c>
-      <c r="G111" s="19" t="s">
+      <c r="G111" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3671,7 +3668,7 @@
       <c r="E112" s="12">
         <v>46569</v>
       </c>
-      <c r="G112" s="19" t="s">
+      <c r="G112" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3685,7 +3682,7 @@
       <c r="E113" s="12">
         <v>46569</v>
       </c>
-      <c r="G113" s="19" t="s">
+      <c r="G113" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3699,7 +3696,7 @@
       <c r="E114" s="12">
         <v>46569</v>
       </c>
-      <c r="G114" s="19" t="s">
+      <c r="G114" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3716,7 +3713,7 @@
       <c r="E115" s="12">
         <v>46569</v>
       </c>
-      <c r="G115" s="19" t="s">
+      <c r="G115" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3733,7 +3730,7 @@
       <c r="E116" s="12">
         <v>46569</v>
       </c>
-      <c r="G116" s="19" t="s">
+      <c r="G116" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3745,7 +3742,7 @@
         <v>10</v>
       </c>
       <c r="E117" s="12"/>
-      <c r="G117" s="19" t="s">
+      <c r="G117" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3762,8 +3759,8 @@
       <c r="E118" s="12">
         <v>46569</v>
       </c>
-      <c r="G118" s="19" t="s">
-        <v>168</v>
+      <c r="G118" s="18" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3779,8 +3776,8 @@
       <c r="E119" s="12">
         <v>46569</v>
       </c>
-      <c r="G119" s="19" t="s">
-        <v>168</v>
+      <c r="G119" s="18" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3796,8 +3793,8 @@
       <c r="E120" s="12">
         <v>46569</v>
       </c>
-      <c r="G120" s="19" t="s">
-        <v>168</v>
+      <c r="G120" s="18" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3814,8 +3811,8 @@
         <v>46569</v>
       </c>
       <c r="F121" s="14"/>
-      <c r="G121" s="19" t="s">
-        <v>168</v>
+      <c r="G121" s="18" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -3828,7 +3825,7 @@
       <c r="E122" s="12">
         <v>46388</v>
       </c>
-      <c r="G122" s="19" t="s">
+      <c r="G122" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3842,7 +3839,7 @@
       <c r="E123" s="12">
         <v>46388</v>
       </c>
-      <c r="G123" s="19" t="s">
+      <c r="G123" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3856,7 +3853,7 @@
       <c r="E124" s="12">
         <v>46388</v>
       </c>
-      <c r="G124" s="19" t="s">
+      <c r="G124" s="18" t="s">
         <v>361</v>
       </c>
     </row>
@@ -3870,12 +3867,12 @@
       <c r="E125" s="12">
         <v>46388</v>
       </c>
-      <c r="G125" s="19" t="s">
+      <c r="G125" s="18" t="s">
         <v>361</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F121" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F125" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B321F63B-2B5A-A64B-ABCD-4CE03C07C9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B6518F-B44B-2C43-9109-C6AFCB1DC937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="372">
   <si>
     <t>Projeto</t>
   </si>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>Consultor TRM</t>
-  </si>
-  <si>
-    <t>Consultor WMS</t>
   </si>
   <si>
     <t>4516 - EPR - S4HANA-PUBLIC - Implantação de Soluções SAP S4/HANA Public Cloud</t>
@@ -1667,19 +1664,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="G1" s="17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1690,14 +1687,14 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="11">
         <v>46388</v>
       </c>
       <c r="G2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1708,14 +1705,14 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="11">
         <v>46388</v>
       </c>
       <c r="G3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1726,14 +1723,14 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="11">
         <v>46388</v>
       </c>
       <c r="G4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1744,14 +1741,14 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="11">
         <v>46388</v>
       </c>
       <c r="G5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1762,14 +1759,14 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="11">
         <v>46388</v>
       </c>
       <c r="G6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1780,14 +1777,14 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="11">
         <v>46388</v>
       </c>
       <c r="G7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1798,14 +1795,14 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="11">
         <v>46388</v>
       </c>
       <c r="G8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1816,14 +1813,14 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="11">
         <v>46388</v>
       </c>
       <c r="G9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1834,17 +1831,17 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="11">
         <v>46388</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1855,17 +1852,17 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="11">
         <v>46388</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1876,17 +1873,17 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="11">
         <v>46388</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1897,17 +1894,17 @@
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="11">
         <v>46388</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1918,16 +1915,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E14" s="11">
         <v>46296</v>
       </c>
       <c r="G14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1938,16 +1935,16 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E15" s="11">
         <v>46296</v>
       </c>
       <c r="G15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1958,14 +1955,14 @@
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="11">
         <v>46296</v>
       </c>
       <c r="G16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1973,15 +1970,15 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="11"/>
       <c r="G17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -1992,14 +1989,14 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="11">
         <v>46296</v>
       </c>
       <c r="G18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2010,14 +2007,14 @@
         <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="11">
         <v>46296</v>
       </c>
       <c r="G19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2028,14 +2025,14 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="11">
         <v>46296</v>
       </c>
       <c r="G20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2046,14 +2043,14 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="11">
         <v>46296</v>
       </c>
       <c r="G21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2064,14 +2061,14 @@
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="11">
         <v>46296</v>
       </c>
       <c r="G22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2082,14 +2079,14 @@
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="11">
         <v>46296</v>
       </c>
       <c r="G23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2100,14 +2097,14 @@
         <v>10</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="11">
         <v>46296</v>
       </c>
       <c r="G24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2118,17 +2115,17 @@
         <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="11">
         <v>46296</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2139,14 +2136,14 @@
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="11">
         <v>46388</v>
       </c>
       <c r="G26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2157,14 +2154,14 @@
         <v>5</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="11">
         <v>46388</v>
       </c>
       <c r="G27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2175,14 +2172,14 @@
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="11">
         <v>46388</v>
       </c>
       <c r="G28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2190,15 +2187,15 @@
         <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="11"/>
       <c r="G29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2214,7 +2211,7 @@
         <v>46388</v>
       </c>
       <c r="G30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2225,14 +2222,14 @@
         <v>24</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="11">
         <v>46388</v>
       </c>
       <c r="G31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2248,7 +2245,7 @@
         <v>46388</v>
       </c>
       <c r="G32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2259,14 +2256,14 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="11">
         <v>46388</v>
       </c>
       <c r="G33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2277,14 +2274,14 @@
         <v>25</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="11">
         <v>46388</v>
       </c>
       <c r="G34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2295,14 +2292,14 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="11">
         <v>46388</v>
       </c>
       <c r="G35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2313,14 +2310,14 @@
         <v>26</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="11">
         <v>46388</v>
       </c>
       <c r="G36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2331,17 +2328,17 @@
         <v>11</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="11">
         <v>46388</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2352,17 +2349,17 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="11">
         <v>46388</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2373,14 +2370,14 @@
         <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="11">
         <v>46661</v>
       </c>
       <c r="G39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2396,7 +2393,7 @@
         <v>46661</v>
       </c>
       <c r="G40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2407,14 +2404,14 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="11">
         <v>46661</v>
       </c>
       <c r="G41" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2425,14 +2422,14 @@
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="11">
         <v>46661</v>
       </c>
       <c r="G42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2443,14 +2440,14 @@
         <v>10</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="11">
         <v>46661</v>
       </c>
       <c r="G43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2461,17 +2458,17 @@
         <v>11</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="11">
         <v>46661</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2482,14 +2479,14 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="11">
         <v>46388</v>
       </c>
       <c r="G45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2500,14 +2497,14 @@
         <v>15</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D46" s="15"/>
       <c r="E46" s="11">
         <v>46388</v>
       </c>
       <c r="G46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2515,7 +2512,7 @@
         <v>29</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2523,7 +2520,7 @@
         <v>46388</v>
       </c>
       <c r="G47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2534,14 +2531,14 @@
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="11">
         <v>46388</v>
       </c>
       <c r="G48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2552,14 +2549,14 @@
         <v>30</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="11">
         <v>46388</v>
       </c>
       <c r="G49" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2570,14 +2567,14 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="11">
         <v>46388</v>
       </c>
       <c r="G50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2588,14 +2585,14 @@
         <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="11">
         <v>46388</v>
       </c>
       <c r="G51" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2606,14 +2603,14 @@
         <v>26</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="11">
         <v>46388</v>
       </c>
       <c r="G52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2629,7 +2626,7 @@
         <v>46388</v>
       </c>
       <c r="G53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2640,16 +2637,16 @@
         <v>32</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E54" s="11">
         <v>46388</v>
       </c>
       <c r="G54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2657,17 +2654,17 @@
         <v>29</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="11">
         <v>46388</v>
       </c>
       <c r="G55" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2678,14 +2675,14 @@
         <v>10</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="11">
         <v>46388</v>
       </c>
       <c r="G56" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2696,17 +2693,17 @@
         <v>11</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="11">
         <v>46388</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G57" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2717,220 +2714,220 @@
         <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="11">
         <v>46388</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G58" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E59" s="11">
         <v>46388</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="11">
         <v>46388</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="11">
         <v>46388</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="11">
         <v>46388</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="11">
         <v>46388</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="11">
         <v>46388</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="11">
         <v>46388</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C66" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="11">
         <v>46388</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E67" s="11">
         <v>46388</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E68" s="11">
         <v>46388</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2938,12 +2935,12 @@
         <v>46388</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>13</v>
@@ -2954,316 +2951,316 @@
         <v>46388</v>
       </c>
       <c r="G70" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B71" t="s">
         <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E71" s="11">
         <v>46388</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B72" t="s">
         <v>7</v>
       </c>
       <c r="C72" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E72" s="11">
         <v>46388</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" t="s">
         <v>38</v>
       </c>
-      <c r="B73" t="s">
-        <v>39</v>
-      </c>
       <c r="C73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E73" s="11">
         <v>46388</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E74" s="11">
         <v>46388</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B75" t="s">
         <v>5</v>
       </c>
       <c r="C75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E75" s="11">
         <v>46388</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E76" s="11">
         <v>46388</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B77" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E77" s="11">
         <v>46388</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C78" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E78" s="11">
         <v>46388</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B79" t="s">
         <v>31</v>
       </c>
       <c r="C79" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E79" s="11">
         <v>46388</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B80" t="s">
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E80" s="11">
         <v>46388</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E81" s="11">
         <v>46388</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E82" s="11">
         <v>46388</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B83" t="s">
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E83" s="11">
         <v>46388</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G83" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E84" s="11">
         <v>46388</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B85" t="s">
         <v>28</v>
       </c>
       <c r="C85" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E85" s="12">
         <v>46388</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E86" s="12">
         <v>46388</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B87" t="s">
         <v>7</v>
       </c>
       <c r="C87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E87" s="12">
         <v>46388</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B88" t="s">
         <v>5</v>
@@ -3272,26 +3269,26 @@
         <v>46388</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B89" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E89" s="12">
         <v>46388</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
@@ -3300,308 +3297,308 @@
         <v>46388</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B91" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E91" s="12">
         <v>46388</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E92" s="12">
         <v>46388</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B93" t="s">
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E93" s="12">
         <v>46388</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E94" s="12">
         <v>46631</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B95" t="s">
         <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E95" s="12">
         <v>46631</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B96" t="s">
         <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E96" s="12">
         <v>46631</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B97" t="s">
         <v>5</v>
       </c>
       <c r="C97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E97" s="12">
         <v>46631</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B98" t="s">
         <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E98" s="12">
         <v>46631</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B99" t="s">
         <v>8</v>
       </c>
       <c r="C99" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E99" s="12">
         <v>46631</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B100" t="s">
         <v>10</v>
       </c>
       <c r="C100" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E100" s="12">
         <v>46631</v>
       </c>
       <c r="G100" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B101" t="s">
         <v>21</v>
       </c>
       <c r="C101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E101" s="12"/>
       <c r="G101" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>41</v>
+      </c>
+      <c r="B102" t="s">
         <v>42</v>
       </c>
-      <c r="B102" t="s">
-        <v>43</v>
-      </c>
       <c r="C102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E102" s="12">
         <v>46631</v>
       </c>
       <c r="G102" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B103" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C103" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E103" s="12">
         <v>46631</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G103" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B104" t="s">
         <v>28</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E104" s="12">
         <v>46631</v>
       </c>
       <c r="G104" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B105" t="s">
         <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E105" s="12">
         <v>46631</v>
       </c>
       <c r="G105" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B106" t="s">
         <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E106" s="12">
         <v>46631</v>
       </c>
       <c r="G106" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B107" t="s">
         <v>10</v>
       </c>
       <c r="C107" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E107" s="12">
         <v>46631</v>
       </c>
       <c r="G107" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B108" t="s">
         <v>28</v>
@@ -3610,12 +3607,12 @@
         <v>46296</v>
       </c>
       <c r="G108" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B109" t="s">
         <v>5</v>
@@ -3624,12 +3621,12 @@
         <v>46296</v>
       </c>
       <c r="G109" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B110" t="s">
         <v>6</v>
@@ -3638,43 +3635,43 @@
         <v>46296</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E111" s="12">
         <v>46296</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E112" s="12">
         <v>46569</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B113" t="s">
         <v>19</v>
@@ -3683,12 +3680,12 @@
         <v>46569</v>
       </c>
       <c r="G113" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
@@ -3697,127 +3694,127 @@
         <v>46569</v>
       </c>
       <c r="G114" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B115" t="s">
         <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E115" s="12">
         <v>46569</v>
       </c>
       <c r="G115" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
+        <v>344</v>
+      </c>
+      <c r="B116" t="s">
         <v>345</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>346</v>
-      </c>
-      <c r="C116" t="s">
-        <v>347</v>
       </c>
       <c r="E116" s="12">
         <v>46569</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B117" t="s">
         <v>10</v>
       </c>
       <c r="E117" s="12"/>
       <c r="G117" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B118" t="s">
         <v>28</v>
       </c>
       <c r="C118" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E118" s="12">
         <v>46569</v>
       </c>
       <c r="G118" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B119" t="s">
         <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E119" s="12">
         <v>46569</v>
       </c>
       <c r="G119" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B120" t="s">
         <v>6</v>
       </c>
       <c r="C120" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E120" s="12">
         <v>46569</v>
       </c>
       <c r="G120" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E121" s="12">
         <v>46569</v>
       </c>
       <c r="F121" s="14"/>
       <c r="G121" s="18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B122" t="s">
         <v>28</v>
@@ -3826,12 +3823,12 @@
         <v>46388</v>
       </c>
       <c r="G122" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B123" t="s">
         <v>5</v>
@@ -3840,12 +3837,12 @@
         <v>46388</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B124" t="s">
         <v>6</v>
@@ -3854,12 +3851,12 @@
         <v>46388</v>
       </c>
       <c r="G124" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
@@ -3868,7 +3865,7 @@
         <v>46388</v>
       </c>
       <c r="G125" s="18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3895,27 +3892,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D2" s="3">
         <v>46113</v>
@@ -3926,13 +3923,13 @@
     </row>
     <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="D3" s="3">
         <v>46113</v>
@@ -3943,13 +3940,13 @@
     </row>
     <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D4" s="3">
         <v>46114</v>
@@ -3960,13 +3957,13 @@
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="3">
         <v>46128</v>
@@ -3977,13 +3974,13 @@
     </row>
     <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3">
         <v>46122</v>
@@ -3994,13 +3991,13 @@
     </row>
     <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" s="3">
         <v>46126</v>
@@ -4011,13 +4008,13 @@
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3">
         <v>46129</v>
@@ -4028,13 +4025,13 @@
     </row>
     <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3">
         <v>46146</v>
@@ -4045,26 +4042,26 @@
     </row>
     <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="D11" s="3">
         <v>46153</v>
@@ -4075,13 +4072,13 @@
     </row>
     <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D12" s="3">
         <v>46140</v>
@@ -4092,13 +4089,13 @@
     </row>
     <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="3">
         <v>46162</v>
@@ -4109,13 +4106,13 @@
     </row>
     <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D14" s="3">
         <v>46163</v>
@@ -4126,10 +4123,10 @@
     </row>
     <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3">
@@ -4141,13 +4138,13 @@
     </row>
     <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="D16" s="3">
         <v>46160</v>
@@ -4158,13 +4155,13 @@
     </row>
     <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="D17" s="3">
         <v>46140</v>
@@ -4175,13 +4172,13 @@
     </row>
     <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D18" s="3">
         <v>46150</v>
@@ -4192,13 +4189,13 @@
     </row>
     <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="3">
         <v>46150</v>
@@ -4209,13 +4206,13 @@
     </row>
     <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="3">
         <v>46147</v>
@@ -4226,13 +4223,13 @@
     </row>
     <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21" s="3">
         <v>46149</v>
@@ -4243,13 +4240,13 @@
     </row>
     <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D22" s="3">
         <v>46181</v>
@@ -4260,13 +4257,13 @@
     </row>
     <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="D23" s="3">
         <v>46170</v>
@@ -4277,13 +4274,13 @@
     </row>
     <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D24" s="3">
         <v>46168</v>
@@ -4294,13 +4291,13 @@
     </row>
     <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D25" s="3">
         <v>46167</v>
@@ -4311,13 +4308,13 @@
     </row>
     <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="3">
         <v>46174</v>
@@ -4328,13 +4325,13 @@
     </row>
     <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D27" s="3">
         <v>46175</v>
@@ -4345,13 +4342,13 @@
     </row>
     <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D28" s="3">
         <v>46171</v>
@@ -4362,13 +4359,13 @@
     </row>
     <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="D29" s="3">
         <v>46170</v>
@@ -4379,13 +4376,13 @@
     </row>
     <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D30" s="3">
         <v>46181</v>
@@ -4396,13 +4393,13 @@
     </row>
     <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D31" s="3">
         <v>46178</v>
@@ -4413,13 +4410,13 @@
     </row>
     <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D32" s="3">
         <v>46170</v>
@@ -4430,13 +4427,13 @@
     </row>
     <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D33" s="3">
         <v>46181</v>
@@ -4447,26 +4444,26 @@
     </row>
     <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D35" s="3">
         <v>46155</v>
@@ -4477,13 +4474,13 @@
     </row>
     <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D36" s="3">
         <v>46167</v>
@@ -4494,13 +4491,13 @@
     </row>
     <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D37" s="3">
         <v>46167</v>
@@ -4511,13 +4508,13 @@
     </row>
     <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D38" s="3">
         <v>46168</v>
@@ -4528,13 +4525,13 @@
     </row>
     <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D39" s="3">
         <v>46175</v>
@@ -4545,13 +4542,13 @@
     </row>
     <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D40" s="3">
         <v>46188</v>
@@ -4562,13 +4559,13 @@
     </row>
     <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D41" s="3">
         <v>46195</v>
@@ -4579,13 +4576,13 @@
     </row>
     <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D42" s="3">
         <v>46202</v>
@@ -4596,10 +4593,10 @@
     </row>
     <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="3">
@@ -4611,10 +4608,10 @@
     </row>
     <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="3">
@@ -4626,13 +4623,13 @@
     </row>
     <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D45" s="3">
         <v>46223</v>
@@ -4643,13 +4640,13 @@
     </row>
     <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D46" s="3">
         <v>46223</v>
@@ -4660,10 +4657,10 @@
     </row>
     <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="3">
@@ -4675,13 +4672,13 @@
     </row>
     <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D48" s="3">
         <v>46230</v>
@@ -4692,13 +4689,13 @@
     </row>
     <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D49" s="3">
         <v>46232</v>
@@ -4709,13 +4706,13 @@
     </row>
     <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D50" s="3">
         <v>46230</v>
@@ -4726,13 +4723,13 @@
     </row>
     <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D51" s="3">
         <v>46161</v>
@@ -4743,13 +4740,13 @@
     </row>
     <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D52" s="3">
         <v>46162</v>
@@ -4760,13 +4757,13 @@
     </row>
     <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="D53" s="3">
         <v>46162</v>
@@ -4777,13 +4774,13 @@
     </row>
     <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D54" s="3">
         <v>46163</v>
@@ -4794,13 +4791,13 @@
     </row>
     <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D55" s="3">
         <v>46174</v>
@@ -4811,13 +4808,13 @@
     </row>
     <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D56" s="3">
         <v>46174</v>
@@ -4828,13 +4825,13 @@
     </row>
     <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="D57" s="3">
         <v>46174</v>
@@ -4845,13 +4842,13 @@
     </row>
     <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="D58" s="3">
         <v>46181</v>
@@ -4862,13 +4859,13 @@
     </row>
     <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="D59" s="3">
         <v>46181</v>
@@ -4879,13 +4876,13 @@
     </row>
     <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D60" s="3">
         <v>46181</v>
@@ -4896,13 +4893,13 @@
     </row>
     <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D61" s="3">
         <v>46181</v>
@@ -4913,13 +4910,13 @@
     </row>
     <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D62" s="3">
         <v>46182</v>
@@ -4930,13 +4927,13 @@
     </row>
     <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D63" s="3">
         <v>46184</v>
@@ -4947,13 +4944,13 @@
     </row>
     <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D64" s="3">
         <v>46188</v>
@@ -4964,13 +4961,13 @@
     </row>
     <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D65" s="3">
         <v>46188</v>
@@ -4981,13 +4978,13 @@
     </row>
     <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D66" s="3">
         <v>46198</v>
@@ -5344,30 +5341,30 @@
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E2" s="6">
         <v>46174</v>
@@ -5381,16 +5378,16 @@
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E3" s="6">
         <v>46175</v>
@@ -5404,16 +5401,16 @@
     </row>
     <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E4" s="6">
         <v>46177</v>
@@ -5427,16 +5424,16 @@
     </row>
     <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E5" s="6">
         <v>46178</v>
@@ -5450,16 +5447,16 @@
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="E6" s="6">
         <v>46167</v>
@@ -5473,16 +5470,16 @@
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="E7" s="6">
         <v>46168</v>
@@ -5496,16 +5493,16 @@
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="E8" s="6">
         <v>46169</v>
@@ -5519,16 +5516,16 @@
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="E9" s="6">
         <v>46170</v>
@@ -5542,16 +5539,16 @@
     </row>
     <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>171</v>
       </c>
       <c r="E10" s="6">
         <v>46171</v>
@@ -5565,16 +5562,16 @@
     </row>
     <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E11" s="6">
         <v>46167</v>
@@ -5588,16 +5585,16 @@
     </row>
     <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E12" s="6">
         <v>46168</v>
@@ -5611,16 +5608,16 @@
     </row>
     <row r="13" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E13" s="6">
         <v>46169</v>
@@ -5634,16 +5631,16 @@
     </row>
     <row r="14" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E14" s="6">
         <v>46170</v>
@@ -5657,16 +5654,16 @@
     </row>
     <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E15" s="6">
         <v>46171</v>
@@ -5680,16 +5677,16 @@
     </row>
     <row r="16" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>174</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>175</v>
       </c>
       <c r="E16" s="6">
         <v>46167</v>
@@ -5703,16 +5700,16 @@
     </row>
     <row r="17" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E17" s="6">
         <v>46168</v>
@@ -5726,16 +5723,16 @@
     </row>
     <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E18" s="6">
         <v>46169</v>
@@ -5749,16 +5746,16 @@
     </row>
     <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E19" s="6">
         <v>46169</v>
@@ -5772,16 +5769,16 @@
     </row>
     <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E20" s="6">
         <v>46170</v>
@@ -5795,16 +5792,16 @@
     </row>
     <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E21" s="6">
         <v>46170</v>
@@ -5818,16 +5815,16 @@
     </row>
     <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E22" s="6">
         <v>46160</v>
@@ -5841,16 +5838,16 @@
     </row>
     <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E23" s="6">
         <v>46161</v>
@@ -5864,16 +5861,16 @@
     </row>
     <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E24" s="6">
         <v>46162</v>
@@ -5887,16 +5884,16 @@
     </row>
     <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E25" s="6">
         <v>46163</v>
@@ -5910,16 +5907,16 @@
     </row>
     <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E26" s="6">
         <v>46164</v>
@@ -5933,16 +5930,16 @@
     </row>
     <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E27" s="6">
         <v>46160</v>
@@ -5956,16 +5953,16 @@
     </row>
     <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E28" s="6">
         <v>46161</v>
@@ -5979,16 +5976,16 @@
     </row>
     <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E29" s="6">
         <v>46162</v>
@@ -6002,16 +5999,16 @@
     </row>
     <row r="30" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E30" s="6">
         <v>46163</v>
@@ -6025,16 +6022,16 @@
     </row>
     <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E31" s="6">
         <v>46164</v>
@@ -6048,16 +6045,16 @@
     </row>
     <row r="32" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E32" s="6">
         <v>46160</v>
@@ -6071,16 +6068,16 @@
     </row>
     <row r="33" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E33" s="6">
         <v>46161</v>
@@ -6094,16 +6091,16 @@
     </row>
     <row r="34" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E34" s="6">
         <v>46162</v>
@@ -6117,16 +6114,16 @@
     </row>
     <row r="35" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E35" s="6">
         <v>46163</v>
@@ -6140,16 +6137,16 @@
     </row>
     <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E36" s="6">
         <v>46163</v>
@@ -6163,16 +6160,16 @@
     </row>
     <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E37" s="6">
         <v>46164</v>
@@ -6186,16 +6183,16 @@
     </row>
     <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E38" s="6">
         <v>46160</v>
@@ -6209,16 +6206,16 @@
     </row>
     <row r="39" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E39" s="6">
         <v>46161</v>
@@ -6232,16 +6229,16 @@
     </row>
     <row r="40" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E40" s="6">
         <v>46162</v>
@@ -6255,16 +6252,16 @@
     </row>
     <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E41" s="6">
         <v>46163</v>
@@ -6278,16 +6275,16 @@
     </row>
     <row r="42" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E42" s="6">
         <v>46164</v>
@@ -6301,16 +6298,16 @@
     </row>
     <row r="43" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E43" s="6">
         <v>46153</v>
@@ -6324,16 +6321,16 @@
     </row>
     <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E44" s="6">
         <v>46154</v>
@@ -6347,16 +6344,16 @@
     </row>
     <row r="45" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E45" s="6">
         <v>46155</v>
@@ -6370,16 +6367,16 @@
     </row>
     <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E46" s="6">
         <v>46156</v>
@@ -6393,16 +6390,16 @@
     </row>
     <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E47" s="6">
         <v>46157</v>
@@ -6416,16 +6413,16 @@
     </row>
     <row r="48" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E48" s="6">
         <v>46153</v>
@@ -6439,16 +6436,16 @@
     </row>
     <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E49" s="6">
         <v>46154</v>
@@ -6462,16 +6459,16 @@
     </row>
     <row r="50" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E50" s="6">
         <v>46155</v>
@@ -6485,16 +6482,16 @@
     </row>
     <row r="51" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E51" s="6">
         <v>46156</v>
@@ -6508,16 +6505,16 @@
     </row>
     <row r="52" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E52" s="6">
         <v>46157</v>
@@ -6531,16 +6528,16 @@
     </row>
     <row r="53" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E53" s="6">
         <v>46153</v>
@@ -6554,16 +6551,16 @@
     </row>
     <row r="54" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E54" s="6">
         <v>46154</v>
@@ -6577,16 +6574,16 @@
     </row>
     <row r="55" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E55" s="6">
         <v>46155</v>
@@ -6600,16 +6597,16 @@
     </row>
     <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E56" s="6">
         <v>46156</v>
@@ -6623,16 +6620,16 @@
     </row>
     <row r="57" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E57" s="6">
         <v>46157</v>
@@ -6646,16 +6643,16 @@
     </row>
     <row r="58" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="E58" s="6">
         <v>46153</v>
@@ -6669,16 +6666,16 @@
     </row>
     <row r="59" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>198</v>
       </c>
       <c r="E59" s="6">
         <v>46153</v>
@@ -6692,16 +6689,16 @@
     </row>
     <row r="60" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="E60" s="6">
         <v>46154</v>
@@ -6715,16 +6712,16 @@
     </row>
     <row r="61" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="E61" s="6">
         <v>46154</v>
@@ -6738,16 +6735,16 @@
     </row>
     <row r="62" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="E62" s="6">
         <v>46155</v>
@@ -6761,16 +6758,16 @@
     </row>
     <row r="63" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E63" s="6">
         <v>46155</v>
@@ -6784,16 +6781,16 @@
     </row>
     <row r="64" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="E64" s="6">
         <v>46156</v>
@@ -6807,16 +6804,16 @@
     </row>
     <row r="65" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E65" s="6">
         <v>46156</v>
@@ -6830,16 +6827,16 @@
     </row>
     <row r="66" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>195</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="E66" s="6">
         <v>46157</v>
@@ -6853,16 +6850,16 @@
     </row>
     <row r="67" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C67" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="E67" s="6">
         <v>46157</v>
@@ -6876,16 +6873,16 @@
     </row>
     <row r="68" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E68" s="6">
         <v>46153</v>
@@ -6899,16 +6896,16 @@
     </row>
     <row r="69" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="E69" s="6">
         <v>46154</v>
@@ -6922,16 +6919,16 @@
     </row>
     <row r="70" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E70" s="6">
         <v>46155</v>
@@ -6945,16 +6942,16 @@
     </row>
     <row r="71" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E71" s="6">
         <v>46155</v>
@@ -6968,16 +6965,16 @@
     </row>
     <row r="72" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E72" s="6">
         <v>46155</v>
@@ -6991,16 +6988,16 @@
     </row>
     <row r="73" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E73" s="6">
         <v>46155</v>
@@ -7014,16 +7011,16 @@
     </row>
     <row r="74" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E74" s="6">
         <v>46156</v>
@@ -7037,16 +7034,16 @@
     </row>
     <row r="75" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E75" s="6">
         <v>46157</v>
@@ -7060,16 +7057,16 @@
     </row>
     <row r="76" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E76" s="6">
         <v>46153</v>
@@ -7083,16 +7080,16 @@
     </row>
     <row r="77" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E77" s="6">
         <v>46154</v>
@@ -7106,16 +7103,16 @@
     </row>
     <row r="78" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E78" s="6">
         <v>46155</v>
@@ -7129,16 +7126,16 @@
     </row>
     <row r="79" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E79" s="6">
         <v>46156</v>
@@ -7152,16 +7149,16 @@
     </row>
     <row r="80" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E80" s="6">
         <v>46157</v>
@@ -7175,16 +7172,16 @@
     </row>
     <row r="81" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E81" s="6">
         <v>46153</v>
@@ -7198,16 +7195,16 @@
     </row>
     <row r="82" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E82" s="6">
         <v>46154</v>
@@ -7221,16 +7218,16 @@
     </row>
     <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E83" s="6">
         <v>46155</v>
@@ -7244,16 +7241,16 @@
     </row>
     <row r="84" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E84" s="6">
         <v>46156</v>
@@ -7267,16 +7264,16 @@
     </row>
     <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E85" s="6">
         <v>46157</v>
@@ -7290,16 +7287,16 @@
     </row>
     <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E86" s="6">
         <v>46146</v>
@@ -7313,16 +7310,16 @@
     </row>
     <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E87" s="6">
         <v>46147</v>
@@ -7336,16 +7333,16 @@
     </row>
     <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E88" s="6">
         <v>46148</v>
@@ -7359,16 +7356,16 @@
     </row>
     <row r="89" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E89" s="6">
         <v>46149</v>
@@ -7382,16 +7379,16 @@
     </row>
     <row r="90" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E90" s="6">
         <v>46150</v>
@@ -7405,16 +7402,16 @@
     </row>
     <row r="91" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E91" s="6">
         <v>46146</v>
@@ -7428,16 +7425,16 @@
     </row>
     <row r="92" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C92" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D92" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>212</v>
       </c>
       <c r="E92" s="6">
         <v>46146</v>
@@ -7451,16 +7448,16 @@
     </row>
     <row r="93" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E93" s="6">
         <v>46147</v>
@@ -7474,16 +7471,16 @@
     </row>
     <row r="94" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E94" s="6">
         <v>46147</v>
@@ -7497,16 +7494,16 @@
     </row>
     <row r="95" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E95" s="6">
         <v>46148</v>
@@ -7520,16 +7517,16 @@
     </row>
     <row r="96" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C96" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D96" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="E96" s="6">
         <v>46149</v>
@@ -7543,16 +7540,16 @@
     </row>
     <row r="97" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E97" s="6">
         <v>46149</v>
@@ -7566,16 +7563,16 @@
     </row>
     <row r="98" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E98" s="6">
         <v>46150</v>
@@ -7589,16 +7586,16 @@
     </row>
     <row r="99" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E99" s="6">
         <v>46146</v>
@@ -7612,16 +7609,16 @@
     </row>
     <row r="100" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E100" s="6">
         <v>46147</v>
@@ -7635,16 +7632,16 @@
     </row>
     <row r="101" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E101" s="6">
         <v>46148</v>
@@ -7658,16 +7655,16 @@
     </row>
     <row r="102" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E102" s="6">
         <v>46149</v>
@@ -7681,16 +7678,16 @@
     </row>
     <row r="103" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E103" s="6">
         <v>46150</v>
@@ -7704,16 +7701,16 @@
     </row>
     <row r="104" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E104" s="6">
         <v>46146</v>
@@ -7727,16 +7724,16 @@
     </row>
     <row r="105" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E105" s="6">
         <v>46147</v>
@@ -7750,16 +7747,16 @@
     </row>
     <row r="106" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E106" s="6">
         <v>46148</v>
@@ -7773,16 +7770,16 @@
     </row>
     <row r="107" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E107" s="6">
         <v>46149</v>
@@ -7796,16 +7793,16 @@
     </row>
     <row r="108" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E108" s="6">
         <v>46150</v>
@@ -7819,16 +7816,16 @@
     </row>
     <row r="109" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E109" s="6">
         <v>46146</v>
@@ -7842,16 +7839,16 @@
     </row>
     <row r="110" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E110" s="6">
         <v>46147</v>
@@ -7865,16 +7862,16 @@
     </row>
     <row r="111" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E111" s="6">
         <v>46148</v>
@@ -7888,16 +7885,16 @@
     </row>
     <row r="112" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E112" s="6">
         <v>46149</v>
@@ -7911,16 +7908,16 @@
     </row>
     <row r="113" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E113" s="6">
         <v>46150</v>
@@ -7934,16 +7931,16 @@
     </row>
     <row r="114" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E114" s="6">
         <v>46146</v>
@@ -7957,16 +7954,16 @@
     </row>
     <row r="115" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E115" s="6">
         <v>46147</v>
@@ -7980,16 +7977,16 @@
     </row>
     <row r="116" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E116" s="6">
         <v>46148</v>
@@ -8003,16 +8000,16 @@
     </row>
     <row r="117" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E117" s="6">
         <v>46149</v>
@@ -8026,16 +8023,16 @@
     </row>
     <row r="118" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E118" s="6">
         <v>46150</v>
@@ -8049,16 +8046,16 @@
     </row>
     <row r="119" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E119" s="6">
         <v>46181</v>
@@ -8073,16 +8070,16 @@
     </row>
     <row r="120" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E120" s="6">
         <v>46182</v>
@@ -8097,16 +8094,16 @@
     </row>
     <row r="121" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E121" s="6">
         <v>46183</v>
@@ -8121,16 +8118,16 @@
     </row>
     <row r="122" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E122" s="6">
         <v>46184</v>
@@ -8145,16 +8142,16 @@
     </row>
     <row r="123" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E123" s="6">
         <v>46185</v>
@@ -8169,16 +8166,16 @@
     </row>
     <row r="124" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E124" s="6">
         <v>46181</v>
@@ -8193,16 +8190,16 @@
     </row>
     <row r="125" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E125" s="6">
         <v>46182</v>
@@ -8217,16 +8214,16 @@
     </row>
     <row r="126" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E126" s="6">
         <v>46183</v>
@@ -8241,16 +8238,16 @@
     </row>
     <row r="127" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E127" s="6">
         <v>46184</v>
@@ -8265,16 +8262,16 @@
     </row>
     <row r="128" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D128" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>368</v>
       </c>
       <c r="E128" s="6">
         <v>46188</v>
@@ -8289,16 +8286,16 @@
     </row>
     <row r="129" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E129" s="6">
         <v>46189</v>
@@ -8313,16 +8310,16 @@
     </row>
     <row r="130" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E130" s="6">
         <v>46190</v>
@@ -8337,16 +8334,16 @@
     </row>
     <row r="131" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E131" s="6">
         <v>46191</v>
@@ -8361,16 +8358,16 @@
     </row>
     <row r="132" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E132" s="6">
         <v>46192</v>
@@ -8403,755 +8400,755 @@
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="R1" s="16" t="s">
         <v>349</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>277</v>
+      </c>
+      <c r="C15" t="s">
         <v>278</v>
       </c>
-      <c r="C15" t="s">
-        <v>279</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>281</v>
+      </c>
+      <c r="C18" t="s">
         <v>282</v>
       </c>
-      <c r="C18" t="s">
-        <v>283</v>
-      </c>
       <c r="D18" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C25" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C26" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C27" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B28" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B29" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C29" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C30" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B31" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C34" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C35" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C36" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C37" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C38" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C41" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C42" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C43" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C44" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C47" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C50" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>315</v>
+      </c>
+      <c r="C51" t="s">
         <v>316</v>
       </c>
-      <c r="C51" t="s">
-        <v>317</v>
-      </c>
       <c r="K51" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C52" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C54" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B6518F-B44B-2C43-9109-C6AFCB1DC937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223F9A0C-BBCD-B146-878A-7FF303AE983B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Cookpit" sheetId="1" r:id="rId1"/>
     <sheet name="2-Agenda Workshop" sheetId="2" r:id="rId2"/>
     <sheet name="3-Atividades da Semana " sheetId="7" r:id="rId3"/>
     <sheet name="4 - Recursos" sheetId="9" r:id="rId4"/>
+    <sheet name="5 - Vagas" sheetId="10" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$F$125</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="374">
   <si>
     <t>Projeto</t>
   </si>
@@ -1157,6 +1158,12 @@
   </si>
   <si>
     <t>Consultor PM</t>
+  </si>
+  <si>
+    <t>Consultor CO Custeio</t>
+  </si>
+  <si>
+    <t>Consultor WM MM</t>
   </si>
 </sst>
 </file>
@@ -9158,4 +9165,47 @@
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93B521C-D2F3-A84A-B840-7FE0E6034A58}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223F9A0C-BBCD-B146-878A-7FF303AE983B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF5512C-2DE1-6144-AF68-2FD5A0526E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Cookpit" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="5 - Vagas" sheetId="10" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$F$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$I$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Agenda Workshop'!$A$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$Q$54</definedName>
   </definedNames>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="379">
   <si>
     <t>Projeto</t>
   </si>
@@ -1164,12 +1164,30 @@
   </si>
   <si>
     <t>Consultor WM MM</t>
+  </si>
+  <si>
+    <t>Complexidade</t>
+  </si>
+  <si>
+    <t>Baixa</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Peso Dedicação</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1305,7 +1323,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1349,6 +1367,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1652,18 +1674,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="58.6640625" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="64.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" customWidth="1"/>
     <col min="3" max="3" width="66.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="21.1640625" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1685,8 +1710,14 @@
       <c r="G1" s="17" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1703,8 +1734,14 @@
       <c r="G2" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>377</v>
+      </c>
+      <c r="I2" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1712,7 +1749,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="11">
@@ -1721,16 +1758,22 @@
       <c r="G3" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I3" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="11">
@@ -1739,16 +1782,22 @@
       <c r="G4" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>377</v>
+      </c>
+      <c r="I4" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="11">
@@ -1757,16 +1806,22 @@
       <c r="G5" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>377</v>
+      </c>
+      <c r="I5" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="11">
@@ -1775,16 +1830,22 @@
       <c r="G6" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>377</v>
+      </c>
+      <c r="I6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="11">
@@ -1793,16 +1854,22 @@
       <c r="G7" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>377</v>
+      </c>
+      <c r="I7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="11">
@@ -1811,34 +1878,49 @@
       <c r="G8" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>377</v>
+      </c>
+      <c r="I8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="11">
         <v>46388</v>
       </c>
+      <c r="F9" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G9" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>377</v>
+      </c>
+      <c r="I9" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="11">
@@ -1850,16 +1932,22 @@
       <c r="G10" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>377</v>
+      </c>
+      <c r="I10" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="11">
@@ -1871,16 +1959,22 @@
       <c r="G11" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>377</v>
+      </c>
+      <c r="I11" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>135</v>
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>357</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="11">
@@ -1892,34 +1986,45 @@
       <c r="G12" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>377</v>
+      </c>
+      <c r="I12" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>357</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="E13" s="11">
-        <v>46388</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>350</v>
+        <v>46296</v>
       </c>
       <c r="G13" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>376</v>
+      </c>
+      <c r="I13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>68</v>
@@ -1933,70 +2038,92 @@
       <c r="G14" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>376</v>
+      </c>
+      <c r="I14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>140</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="11">
         <v>46296</v>
       </c>
       <c r="G15" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>376</v>
+      </c>
+      <c r="I15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>356</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="11">
-        <v>46296</v>
-      </c>
+      <c r="E16" s="11"/>
       <c r="G16" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>376</v>
+      </c>
+      <c r="I16" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>356</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="11"/>
+      <c r="E17" s="11">
+        <v>46296</v>
+      </c>
       <c r="G17" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>376</v>
+      </c>
+      <c r="I17" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="11">
@@ -2005,16 +2132,22 @@
       <c r="G18" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>376</v>
+      </c>
+      <c r="I18" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="11">
@@ -2023,16 +2156,22 @@
       <c r="G19" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>376</v>
+      </c>
+      <c r="I19" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="11">
@@ -2041,16 +2180,22 @@
       <c r="G20" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>376</v>
+      </c>
+      <c r="I20" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="11">
@@ -2059,16 +2204,22 @@
       <c r="G21" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>376</v>
+      </c>
+      <c r="I21" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="11">
@@ -2077,16 +2228,22 @@
       <c r="G22" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>376</v>
+      </c>
+      <c r="I22" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="11">
@@ -2095,55 +2252,73 @@
       <c r="G23" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>376</v>
+      </c>
+      <c r="I23" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="11">
         <v>46296</v>
       </c>
+      <c r="F24" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G24" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>376</v>
+      </c>
+      <c r="I24" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="11">
-        <v>46296</v>
-      </c>
-      <c r="F25" s="14" t="s">
-        <v>350</v>
+        <v>46388</v>
       </c>
       <c r="G25" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>375</v>
+      </c>
+      <c r="I25" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="11">
@@ -2152,67 +2327,91 @@
       <c r="G26" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>375</v>
+      </c>
+      <c r="I26" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="11">
         <v>46388</v>
       </c>
       <c r="G27" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+      <c r="H27" t="s">
+        <v>375</v>
+      </c>
+      <c r="I27" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>16</v>
+        <v>356</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="11">
-        <v>46388</v>
-      </c>
+      <c r="E28" s="11"/>
       <c r="G28" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>375</v>
+      </c>
+      <c r="I28" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="11"/>
+      <c r="E29" s="11">
+        <v>46388</v>
+      </c>
       <c r="G29" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>375</v>
+      </c>
+      <c r="I29" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="D30" s="2"/>
       <c r="E30" s="11">
         <v>46388</v>
@@ -2220,17 +2419,21 @@
       <c r="G30" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H30" t="s">
+        <v>375</v>
+      </c>
+      <c r="I30" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>49</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="11">
         <v>46388</v>
@@ -2238,15 +2441,23 @@
       <c r="G31" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>375</v>
+      </c>
+      <c r="I31" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D32" s="2"/>
       <c r="E32" s="11">
         <v>46388</v>
@@ -2254,16 +2465,22 @@
       <c r="G32" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>375</v>
+      </c>
+      <c r="I32" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="11">
@@ -2272,16 +2489,22 @@
       <c r="G33" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>375</v>
+      </c>
+      <c r="I33" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="11">
@@ -2290,16 +2513,22 @@
       <c r="G34" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>375</v>
+      </c>
+      <c r="I34" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="11">
@@ -2308,34 +2537,49 @@
       <c r="G35" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>375</v>
+      </c>
+      <c r="I35" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="11">
         <v>46388</v>
       </c>
+      <c r="F36" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G36" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>375</v>
+      </c>
+      <c r="I36" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="11">
@@ -2347,38 +2591,45 @@
       <c r="G37" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>375</v>
+      </c>
+      <c r="I37" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="11">
-        <v>46388</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>350</v>
+        <v>46661</v>
       </c>
       <c r="G38" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>375</v>
+      </c>
+      <c r="I38" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="11">
         <v>46661</v>
@@ -2386,15 +2637,23 @@
       <c r="G39" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>375</v>
+      </c>
+      <c r="I39" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="D40" s="2"/>
       <c r="E40" s="11">
         <v>46661</v>
@@ -2402,16 +2661,22 @@
       <c r="G40" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
+        <v>375</v>
+      </c>
+      <c r="I40" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="11">
@@ -2420,16 +2685,22 @@
       <c r="G41" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>375</v>
+      </c>
+      <c r="I41" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="11">
@@ -2438,52 +2709,70 @@
       <c r="G42" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>375</v>
+      </c>
+      <c r="I42" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="11">
         <v>46661</v>
       </c>
+      <c r="F43" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G43" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>375</v>
+      </c>
+      <c r="I43" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D44" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="D44" s="15"/>
       <c r="E44" s="11">
-        <v>46661</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>350</v>
+        <v>46388</v>
       </c>
       <c r="G44" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+      <c r="H44" t="s">
+        <v>376</v>
+      </c>
+      <c r="I44" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>68</v>
@@ -2495,33 +2784,45 @@
       <c r="G45" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>376</v>
+      </c>
+      <c r="I45" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D46" s="15"/>
+        <v>358</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="11">
         <v>46388</v>
       </c>
       <c r="G46" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
+        <v>376</v>
+      </c>
+      <c r="I46" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>79</v>
+      </c>
       <c r="D47" s="2"/>
       <c r="E47" s="11">
         <v>46388</v>
@@ -2529,16 +2830,22 @@
       <c r="G47" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
+        <v>376</v>
+      </c>
+      <c r="I47" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="11">
@@ -2547,16 +2854,22 @@
       <c r="G48" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H48" t="s">
+        <v>376</v>
+      </c>
+      <c r="I48" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="11">
@@ -2565,16 +2878,22 @@
       <c r="G49" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H49" t="s">
+        <v>376</v>
+      </c>
+      <c r="I49" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="11">
@@ -2583,16 +2902,22 @@
       <c r="G50" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H50" t="s">
+        <v>376</v>
+      </c>
+      <c r="I50" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="11">
@@ -2601,17 +2926,21 @@
       <c r="G51" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H51" t="s">
+        <v>376</v>
+      </c>
+      <c r="I51" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>127</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="11">
         <v>46388</v>
@@ -2619,52 +2948,72 @@
       <c r="G52" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H52" t="s">
+        <v>376</v>
+      </c>
+      <c r="I52" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>352</v>
+      </c>
       <c r="E53" s="11">
         <v>46388</v>
       </c>
       <c r="G53" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H53" t="s">
+        <v>376</v>
+      </c>
+      <c r="I53" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>352</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D54" s="2"/>
       <c r="E54" s="11">
         <v>46388</v>
       </c>
       <c r="G54" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H54" t="s">
+        <v>376</v>
+      </c>
+      <c r="I54" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="11">
@@ -2673,34 +3022,49 @@
       <c r="G55" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
+        <v>376</v>
+      </c>
+      <c r="I55" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="11">
         <v>46388</v>
       </c>
+      <c r="F56" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G56" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H56" t="s">
+        <v>376</v>
+      </c>
+      <c r="I56" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="11">
@@ -2712,57 +3076,72 @@
       <c r="G57" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H57" t="s">
+        <v>376</v>
+      </c>
+      <c r="I57" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D58" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="E58" s="11">
         <v>46388</v>
       </c>
-      <c r="F58" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="G58" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G58" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I58" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>149</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D59" s="2"/>
       <c r="E59" s="11">
         <v>46388</v>
       </c>
       <c r="G59" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H59" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I59" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>6</v>
+        <v>354</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="11">
@@ -2771,16 +3150,22 @@
       <c r="G60" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H60" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I60" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>354</v>
+        <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="11">
@@ -2789,16 +3174,22 @@
       <c r="G61" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H61" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I61" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="11">
@@ -2807,16 +3198,22 @@
       <c r="G62" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H62" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I62" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="11">
@@ -2825,8 +3222,14 @@
       <c r="G63" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H63" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I63" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>33</v>
       </c>
@@ -2834,25 +3237,34 @@
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="11">
         <v>46388</v>
       </c>
+      <c r="F64" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G64" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H64" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I64" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="11">
@@ -2864,77 +3276,96 @@
       <c r="G65" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H65" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I65" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D66" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="E66" s="11">
         <v>46388</v>
       </c>
-      <c r="F66" s="14" t="s">
-        <v>350</v>
-      </c>
       <c r="G66" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H66" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I66" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>144</v>
+        <v>355</v>
       </c>
       <c r="E67" s="11">
         <v>46388</v>
       </c>
+      <c r="F67" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G67" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H67" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I67" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>355</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
       <c r="E68" s="11">
         <v>46388</v>
       </c>
-      <c r="F68" s="14" t="s">
-        <v>350</v>
-      </c>
       <c r="G68" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H68" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I68" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>150</v>
+        <v>13</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -2944,32 +3375,45 @@
       <c r="G69" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
+      <c r="H69" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I69" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" t="s">
+        <v>64</v>
+      </c>
       <c r="E70" s="11">
         <v>46388</v>
       </c>
       <c r="G70" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H70" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I70" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>37</v>
       </c>
       <c r="B71" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E71" s="11">
         <v>46388</v>
@@ -2977,16 +3421,25 @@
       <c r="G71" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H71" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I71" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C72" t="s">
-        <v>68</v>
+        <v>46</v>
+      </c>
+      <c r="D72" t="s">
+        <v>49</v>
       </c>
       <c r="E72" s="11">
         <v>46388</v>
@@ -2994,18 +3447,21 @@
       <c r="G72" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H72" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I72" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>37</v>
       </c>
       <c r="B73" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>46</v>
-      </c>
-      <c r="D73" t="s">
         <v>49</v>
       </c>
       <c r="E73" s="11">
@@ -3014,16 +3470,22 @@
       <c r="G73" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H73" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I73" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>37</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C74" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="E74" s="11">
         <v>46388</v>
@@ -3031,16 +3493,22 @@
       <c r="G74" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H74" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I74" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>37</v>
       </c>
       <c r="B75" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="C75" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="E75" s="11">
         <v>46388</v>
@@ -3048,16 +3516,22 @@
       <c r="G75" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H75" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I75" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
+        <v>371</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E76" s="11">
         <v>46388</v>
@@ -3065,16 +3539,22 @@
       <c r="G76" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H76" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I76" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>37</v>
       </c>
       <c r="B77" t="s">
-        <v>371</v>
+        <v>39</v>
       </c>
       <c r="C77" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="E77" s="11">
         <v>46388</v>
@@ -3082,16 +3562,22 @@
       <c r="G77" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H77" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I77" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>37</v>
       </c>
       <c r="B78" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="E78" s="11">
         <v>46388</v>
@@ -3099,16 +3585,22 @@
       <c r="G78" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H78" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I78" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>37</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="E79" s="11">
         <v>46388</v>
@@ -3116,33 +3608,48 @@
       <c r="G79" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H79" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I79" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>37</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E80" s="11">
         <v>46388</v>
       </c>
+      <c r="F80" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G80" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H80" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I80" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>37</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E81" s="11">
         <v>46388</v>
@@ -3153,16 +3660,22 @@
       <c r="G81" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H81" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I81" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>37</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E82" s="11">
         <v>46388</v>
@@ -3173,16 +3686,22 @@
       <c r="G82" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H82" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I82" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>37</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E83" s="11">
         <v>46388</v>
@@ -3193,36 +3712,45 @@
       <c r="G83" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H83" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="I83" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>132</v>
-      </c>
-      <c r="E84" s="11">
+        <v>147</v>
+      </c>
+      <c r="E84" s="12">
         <v>46388</v>
       </c>
-      <c r="F84" s="14" t="s">
-        <v>350</v>
-      </c>
       <c r="G84" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+      <c r="H84" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I84" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>40</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C85" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E85" s="12">
         <v>46388</v>
@@ -3230,16 +3758,22 @@
       <c r="G85" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H85" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I85" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>40</v>
       </c>
       <c r="B86" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="E86" s="12">
         <v>46388</v>
@@ -3247,16 +3781,19 @@
       <c r="G86" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H86" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I86" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>40</v>
       </c>
       <c r="B87" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E87" s="12">
         <v>46388</v>
@@ -3264,13 +3801,19 @@
       <c r="G87" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H87" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I87" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>40</v>
       </c>
       <c r="B88" t="s">
-        <v>5</v>
+        <v>151</v>
       </c>
       <c r="E88" s="12">
         <v>46388</v>
@@ -3278,13 +3821,19 @@
       <c r="G88" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H88" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I88" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>40</v>
       </c>
       <c r="B89" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="E89" s="12">
         <v>46388</v>
@@ -3292,13 +3841,22 @@
       <c r="G89" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H89" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I89" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>40</v>
       </c>
       <c r="B90" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="E90" s="12">
         <v>46388</v>
@@ -3306,25 +3864,40 @@
       <c r="G90" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H90" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I90" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>40</v>
       </c>
       <c r="B91" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>109</v>
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>152</v>
       </c>
       <c r="E91" s="12">
         <v>46388</v>
       </c>
+      <c r="F91" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G91" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+      <c r="H91" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I91" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>40</v>
       </c>
@@ -3332,7 +3905,7 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E92" s="12">
         <v>46388</v>
@@ -3343,36 +3916,45 @@
       <c r="G92" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H92" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I92" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E93" s="12">
-        <v>46388</v>
-      </c>
-      <c r="F93" s="14" t="s">
-        <v>350</v>
+        <v>46631</v>
       </c>
       <c r="G93" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H93" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I93" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C94" t="s">
-        <v>154</v>
+        <v>77</v>
       </c>
       <c r="E94" s="12">
         <v>46631</v>
@@ -3380,16 +3962,22 @@
       <c r="G94" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H94" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I94" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C95" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="E95" s="12">
         <v>46631</v>
@@ -3397,16 +3985,22 @@
       <c r="G95" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H95" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I95" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C96" t="s">
-        <v>155</v>
+        <v>56</v>
       </c>
       <c r="E96" s="12">
         <v>46631</v>
@@ -3414,16 +4008,22 @@
       <c r="G96" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H96" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I96" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E97" s="12">
         <v>46631</v>
@@ -3431,16 +4031,22 @@
       <c r="G97" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H97" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I97" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="E98" s="12">
         <v>46631</v>
@@ -3448,16 +4054,22 @@
       <c r="G98" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H98" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I98" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C99" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="E99" s="12">
         <v>46631</v>
@@ -3465,85 +4077,115 @@
       <c r="G99" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H99" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I99" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>41</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C100" t="s">
-        <v>128</v>
-      </c>
-      <c r="E100" s="12">
-        <v>46631</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="E100" s="12"/>
       <c r="G100" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H100" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I100" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C101" t="s">
-        <v>107</v>
-      </c>
-      <c r="E101" s="12"/>
+        <v>116</v>
+      </c>
+      <c r="E101" s="12">
+        <v>46631</v>
+      </c>
       <c r="G101" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H101" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I101" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C102" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="E102" s="12">
         <v>46631</v>
       </c>
+      <c r="F102" s="14" t="s">
+        <v>350</v>
+      </c>
       <c r="G102" s="18" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H102" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I102" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="B103" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E103" s="12">
         <v>46631</v>
       </c>
-      <c r="F103" s="14" t="s">
-        <v>350</v>
-      </c>
       <c r="G103" s="18" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+      <c r="H103" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I103" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>157</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C104" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="E104" s="12">
         <v>46631</v>
@@ -3551,16 +4193,22 @@
       <c r="G104" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H104" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I104" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>157</v>
       </c>
       <c r="B105" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C105" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E105" s="12">
         <v>46631</v>
@@ -3568,16 +4216,22 @@
       <c r="G105" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H105" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I105" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>157</v>
       </c>
       <c r="B106" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="E106" s="12">
         <v>46631</v>
@@ -3585,30 +4239,39 @@
       <c r="G106" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H106" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I106" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>344</v>
       </c>
       <c r="B107" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="E107" s="12">
-        <v>46631</v>
+        <v>46296</v>
       </c>
       <c r="G107" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H107" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I107" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>344</v>
       </c>
       <c r="B108" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E108" s="12">
         <v>46296</v>
@@ -3616,13 +4279,19 @@
       <c r="G108" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H108" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I108" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>344</v>
       </c>
       <c r="B109" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E109" s="12">
         <v>46296</v>
@@ -3630,13 +4299,22 @@
       <c r="G109" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H109" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I109" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>344</v>
       </c>
       <c r="B110" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="C110" t="s">
+        <v>155</v>
       </c>
       <c r="E110" s="12">
         <v>46296</v>
@@ -3644,30 +4322,39 @@
       <c r="G110" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H110" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I110" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>344</v>
       </c>
       <c r="B111" t="s">
-        <v>7</v>
-      </c>
-      <c r="C111" t="s">
-        <v>155</v>
+        <v>8</v>
       </c>
       <c r="E111" s="12">
-        <v>46296</v>
+        <v>46569</v>
       </c>
       <c r="G111" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H111" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I111" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>344</v>
       </c>
       <c r="B112" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E112" s="12">
         <v>46569</v>
@@ -3675,13 +4362,19 @@
       <c r="G112" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H112" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I112" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>344</v>
       </c>
       <c r="B113" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E113" s="12">
         <v>46569</v>
@@ -3689,13 +4382,22 @@
       <c r="G113" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H113" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I113" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>344</v>
       </c>
       <c r="B114" t="s">
-        <v>17</v>
+        <v>26</v>
+      </c>
+      <c r="C114" t="s">
+        <v>127</v>
       </c>
       <c r="E114" s="12">
         <v>46569</v>
@@ -3703,16 +4405,22 @@
       <c r="G114" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H114" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I114" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>344</v>
       </c>
       <c r="B115" t="s">
-        <v>26</v>
+        <v>345</v>
       </c>
       <c r="C115" t="s">
-        <v>127</v>
+        <v>346</v>
       </c>
       <c r="E115" s="12">
         <v>46569</v>
@@ -3720,16 +4428,19 @@
       <c r="G115" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H115" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I115" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>344</v>
       </c>
       <c r="B116" t="s">
-        <v>345</v>
-      </c>
-      <c r="C116" t="s">
-        <v>346</v>
+        <v>10</v>
       </c>
       <c r="E116" s="12">
         <v>46569</v>
@@ -3737,28 +4448,45 @@
       <c r="G116" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H116" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I116" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
-      </c>
-      <c r="E117" s="12"/>
+        <v>28</v>
+      </c>
+      <c r="C117" t="s">
+        <v>49</v>
+      </c>
+      <c r="E117" s="12">
+        <v>46569</v>
+      </c>
       <c r="G117" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+      <c r="H117" t="s">
+        <v>375</v>
+      </c>
+      <c r="I117" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>342</v>
       </c>
       <c r="B118" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C118" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="E118" s="12">
         <v>46569</v>
@@ -3766,16 +4494,22 @@
       <c r="G118" s="18" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H118" t="s">
+        <v>375</v>
+      </c>
+      <c r="I118" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>342</v>
       </c>
       <c r="B119" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C119" t="s">
-        <v>71</v>
+        <v>343</v>
       </c>
       <c r="E119" s="12">
         <v>46569</v>
@@ -3783,13 +4517,19 @@
       <c r="G119" s="18" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H119" t="s">
+        <v>375</v>
+      </c>
+      <c r="I119" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>342</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C120" t="s">
         <v>343</v>
@@ -3797,34 +4537,43 @@
       <c r="E120" s="12">
         <v>46569</v>
       </c>
+      <c r="F120" s="14"/>
       <c r="G120" s="18" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H120" t="s">
+        <v>375</v>
+      </c>
+      <c r="I120" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="B121" t="s">
-        <v>7</v>
-      </c>
-      <c r="C121" t="s">
-        <v>343</v>
+        <v>28</v>
       </c>
       <c r="E121" s="12">
-        <v>46569</v>
-      </c>
-      <c r="F121" s="14"/>
+        <v>46388</v>
+      </c>
       <c r="G121" s="18" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+      <c r="H121" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I121" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>361</v>
       </c>
       <c r="B122" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E122" s="12">
         <v>46388</v>
@@ -3832,13 +4581,19 @@
       <c r="G122" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H122" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I122" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>361</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E123" s="12">
         <v>46388</v>
@@ -3846,13 +4601,19 @@
       <c r="G123" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H123" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I123" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>361</v>
       </c>
       <c r="B124" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E124" s="12">
         <v>46388</v>
@@ -3860,23 +4621,15 @@
       <c r="G124" s="18" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
-        <v>361</v>
-      </c>
-      <c r="B125" t="s">
-        <v>17</v>
-      </c>
-      <c r="E125" s="12">
-        <v>46388</v>
-      </c>
-      <c r="G125" s="18" t="s">
-        <v>360</v>
+      <c r="H124" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="I124" s="20">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F125" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF5512C-2DE1-6144-AF68-2FD5A0526E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9750D81D-6223-CA4D-959C-00477D6BB81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="379">
   <si>
     <t>Projeto</t>
   </si>
@@ -158,9 +158,6 @@
     <t>4299 - ERO - SAP CLOUD ERP GROW</t>
   </si>
   <si>
-    <t>Consultor FI PL</t>
-  </si>
-  <si>
     <t>Consultor Group Reporting SR</t>
   </si>
   <si>
@@ -1178,7 +1175,10 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Peso Dedicação</t>
+    <t>Peso Dedicação Sombra</t>
+  </si>
+  <si>
+    <t>Peso Dedicação Principal</t>
   </si>
 </sst>
 </file>
@@ -1674,21 +1674,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="64.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
+    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="2" max="2" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="66.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.1640625" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1696,28 +1697,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="G1" s="17" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I1" s="17" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J1" s="17" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1725,23 +1729,23 @@
         <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="11">
         <v>46388</v>
       </c>
       <c r="G2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I2" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1749,23 +1753,23 @@
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="11">
         <v>46388</v>
       </c>
       <c r="G3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I3" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1773,23 +1777,23 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="11">
         <v>46388</v>
       </c>
       <c r="G4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I4" s="20">
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1797,23 +1801,23 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="11">
         <v>46388</v>
       </c>
       <c r="G5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I5" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1821,23 +1825,23 @@
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="11">
         <v>46388</v>
       </c>
       <c r="G6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I6" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1845,23 +1849,23 @@
         <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="11">
         <v>46388</v>
       </c>
       <c r="G7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I7" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1869,23 +1873,23 @@
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="11">
         <v>46388</v>
       </c>
       <c r="G8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I8" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1893,26 +1897,26 @@
         <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="11">
         <v>46388</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I9" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1920,26 +1924,26 @@
         <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="11">
         <v>46388</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I10" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1947,26 +1951,26 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="11">
         <v>46388</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I11" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -1974,26 +1978,26 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="11">
         <v>46388</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I12" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -2001,25 +2005,28 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E13" s="11">
         <v>46296</v>
       </c>
       <c r="G13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I13" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+      <c r="J13">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -2027,25 +2034,28 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E14" s="11">
         <v>46296</v>
       </c>
       <c r="G14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I14" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+      <c r="J14">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2053,42 +2063,44 @@
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="11">
         <v>46296</v>
       </c>
       <c r="G15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I15" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="11"/>
+      <c r="E16" s="11">
+        <v>46296</v>
+      </c>
       <c r="G16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H16" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I16" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2099,17 +2111,17 @@
         <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="11">
         <v>46296</v>
       </c>
       <c r="G17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I17" s="20">
         <v>0.4</v>
@@ -2123,20 +2135,20 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="11">
         <v>46296</v>
       </c>
       <c r="G18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H18" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I18" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2147,17 +2159,17 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="11">
         <v>46296</v>
       </c>
       <c r="G19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H19" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I19" s="20">
         <v>1</v>
@@ -2171,20 +2183,20 @@
         <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="11">
         <v>46296</v>
       </c>
       <c r="G20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H20" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I20" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2195,20 +2207,20 @@
         <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="11">
         <v>46296</v>
       </c>
       <c r="G21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H21" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I21" s="20">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2219,20 +2231,20 @@
         <v>19</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="11">
         <v>46296</v>
       </c>
       <c r="G22" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H22" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I22" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2243,17 +2255,17 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="11">
         <v>46296</v>
       </c>
       <c r="G23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H23" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I23" s="20">
         <v>0.4</v>
@@ -2267,20 +2279,20 @@
         <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="11">
         <v>46296</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G24" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I24" s="20">
         <v>0.4</v>
@@ -2294,17 +2306,17 @@
         <v>21</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="11">
         <v>46388</v>
       </c>
       <c r="G25" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H25" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I25" s="20">
         <v>0.4</v>
@@ -2318,20 +2330,20 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="11">
         <v>46388</v>
       </c>
       <c r="G26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H26" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I26" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2342,20 +2354,20 @@
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="11">
         <v>46388</v>
       </c>
       <c r="G27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I27" s="20">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2363,18 +2375,18 @@
         <v>22</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="11"/>
       <c r="G28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H28" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I28" s="20">
         <v>0.4</v>
@@ -2393,10 +2405,10 @@
         <v>46388</v>
       </c>
       <c r="G29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H29" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I29" s="20">
         <v>0.4</v>
@@ -2410,20 +2422,20 @@
         <v>24</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="11">
         <v>46388</v>
       </c>
       <c r="G30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I30" s="20">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2439,13 +2451,13 @@
         <v>46388</v>
       </c>
       <c r="G31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H31" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I31" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2456,17 +2468,17 @@
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="11">
         <v>46388</v>
       </c>
       <c r="G32" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H32" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I32" s="20">
         <v>1</v>
@@ -2480,17 +2492,17 @@
         <v>25</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="11">
         <v>46388</v>
       </c>
       <c r="G33" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H33" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I33" s="20">
         <v>0.4</v>
@@ -2504,17 +2516,17 @@
         <v>10</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="11">
         <v>46388</v>
       </c>
       <c r="G34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H34" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I34" s="20">
         <v>0.4</v>
@@ -2528,17 +2540,17 @@
         <v>26</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="11">
         <v>46388</v>
       </c>
       <c r="G35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H35" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I35" s="20">
         <v>0.4</v>
@@ -2552,20 +2564,20 @@
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="11">
         <v>46388</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H36" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I36" s="20">
         <v>0.4</v>
@@ -2579,20 +2591,20 @@
         <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="11">
         <v>46388</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H37" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I37" s="20">
         <v>0.4</v>
@@ -2606,17 +2618,17 @@
         <v>28</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="11">
         <v>46661</v>
       </c>
       <c r="G38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H38" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I38" s="20">
         <v>1</v>
@@ -2635,13 +2647,13 @@
         <v>46661</v>
       </c>
       <c r="G39" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I39" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2652,20 +2664,20 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="11">
         <v>46661</v>
       </c>
       <c r="G40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H40" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I40" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2676,17 +2688,17 @@
         <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="11">
         <v>46661</v>
       </c>
       <c r="G41" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H41" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I41" s="20">
         <v>1</v>
@@ -2700,17 +2712,17 @@
         <v>10</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="11">
         <v>46661</v>
       </c>
       <c r="G42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H42" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I42" s="20">
         <v>0.4</v>
@@ -2724,20 +2736,20 @@
         <v>11</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="11">
         <v>46661</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G43" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H43" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I43" s="20">
         <v>0.4</v>
@@ -2751,20 +2763,20 @@
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D44" s="15"/>
       <c r="E44" s="11">
         <v>46388</v>
       </c>
       <c r="G44" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H44" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I44" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2775,17 +2787,17 @@
         <v>15</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="11">
         <v>46388</v>
       </c>
       <c r="G45" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H45" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I45" s="20">
         <v>0.4</v>
@@ -2796,7 +2808,7 @@
         <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -2804,13 +2816,13 @@
         <v>46388</v>
       </c>
       <c r="G46" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I46" s="20">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -2821,17 +2833,17 @@
         <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="11">
         <v>46388</v>
       </c>
       <c r="G47" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H47" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I47" s="20">
         <v>1</v>
@@ -2845,23 +2857,23 @@
         <v>30</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="11">
         <v>46388</v>
       </c>
       <c r="G48" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H48" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I48" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>29</v>
       </c>
@@ -2869,23 +2881,23 @@
         <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="11">
         <v>46388</v>
       </c>
       <c r="G49" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H49" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I49" s="20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>29</v>
       </c>
@@ -2893,23 +2905,23 @@
         <v>19</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="11">
         <v>46388</v>
       </c>
       <c r="G50" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H50" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I50" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>29</v>
       </c>
@@ -2917,23 +2929,23 @@
         <v>26</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="11">
         <v>46388</v>
       </c>
       <c r="G51" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H51" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I51" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>29</v>
       </c>
@@ -2946,16 +2958,16 @@
         <v>46388</v>
       </c>
       <c r="G52" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H52" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I52" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>29</v>
       </c>
@@ -2963,25 +2975,28 @@
         <v>32</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E53" s="11">
         <v>46388</v>
       </c>
       <c r="G53" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H53" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I53" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J53">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>29</v>
       </c>
@@ -2989,23 +3004,23 @@
         <v>8</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="11">
         <v>46388</v>
       </c>
       <c r="G54" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I54" s="20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>29</v>
       </c>
@@ -3013,23 +3028,23 @@
         <v>10</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="11">
         <v>46388</v>
       </c>
       <c r="G55" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H55" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I55" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>29</v>
       </c>
@@ -3037,26 +3052,26 @@
         <v>11</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="11">
         <v>46388</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G56" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H56" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I56" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>29</v>
       </c>
@@ -3064,26 +3079,26 @@
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="11">
         <v>46388</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G57" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H57" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I57" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>33</v>
       </c>
@@ -3091,25 +3106,28 @@
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E58" s="11">
         <v>46388</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I58" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+      <c r="J58">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>33</v>
       </c>
@@ -3117,47 +3135,47 @@
         <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="11">
         <v>46388</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I59" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="11">
         <v>46388</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I60" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>33</v>
       </c>
@@ -3165,23 +3183,23 @@
         <v>10</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="11">
         <v>46388</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I61" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>33</v>
       </c>
@@ -3189,23 +3207,26 @@
         <v>11</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="11">
         <v>46388</v>
       </c>
+      <c r="F62" s="14" t="s">
+        <v>349</v>
+      </c>
       <c r="G62" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I62" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>33</v>
       </c>
@@ -3213,23 +3234,26 @@
         <v>12</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="11">
         <v>46388</v>
       </c>
+      <c r="F63" s="14" t="s">
+        <v>349</v>
+      </c>
       <c r="G63" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I63" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>33</v>
       </c>
@@ -3237,26 +3261,26 @@
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="11">
         <v>46388</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I64" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>33</v>
       </c>
@@ -3264,26 +3288,26 @@
         <v>34</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="11">
         <v>46388</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I65" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>33</v>
       </c>
@@ -3291,25 +3315,28 @@
         <v>35</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E66" s="11">
         <v>46388</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I66" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+      <c r="J66">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>33</v>
       </c>
@@ -3317,33 +3344,36 @@
         <v>36</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E67" s="11">
         <v>46388</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I67" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J67">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -3351,16 +3381,16 @@
         <v>46388</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I68" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>33</v>
       </c>
@@ -3372,17 +3402,20 @@
       <c r="E69" s="11">
         <v>46388</v>
       </c>
+      <c r="F69" s="14" t="s">
+        <v>349</v>
+      </c>
       <c r="G69" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I69" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>37</v>
       </c>
@@ -3390,22 +3423,22 @@
         <v>6</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E70" s="11">
         <v>46388</v>
       </c>
       <c r="G70" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I70" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>37</v>
       </c>
@@ -3413,48 +3446,51 @@
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E71" s="11">
         <v>46388</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I71" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>37</v>
       </c>
       <c r="B72" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D72" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E72" s="11">
         <v>46388</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I72" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J72">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>37</v>
       </c>
@@ -3462,22 +3498,22 @@
         <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E73" s="11">
         <v>46388</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I73" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>37</v>
       </c>
@@ -3485,91 +3521,91 @@
         <v>5</v>
       </c>
       <c r="C74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E74" s="11">
         <v>46388</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I74" s="20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>37</v>
       </c>
       <c r="B75" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E75" s="11">
         <v>46388</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I75" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>37</v>
       </c>
       <c r="B76" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E76" s="11">
         <v>46388</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I76" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>37</v>
       </c>
       <c r="B77" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C77" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E77" s="11">
         <v>46388</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I77" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>37</v>
       </c>
@@ -3577,22 +3613,22 @@
         <v>31</v>
       </c>
       <c r="C78" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E78" s="11">
         <v>46388</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I78" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>37</v>
       </c>
@@ -3600,22 +3636,22 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E79" s="11">
         <v>46388</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I79" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>37</v>
       </c>
@@ -3623,19 +3659,19 @@
         <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E80" s="11">
         <v>46388</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G80" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I80" s="20">
         <v>0.4</v>
@@ -3649,19 +3685,19 @@
         <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E81" s="11">
         <v>46388</v>
       </c>
       <c r="F81" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H81" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I81" s="20">
         <v>0.4</v>
@@ -3675,19 +3711,19 @@
         <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E82" s="11">
         <v>46388</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H82" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I82" s="20">
         <v>0.4</v>
@@ -3701,19 +3737,19 @@
         <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E83" s="11">
         <v>46388</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G83" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H83" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I83" s="20">
         <v>0.4</v>
@@ -3721,22 +3757,22 @@
     </row>
     <row r="84" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B84" t="s">
         <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E84" s="12">
         <v>46388</v>
       </c>
       <c r="G84" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H84" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I84" s="20">
         <v>1</v>
@@ -3744,22 +3780,22 @@
     </row>
     <row r="85" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B85" t="s">
         <v>6</v>
       </c>
       <c r="C85" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E85" s="12">
         <v>46388</v>
       </c>
       <c r="G85" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H85" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I85" s="20">
         <v>1</v>
@@ -3767,30 +3803,30 @@
     </row>
     <row r="86" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B86" t="s">
         <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E86" s="12">
         <v>46388</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H86" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I86" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B87" t="s">
         <v>5</v>
@@ -3799,30 +3835,30 @@
         <v>46388</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H87" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I87" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B88" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E88" s="12">
         <v>46388</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H88" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I88" s="20">
         <v>1</v>
@@ -3830,7 +3866,7 @@
     </row>
     <row r="89" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B89" t="s">
         <v>17</v>
@@ -3839,10 +3875,10 @@
         <v>46388</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H89" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I89" s="20">
         <v>0.4</v>
@@ -3850,22 +3886,22 @@
     </row>
     <row r="90" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B90" t="s">
         <v>10</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E90" s="12">
         <v>46388</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H90" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I90" s="20">
         <v>0.4</v>
@@ -3873,25 +3909,25 @@
     </row>
     <row r="91" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B91" t="s">
         <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E91" s="12">
         <v>46388</v>
       </c>
       <c r="F91" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H91" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I91" s="20">
         <v>0.4</v>
@@ -3899,25 +3935,25 @@
     </row>
     <row r="92" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B92" t="s">
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E92" s="12">
         <v>46388</v>
       </c>
       <c r="F92" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H92" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I92" s="20">
         <v>0.4</v>
@@ -3925,22 +3961,22 @@
     </row>
     <row r="93" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B93" t="s">
         <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E93" s="12">
         <v>46631</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I93" s="20">
         <v>1</v>
@@ -3948,22 +3984,22 @@
     </row>
     <row r="94" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B94" t="s">
         <v>6</v>
       </c>
       <c r="C94" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E94" s="12">
         <v>46631</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H94" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I94" s="20">
         <v>0.7</v>
@@ -3971,68 +4007,68 @@
     </row>
     <row r="95" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B95" t="s">
         <v>7</v>
       </c>
       <c r="C95" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E95" s="12">
         <v>46631</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H95" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I95" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B96" t="s">
         <v>5</v>
       </c>
       <c r="C96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E96" s="12">
         <v>46631</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H96" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I96" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E97" s="12">
         <v>46631</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H97" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I97" s="20">
         <v>0.4</v>
@@ -4040,22 +4076,22 @@
     </row>
     <row r="98" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B98" t="s">
         <v>8</v>
       </c>
       <c r="C98" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E98" s="12">
         <v>46631</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H98" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I98" s="20">
         <v>0.7</v>
@@ -4063,22 +4099,22 @@
     </row>
     <row r="99" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B99" t="s">
         <v>10</v>
       </c>
       <c r="C99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E99" s="12">
         <v>46631</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H99" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I99" s="20">
         <v>0.4</v>
@@ -4086,69 +4122,69 @@
     </row>
     <row r="100" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B100" t="s">
         <v>21</v>
       </c>
       <c r="C100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E100" s="12"/>
       <c r="G100" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H100" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I100" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
+        <v>40</v>
+      </c>
+      <c r="B101" t="s">
         <v>41</v>
       </c>
-      <c r="B101" t="s">
-        <v>42</v>
-      </c>
       <c r="C101" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E101" s="12">
         <v>46631</v>
       </c>
       <c r="G101" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H101" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I101" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B102" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C102" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E102" s="12">
         <v>46631</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G102" s="18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H102" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I102" s="20">
         <v>0.4</v>
@@ -4156,22 +4192,22 @@
     </row>
     <row r="103" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B103" t="s">
         <v>28</v>
       </c>
       <c r="C103" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E103" s="12">
         <v>46631</v>
       </c>
       <c r="G103" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H103" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I103" s="20">
         <v>0.4</v>
@@ -4179,22 +4215,22 @@
     </row>
     <row r="104" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B104" t="s">
         <v>6</v>
       </c>
       <c r="C104" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E104" s="12">
         <v>46631</v>
       </c>
       <c r="G104" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H104" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I104" s="20">
         <v>0.4</v>
@@ -4202,45 +4238,45 @@
     </row>
     <row r="105" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B105" t="s">
         <v>5</v>
       </c>
       <c r="C105" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E105" s="12">
         <v>46631</v>
       </c>
       <c r="G105" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H105" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I105" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B106" t="s">
         <v>10</v>
       </c>
       <c r="C106" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E106" s="12">
         <v>46631</v>
       </c>
       <c r="G106" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H106" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I106" s="20">
         <v>0.4</v>
@@ -4248,7 +4284,7 @@
     </row>
     <row r="107" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B107" t="s">
         <v>28</v>
@@ -4257,18 +4293,18 @@
         <v>46296</v>
       </c>
       <c r="G107" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H107" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I107" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B108" t="s">
         <v>5</v>
@@ -4277,18 +4313,18 @@
         <v>46296</v>
       </c>
       <c r="G108" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H108" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I108" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B109" t="s">
         <v>6</v>
@@ -4297,10 +4333,10 @@
         <v>46296</v>
       </c>
       <c r="G109" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H109" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I109" s="20">
         <v>1</v>
@@ -4308,30 +4344,30 @@
     </row>
     <row r="110" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E110" s="12">
         <v>46296</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H110" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I110" s="20">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B111" t="s">
         <v>8</v>
@@ -4340,18 +4376,18 @@
         <v>46569</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H111" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I111" s="20">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B112" t="s">
         <v>19</v>
@@ -4360,18 +4396,18 @@
         <v>46569</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H112" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I112" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
@@ -4380,10 +4416,10 @@
         <v>46569</v>
       </c>
       <c r="G113" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H113" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I113" s="20">
         <v>0.4</v>
@@ -4391,22 +4427,22 @@
     </row>
     <row r="114" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B114" t="s">
         <v>26</v>
       </c>
       <c r="C114" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E114" s="12">
         <v>46569</v>
       </c>
       <c r="G114" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H114" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I114" s="20">
         <v>0.4</v>
@@ -4414,22 +4450,22 @@
     </row>
     <row r="115" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>343</v>
+      </c>
+      <c r="B115" t="s">
         <v>344</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>345</v>
-      </c>
-      <c r="C115" t="s">
-        <v>346</v>
       </c>
       <c r="E115" s="12">
         <v>46569</v>
       </c>
       <c r="G115" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H115" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I115" s="20">
         <v>0.4</v>
@@ -4437,7 +4473,7 @@
     </row>
     <row r="116" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B116" t="s">
         <v>10</v>
@@ -4446,10 +4482,10 @@
         <v>46569</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H116" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I116" s="20">
         <v>0.4</v>
@@ -4457,22 +4493,22 @@
     </row>
     <row r="117" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B117" t="s">
         <v>28</v>
       </c>
       <c r="C117" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E117" s="12">
         <v>46569</v>
       </c>
       <c r="G117" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H117" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I117" s="20">
         <v>0.4</v>
@@ -4480,45 +4516,45 @@
     </row>
     <row r="118" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B118" t="s">
         <v>5</v>
       </c>
       <c r="C118" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E118" s="12">
         <v>46569</v>
       </c>
       <c r="G118" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H118" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I118" s="20">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B119" t="s">
         <v>6</v>
       </c>
       <c r="C119" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E119" s="12">
         <v>46569</v>
       </c>
       <c r="G119" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H119" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I119" s="20">
         <v>0.4</v>
@@ -4526,23 +4562,23 @@
     </row>
     <row r="120" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B120" t="s">
         <v>7</v>
       </c>
       <c r="C120" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E120" s="12">
         <v>46569</v>
       </c>
       <c r="F120" s="14"/>
       <c r="G120" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H120" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I120" s="20">
         <v>0.4</v>
@@ -4550,7 +4586,7 @@
     </row>
     <row r="121" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B121" t="s">
         <v>28</v>
@@ -4559,18 +4595,18 @@
         <v>46388</v>
       </c>
       <c r="G121" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H121" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I121" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B122" t="s">
         <v>5</v>
@@ -4579,18 +4615,18 @@
         <v>46388</v>
       </c>
       <c r="G122" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H122" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I122" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B123" t="s">
         <v>6</v>
@@ -4599,10 +4635,10 @@
         <v>46388</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I123" s="20">
         <v>1</v>
@@ -4610,7 +4646,7 @@
     </row>
     <row r="124" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B124" t="s">
         <v>17</v>
@@ -4619,10 +4655,10 @@
         <v>46388</v>
       </c>
       <c r="G124" s="18" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I124" s="20">
         <v>0.4</v>
@@ -4652,27 +4688,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="D2" s="3">
         <v>46113</v>
@@ -4683,13 +4719,13 @@
     </row>
     <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="D3" s="3">
         <v>46113</v>
@@ -4700,13 +4736,13 @@
     </row>
     <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="D4" s="3">
         <v>46114</v>
@@ -4717,13 +4753,13 @@
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="3">
         <v>46128</v>
@@ -4734,13 +4770,13 @@
     </row>
     <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3">
         <v>46122</v>
@@ -4751,13 +4787,13 @@
     </row>
     <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" s="3">
         <v>46126</v>
@@ -4768,13 +4804,13 @@
     </row>
     <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3">
         <v>46129</v>
@@ -4785,13 +4821,13 @@
     </row>
     <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3">
         <v>46146</v>
@@ -4802,26 +4838,26 @@
     </row>
     <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="D11" s="3">
         <v>46153</v>
@@ -4832,13 +4868,13 @@
     </row>
     <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D12" s="3">
         <v>46140</v>
@@ -4849,13 +4885,13 @@
     </row>
     <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" s="3">
         <v>46162</v>
@@ -4866,13 +4902,13 @@
     </row>
     <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D14" s="3">
         <v>46163</v>
@@ -4883,10 +4919,10 @@
     </row>
     <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3">
@@ -4898,13 +4934,13 @@
     </row>
     <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="D16" s="3">
         <v>46160</v>
@@ -4915,13 +4951,13 @@
     </row>
     <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="D17" s="3">
         <v>46140</v>
@@ -4932,13 +4968,13 @@
     </row>
     <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D18" s="3">
         <v>46150</v>
@@ -4949,13 +4985,13 @@
     </row>
     <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="3">
         <v>46150</v>
@@ -4966,13 +5002,13 @@
     </row>
     <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="3">
         <v>46147</v>
@@ -4983,13 +5019,13 @@
     </row>
     <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D21" s="3">
         <v>46149</v>
@@ -5000,13 +5036,13 @@
     </row>
     <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3">
         <v>46181</v>
@@ -5017,13 +5053,13 @@
     </row>
     <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="D23" s="3">
         <v>46170</v>
@@ -5034,13 +5070,13 @@
     </row>
     <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" s="3">
         <v>46168</v>
@@ -5051,13 +5087,13 @@
     </row>
     <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" s="3">
         <v>46167</v>
@@ -5068,13 +5104,13 @@
     </row>
     <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="3">
         <v>46174</v>
@@ -5085,13 +5121,13 @@
     </row>
     <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="D27" s="3">
         <v>46175</v>
@@ -5102,13 +5138,13 @@
     </row>
     <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28" s="3">
         <v>46171</v>
@@ -5119,13 +5155,13 @@
     </row>
     <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="D29" s="3">
         <v>46170</v>
@@ -5136,13 +5172,13 @@
     </row>
     <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D30" s="3">
         <v>46181</v>
@@ -5153,13 +5189,13 @@
     </row>
     <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D31" s="3">
         <v>46178</v>
@@ -5170,13 +5206,13 @@
     </row>
     <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D32" s="3">
         <v>46170</v>
@@ -5187,13 +5223,13 @@
     </row>
     <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D33" s="3">
         <v>46181</v>
@@ -5204,26 +5240,26 @@
     </row>
     <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D35" s="3">
         <v>46155</v>
@@ -5234,13 +5270,13 @@
     </row>
     <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D36" s="3">
         <v>46167</v>
@@ -5251,13 +5287,13 @@
     </row>
     <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D37" s="3">
         <v>46167</v>
@@ -5268,13 +5304,13 @@
     </row>
     <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D38" s="3">
         <v>46168</v>
@@ -5285,13 +5321,13 @@
     </row>
     <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D39" s="3">
         <v>46175</v>
@@ -5302,13 +5338,13 @@
     </row>
     <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" s="3">
         <v>46188</v>
@@ -5319,13 +5355,13 @@
     </row>
     <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D41" s="3">
         <v>46195</v>
@@ -5336,13 +5372,13 @@
     </row>
     <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D42" s="3">
         <v>46202</v>
@@ -5353,10 +5389,10 @@
     </row>
     <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="3">
@@ -5368,10 +5404,10 @@
     </row>
     <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="3">
@@ -5383,13 +5419,13 @@
     </row>
     <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D45" s="3">
         <v>46223</v>
@@ -5400,13 +5436,13 @@
     </row>
     <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D46" s="3">
         <v>46223</v>
@@ -5417,10 +5453,10 @@
     </row>
     <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="3">
@@ -5432,13 +5468,13 @@
     </row>
     <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D48" s="3">
         <v>46230</v>
@@ -5449,13 +5485,13 @@
     </row>
     <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D49" s="3">
         <v>46232</v>
@@ -5466,13 +5502,13 @@
     </row>
     <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D50" s="3">
         <v>46230</v>
@@ -5483,13 +5519,13 @@
     </row>
     <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51" s="3">
         <v>46161</v>
@@ -5500,13 +5536,13 @@
     </row>
     <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D52" s="3">
         <v>46162</v>
@@ -5517,13 +5553,13 @@
     </row>
     <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="D53" s="3">
         <v>46162</v>
@@ -5534,13 +5570,13 @@
     </row>
     <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D54" s="3">
         <v>46163</v>
@@ -5551,13 +5587,13 @@
     </row>
     <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D55" s="3">
         <v>46174</v>
@@ -5568,13 +5604,13 @@
     </row>
     <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D56" s="3">
         <v>46174</v>
@@ -5585,13 +5621,13 @@
     </row>
     <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="D57" s="3">
         <v>46174</v>
@@ -5602,13 +5638,13 @@
     </row>
     <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="D58" s="3">
         <v>46181</v>
@@ -5619,13 +5655,13 @@
     </row>
     <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="D59" s="3">
         <v>46181</v>
@@ -5636,13 +5672,13 @@
     </row>
     <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D60" s="3">
         <v>46181</v>
@@ -5653,13 +5689,13 @@
     </row>
     <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D61" s="3">
         <v>46181</v>
@@ -5670,13 +5706,13 @@
     </row>
     <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D62" s="3">
         <v>46182</v>
@@ -5687,13 +5723,13 @@
     </row>
     <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D63" s="3">
         <v>46184</v>
@@ -5704,13 +5740,13 @@
     </row>
     <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D64" s="3">
         <v>46188</v>
@@ -5721,13 +5757,13 @@
     </row>
     <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D65" s="3">
         <v>46188</v>
@@ -5738,13 +5774,13 @@
     </row>
     <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D66" s="3">
         <v>46198</v>
@@ -6101,30 +6137,30 @@
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="6">
         <v>46174</v>
@@ -6138,16 +6174,16 @@
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E3" s="6">
         <v>46175</v>
@@ -6161,16 +6197,16 @@
     </row>
     <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E4" s="6">
         <v>46177</v>
@@ -6184,16 +6220,16 @@
     </row>
     <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E5" s="6">
         <v>46178</v>
@@ -6207,16 +6243,16 @@
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E6" s="6">
         <v>46167</v>
@@ -6230,16 +6266,16 @@
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E7" s="6">
         <v>46168</v>
@@ -6253,16 +6289,16 @@
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E8" s="6">
         <v>46169</v>
@@ -6276,16 +6312,16 @@
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E9" s="6">
         <v>46170</v>
@@ -6299,16 +6335,16 @@
     </row>
     <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E10" s="6">
         <v>46171</v>
@@ -6322,16 +6358,16 @@
     </row>
     <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E11" s="6">
         <v>46167</v>
@@ -6345,16 +6381,16 @@
     </row>
     <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E12" s="6">
         <v>46168</v>
@@ -6368,16 +6404,16 @@
     </row>
     <row r="13" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E13" s="6">
         <v>46169</v>
@@ -6391,16 +6427,16 @@
     </row>
     <row r="14" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E14" s="6">
         <v>46170</v>
@@ -6414,16 +6450,16 @@
     </row>
     <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E15" s="6">
         <v>46171</v>
@@ -6437,16 +6473,16 @@
     </row>
     <row r="16" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>173</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>174</v>
       </c>
       <c r="E16" s="6">
         <v>46167</v>
@@ -6460,16 +6496,16 @@
     </row>
     <row r="17" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E17" s="6">
         <v>46168</v>
@@ -6483,16 +6519,16 @@
     </row>
     <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E18" s="6">
         <v>46169</v>
@@ -6506,16 +6542,16 @@
     </row>
     <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E19" s="6">
         <v>46169</v>
@@ -6529,16 +6565,16 @@
     </row>
     <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E20" s="6">
         <v>46170</v>
@@ -6552,16 +6588,16 @@
     </row>
     <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E21" s="6">
         <v>46170</v>
@@ -6575,16 +6611,16 @@
     </row>
     <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E22" s="6">
         <v>46160</v>
@@ -6598,16 +6634,16 @@
     </row>
     <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E23" s="6">
         <v>46161</v>
@@ -6621,16 +6657,16 @@
     </row>
     <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E24" s="6">
         <v>46162</v>
@@ -6644,16 +6680,16 @@
     </row>
     <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E25" s="6">
         <v>46163</v>
@@ -6667,16 +6703,16 @@
     </row>
     <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E26" s="6">
         <v>46164</v>
@@ -6690,16 +6726,16 @@
     </row>
     <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E27" s="6">
         <v>46160</v>
@@ -6713,16 +6749,16 @@
     </row>
     <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E28" s="6">
         <v>46161</v>
@@ -6736,16 +6772,16 @@
     </row>
     <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E29" s="6">
         <v>46162</v>
@@ -6759,16 +6795,16 @@
     </row>
     <row r="30" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E30" s="6">
         <v>46163</v>
@@ -6782,16 +6818,16 @@
     </row>
     <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E31" s="6">
         <v>46164</v>
@@ -6805,16 +6841,16 @@
     </row>
     <row r="32" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E32" s="6">
         <v>46160</v>
@@ -6828,16 +6864,16 @@
     </row>
     <row r="33" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E33" s="6">
         <v>46161</v>
@@ -6851,16 +6887,16 @@
     </row>
     <row r="34" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E34" s="6">
         <v>46162</v>
@@ -6874,16 +6910,16 @@
     </row>
     <row r="35" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E35" s="6">
         <v>46163</v>
@@ -6897,16 +6933,16 @@
     </row>
     <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E36" s="6">
         <v>46163</v>
@@ -6920,16 +6956,16 @@
     </row>
     <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E37" s="6">
         <v>46164</v>
@@ -6943,16 +6979,16 @@
     </row>
     <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E38" s="6">
         <v>46160</v>
@@ -6966,16 +7002,16 @@
     </row>
     <row r="39" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E39" s="6">
         <v>46161</v>
@@ -6989,16 +7025,16 @@
     </row>
     <row r="40" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E40" s="6">
         <v>46162</v>
@@ -7012,16 +7048,16 @@
     </row>
     <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E41" s="6">
         <v>46163</v>
@@ -7035,16 +7071,16 @@
     </row>
     <row r="42" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E42" s="6">
         <v>46164</v>
@@ -7058,16 +7094,16 @@
     </row>
     <row r="43" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E43" s="6">
         <v>46153</v>
@@ -7081,16 +7117,16 @@
     </row>
     <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E44" s="6">
         <v>46154</v>
@@ -7104,16 +7140,16 @@
     </row>
     <row r="45" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E45" s="6">
         <v>46155</v>
@@ -7127,16 +7163,16 @@
     </row>
     <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E46" s="6">
         <v>46156</v>
@@ -7150,16 +7186,16 @@
     </row>
     <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E47" s="6">
         <v>46157</v>
@@ -7173,16 +7209,16 @@
     </row>
     <row r="48" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E48" s="6">
         <v>46153</v>
@@ -7196,16 +7232,16 @@
     </row>
     <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E49" s="6">
         <v>46154</v>
@@ -7219,16 +7255,16 @@
     </row>
     <row r="50" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E50" s="6">
         <v>46155</v>
@@ -7242,16 +7278,16 @@
     </row>
     <row r="51" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E51" s="6">
         <v>46156</v>
@@ -7265,16 +7301,16 @@
     </row>
     <row r="52" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E52" s="6">
         <v>46157</v>
@@ -7288,16 +7324,16 @@
     </row>
     <row r="53" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E53" s="6">
         <v>46153</v>
@@ -7311,16 +7347,16 @@
     </row>
     <row r="54" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E54" s="6">
         <v>46154</v>
@@ -7334,16 +7370,16 @@
     </row>
     <row r="55" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E55" s="6">
         <v>46155</v>
@@ -7357,16 +7393,16 @@
     </row>
     <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E56" s="6">
         <v>46156</v>
@@ -7380,16 +7416,16 @@
     </row>
     <row r="57" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E57" s="6">
         <v>46157</v>
@@ -7403,16 +7439,16 @@
     </row>
     <row r="58" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="E58" s="6">
         <v>46153</v>
@@ -7426,16 +7462,16 @@
     </row>
     <row r="59" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D59" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>197</v>
       </c>
       <c r="E59" s="6">
         <v>46153</v>
@@ -7449,16 +7485,16 @@
     </row>
     <row r="60" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="E60" s="6">
         <v>46154</v>
@@ -7472,16 +7508,16 @@
     </row>
     <row r="61" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C61" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="E61" s="6">
         <v>46154</v>
@@ -7495,16 +7531,16 @@
     </row>
     <row r="62" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="E62" s="6">
         <v>46155</v>
@@ -7518,16 +7554,16 @@
     </row>
     <row r="63" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E63" s="6">
         <v>46155</v>
@@ -7541,16 +7577,16 @@
     </row>
     <row r="64" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="E64" s="6">
         <v>46156</v>
@@ -7564,16 +7600,16 @@
     </row>
     <row r="65" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E65" s="6">
         <v>46156</v>
@@ -7587,16 +7623,16 @@
     </row>
     <row r="66" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="E66" s="6">
         <v>46157</v>
@@ -7610,16 +7646,16 @@
     </row>
     <row r="67" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C67" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>198</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="E67" s="6">
         <v>46157</v>
@@ -7633,16 +7669,16 @@
     </row>
     <row r="68" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E68" s="6">
         <v>46153</v>
@@ -7656,16 +7692,16 @@
     </row>
     <row r="69" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E69" s="6">
         <v>46154</v>
@@ -7679,16 +7715,16 @@
     </row>
     <row r="70" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E70" s="6">
         <v>46155</v>
@@ -7702,16 +7738,16 @@
     </row>
     <row r="71" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E71" s="6">
         <v>46155</v>
@@ -7725,16 +7761,16 @@
     </row>
     <row r="72" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E72" s="6">
         <v>46155</v>
@@ -7748,16 +7784,16 @@
     </row>
     <row r="73" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E73" s="6">
         <v>46155</v>
@@ -7771,16 +7807,16 @@
     </row>
     <row r="74" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E74" s="6">
         <v>46156</v>
@@ -7794,16 +7830,16 @@
     </row>
     <row r="75" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E75" s="6">
         <v>46157</v>
@@ -7817,16 +7853,16 @@
     </row>
     <row r="76" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E76" s="6">
         <v>46153</v>
@@ -7840,16 +7876,16 @@
     </row>
     <row r="77" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E77" s="6">
         <v>46154</v>
@@ -7863,16 +7899,16 @@
     </row>
     <row r="78" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E78" s="6">
         <v>46155</v>
@@ -7886,16 +7922,16 @@
     </row>
     <row r="79" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E79" s="6">
         <v>46156</v>
@@ -7909,16 +7945,16 @@
     </row>
     <row r="80" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E80" s="6">
         <v>46157</v>
@@ -7932,16 +7968,16 @@
     </row>
     <row r="81" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E81" s="6">
         <v>46153</v>
@@ -7955,16 +7991,16 @@
     </row>
     <row r="82" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E82" s="6">
         <v>46154</v>
@@ -7978,16 +8014,16 @@
     </row>
     <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E83" s="6">
         <v>46155</v>
@@ -8001,16 +8037,16 @@
     </row>
     <row r="84" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E84" s="6">
         <v>46156</v>
@@ -8024,16 +8060,16 @@
     </row>
     <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E85" s="6">
         <v>46157</v>
@@ -8047,16 +8083,16 @@
     </row>
     <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E86" s="6">
         <v>46146</v>
@@ -8070,16 +8106,16 @@
     </row>
     <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E87" s="6">
         <v>46147</v>
@@ -8093,16 +8129,16 @@
     </row>
     <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E88" s="6">
         <v>46148</v>
@@ -8116,16 +8152,16 @@
     </row>
     <row r="89" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E89" s="6">
         <v>46149</v>
@@ -8139,16 +8175,16 @@
     </row>
     <row r="90" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E90" s="6">
         <v>46150</v>
@@ -8162,16 +8198,16 @@
     </row>
     <row r="91" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E91" s="6">
         <v>46146</v>
@@ -8185,16 +8221,16 @@
     </row>
     <row r="92" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C92" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D92" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="E92" s="6">
         <v>46146</v>
@@ -8208,16 +8244,16 @@
     </row>
     <row r="93" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E93" s="6">
         <v>46147</v>
@@ -8231,16 +8267,16 @@
     </row>
     <row r="94" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E94" s="6">
         <v>46147</v>
@@ -8254,16 +8290,16 @@
     </row>
     <row r="95" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E95" s="6">
         <v>46148</v>
@@ -8277,16 +8313,16 @@
     </row>
     <row r="96" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C96" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D96" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>215</v>
       </c>
       <c r="E96" s="6">
         <v>46149</v>
@@ -8300,16 +8336,16 @@
     </row>
     <row r="97" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E97" s="6">
         <v>46149</v>
@@ -8323,16 +8359,16 @@
     </row>
     <row r="98" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E98" s="6">
         <v>46150</v>
@@ -8346,16 +8382,16 @@
     </row>
     <row r="99" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E99" s="6">
         <v>46146</v>
@@ -8369,16 +8405,16 @@
     </row>
     <row r="100" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E100" s="6">
         <v>46147</v>
@@ -8392,16 +8428,16 @@
     </row>
     <row r="101" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E101" s="6">
         <v>46148</v>
@@ -8415,16 +8451,16 @@
     </row>
     <row r="102" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E102" s="6">
         <v>46149</v>
@@ -8438,16 +8474,16 @@
     </row>
     <row r="103" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E103" s="6">
         <v>46150</v>
@@ -8461,16 +8497,16 @@
     </row>
     <row r="104" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E104" s="6">
         <v>46146</v>
@@ -8484,16 +8520,16 @@
     </row>
     <row r="105" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E105" s="6">
         <v>46147</v>
@@ -8507,16 +8543,16 @@
     </row>
     <row r="106" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E106" s="6">
         <v>46148</v>
@@ -8530,16 +8566,16 @@
     </row>
     <row r="107" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E107" s="6">
         <v>46149</v>
@@ -8553,16 +8589,16 @@
     </row>
     <row r="108" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E108" s="6">
         <v>46150</v>
@@ -8576,16 +8612,16 @@
     </row>
     <row r="109" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E109" s="6">
         <v>46146</v>
@@ -8599,16 +8635,16 @@
     </row>
     <row r="110" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E110" s="6">
         <v>46147</v>
@@ -8622,16 +8658,16 @@
     </row>
     <row r="111" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E111" s="6">
         <v>46148</v>
@@ -8645,16 +8681,16 @@
     </row>
     <row r="112" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E112" s="6">
         <v>46149</v>
@@ -8668,16 +8704,16 @@
     </row>
     <row r="113" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E113" s="6">
         <v>46150</v>
@@ -8691,16 +8727,16 @@
     </row>
     <row r="114" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E114" s="6">
         <v>46146</v>
@@ -8714,16 +8750,16 @@
     </row>
     <row r="115" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E115" s="6">
         <v>46147</v>
@@ -8737,16 +8773,16 @@
     </row>
     <row r="116" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E116" s="6">
         <v>46148</v>
@@ -8760,16 +8796,16 @@
     </row>
     <row r="117" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E117" s="6">
         <v>46149</v>
@@ -8783,16 +8819,16 @@
     </row>
     <row r="118" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E118" s="6">
         <v>46150</v>
@@ -8806,16 +8842,16 @@
     </row>
     <row r="119" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E119" s="6">
         <v>46181</v>
@@ -8830,16 +8866,16 @@
     </row>
     <row r="120" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E120" s="6">
         <v>46182</v>
@@ -8854,16 +8890,16 @@
     </row>
     <row r="121" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E121" s="6">
         <v>46183</v>
@@ -8878,16 +8914,16 @@
     </row>
     <row r="122" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E122" s="6">
         <v>46184</v>
@@ -8902,16 +8938,16 @@
     </row>
     <row r="123" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E123" s="6">
         <v>46185</v>
@@ -8926,16 +8962,16 @@
     </row>
     <row r="124" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E124" s="6">
         <v>46181</v>
@@ -8950,16 +8986,16 @@
     </row>
     <row r="125" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E125" s="6">
         <v>46182</v>
@@ -8974,16 +9010,16 @@
     </row>
     <row r="126" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E126" s="6">
         <v>46183</v>
@@ -8998,16 +9034,16 @@
     </row>
     <row r="127" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E127" s="6">
         <v>46184</v>
@@ -9022,16 +9058,16 @@
     </row>
     <row r="128" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D128" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>367</v>
       </c>
       <c r="E128" s="6">
         <v>46188</v>
@@ -9046,16 +9082,16 @@
     </row>
     <row r="129" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E129" s="6">
         <v>46189</v>
@@ -9070,16 +9106,16 @@
     </row>
     <row r="130" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E130" s="6">
         <v>46190</v>
@@ -9094,16 +9130,16 @@
     </row>
     <row r="131" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E131" s="6">
         <v>46191</v>
@@ -9118,16 +9154,16 @@
     </row>
     <row r="132" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E132" s="6">
         <v>46192</v>
@@ -9160,755 +9196,755 @@
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="R1" s="16" t="s">
         <v>348</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>276</v>
+      </c>
+      <c r="C15" t="s">
         <v>277</v>
       </c>
-      <c r="C15" t="s">
-        <v>278</v>
-      </c>
       <c r="E15" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" t="s">
         <v>281</v>
       </c>
-      <c r="C18" t="s">
-        <v>282</v>
-      </c>
       <c r="D18" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C27" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B28" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B29" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B30" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C30" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B31" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C32" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C33" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C35" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C36" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C40" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C42" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C44" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C45" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C47" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C48" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C50" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>314</v>
+      </c>
+      <c r="C51" t="s">
         <v>315</v>
       </c>
-      <c r="C51" t="s">
-        <v>316</v>
-      </c>
       <c r="K51" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C52" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C54" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -9940,7 +9976,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
@@ -9950,7 +9986,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9750D81D-6223-CA4D-959C-00477D6BB81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167C8F10-E514-0347-A440-80C88B225178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1674,6 +1674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1721,7 +1722,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1745,7 +1746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1769,7 +1770,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1793,7 +1794,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1817,7 +1818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1841,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1865,7 +1866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1889,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1916,7 +1917,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1943,7 +1944,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1970,7 +1971,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -1997,7 +1998,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -2026,7 +2027,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -2055,7 +2056,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -2103,7 +2104,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>14</v>
       </c>
@@ -2127,7 +2128,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
@@ -2151,7 +2152,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
@@ -2196,10 +2197,10 @@
         <v>375</v>
       </c>
       <c r="I20" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
@@ -2223,7 +2224,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>14</v>
       </c>
@@ -2247,7 +2248,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
@@ -2271,7 +2272,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>14</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
@@ -2322,7 +2323,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -2346,7 +2347,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
@@ -2370,7 +2371,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>22</v>
       </c>
@@ -2392,7 +2393,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
@@ -2414,7 +2415,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>22</v>
       </c>
@@ -2438,7 +2439,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>22</v>
       </c>
@@ -2460,7 +2461,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>22</v>
       </c>
@@ -2484,7 +2485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>22</v>
       </c>
@@ -2508,7 +2509,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>22</v>
       </c>
@@ -2532,7 +2533,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>22</v>
       </c>
@@ -2556,7 +2557,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>22</v>
       </c>
@@ -2583,7 +2584,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>22</v>
       </c>
@@ -2610,7 +2611,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>27</v>
       </c>
@@ -2634,7 +2635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>27</v>
       </c>
@@ -2656,7 +2657,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>27</v>
       </c>
@@ -2680,7 +2681,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>27</v>
       </c>
@@ -2704,7 +2705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>27</v>
       </c>
@@ -2728,7 +2729,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>27</v>
       </c>
@@ -2755,7 +2756,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>29</v>
       </c>
@@ -2779,7 +2780,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>29</v>
       </c>
@@ -2803,7 +2804,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>29</v>
       </c>
@@ -2825,7 +2826,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>29</v>
       </c>
@@ -2849,7 +2850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>29</v>
       </c>
@@ -2873,7 +2874,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>29</v>
       </c>
@@ -2897,7 +2898,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>29</v>
       </c>
@@ -2921,7 +2922,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>29</v>
       </c>
@@ -2945,7 +2946,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>29</v>
       </c>
@@ -2967,7 +2968,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>29</v>
       </c>
@@ -3017,10 +3018,10 @@
         <v>375</v>
       </c>
       <c r="I54" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>29</v>
       </c>
@@ -3044,7 +3045,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>29</v>
       </c>
@@ -3071,7 +3072,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>29</v>
       </c>
@@ -3098,7 +3099,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>33</v>
       </c>
@@ -3127,7 +3128,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>33</v>
       </c>
@@ -3151,7 +3152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>33</v>
       </c>
@@ -3175,7 +3176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>33</v>
       </c>
@@ -3199,7 +3200,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>33</v>
       </c>
@@ -3226,7 +3227,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>33</v>
       </c>
@@ -3253,7 +3254,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>33</v>
       </c>
@@ -3280,7 +3281,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>33</v>
       </c>
@@ -3307,7 +3308,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>33</v>
       </c>
@@ -3336,7 +3337,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>33</v>
       </c>
@@ -3368,7 +3369,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>33</v>
       </c>
@@ -3390,7 +3391,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>33</v>
       </c>
@@ -3415,7 +3416,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>37</v>
       </c>
@@ -3438,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>37</v>
       </c>
@@ -3461,7 +3462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>37</v>
       </c>
@@ -3490,7 +3491,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>37</v>
       </c>
@@ -3513,7 +3514,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>37</v>
       </c>
@@ -3536,7 +3537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>37</v>
       </c>
@@ -3559,7 +3560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>37</v>
       </c>
@@ -3582,7 +3583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>37</v>
       </c>
@@ -3605,7 +3606,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>37</v>
       </c>
@@ -3628,7 +3629,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>37</v>
       </c>
@@ -3651,7 +3652,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>37</v>
       </c>
@@ -3677,7 +3678,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>37</v>
       </c>
@@ -3703,7 +3704,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>37</v>
       </c>
@@ -3729,7 +3730,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>37</v>
       </c>
@@ -3755,7 +3756,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -3778,7 +3779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>39</v>
       </c>
@@ -3801,7 +3802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -3824,7 +3825,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -3844,7 +3845,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -3864,7 +3865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>39</v>
       </c>
@@ -3884,7 +3885,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>39</v>
       </c>
@@ -3907,7 +3908,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -3933,7 +3934,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -3959,7 +3960,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>40</v>
       </c>
@@ -4005,7 +4006,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -4028,7 +4029,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -4051,7 +4052,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -4097,7 +4098,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -4120,7 +4121,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -4141,7 +4142,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -4164,7 +4165,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -4190,7 +4191,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>156</v>
       </c>
@@ -4213,7 +4214,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>156</v>
       </c>
@@ -4236,7 +4237,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>156</v>
       </c>
@@ -4259,7 +4260,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>156</v>
       </c>
@@ -4282,7 +4283,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>343</v>
       </c>
@@ -4302,7 +4303,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>343</v>
       </c>
@@ -4322,7 +4323,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>343</v>
       </c>
@@ -4342,7 +4343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>343</v>
       </c>
@@ -4365,7 +4366,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>343</v>
       </c>
@@ -4385,7 +4386,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>343</v>
       </c>
@@ -4405,7 +4406,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>343</v>
       </c>
@@ -4425,7 +4426,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>343</v>
       </c>
@@ -4448,7 +4449,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>343</v>
       </c>
@@ -4471,7 +4472,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>343</v>
       </c>
@@ -4491,7 +4492,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>341</v>
       </c>
@@ -4514,7 +4515,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>341</v>
       </c>
@@ -4537,7 +4538,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>341</v>
       </c>
@@ -4560,7 +4561,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>341</v>
       </c>
@@ -4584,7 +4585,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>360</v>
       </c>
@@ -4604,7 +4605,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>360</v>
       </c>
@@ -4624,7 +4625,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>360</v>
       </c>
@@ -4644,7 +4645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>360</v>
       </c>
@@ -4665,7 +4666,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I124" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Erivan Vale de Souza &lt;erivan.souza@numenit.com&gt;"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4673,6 +4680,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4700,7 +4708,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>81</v>
       </c>
@@ -4717,7 +4725,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>81</v>
       </c>
@@ -4734,7 +4742,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>81</v>
       </c>
@@ -4751,7 +4759,7 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>81</v>
       </c>
@@ -4768,7 +4776,7 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>81</v>
       </c>
@@ -4785,7 +4793,7 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>81</v>
       </c>
@@ -4802,7 +4810,7 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>81</v>
       </c>
@@ -4819,7 +4827,7 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>81</v>
       </c>
@@ -4836,7 +4844,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>81</v>
       </c>
@@ -4849,7 +4857,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>81</v>
       </c>
@@ -4866,7 +4874,7 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>81</v>
       </c>
@@ -4883,7 +4891,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>81</v>
       </c>
@@ -4900,7 +4908,7 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>81</v>
       </c>
@@ -4917,7 +4925,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>81</v>
       </c>
@@ -4932,7 +4940,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>81</v>
       </c>
@@ -4949,7 +4957,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>89</v>
       </c>
@@ -4966,7 +4974,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>89</v>
       </c>
@@ -4983,7 +4991,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>89</v>
       </c>
@@ -5000,7 +5008,7 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>89</v>
       </c>
@@ -5017,7 +5025,7 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>89</v>
       </c>
@@ -5034,7 +5042,7 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>89</v>
       </c>
@@ -5051,7 +5059,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>89</v>
       </c>
@@ -5068,7 +5076,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>89</v>
       </c>
@@ -5085,7 +5093,7 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>89</v>
       </c>
@@ -5102,7 +5110,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>89</v>
       </c>
@@ -5119,7 +5127,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>89</v>
       </c>
@@ -5136,7 +5144,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>89</v>
       </c>
@@ -5153,7 +5161,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>89</v>
       </c>
@@ -5170,7 +5178,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>89</v>
       </c>
@@ -5187,7 +5195,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>89</v>
       </c>
@@ -5204,7 +5212,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>89</v>
       </c>
@@ -5221,7 +5229,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>89</v>
       </c>
@@ -5238,7 +5246,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>89</v>
       </c>
@@ -5251,7 +5259,7 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>101</v>
       </c>
@@ -5268,7 +5276,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>101</v>
       </c>
@@ -5285,7 +5293,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>101</v>
       </c>
@@ -5302,7 +5310,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>101</v>
       </c>
@@ -5319,7 +5327,7 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>101</v>
       </c>
@@ -5336,7 +5344,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>101</v>
       </c>
@@ -5353,7 +5361,7 @@
         <v>46192</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>101</v>
       </c>
@@ -5370,7 +5378,7 @@
         <v>46199</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>101</v>
       </c>
@@ -5387,7 +5395,7 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>101</v>
       </c>
@@ -5402,7 +5410,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>101</v>
       </c>
@@ -5417,7 +5425,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>101</v>
       </c>
@@ -5434,7 +5442,7 @@
         <v>46223</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>101</v>
       </c>
@@ -5451,7 +5459,7 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>101</v>
       </c>
@@ -5466,7 +5474,7 @@
         <v>46223</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>101</v>
       </c>
@@ -5483,7 +5491,7 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>101</v>
       </c>
@@ -5500,7 +5508,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>101</v>
       </c>
@@ -5517,7 +5525,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>109</v>
       </c>
@@ -5534,7 +5542,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>109</v>
       </c>
@@ -5551,7 +5559,7 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>109</v>
       </c>
@@ -5568,7 +5576,7 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>109</v>
       </c>
@@ -5619,7 +5627,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>109</v>
       </c>
@@ -5636,7 +5644,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>109</v>
       </c>
@@ -5653,7 +5661,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>109</v>
       </c>
@@ -5670,7 +5678,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>109</v>
       </c>
@@ -5687,7 +5695,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>109</v>
       </c>
@@ -5704,7 +5712,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>109</v>
       </c>
@@ -5721,7 +5729,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>109</v>
       </c>
@@ -5738,7 +5746,7 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>109</v>
       </c>
@@ -5755,7 +5763,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>109</v>
       </c>
@@ -5772,7 +5780,7 @@
         <v>46192</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>109</v>
       </c>
@@ -6112,6 +6120,13 @@
       <c r="E112" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E66" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Erivan Vale de Souza &lt;erivan.souza@numenit.com&gt;"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167C8F10-E514-0347-A440-80C88B225178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12984361-189C-A147-88EA-6F11D577DF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="5 - Vagas" sheetId="10" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$I$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$I$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Agenda Workshop'!$A$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$Q$54</definedName>
   </definedNames>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="353">
   <si>
     <t>Projeto</t>
   </si>
@@ -62,48 +62,12 @@
     <t>Consultor CO</t>
   </si>
   <si>
-    <t>Consultor MM</t>
-  </si>
-  <si>
     <t>Consultor SD</t>
   </si>
   <si>
-    <t>Consultor WM</t>
-  </si>
-  <si>
-    <t>Consultor PP / QM / PM</t>
-  </si>
-  <si>
-    <t>Consultor Avalara</t>
-  </si>
-  <si>
-    <t>Consultor Jr. MM</t>
-  </si>
-  <si>
-    <t>Consultor Jr. SD</t>
-  </si>
-  <si>
-    <t>Consultor Jr. FI</t>
-  </si>
-  <si>
     <t>4062 - Airfix - Implementação SAP Cloud ERP</t>
   </si>
   <si>
-    <t>Consultor SERVIÇO</t>
-  </si>
-  <si>
-    <t>Consultor AP / AR / Bancos</t>
-  </si>
-  <si>
-    <t>Consultor PS</t>
-  </si>
-  <si>
-    <t>Consultor FI AA GL</t>
-  </si>
-  <si>
-    <t>Consultor PP / PM / QM</t>
-  </si>
-  <si>
     <t>3101 - Supley - Implementação SAP Cloud ERP Private</t>
   </si>
   <si>
@@ -113,66 +77,24 @@
     <t>4254 - Ademicon - Projeto 2032</t>
   </si>
   <si>
-    <t>Consultor Leasing</t>
-  </si>
-  <si>
-    <t>Consultor GL / AA / PS / CO</t>
-  </si>
-  <si>
-    <t>Consultor TRM / Fluxo Caixa</t>
-  </si>
-  <si>
-    <t>Consultor Group Report</t>
-  </si>
-  <si>
     <t>3338 - BRW - Implantação SAP S/4HANA (GROW)</t>
   </si>
   <si>
-    <t>Consultor FI / GL</t>
-  </si>
-  <si>
     <t>3464 - Solinfitec - Implantação S4HANA</t>
   </si>
   <si>
-    <t>Consultor FI / GL / PS</t>
-  </si>
-  <si>
-    <t>Consultor RE</t>
-  </si>
-  <si>
-    <t>Consultor TRM</t>
-  </si>
-  <si>
     <t>4516 - EPR - S4HANA-PUBLIC - Implantação de Soluções SAP S4/HANA Public Cloud</t>
   </si>
   <si>
-    <t>Consultor de Group Reporting</t>
-  </si>
-  <si>
-    <t>Consultor de PM</t>
-  </si>
-  <si>
-    <t>Consultor de TRM</t>
-  </si>
-  <si>
     <t>4299 - ERO - SAP CLOUD ERP GROW</t>
   </si>
   <si>
-    <t>Consultor Group Reporting SR</t>
-  </si>
-  <si>
     <t>4723 - Sooro Renner Nutricao S/A | Grow</t>
   </si>
   <si>
     <t>4886 - PRINCIPIA COSMÉTICOS</t>
   </si>
   <si>
-    <t>Consultor PP, QM e PM</t>
-  </si>
-  <si>
-    <t>Consultor MM Jr.</t>
-  </si>
-  <si>
     <t>Consultor</t>
   </si>
   <si>
@@ -491,12 +413,6 @@
     <t>Juliana Furlan Celidonio &lt;juliana.celidonio@numenit.com&gt;</t>
   </si>
   <si>
-    <t>Consultor de SAC Planning</t>
-  </si>
-  <si>
-    <t>Consultor PP / QM</t>
-  </si>
-  <si>
     <t>Victor Lino Silva &lt;victor.silva@numenit.com&gt;</t>
   </si>
   <si>
@@ -995,60 +911,6 @@
     <t>Paulo Henrique Soares Loiola &lt;paulo.loiola@numenit.com&gt;</t>
   </si>
   <si>
-    <t>Gustavo Henrique Conrado dos Santos (Jr.)</t>
-  </si>
-  <si>
-    <t>Felipe Soares Galvao (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Juliana Furlan Celidonio (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Mauricio Lemes Silva (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Valdir Da Silva Brito Junior(Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Arthur Menezes Pinto (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Felipe De Carvalho Medeiros (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Claudio Gastao Junior (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Jhonatta Jean Hollupi (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Thiago Vinicius Moreira Silva (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Vinicius Pereira Bueno (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Renan Rodrigues de Melo (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Karen Dos Reis Mascaro (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Victor Lino Silva (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Alyson Henrique Eleuterio De Souza (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Anderson Leonardo Mendonca Hilario (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Alexandre Pereira (Consultor Jr.)</t>
-  </si>
-  <si>
-    <t>Guilherme Souza Do Espirito Santo (Consultor Jr.)</t>
-  </si>
-  <si>
     <t>João Gabriel Rocha De Araujo</t>
   </si>
   <si>
@@ -1064,9 +926,6 @@
     <t>vinicius.cabral@numenit.com</t>
   </si>
   <si>
-    <t>Vinicius Diniz Cabral (Consultor Jr.)</t>
-  </si>
-  <si>
     <t>2943 - Thermas ERP SAP Grow</t>
   </si>
   <si>
@@ -1076,9 +935,6 @@
     <t>4676 - Itaipu - Implementação SAP Cloud ERP</t>
   </si>
   <si>
-    <t>Consultor SD Jr.</t>
-  </si>
-  <si>
     <t>Renan Rodrigues de Melo &lt;renan.rodrigues@numenit.com&gt;</t>
   </si>
   <si>
@@ -1103,21 +959,12 @@
     <t>Consultor secundário</t>
   </si>
   <si>
-    <t>Consultor FI / CO / PS</t>
-  </si>
-  <si>
     <t>Matheus Golin &lt;matheus.golin@nunenit.com&gt;</t>
   </si>
   <si>
-    <t>Consultor GL</t>
-  </si>
-  <si>
     <t>Guilherme Souza Do Espirito Santo (Consultor Jr.) &lt;guilherme.santo@numenit.com&gt;</t>
   </si>
   <si>
-    <t>Consultor AP / AR</t>
-  </si>
-  <si>
     <t>Fase</t>
   </si>
   <si>
@@ -1154,9 +1001,6 @@
     <t>Atividade de Realize: Estrutura de custo</t>
   </si>
   <si>
-    <t>Consultor PM</t>
-  </si>
-  <si>
     <t>Consultor CO Custeio</t>
   </si>
   <si>
@@ -1179,6 +1023,84 @@
   </si>
   <si>
     <t>Peso Dedicação Principal</t>
+  </si>
+  <si>
+    <t>AVALARA</t>
+  </si>
+  <si>
+    <t>Group Report</t>
+  </si>
+  <si>
+    <t>SAC Planning</t>
+  </si>
+  <si>
+    <t>PP;QM</t>
+  </si>
+  <si>
+    <t>PP;QM;PM</t>
+  </si>
+  <si>
+    <t>PP;PM;QM</t>
+  </si>
+  <si>
+    <t>SERVIÇO</t>
+  </si>
+  <si>
+    <t>Gustavo Henrique Conrado dos Santos</t>
+  </si>
+  <si>
+    <t>Felipe Soares Galvao</t>
+  </si>
+  <si>
+    <t>Juliana Furlan Celidonio</t>
+  </si>
+  <si>
+    <t>Mauricio Lemes Silva</t>
+  </si>
+  <si>
+    <t>Valdir Da Silva Brito Junior</t>
+  </si>
+  <si>
+    <t>Arthur Menezes Pinto</t>
+  </si>
+  <si>
+    <t>Felipe De Carvalho Medeiros</t>
+  </si>
+  <si>
+    <t>Claudio Gastao Junior</t>
+  </si>
+  <si>
+    <t>Jhonatta Jean Hollupi</t>
+  </si>
+  <si>
+    <t>Thiago Vinicius Moreira Silva</t>
+  </si>
+  <si>
+    <t>Vinicius Pereira Bueno</t>
+  </si>
+  <si>
+    <t>Renan Rodrigues de Melo</t>
+  </si>
+  <si>
+    <t>Karen Dos Reis Mascaro</t>
+  </si>
+  <si>
+    <t>Victor Lino Silva</t>
+  </si>
+  <si>
+    <t>Alyson Henrique Eleuterio De Souza</t>
+  </si>
+  <si>
+    <t>Anderson Leonardo Mendonca Hilario</t>
+  </si>
+  <si>
+    <t>Alexandre Pereira</t>
+  </si>
+  <si>
+    <t>Guilherme Souza Do Espirito Santo</t>
+  </si>
+  <si>
+    <t>Vinicius Diniz Cabral</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1245,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1371,6 +1293,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1674,8 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:J124"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -1698,327 +1622,327 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>350</v>
+        <v>302</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>352</v>
+        <v>304</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>346</v>
+        <v>298</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>358</v>
+        <v>307</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>373</v>
+        <v>321</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>378</v>
+        <v>326</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>234</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="11">
         <v>46388</v>
       </c>
       <c r="G2" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I2" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>234</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="11">
         <v>46388</v>
       </c>
       <c r="G3" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H3" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I3" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="11">
         <v>46388</v>
       </c>
       <c r="G4" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H4" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I4" s="20">
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>221</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="11">
         <v>46388</v>
       </c>
       <c r="G5" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H5" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I5" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>225</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="11">
         <v>46388</v>
       </c>
       <c r="G6" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H6" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I6" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>230</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="11">
         <v>46388</v>
       </c>
       <c r="G7" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H7" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I7" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>331</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="11">
         <v>46388</v>
       </c>
       <c r="G8" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H8" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I8" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>327</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="11">
         <v>46388</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G9" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H9" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I9" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
+        <v>221</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="11">
         <v>46388</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G10" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H10" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I10" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>225</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="11">
         <v>46388</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G11" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H11" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I11" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>234</v>
       </c>
       <c r="C12" t="s">
-        <v>356</v>
+        <v>306</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="11">
         <v>46388</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G12" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H12" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I12" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>7</v>
+        <v>225</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E13" s="11">
         <v>46296</v>
       </c>
       <c r="G13" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H13" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I13" s="20">
         <v>0.4</v>
@@ -2027,27 +1951,27 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>333</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E14" s="11">
         <v>46296</v>
       </c>
       <c r="G14" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H14" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I14" s="20">
         <v>0.4</v>
@@ -2056,121 +1980,121 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="11">
         <v>46296</v>
       </c>
       <c r="G15" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H15" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I15" s="20">
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>355</v>
+        <v>234</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="11">
         <v>46296</v>
       </c>
       <c r="G16" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H16" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I16" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="11">
         <v>46296</v>
       </c>
       <c r="G17" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H17" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I17" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="11">
         <v>46296</v>
       </c>
       <c r="G18" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H18" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I18" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>6</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="11">
         <v>46296</v>
       </c>
       <c r="G19" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H19" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I19" s="20">
         <v>1</v>
@@ -2178,227 +2102,227 @@
     </row>
     <row r="20" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>8</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="11">
         <v>46296</v>
       </c>
       <c r="G20" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H20" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I20" s="20">
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="11">
         <v>46296</v>
       </c>
       <c r="G21" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H21" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I21" s="20">
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="11">
         <v>46296</v>
       </c>
       <c r="G22" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H22" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I22" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>10</v>
+        <v>327</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="11">
         <v>46296</v>
       </c>
       <c r="G23" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H23" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I23" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>13</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="11">
         <v>46296</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G24" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H24" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I24" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="11">
         <v>46388</v>
       </c>
       <c r="G25" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H25" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I25" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>5</v>
+        <v>222</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="11">
         <v>46388</v>
       </c>
       <c r="G26" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H26" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I26" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="11">
         <v>46388</v>
       </c>
       <c r="G27" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H27" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I27" s="20">
         <v>0.7</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>355</v>
+        <v>234</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="11"/>
       <c r="G28" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H28" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I28" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>23</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -2406,45 +2330,45 @@
         <v>46388</v>
       </c>
       <c r="G29" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H29" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I29" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="11">
         <v>46388</v>
       </c>
       <c r="G30" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H30" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I30" s="20">
         <v>0.7</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>7</v>
+        <v>225</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -2452,915 +2376,898 @@
         <v>46388</v>
       </c>
       <c r="G31" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H31" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I31" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>6</v>
+        <v>221</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="11">
         <v>46388</v>
       </c>
       <c r="G32" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H32" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I32" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>25</v>
+        <v>226</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="11">
         <v>46388</v>
       </c>
       <c r="G33" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H33" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I33" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>10</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="11">
         <v>46388</v>
       </c>
       <c r="G34" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H34" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I34" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>26</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="11">
         <v>46388</v>
       </c>
       <c r="G35" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H35" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I35" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>11</v>
+        <v>221</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="11">
         <v>46388</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G36" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H36" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I36" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>13</v>
+        <v>234</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="11">
         <v>46388</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G37" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H37" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I37" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="11">
-        <v>46661</v>
-      </c>
-      <c r="G38" t="s">
-        <v>166</v>
-      </c>
-      <c r="H38" t="s">
-        <v>374</v>
-      </c>
-      <c r="I38" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E38" s="11"/>
+      <c r="F38" s="21"/>
+      <c r="I38" s="20"/>
+    </row>
+    <row r="39" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="D39" s="2"/>
       <c r="E39" s="11">
         <v>46661</v>
       </c>
       <c r="G39" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H39" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I39" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>139</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="11">
         <v>46661</v>
       </c>
       <c r="G40" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H40" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I40" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>6</v>
+        <v>225</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="11">
         <v>46661</v>
       </c>
       <c r="G41" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I41" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="11">
         <v>46661</v>
       </c>
       <c r="G42" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H42" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I42" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>11</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="11">
         <v>46661</v>
       </c>
-      <c r="F43" s="14" t="s">
-        <v>349</v>
-      </c>
       <c r="G43" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H43" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I43" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>7</v>
+        <v>221</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D44" s="15"/>
+        <v>116</v>
+      </c>
+      <c r="D44" s="2"/>
       <c r="E44" s="11">
-        <v>46388</v>
+        <v>46661</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>301</v>
       </c>
       <c r="G44" t="s">
-        <v>218</v>
+        <v>138</v>
       </c>
       <c r="H44" t="s">
-        <v>375</v>
+        <v>322</v>
       </c>
       <c r="I44" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="11">
         <v>46388</v>
       </c>
       <c r="G45" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H45" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I45" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="15"/>
       <c r="E46" s="11">
         <v>46388</v>
       </c>
       <c r="G46" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H46" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I46" s="20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>78</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="11">
         <v>46388</v>
       </c>
       <c r="G47" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H47" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I47" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>30</v>
+        <v>221</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="11">
         <v>46388</v>
       </c>
       <c r="G48" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H48" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I48" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>5</v>
+        <v>234</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="11">
         <v>46388</v>
       </c>
       <c r="G49" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H49" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I49" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>143</v>
+        <v>45</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="11">
         <v>46388</v>
       </c>
       <c r="G50" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H50" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I50" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="11">
         <v>46388</v>
       </c>
       <c r="G51" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H51" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I51" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="D52" s="2"/>
       <c r="E52" s="11">
         <v>46388</v>
       </c>
       <c r="G52" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H52" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I52" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>351</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
       <c r="E53" s="11">
         <v>46388</v>
       </c>
       <c r="G53" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H53" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I53" s="20">
         <v>0.4</v>
       </c>
-      <c r="J53">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="54" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D54" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>303</v>
+      </c>
       <c r="E54" s="11">
         <v>46388</v>
       </c>
       <c r="G54" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H54" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I54" s="20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+      <c r="J54">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>10</v>
+        <v>230</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="11">
         <v>46388</v>
       </c>
       <c r="G55" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H55" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I55" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>11</v>
+        <v>327</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="11">
         <v>46388</v>
       </c>
-      <c r="F56" s="14" t="s">
-        <v>349</v>
-      </c>
       <c r="G56" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H56" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I56" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>13</v>
+        <v>221</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="11">
         <v>46388</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G57" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H57" t="s">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="I57" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>7</v>
+        <v>234</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>148</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="D58" s="2"/>
       <c r="E58" s="11">
         <v>46388</v>
       </c>
-      <c r="G58" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="H58" s="19" t="s">
-        <v>376</v>
+      <c r="F58" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="G58" t="s">
+        <v>190</v>
+      </c>
+      <c r="H58" t="s">
+        <v>323</v>
       </c>
       <c r="I58" s="20">
         <v>0.4</v>
       </c>
-      <c r="J58">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>6</v>
+        <v>225</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D59" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="E59" s="11">
         <v>46388</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I59" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+      <c r="J59">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>353</v>
+        <v>221</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>146</v>
+        <v>52</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="11">
         <v>46388</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I60" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>10</v>
+        <v>234</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="11">
         <v>46388</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I61" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>11</v>
+        <v>327</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="11">
         <v>46388</v>
       </c>
-      <c r="F62" s="14" t="s">
-        <v>349</v>
-      </c>
       <c r="G62" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I62" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>12</v>
+        <v>221</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="11">
         <v>46388</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I63" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>12</v>
+        <v>225</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="11">
         <v>46388</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I64" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>34</v>
+        <v>225</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="11">
         <v>46388</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I65" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>35</v>
+        <v>328</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>143</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D66" s="2"/>
       <c r="E66" s="11">
         <v>46388</v>
       </c>
+      <c r="F66" s="14" t="s">
+        <v>301</v>
+      </c>
       <c r="G66" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I66" s="20">
         <v>0.4</v>
       </c>
-      <c r="J66">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>36</v>
+        <v>229</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>354</v>
+        <v>117</v>
       </c>
       <c r="E67" s="11">
         <v>46388</v>
       </c>
-      <c r="F67" s="14" t="s">
-        <v>349</v>
-      </c>
       <c r="G67" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I67" s="20">
         <v>0.4</v>
@@ -3369,707 +3276,708 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>305</v>
+      </c>
       <c r="E68" s="11">
         <v>46388</v>
       </c>
+      <c r="F68" s="14" t="s">
+        <v>301</v>
+      </c>
       <c r="G68" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I68" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J68">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>13</v>
+        <v>329</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="11">
         <v>46388</v>
       </c>
-      <c r="F69" s="14" t="s">
-        <v>349</v>
-      </c>
       <c r="G69" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I69" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" t="s">
-        <v>63</v>
-      </c>
+    <row r="70" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
       <c r="E70" s="11">
         <v>46388</v>
       </c>
+      <c r="F70" s="14" t="s">
+        <v>301</v>
+      </c>
       <c r="G70" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I70" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71" t="s">
+        <v>221</v>
+      </c>
+      <c r="C71" t="s">
         <v>37</v>
-      </c>
-      <c r="B71" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" t="s">
-        <v>67</v>
       </c>
       <c r="E71" s="11">
         <v>46388</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I71" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" t="s">
-        <v>4</v>
+        <v>14</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="C72" t="s">
-        <v>45</v>
-      </c>
-      <c r="D72" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E72" s="11">
         <v>46388</v>
       </c>
       <c r="G72" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I72" s="20">
         <v>1</v>
       </c>
-      <c r="J72">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" t="s">
-        <v>48</v>
-      </c>
-      <c r="E73" s="11">
-        <v>46388</v>
-      </c>
-      <c r="G73" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="H73" s="19" t="s">
-        <v>376</v>
-      </c>
-      <c r="I73" s="20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E73" s="11"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="20"/>
+    </row>
+    <row r="74" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" t="s">
-        <v>5</v>
+        <v>14</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="C74" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="D74" t="s">
+        <v>22</v>
       </c>
       <c r="E74" s="11">
         <v>46388</v>
       </c>
       <c r="G74" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I74" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J74">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" t="s">
-        <v>150</v>
+        <v>14</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="C75" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="E75" s="11">
         <v>46388</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I75" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" t="s">
-        <v>370</v>
+        <v>14</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="C76" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="E76" s="11">
         <v>46388</v>
       </c>
       <c r="G76" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I76" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>67</v>
       </c>
       <c r="E77" s="11">
         <v>46388</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I77" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>37</v>
-      </c>
-      <c r="B78" t="s">
-        <v>31</v>
+        <v>14</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="C78" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E78" s="11">
         <v>46388</v>
       </c>
       <c r="G78" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I78" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>37</v>
-      </c>
-      <c r="B79" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>328</v>
       </c>
       <c r="C79" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="E79" s="11">
         <v>46388</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I79" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>233</v>
       </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>19</v>
       </c>
       <c r="E80" s="11">
         <v>46388</v>
       </c>
-      <c r="F80" s="14" t="s">
-        <v>349</v>
-      </c>
       <c r="G80" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I80" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>37</v>
-      </c>
-      <c r="B81" t="s">
-        <v>12</v>
+        <v>14</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="C81" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E81" s="11">
         <v>46388</v>
       </c>
-      <c r="F81" s="14" t="s">
-        <v>349</v>
-      </c>
       <c r="G81" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H81" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I81" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>221</v>
       </c>
       <c r="C82" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="E82" s="11">
         <v>46388</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G82" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H82" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I82" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>225</v>
       </c>
       <c r="C83" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="E83" s="11">
         <v>46388</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="G83" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H83" s="19" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="I83" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>221</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
-      </c>
-      <c r="E84" s="12">
+        <v>104</v>
+      </c>
+      <c r="E84" s="11">
         <v>46388</v>
       </c>
+      <c r="F84" s="14" t="s">
+        <v>301</v>
+      </c>
       <c r="G84" s="18" t="s">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="H84" s="19" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="I84" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>6</v>
+        <v>234</v>
       </c>
       <c r="C85" t="s">
-        <v>140</v>
-      </c>
-      <c r="E85" s="12">
+        <v>105</v>
+      </c>
+      <c r="E85" s="11">
         <v>46388</v>
       </c>
+      <c r="F85" s="14" t="s">
+        <v>301</v>
+      </c>
       <c r="G85" s="18" t="s">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="H85" s="19" t="s">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="I85" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>39</v>
-      </c>
-      <c r="B86" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="C86" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="E86" s="12">
         <v>46388</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H86" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I86" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B87" t="s">
-        <v>5</v>
+        <v>221</v>
+      </c>
+      <c r="C87" t="s">
+        <v>114</v>
       </c>
       <c r="E87" s="12">
         <v>46388</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H87" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I87" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B88" t="s">
-        <v>150</v>
+        <v>225</v>
+      </c>
+      <c r="C88" t="s">
+        <v>41</v>
       </c>
       <c r="E88" s="12">
         <v>46388</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H88" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I88" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>39</v>
-      </c>
-      <c r="B89" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="E89" s="12">
         <v>46388</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H89" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I89" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>108</v>
+        <v>330</v>
       </c>
       <c r="E90" s="12">
         <v>46388</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H90" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I90" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>39</v>
-      </c>
-      <c r="B91" t="s">
-        <v>11</v>
-      </c>
-      <c r="C91" t="s">
-        <v>151</v>
+        <v>15</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="E91" s="12">
         <v>46388</v>
       </c>
-      <c r="F91" s="14" t="s">
-        <v>349</v>
-      </c>
       <c r="G91" s="18" t="s">
-        <v>166</v>
+        <v>308</v>
       </c>
       <c r="H91" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I91" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>39</v>
-      </c>
-      <c r="B92" t="s">
-        <v>11</v>
-      </c>
-      <c r="C92" t="s">
-        <v>152</v>
+        <v>15</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="E92" s="12">
         <v>46388</v>
       </c>
-      <c r="F92" s="14" t="s">
-        <v>349</v>
-      </c>
       <c r="G92" s="18" t="s">
-        <v>166</v>
+        <v>308</v>
       </c>
       <c r="H92" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I92" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B93" t="s">
-        <v>4</v>
+        <v>221</v>
       </c>
       <c r="C93" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E93" s="12">
-        <v>46631</v>
+        <v>46388</v>
+      </c>
+      <c r="F93" s="14" t="s">
+        <v>301</v>
       </c>
       <c r="G93" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I93" s="20">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B94" t="s">
-        <v>6</v>
+        <v>221</v>
       </c>
       <c r="C94" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="E94" s="12">
-        <v>46631</v>
+        <v>46388</v>
+      </c>
+      <c r="F94" s="14" t="s">
+        <v>301</v>
       </c>
       <c r="G94" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H94" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I94" s="20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>40</v>
-      </c>
-      <c r="B95" t="s">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="C95" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="E95" s="12">
         <v>46631</v>
       </c>
       <c r="G95" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H95" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I95" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>221</v>
       </c>
       <c r="C96" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E96" s="12">
         <v>46631</v>
       </c>
       <c r="G96" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H96" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I96" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B97" t="s">
-        <v>17</v>
+        <v>225</v>
       </c>
       <c r="C97" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E97" s="12">
         <v>46631</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H97" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I97" s="20">
         <v>0.4</v>
@@ -4077,602 +3985,642 @@
     </row>
     <row r="98" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>40</v>
-      </c>
-      <c r="B98" t="s">
-        <v>8</v>
+        <v>16</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="C98" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="E98" s="12">
         <v>46631</v>
       </c>
       <c r="G98" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H98" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I98" s="20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>40</v>
-      </c>
-      <c r="B99" t="s">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="C99" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="E99" s="12">
         <v>46631</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H99" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I99" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="C100" t="s">
-        <v>106</v>
-      </c>
-      <c r="E100" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="E100" s="12">
+        <v>46631</v>
+      </c>
       <c r="G100" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H100" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I100" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>40</v>
-      </c>
-      <c r="B101" t="s">
-        <v>41</v>
+        <v>16</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="C101" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E101" s="12">
         <v>46631</v>
       </c>
       <c r="G101" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H101" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I101" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B102" t="s">
-        <v>42</v>
+        <v>232</v>
       </c>
       <c r="C102" t="s">
-        <v>155</v>
-      </c>
-      <c r="E102" s="12">
-        <v>46631</v>
-      </c>
-      <c r="F102" s="14" t="s">
-        <v>349</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="E102" s="12"/>
       <c r="G102" s="18" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H102" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I102" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="B103" t="s">
-        <v>28</v>
+        <v>331</v>
       </c>
       <c r="C103" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="E103" s="12">
         <v>46631</v>
       </c>
       <c r="G103" s="18" t="s">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="H103" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I103" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="B104" t="s">
-        <v>6</v>
+        <v>221</v>
       </c>
       <c r="C104" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E104" s="12">
         <v>46631</v>
       </c>
+      <c r="F104" s="14" t="s">
+        <v>301</v>
+      </c>
       <c r="G104" s="18" t="s">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="H104" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I104" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>156</v>
-      </c>
-      <c r="B105" t="s">
-        <v>5</v>
+        <v>128</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="C105" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="E105" s="12">
         <v>46631</v>
       </c>
       <c r="G105" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H105" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I105" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="B106" t="s">
-        <v>10</v>
+        <v>221</v>
       </c>
       <c r="C106" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="E106" s="12">
         <v>46631</v>
       </c>
       <c r="G106" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H106" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I106" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>343</v>
-      </c>
-      <c r="B107" t="s">
-        <v>28</v>
+        <v>128</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C107" t="s">
+        <v>29</v>
       </c>
       <c r="E107" s="12">
-        <v>46296</v>
+        <v>46631</v>
       </c>
       <c r="G107" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H107" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I107" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>343</v>
-      </c>
-      <c r="B108" t="s">
-        <v>5</v>
+        <v>128</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C108" t="s">
+        <v>101</v>
       </c>
       <c r="E108" s="12">
-        <v>46296</v>
+        <v>46631</v>
       </c>
       <c r="G108" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H108" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I108" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>343</v>
-      </c>
-      <c r="B109" t="s">
-        <v>6</v>
+        <v>296</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="E109" s="12">
         <v>46296</v>
       </c>
       <c r="G109" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H109" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I109" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>343</v>
-      </c>
-      <c r="B110" t="s">
-        <v>7</v>
-      </c>
-      <c r="C110" t="s">
-        <v>154</v>
+        <v>296</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="E110" s="12">
         <v>46296</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H110" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I110" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>296</v>
+      </c>
+      <c r="B111" t="s">
+        <v>221</v>
+      </c>
+      <c r="E111" s="12">
+        <v>46296</v>
+      </c>
+      <c r="G111" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="H111" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="I111" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>296</v>
+      </c>
+      <c r="B112" t="s">
+        <v>225</v>
+      </c>
+      <c r="C112" t="s">
+        <v>126</v>
+      </c>
+      <c r="E112" s="12">
+        <v>46296</v>
+      </c>
+      <c r="G112" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="H112" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="I112" s="20">
         <v>0.7</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>343</v>
-      </c>
-      <c r="B111" t="s">
-        <v>8</v>
-      </c>
-      <c r="E111" s="12">
-        <v>46569</v>
-      </c>
-      <c r="G111" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="H111" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="I111" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>343</v>
-      </c>
-      <c r="B112" t="s">
-        <v>19</v>
-      </c>
-      <c r="E112" s="12">
-        <v>46569</v>
-      </c>
-      <c r="G112" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="H112" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="I112" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>343</v>
+        <v>296</v>
       </c>
       <c r="B113" t="s">
-        <v>17</v>
+        <v>230</v>
       </c>
       <c r="E113" s="12">
         <v>46569</v>
       </c>
       <c r="G113" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H113" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I113" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>343</v>
+        <v>296</v>
       </c>
       <c r="B114" t="s">
-        <v>26</v>
-      </c>
-      <c r="C114" t="s">
-        <v>126</v>
+        <v>331</v>
       </c>
       <c r="E114" s="12">
         <v>46569</v>
       </c>
       <c r="G114" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H114" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I114" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>343</v>
-      </c>
-      <c r="B115" t="s">
-        <v>344</v>
-      </c>
-      <c r="C115" t="s">
-        <v>345</v>
+        <v>296</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="E115" s="12">
         <v>46569</v>
       </c>
       <c r="G115" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H115" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I115" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>343</v>
-      </c>
-      <c r="B116" t="s">
-        <v>10</v>
+        <v>296</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C116" t="s">
+        <v>100</v>
       </c>
       <c r="E116" s="12">
         <v>46569</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H116" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I116" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>225</v>
       </c>
       <c r="C117" t="s">
-        <v>48</v>
+        <v>297</v>
       </c>
       <c r="E117" s="12">
         <v>46569</v>
       </c>
       <c r="G117" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="H117" t="s">
-        <v>374</v>
+        <v>308</v>
+      </c>
+      <c r="H117" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="I117" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>341</v>
-      </c>
-      <c r="B118" t="s">
-        <v>5</v>
-      </c>
-      <c r="C118" t="s">
-        <v>70</v>
+        <v>296</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="E118" s="12">
         <v>46569</v>
       </c>
       <c r="G118" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="H118" t="s">
-        <v>374</v>
+        <v>308</v>
+      </c>
+      <c r="H118" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="I118" s="20">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>341</v>
-      </c>
-      <c r="B119" t="s">
-        <v>6</v>
+        <v>294</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="C119" t="s">
-        <v>342</v>
+        <v>22</v>
       </c>
       <c r="E119" s="12">
         <v>46569</v>
       </c>
       <c r="G119" s="18" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H119" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I119" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>341</v>
-      </c>
-      <c r="B120" t="s">
-        <v>7</v>
+        <v>294</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="C120" t="s">
-        <v>342</v>
+        <v>44</v>
       </c>
       <c r="E120" s="12">
         <v>46569</v>
       </c>
-      <c r="F120" s="14"/>
       <c r="G120" s="18" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="H120" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I120" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>360</v>
+        <v>294</v>
       </c>
       <c r="B121" t="s">
-        <v>28</v>
+        <v>221</v>
+      </c>
+      <c r="C121" t="s">
+        <v>295</v>
       </c>
       <c r="E121" s="12">
-        <v>46388</v>
+        <v>46569</v>
       </c>
       <c r="G121" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="H121" s="19" t="s">
-        <v>374</v>
+        <v>190</v>
+      </c>
+      <c r="H121" t="s">
+        <v>322</v>
       </c>
       <c r="I121" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>360</v>
+        <v>294</v>
       </c>
       <c r="B122" t="s">
-        <v>5</v>
+        <v>225</v>
+      </c>
+      <c r="C122" t="s">
+        <v>295</v>
       </c>
       <c r="E122" s="12">
-        <v>46388</v>
-      </c>
+        <v>46569</v>
+      </c>
+      <c r="F122" s="14"/>
       <c r="G122" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="H122" s="19" t="s">
-        <v>374</v>
+        <v>190</v>
+      </c>
+      <c r="H122" t="s">
+        <v>322</v>
       </c>
       <c r="I122" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>360</v>
-      </c>
-      <c r="B123" t="s">
-        <v>6</v>
+        <v>309</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="E123" s="12">
         <v>46388</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I123" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>360</v>
-      </c>
-      <c r="B124" t="s">
-        <v>17</v>
+        <v>309</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="E124" s="12">
         <v>46388</v>
       </c>
       <c r="G124" s="18" t="s">
-        <v>359</v>
+        <v>308</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>374</v>
+        <v>322</v>
       </c>
       <c r="I124" s="20">
         <v>0.4</v>
       </c>
     </row>
+    <row r="125" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>309</v>
+      </c>
+      <c r="B125" t="s">
+        <v>221</v>
+      </c>
+      <c r="E125" s="12">
+        <v>46388</v>
+      </c>
+      <c r="G125" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="H125" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="I125" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>309</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E126" s="12">
+        <v>46388</v>
+      </c>
+      <c r="G126" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="H126" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="I126" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I124" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Erivan Vale de Souza &lt;erivan.souza@numenit.com&gt;"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4680,7 +4628,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -4696,27 +4643,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D2" s="3">
         <v>46113</v>
@@ -4725,15 +4672,15 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="D3" s="3">
         <v>46113</v>
@@ -4742,15 +4689,15 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3">
         <v>46114</v>
@@ -4759,15 +4706,15 @@
         <v>46114</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3">
         <v>46128</v>
@@ -4776,15 +4723,15 @@
         <v>46128</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>46122</v>
@@ -4793,15 +4740,15 @@
         <v>46122</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3">
         <v>46126</v>
@@ -4810,15 +4757,15 @@
         <v>46126</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="D8" s="3">
         <v>46129</v>
@@ -4827,15 +4774,15 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3">
         <v>46146</v>
@@ -4844,28 +4791,28 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="D11" s="3">
         <v>46153</v>
@@ -4874,15 +4821,15 @@
         <v>46157</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3">
         <v>46140</v>
@@ -4891,15 +4838,15 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D13" s="3">
         <v>46162</v>
@@ -4908,15 +4855,15 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3">
         <v>46163</v>
@@ -4925,12 +4872,12 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="3">
@@ -4940,15 +4887,15 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D16" s="3">
         <v>46160</v>
@@ -4957,15 +4904,15 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D17" s="3">
         <v>46140</v>
@@ -4974,15 +4921,15 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D18" s="3">
         <v>46150</v>
@@ -4991,15 +4938,15 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D19" s="3">
         <v>46150</v>
@@ -5008,15 +4955,15 @@
         <v>46150</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D20" s="3">
         <v>46147</v>
@@ -5025,15 +4972,15 @@
         <v>46147</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D21" s="3">
         <v>46149</v>
@@ -5042,15 +4989,15 @@
         <v>46149</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D22" s="3">
         <v>46181</v>
@@ -5059,15 +5006,15 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D23" s="3">
         <v>46170</v>
@@ -5076,15 +5023,15 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="D24" s="3">
         <v>46168</v>
@@ -5093,15 +5040,15 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="D25" s="3">
         <v>46167</v>
@@ -5110,15 +5057,15 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="D26" s="3">
         <v>46174</v>
@@ -5127,15 +5074,15 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="D27" s="3">
         <v>46175</v>
@@ -5144,15 +5091,15 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="D28" s="3">
         <v>46171</v>
@@ -5161,15 +5108,15 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="D29" s="3">
         <v>46170</v>
@@ -5178,15 +5125,15 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D30" s="3">
         <v>46181</v>
@@ -5195,15 +5142,15 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="D31" s="3">
         <v>46178</v>
@@ -5212,15 +5159,15 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D32" s="3">
         <v>46170</v>
@@ -5229,15 +5176,15 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D33" s="3">
         <v>46181</v>
@@ -5246,28 +5193,28 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D35" s="3">
         <v>46155</v>
@@ -5276,15 +5223,15 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="D36" s="3">
         <v>46167</v>
@@ -5293,15 +5240,15 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D37" s="3">
         <v>46167</v>
@@ -5310,15 +5257,15 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="D38" s="3">
         <v>46168</v>
@@ -5327,15 +5274,15 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D39" s="3">
         <v>46175</v>
@@ -5344,15 +5291,15 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D40" s="3">
         <v>46188</v>
@@ -5361,15 +5308,15 @@
         <v>46192</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D41" s="3">
         <v>46195</v>
@@ -5378,15 +5325,15 @@
         <v>46199</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D42" s="3">
         <v>46202</v>
@@ -5395,12 +5342,12 @@
         <v>46206</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="3">
@@ -5410,12 +5357,12 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="3">
@@ -5425,15 +5372,15 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D45" s="3">
         <v>46223</v>
@@ -5442,15 +5389,15 @@
         <v>46223</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D46" s="3">
         <v>46223</v>
@@ -5459,12 +5406,12 @@
         <v>46227</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="3">
@@ -5474,15 +5421,15 @@
         <v>46223</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D48" s="3">
         <v>46230</v>
@@ -5491,15 +5438,15 @@
         <v>46230</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="D49" s="3">
         <v>46232</v>
@@ -5508,15 +5455,15 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="D50" s="3">
         <v>46230</v>
@@ -5525,15 +5472,15 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D51" s="3">
         <v>46161</v>
@@ -5542,15 +5489,15 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="D52" s="3">
         <v>46162</v>
@@ -5559,15 +5506,15 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="D53" s="3">
         <v>46162</v>
@@ -5576,15 +5523,15 @@
         <v>46162</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="D54" s="3">
         <v>46163</v>
@@ -5595,13 +5542,13 @@
     </row>
     <row r="55" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D55" s="3">
         <v>46174</v>
@@ -5612,13 +5559,13 @@
     </row>
     <row r="56" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D56" s="3">
         <v>46174</v>
@@ -5627,15 +5574,15 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="D57" s="3">
         <v>46174</v>
@@ -5644,15 +5591,15 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="D58" s="3">
         <v>46181</v>
@@ -5661,15 +5608,15 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="D59" s="3">
         <v>46181</v>
@@ -5678,15 +5625,15 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="D60" s="3">
         <v>46181</v>
@@ -5695,15 +5642,15 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="D61" s="3">
         <v>46181</v>
@@ -5712,15 +5659,15 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D62" s="3">
         <v>46182</v>
@@ -5729,15 +5676,15 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D63" s="3">
         <v>46184</v>
@@ -5746,15 +5693,15 @@
         <v>46185</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D64" s="3">
         <v>46188</v>
@@ -5763,15 +5710,15 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D65" s="3">
         <v>46188</v>
@@ -5780,15 +5727,15 @@
         <v>46192</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D66" s="3">
         <v>46198</v>
@@ -6120,13 +6067,6 @@
       <c r="E112" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E66" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Erivan Vale de Souza &lt;erivan.souza@numenit.com&gt;"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6152,30 +6092,30 @@
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E2" s="6">
         <v>46174</v>
@@ -6189,16 +6129,16 @@
     </row>
     <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E3" s="6">
         <v>46175</v>
@@ -6212,16 +6152,16 @@
     </row>
     <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E4" s="6">
         <v>46177</v>
@@ -6235,16 +6175,16 @@
     </row>
     <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E5" s="6">
         <v>46178</v>
@@ -6258,16 +6198,16 @@
     </row>
     <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="E6" s="6">
         <v>46167</v>
@@ -6281,16 +6221,16 @@
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="E7" s="6">
         <v>46168</v>
@@ -6304,16 +6244,16 @@
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="E8" s="6">
         <v>46169</v>
@@ -6327,16 +6267,16 @@
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="E9" s="6">
         <v>46170</v>
@@ -6350,16 +6290,16 @@
     </row>
     <row r="10" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="E10" s="6">
         <v>46171</v>
@@ -6373,16 +6313,16 @@
     </row>
     <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="E11" s="6">
         <v>46167</v>
@@ -6396,16 +6336,16 @@
     </row>
     <row r="12" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="E12" s="6">
         <v>46168</v>
@@ -6419,16 +6359,16 @@
     </row>
     <row r="13" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="E13" s="6">
         <v>46169</v>
@@ -6442,16 +6382,16 @@
     </row>
     <row r="14" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="E14" s="6">
         <v>46170</v>
@@ -6465,16 +6405,16 @@
     </row>
     <row r="15" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="E15" s="6">
         <v>46171</v>
@@ -6488,16 +6428,16 @@
     </row>
     <row r="16" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="E16" s="6">
         <v>46167</v>
@@ -6511,16 +6451,16 @@
     </row>
     <row r="17" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="E17" s="6">
         <v>46168</v>
@@ -6534,16 +6474,16 @@
     </row>
     <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="E18" s="6">
         <v>46169</v>
@@ -6557,16 +6497,16 @@
     </row>
     <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="E19" s="6">
         <v>46169</v>
@@ -6580,16 +6520,16 @@
     </row>
     <row r="20" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E20" s="6">
         <v>46170</v>
@@ -6603,16 +6543,16 @@
     </row>
     <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E21" s="6">
         <v>46170</v>
@@ -6626,16 +6566,16 @@
     </row>
     <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="E22" s="6">
         <v>46160</v>
@@ -6649,16 +6589,16 @@
     </row>
     <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="E23" s="6">
         <v>46161</v>
@@ -6672,16 +6612,16 @@
     </row>
     <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="E24" s="6">
         <v>46162</v>
@@ -6695,16 +6635,16 @@
     </row>
     <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="E25" s="6">
         <v>46163</v>
@@ -6718,16 +6658,16 @@
     </row>
     <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="E26" s="6">
         <v>46164</v>
@@ -6741,16 +6681,16 @@
     </row>
     <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="E27" s="6">
         <v>46160</v>
@@ -6764,16 +6704,16 @@
     </row>
     <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B28" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="E28" s="6">
         <v>46161</v>
@@ -6787,16 +6727,16 @@
     </row>
     <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="E29" s="6">
         <v>46162</v>
@@ -6810,16 +6750,16 @@
     </row>
     <row r="30" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="E30" s="6">
         <v>46163</v>
@@ -6833,16 +6773,16 @@
     </row>
     <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="E31" s="6">
         <v>46164</v>
@@ -6856,16 +6796,16 @@
     </row>
     <row r="32" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E32" s="6">
         <v>46160</v>
@@ -6879,16 +6819,16 @@
     </row>
     <row r="33" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E33" s="6">
         <v>46161</v>
@@ -6902,16 +6842,16 @@
     </row>
     <row r="34" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E34" s="6">
         <v>46162</v>
@@ -6925,16 +6865,16 @@
     </row>
     <row r="35" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="E35" s="6">
         <v>46163</v>
@@ -6948,16 +6888,16 @@
     </row>
     <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E36" s="6">
         <v>46163</v>
@@ -6971,16 +6911,16 @@
     </row>
     <row r="37" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="E37" s="6">
         <v>46164</v>
@@ -6994,16 +6934,16 @@
     </row>
     <row r="38" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E38" s="6">
         <v>46160</v>
@@ -7017,16 +6957,16 @@
     </row>
     <row r="39" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E39" s="6">
         <v>46161</v>
@@ -7040,16 +6980,16 @@
     </row>
     <row r="40" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E40" s="6">
         <v>46162</v>
@@ -7063,16 +7003,16 @@
     </row>
     <row r="41" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E41" s="6">
         <v>46163</v>
@@ -7086,16 +7026,16 @@
     </row>
     <row r="42" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E42" s="6">
         <v>46164</v>
@@ -7109,16 +7049,16 @@
     </row>
     <row r="43" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="E43" s="6">
         <v>46153</v>
@@ -7132,16 +7072,16 @@
     </row>
     <row r="44" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="E44" s="6">
         <v>46154</v>
@@ -7155,16 +7095,16 @@
     </row>
     <row r="45" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="E45" s="6">
         <v>46155</v>
@@ -7178,16 +7118,16 @@
     </row>
     <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="E46" s="6">
         <v>46156</v>
@@ -7201,16 +7141,16 @@
     </row>
     <row r="47" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>189</v>
+        <v>161</v>
       </c>
       <c r="E47" s="6">
         <v>46157</v>
@@ -7224,16 +7164,16 @@
     </row>
     <row r="48" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E48" s="6">
         <v>46153</v>
@@ -7247,16 +7187,16 @@
     </row>
     <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E49" s="6">
         <v>46154</v>
@@ -7270,16 +7210,16 @@
     </row>
     <row r="50" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E50" s="6">
         <v>46155</v>
@@ -7293,16 +7233,16 @@
     </row>
     <row r="51" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E51" s="6">
         <v>46156</v>
@@ -7316,16 +7256,16 @@
     </row>
     <row r="52" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E52" s="6">
         <v>46157</v>
@@ -7339,16 +7279,16 @@
     </row>
     <row r="53" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E53" s="6">
         <v>46153</v>
@@ -7362,16 +7302,16 @@
     </row>
     <row r="54" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E54" s="6">
         <v>46154</v>
@@ -7385,16 +7325,16 @@
     </row>
     <row r="55" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E55" s="6">
         <v>46155</v>
@@ -7408,16 +7348,16 @@
     </row>
     <row r="56" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E56" s="6">
         <v>46156</v>
@@ -7431,16 +7371,16 @@
     </row>
     <row r="57" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="E57" s="6">
         <v>46157</v>
@@ -7454,16 +7394,16 @@
     </row>
     <row r="58" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="E58" s="6">
         <v>46153</v>
@@ -7477,16 +7417,16 @@
     </row>
     <row r="59" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="E59" s="6">
         <v>46153</v>
@@ -7500,16 +7440,16 @@
     </row>
     <row r="60" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="E60" s="6">
         <v>46154</v>
@@ -7523,16 +7463,16 @@
     </row>
     <row r="61" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="E61" s="6">
         <v>46154</v>
@@ -7546,16 +7486,16 @@
     </row>
     <row r="62" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="E62" s="6">
         <v>46155</v>
@@ -7569,16 +7509,16 @@
     </row>
     <row r="63" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="E63" s="6">
         <v>46155</v>
@@ -7592,16 +7532,16 @@
     </row>
     <row r="64" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="E64" s="6">
         <v>46156</v>
@@ -7615,16 +7555,16 @@
     </row>
     <row r="65" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="E65" s="6">
         <v>46156</v>
@@ -7638,16 +7578,16 @@
     </row>
     <row r="66" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="E66" s="6">
         <v>46157</v>
@@ -7661,16 +7601,16 @@
     </row>
     <row r="67" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="E67" s="6">
         <v>46157</v>
@@ -7684,16 +7624,16 @@
     </row>
     <row r="68" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E68" s="6">
         <v>46153</v>
@@ -7707,16 +7647,16 @@
     </row>
     <row r="69" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>202</v>
+        <v>174</v>
       </c>
       <c r="E69" s="6">
         <v>46154</v>
@@ -7730,16 +7670,16 @@
     </row>
     <row r="70" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E70" s="6">
         <v>46155</v>
@@ -7753,16 +7693,16 @@
     </row>
     <row r="71" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E71" s="6">
         <v>46155</v>
@@ -7776,16 +7716,16 @@
     </row>
     <row r="72" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
       <c r="E72" s="6">
         <v>46155</v>
@@ -7799,16 +7739,16 @@
     </row>
     <row r="73" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E73" s="6">
         <v>46155</v>
@@ -7822,16 +7762,16 @@
     </row>
     <row r="74" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E74" s="6">
         <v>46156</v>
@@ -7845,16 +7785,16 @@
     </row>
     <row r="75" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E75" s="6">
         <v>46157</v>
@@ -7868,16 +7808,16 @@
     </row>
     <row r="76" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="E76" s="6">
         <v>46153</v>
@@ -7891,16 +7831,16 @@
     </row>
     <row r="77" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E77" s="6">
         <v>46154</v>
@@ -7914,16 +7854,16 @@
     </row>
     <row r="78" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E78" s="6">
         <v>46155</v>
@@ -7937,16 +7877,16 @@
     </row>
     <row r="79" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E79" s="6">
         <v>46156</v>
@@ -7960,16 +7900,16 @@
     </row>
     <row r="80" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E80" s="6">
         <v>46157</v>
@@ -7983,16 +7923,16 @@
     </row>
     <row r="81" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="E81" s="6">
         <v>46153</v>
@@ -8006,16 +7946,16 @@
     </row>
     <row r="82" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="E82" s="6">
         <v>46154</v>
@@ -8029,16 +7969,16 @@
     </row>
     <row r="83" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="E83" s="6">
         <v>46155</v>
@@ -8052,16 +7992,16 @@
     </row>
     <row r="84" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="E84" s="6">
         <v>46156</v>
@@ -8075,16 +8015,16 @@
     </row>
     <row r="85" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="E85" s="6">
         <v>46157</v>
@@ -8098,16 +8038,16 @@
     </row>
     <row r="86" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E86" s="6">
         <v>46146</v>
@@ -8121,16 +8061,16 @@
     </row>
     <row r="87" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E87" s="6">
         <v>46147</v>
@@ -8144,16 +8084,16 @@
     </row>
     <row r="88" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E88" s="6">
         <v>46148</v>
@@ -8167,16 +8107,16 @@
     </row>
     <row r="89" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E89" s="6">
         <v>46149</v>
@@ -8190,16 +8130,16 @@
     </row>
     <row r="90" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E90" s="6">
         <v>46150</v>
@@ -8213,16 +8153,16 @@
     </row>
     <row r="91" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="E91" s="6">
         <v>46146</v>
@@ -8236,16 +8176,16 @@
     </row>
     <row r="92" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="E92" s="6">
         <v>46146</v>
@@ -8259,16 +8199,16 @@
     </row>
     <row r="93" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="E93" s="6">
         <v>46147</v>
@@ -8282,16 +8222,16 @@
     </row>
     <row r="94" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="E94" s="6">
         <v>46147</v>
@@ -8305,16 +8245,16 @@
     </row>
     <row r="95" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="E95" s="6">
         <v>46148</v>
@@ -8328,16 +8268,16 @@
     </row>
     <row r="96" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="E96" s="6">
         <v>46149</v>
@@ -8351,16 +8291,16 @@
     </row>
     <row r="97" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="E97" s="6">
         <v>46149</v>
@@ -8374,16 +8314,16 @@
     </row>
     <row r="98" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E98" s="6">
         <v>46150</v>
@@ -8397,16 +8337,16 @@
     </row>
     <row r="99" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="E99" s="6">
         <v>46146</v>
@@ -8420,16 +8360,16 @@
     </row>
     <row r="100" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="E100" s="6">
         <v>46147</v>
@@ -8443,16 +8383,16 @@
     </row>
     <row r="101" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="E101" s="6">
         <v>46148</v>
@@ -8466,16 +8406,16 @@
     </row>
     <row r="102" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="E102" s="6">
         <v>46149</v>
@@ -8489,16 +8429,16 @@
     </row>
     <row r="103" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="E103" s="6">
         <v>46150</v>
@@ -8512,16 +8452,16 @@
     </row>
     <row r="104" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E104" s="6">
         <v>46146</v>
@@ -8535,16 +8475,16 @@
     </row>
     <row r="105" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E105" s="6">
         <v>46147</v>
@@ -8558,16 +8498,16 @@
     </row>
     <row r="106" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E106" s="6">
         <v>46148</v>
@@ -8581,16 +8521,16 @@
     </row>
     <row r="107" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E107" s="6">
         <v>46149</v>
@@ -8604,16 +8544,16 @@
     </row>
     <row r="108" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="E108" s="6">
         <v>46150</v>
@@ -8627,16 +8567,16 @@
     </row>
     <row r="109" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E109" s="6">
         <v>46146</v>
@@ -8650,16 +8590,16 @@
     </row>
     <row r="110" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E110" s="6">
         <v>46147</v>
@@ -8673,16 +8613,16 @@
     </row>
     <row r="111" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E111" s="6">
         <v>46148</v>
@@ -8696,16 +8636,16 @@
     </row>
     <row r="112" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E112" s="6">
         <v>46149</v>
@@ -8719,16 +8659,16 @@
     </row>
     <row r="113" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="E113" s="6">
         <v>46150</v>
@@ -8742,16 +8682,16 @@
     </row>
     <row r="114" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="E114" s="6">
         <v>46146</v>
@@ -8765,16 +8705,16 @@
     </row>
     <row r="115" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="E115" s="6">
         <v>46147</v>
@@ -8788,16 +8728,16 @@
     </row>
     <row r="116" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E116" s="6">
         <v>46148</v>
@@ -8811,16 +8751,16 @@
     </row>
     <row r="117" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E117" s="6">
         <v>46149</v>
@@ -8834,16 +8774,16 @@
     </row>
     <row r="118" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>316</v>
+        <v>288</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="E118" s="6">
         <v>46150</v>
@@ -8857,16 +8797,16 @@
     </row>
     <row r="119" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>361</v>
+        <v>310</v>
       </c>
       <c r="E119" s="6">
         <v>46181</v>
@@ -8881,16 +8821,16 @@
     </row>
     <row r="120" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>361</v>
+        <v>310</v>
       </c>
       <c r="E120" s="6">
         <v>46182</v>
@@ -8905,16 +8845,16 @@
     </row>
     <row r="121" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="E121" s="6">
         <v>46183</v>
@@ -8929,16 +8869,16 @@
     </row>
     <row r="122" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>363</v>
+        <v>312</v>
       </c>
       <c r="E122" s="6">
         <v>46184</v>
@@ -8953,16 +8893,16 @@
     </row>
     <row r="123" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>364</v>
+        <v>313</v>
       </c>
       <c r="E123" s="6">
         <v>46185</v>
@@ -8977,16 +8917,16 @@
     </row>
     <row r="124" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="E124" s="6">
         <v>46181</v>
@@ -9001,16 +8941,16 @@
     </row>
     <row r="125" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="E125" s="6">
         <v>46182</v>
@@ -9025,16 +8965,16 @@
     </row>
     <row r="126" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="E126" s="6">
         <v>46183</v>
@@ -9049,16 +8989,16 @@
     </row>
     <row r="127" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>186</v>
+        <v>158</v>
       </c>
       <c r="E127" s="6">
         <v>46184</v>
@@ -9073,16 +9013,16 @@
     </row>
     <row r="128" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>365</v>
+        <v>314</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="E128" s="6">
         <v>46188</v>
@@ -9097,16 +9037,16 @@
     </row>
     <row r="129" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>365</v>
+        <v>314</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="E129" s="6">
         <v>46189</v>
@@ -9121,16 +9061,16 @@
     </row>
     <row r="130" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>365</v>
+        <v>314</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="E130" s="6">
         <v>46190</v>
@@ -9145,16 +9085,16 @@
     </row>
     <row r="131" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>365</v>
+        <v>314</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="E131" s="6">
         <v>46191</v>
@@ -9169,16 +9109,16 @@
     </row>
     <row r="132" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>365</v>
+        <v>314</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>369</v>
+        <v>318</v>
       </c>
       <c r="E132" s="6">
         <v>46192</v>
@@ -9204,762 +9144,762 @@
   <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="30.33203125" customWidth="1"/>
     <col min="4" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" t="s">
-        <v>347</v>
+      <c r="A1" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>299</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>261</v>
+        <v>233</v>
       </c>
       <c r="R1" s="16" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>223</v>
+        <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="C6" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C8" t="s">
+        <v>241</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>227</v>
-      </c>
-      <c r="C8" t="s">
-        <v>269</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="C11" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>203</v>
       </c>
       <c r="C12" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="C15" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="C16" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>235</v>
+        <v>207</v>
       </c>
       <c r="C17" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="C18" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="C19" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="C20" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="P20" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>238</v>
+        <v>210</v>
       </c>
       <c r="C21" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M21" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="C22" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="N22" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="C23" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="B26" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C26" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B27" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C27" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="B28" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C28" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B29" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C29" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="B30" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C30" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B31" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C31" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C32" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="B33" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C33" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="B34" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C34" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C35" t="s">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C36" t="s">
-        <v>299</v>
+        <v>271</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C37" t="s">
-        <v>300</v>
+        <v>272</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="B38" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C38" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C39" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C40" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C41" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C42" t="s">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C43" t="s">
-        <v>306</v>
+        <v>278</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="C44" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>244</v>
+        <v>216</v>
       </c>
       <c r="C45" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="K45" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="C46" t="s">
-        <v>309</v>
+        <v>281</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="C47" t="s">
-        <v>310</v>
+        <v>282</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="C48" t="s">
-        <v>311</v>
+        <v>283</v>
       </c>
       <c r="K48" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="O48" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>312</v>
+        <v>284</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>314</v>
+        <v>286</v>
       </c>
       <c r="C51" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="C52" t="s">
-        <v>337</v>
+        <v>291</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>338</v>
+        <v>292</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="C54" t="s">
-        <v>339</v>
+        <v>293</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -9981,7 +9921,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
@@ -9991,7 +9931,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>371</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
@@ -10001,12 +9941,12 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>372</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12984361-189C-A147-88EA-6F11D577DF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0C79BC-F589-BB4D-8BCB-E32B04C6DCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$I$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Agenda Workshop'!$A$1:$E$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$Q$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$P$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="353">
   <si>
     <t>Projeto</t>
   </si>
@@ -1599,6 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1646,7 +1647,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1670,7 +1671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1694,7 +1695,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1718,7 +1719,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1742,7 +1743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1766,7 +1767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1790,7 +1791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1828,9 +1829,7 @@
       <c r="E9" s="11">
         <v>46388</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>301</v>
-      </c>
+      <c r="F9" s="14"/>
       <c r="G9" t="s">
         <v>190</v>
       </c>
@@ -1922,7 +1921,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1951,7 +1950,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1980,7 +1979,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -2004,7 +2003,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2028,7 +2027,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -2052,7 +2051,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -2076,7 +2075,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -2100,7 +2099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -2124,7 +2123,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -2148,7 +2147,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -2172,7 +2171,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -2223,7 +2222,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -2247,7 +2246,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>8</v>
       </c>
@@ -2271,7 +2270,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
@@ -2295,7 +2294,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -2306,7 +2305,9 @@
         <v>19</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="11"/>
+      <c r="E28" s="11">
+        <v>46388</v>
+      </c>
       <c r="G28" t="s">
         <v>138</v>
       </c>
@@ -2317,7 +2318,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -2339,7 +2340,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>10</v>
       </c>
@@ -2363,7 +2364,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -2385,7 +2386,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -2409,7 +2410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
@@ -2433,7 +2434,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -2457,7 +2458,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
@@ -2535,7 +2536,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
@@ -2546,11 +2547,13 @@
         <v>22</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="11"/>
+      <c r="E38" s="11">
+        <v>46388</v>
+      </c>
       <c r="F38" s="21"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
@@ -2574,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -2596,7 +2599,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -2620,7 +2623,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
@@ -2644,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
@@ -2695,7 +2698,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -2719,7 +2722,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>12</v>
       </c>
@@ -2743,7 +2746,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
@@ -2765,7 +2768,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>12</v>
       </c>
@@ -2789,7 +2792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -2813,7 +2816,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>12</v>
       </c>
@@ -2837,7 +2840,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>12</v>
       </c>
@@ -2861,7 +2864,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
@@ -2885,7 +2888,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>12</v>
       </c>
@@ -2907,7 +2910,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
@@ -2936,7 +2939,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -3038,7 +3041,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>13</v>
       </c>
@@ -3067,7 +3070,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>13</v>
       </c>
@@ -3091,7 +3094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>13</v>
       </c>
@@ -3115,7 +3118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>13</v>
       </c>
@@ -3247,7 +3250,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>13</v>
       </c>
@@ -3308,7 +3311,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>13</v>
       </c>
@@ -3355,7 +3358,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -3378,7 +3381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -3401,7 +3404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -3411,12 +3414,14 @@
       <c r="C73" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E73" s="11"/>
+      <c r="E73" s="11">
+        <v>46388</v>
+      </c>
       <c r="G73" s="18"/>
       <c r="H73" s="19"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -3445,7 +3450,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -3468,7 +3473,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -3491,7 +3496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -3514,7 +3519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -3537,7 +3542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>14</v>
       </c>
@@ -3560,7 +3565,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -3583,7 +3588,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -3710,7 +3715,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -3733,7 +3738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -3756,7 +3761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -3779,7 +3784,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -3799,7 +3804,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -3819,7 +3824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -3839,7 +3844,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -3914,7 +3919,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -3937,7 +3942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -3960,7 +3965,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -3983,7 +3988,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -4006,7 +4011,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -4029,7 +4034,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -4052,7 +4057,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -4075,7 +4080,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -4085,7 +4090,9 @@
       <c r="C102" t="s">
         <v>80</v>
       </c>
-      <c r="E102" s="12"/>
+      <c r="E102" s="12">
+        <v>46631</v>
+      </c>
       <c r="G102" s="18" t="s">
         <v>138</v>
       </c>
@@ -4096,7 +4103,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -4145,7 +4152,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>128</v>
       </c>
@@ -4168,7 +4175,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>128</v>
       </c>
@@ -4191,7 +4198,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>128</v>
       </c>
@@ -4214,7 +4221,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>128</v>
       </c>
@@ -4237,7 +4244,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>296</v>
       </c>
@@ -4257,7 +4264,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>296</v>
       </c>
@@ -4277,7 +4284,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>296</v>
       </c>
@@ -4297,7 +4304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>296</v>
       </c>
@@ -4320,7 +4327,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>296</v>
       </c>
@@ -4340,7 +4347,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>296</v>
       </c>
@@ -4360,7 +4367,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>296</v>
       </c>
@@ -4380,7 +4387,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>296</v>
       </c>
@@ -4403,7 +4410,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>296</v>
       </c>
@@ -4426,7 +4433,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>296</v>
       </c>
@@ -4446,7 +4453,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>294</v>
       </c>
@@ -4469,7 +4476,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>294</v>
       </c>
@@ -4492,7 +4499,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>294</v>
       </c>
@@ -4515,7 +4522,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>294</v>
       </c>
@@ -4539,7 +4546,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>309</v>
       </c>
@@ -4559,7 +4566,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>309</v>
       </c>
@@ -4579,7 +4586,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>309</v>
       </c>
@@ -4599,7 +4606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>309</v>
       </c>
@@ -4620,7 +4627,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I126" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="5">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6067,6 +6080,7 @@
       <c r="E112" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E66" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9141,7 +9155,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19289A2C-A77A-0743-A158-A32EED5567A2}">
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
@@ -9149,7 +9163,7 @@
     <col min="4" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>17</v>
       </c>
@@ -9196,13 +9210,10 @@
         <v>232</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="R1" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>193</v>
       </c>
@@ -9213,7 +9224,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>194</v>
       </c>
@@ -9224,7 +9235,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>195</v>
       </c>
@@ -9235,7 +9246,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>196</v>
       </c>
@@ -9249,7 +9260,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -9263,7 +9274,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>198</v>
       </c>
@@ -9277,7 +9288,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>199</v>
       </c>
@@ -9288,7 +9299,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>200</v>
       </c>
@@ -9299,7 +9310,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>201</v>
       </c>
@@ -9316,7 +9327,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>202</v>
       </c>
@@ -9329,14 +9340,11 @@
       <c r="N11" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="Q11" s="9" t="s">
+      <c r="Q11" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="R11" s="13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>203</v>
       </c>
@@ -9350,7 +9358,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>204</v>
       </c>
@@ -9364,7 +9372,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>205</v>
       </c>
@@ -9375,7 +9383,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>248</v>
       </c>
@@ -9389,7 +9397,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>206</v>
       </c>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C0C79BC-F589-BB4D-8BCB-E32B04C6DCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3962343E-3352-CA4C-9489-8FA7F994DED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Cookpit" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="353">
   <si>
     <t>Projeto</t>
   </si>
@@ -743,9 +743,6 @@
     <t>QM</t>
   </si>
   <si>
-    <t>RE</t>
-  </si>
-  <si>
     <t>FI</t>
   </si>
   <si>
@@ -1101,6 +1098,9 @@
   </si>
   <si>
     <t>Vinicius Diniz Cabral</t>
+  </si>
+  <si>
+    <t>xx</t>
   </si>
 </sst>
 </file>
@@ -1623,28 +1623,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="G1" s="17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I1" s="17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J1" s="17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1652,7 +1652,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>27</v>
@@ -1665,7 +1665,7 @@
         <v>190</v>
       </c>
       <c r="H2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I2" s="20">
         <v>1</v>
@@ -1676,7 +1676,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -1689,7 +1689,7 @@
         <v>190</v>
       </c>
       <c r="H3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I3" s="20">
         <v>0.4</v>
@@ -1713,7 +1713,7 @@
         <v>190</v>
       </c>
       <c r="H4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I4" s="20">
         <v>0.7</v>
@@ -1737,7 +1737,7 @@
         <v>190</v>
       </c>
       <c r="H5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I5" s="20">
         <v>1</v>
@@ -1761,7 +1761,7 @@
         <v>190</v>
       </c>
       <c r="H6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I6" s="20">
         <v>1</v>
@@ -1785,7 +1785,7 @@
         <v>190</v>
       </c>
       <c r="H7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I7" s="20">
         <v>1</v>
@@ -1796,7 +1796,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>38</v>
@@ -1809,18 +1809,18 @@
         <v>190</v>
       </c>
       <c r="H8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I8" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>106</v>
@@ -1834,13 +1834,13 @@
         <v>190</v>
       </c>
       <c r="H9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I9" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1855,19 +1855,19 @@
         <v>46388</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G10" t="s">
         <v>190</v>
       </c>
       <c r="H10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I10" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1882,40 +1882,40 @@
         <v>46388</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G11" t="s">
         <v>190</v>
       </c>
       <c r="H11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I11" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="11">
         <v>46388</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G12" t="s">
         <v>190</v>
       </c>
       <c r="H12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I12" s="20">
         <v>0.4</v>
@@ -1941,7 +1941,7 @@
         <v>190</v>
       </c>
       <c r="H13" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I13" s="20">
         <v>0.4</v>
@@ -1955,7 +1955,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>41</v>
@@ -1970,7 +1970,7 @@
         <v>190</v>
       </c>
       <c r="H14" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I14" s="20">
         <v>0.4</v>
@@ -1984,7 +1984,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>40</v>
@@ -1997,7 +1997,7 @@
         <v>190</v>
       </c>
       <c r="H15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I15" s="20">
         <v>0.7</v>
@@ -2008,7 +2008,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>19</v>
@@ -2021,7 +2021,7 @@
         <v>190</v>
       </c>
       <c r="H16" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I16" s="20">
         <v>0.4</v>
@@ -2045,7 +2045,7 @@
         <v>190</v>
       </c>
       <c r="H17" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I17" s="20">
         <v>0.4</v>
@@ -2069,7 +2069,7 @@
         <v>190</v>
       </c>
       <c r="H18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I18" s="20">
         <v>0.4</v>
@@ -2093,7 +2093,7 @@
         <v>190</v>
       </c>
       <c r="H19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I19" s="20">
         <v>1</v>
@@ -2117,7 +2117,7 @@
         <v>190</v>
       </c>
       <c r="H20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I20" s="20">
         <v>0.7</v>
@@ -2128,7 +2128,7 @@
         <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>44</v>
@@ -2141,7 +2141,7 @@
         <v>190</v>
       </c>
       <c r="H21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I21" s="20">
         <v>0.7</v>
@@ -2152,7 +2152,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>89</v>
@@ -2165,10 +2165,10 @@
         <v>190</v>
       </c>
       <c r="H22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I22" s="20">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2176,7 +2176,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>101</v>
@@ -2189,18 +2189,18 @@
         <v>190</v>
       </c>
       <c r="H23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I23" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>109</v>
@@ -2210,13 +2210,13 @@
         <v>46296</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G24" t="s">
         <v>190</v>
       </c>
       <c r="H24" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I24" s="20">
         <v>0.4</v>
@@ -2240,7 +2240,7 @@
         <v>190</v>
       </c>
       <c r="H25" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I25" s="20">
         <v>0.4</v>
@@ -2264,7 +2264,7 @@
         <v>190</v>
       </c>
       <c r="H26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I26" s="20">
         <v>0.4</v>
@@ -2275,7 +2275,7 @@
         <v>10</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>40</v>
@@ -2288,7 +2288,7 @@
         <v>138</v>
       </c>
       <c r="H27" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I27" s="20">
         <v>0.7</v>
@@ -2299,7 +2299,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>19</v>
@@ -2312,7 +2312,7 @@
         <v>138</v>
       </c>
       <c r="H28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I28" s="20">
         <v>0.4</v>
@@ -2323,7 +2323,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -2334,7 +2334,7 @@
         <v>138</v>
       </c>
       <c r="H29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I29" s="20">
         <v>0.4</v>
@@ -2345,7 +2345,7 @@
         <v>10</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>22</v>
@@ -2358,7 +2358,7 @@
         <v>138</v>
       </c>
       <c r="H30" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I30" s="20">
         <v>0.7</v>
@@ -2380,7 +2380,7 @@
         <v>138</v>
       </c>
       <c r="H31" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I31" s="20">
         <v>0.4</v>
@@ -2404,7 +2404,7 @@
         <v>138</v>
       </c>
       <c r="H32" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I32" s="20">
         <v>1</v>
@@ -2428,7 +2428,7 @@
         <v>138</v>
       </c>
       <c r="H33" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I33" s="20">
         <v>0.4</v>
@@ -2439,7 +2439,7 @@
         <v>10</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>106</v>
@@ -2452,18 +2452,18 @@
         <v>138</v>
       </c>
       <c r="H34" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I34" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>100</v>
@@ -2476,13 +2476,13 @@
         <v>138</v>
       </c>
       <c r="H35" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I35" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
@@ -2497,24 +2497,24 @@
         <v>46388</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G36" t="s">
         <v>138</v>
       </c>
       <c r="H36" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I36" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>112</v>
@@ -2524,13 +2524,13 @@
         <v>46388</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G37" t="s">
         <v>138</v>
       </c>
       <c r="H37" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I37" s="20">
         <v>0.4</v>
@@ -2558,7 +2558,7 @@
         <v>11</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>56</v>
@@ -2571,7 +2571,7 @@
         <v>138</v>
       </c>
       <c r="H39" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I39" s="20">
         <v>1</v>
@@ -2593,7 +2593,7 @@
         <v>138</v>
       </c>
       <c r="H40" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I40" s="20">
         <v>0.4</v>
@@ -2617,7 +2617,7 @@
         <v>138</v>
       </c>
       <c r="H41" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I41" s="20">
         <v>0.4</v>
@@ -2641,7 +2641,7 @@
         <v>138</v>
       </c>
       <c r="H42" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I42" s="20">
         <v>1</v>
@@ -2652,7 +2652,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>115</v>
@@ -2665,13 +2665,13 @@
         <v>138</v>
       </c>
       <c r="H43" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I43" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
@@ -2686,13 +2686,13 @@
         <v>46661</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G44" t="s">
         <v>138</v>
       </c>
       <c r="H44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I44" s="20">
         <v>0.4</v>
@@ -2716,7 +2716,7 @@
         <v>190</v>
       </c>
       <c r="H45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I45" s="20">
         <v>0.4</v>
@@ -2727,7 +2727,7 @@
         <v>12</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>41</v>
@@ -2740,7 +2740,7 @@
         <v>190</v>
       </c>
       <c r="H46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I46" s="20">
         <v>0.4</v>
@@ -2751,7 +2751,7 @@
         <v>12</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -2762,7 +2762,7 @@
         <v>190</v>
       </c>
       <c r="H47" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I47" s="20">
         <v>0.7</v>
@@ -2786,7 +2786,7 @@
         <v>190</v>
       </c>
       <c r="H48" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I48" s="20">
         <v>1</v>
@@ -2797,7 +2797,7 @@
         <v>12</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>22</v>
@@ -2810,7 +2810,7 @@
         <v>190</v>
       </c>
       <c r="H49" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I49" s="20">
         <v>0.4</v>
@@ -2834,7 +2834,7 @@
         <v>190</v>
       </c>
       <c r="H50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I50" s="20">
         <v>0.4</v>
@@ -2845,7 +2845,7 @@
         <v>12</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>117</v>
@@ -2858,18 +2858,18 @@
         <v>190</v>
       </c>
       <c r="H51" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I51" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>100</v>
@@ -2882,7 +2882,7 @@
         <v>190</v>
       </c>
       <c r="H52" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I52" s="20">
         <v>0.4</v>
@@ -2893,7 +2893,7 @@
         <v>12</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>233</v>
+        <v>299</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -2904,7 +2904,7 @@
         <v>190</v>
       </c>
       <c r="H53" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I53" s="20">
         <v>0.4</v>
@@ -2921,7 +2921,7 @@
         <v>110</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E54" s="11">
         <v>46388</v>
@@ -2930,7 +2930,7 @@
         <v>190</v>
       </c>
       <c r="H54" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I54" s="20">
         <v>0.4</v>
@@ -2957,7 +2957,7 @@
         <v>190</v>
       </c>
       <c r="H55" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I55" s="20">
         <v>0.7</v>
@@ -2968,7 +2968,7 @@
         <v>12</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>82</v>
@@ -2981,13 +2981,13 @@
         <v>190</v>
       </c>
       <c r="H56" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I56" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -3002,24 +3002,24 @@
         <v>46388</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G57" t="s">
         <v>190</v>
       </c>
       <c r="H57" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I57" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>119</v>
@@ -3029,13 +3029,13 @@
         <v>46388</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G58" t="s">
         <v>190</v>
       </c>
       <c r="H58" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I58" s="20">
         <v>0.4</v>
@@ -3061,7 +3061,7 @@
         <v>138</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I59" s="20">
         <v>0.4</v>
@@ -3088,7 +3088,7 @@
         <v>138</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I60" s="20">
         <v>1</v>
@@ -3099,7 +3099,7 @@
         <v>13</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>120</v>
@@ -3112,7 +3112,7 @@
         <v>138</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I61" s="20">
         <v>1</v>
@@ -3123,7 +3123,7 @@
         <v>13</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>106</v>
@@ -3136,13 +3136,13 @@
         <v>138</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I62" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>13</v>
       </c>
@@ -3157,19 +3157,19 @@
         <v>46388</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G63" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I63" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>13</v>
       </c>
@@ -3184,19 +3184,19 @@
         <v>46388</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G64" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I64" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>13</v>
       </c>
@@ -3211,13 +3211,13 @@
         <v>46388</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G65" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I65" s="20">
         <v>0.4</v>
@@ -3228,7 +3228,7 @@
         <v>13</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>100</v>
@@ -3238,13 +3238,13 @@
         <v>46388</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G66" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I66" s="20">
         <v>0.4</v>
@@ -3270,7 +3270,7 @@
         <v>138</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I67" s="20">
         <v>0.4</v>
@@ -3279,7 +3279,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>13</v>
       </c>
@@ -3290,19 +3290,19 @@
         <v>110</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E68" s="11">
         <v>46388</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G68" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I68" s="20">
         <v>0.4</v>
@@ -3316,7 +3316,7 @@
         <v>13</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -3327,18 +3327,18 @@
         <v>138</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I69" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -3346,13 +3346,13 @@
         <v>46388</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G70" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I70" s="20">
         <v>0.4</v>
@@ -3375,7 +3375,7 @@
         <v>138</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I71" s="20">
         <v>1</v>
@@ -3398,7 +3398,7 @@
         <v>138</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I72" s="20">
         <v>1</v>
@@ -3426,7 +3426,7 @@
         <v>14</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C74" t="s">
         <v>19</v>
@@ -3441,7 +3441,7 @@
         <v>138</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I74" s="20">
         <v>1</v>
@@ -3467,7 +3467,7 @@
         <v>138</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I75" s="20">
         <v>0.7</v>
@@ -3490,7 +3490,7 @@
         <v>138</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I76" s="20">
         <v>1</v>
@@ -3501,7 +3501,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C77" t="s">
         <v>67</v>
@@ -3513,7 +3513,7 @@
         <v>138</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I77" s="20">
         <v>1</v>
@@ -3536,18 +3536,18 @@
         <v>138</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I78" s="20">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>14</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C79" t="s">
         <v>100</v>
@@ -3559,18 +3559,18 @@
         <v>138</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I79" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>233</v>
+        <v>299</v>
       </c>
       <c r="C80" t="s">
         <v>19</v>
@@ -3582,7 +3582,7 @@
         <v>138</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I80" s="20">
         <v>0.4</v>
@@ -3593,7 +3593,7 @@
         <v>14</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C81" t="s">
         <v>101</v>
@@ -3605,13 +3605,13 @@
         <v>138</v>
       </c>
       <c r="H81" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I81" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -3625,19 +3625,19 @@
         <v>46388</v>
       </c>
       <c r="F82" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G82" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H82" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I82" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -3651,19 +3651,19 @@
         <v>46388</v>
       </c>
       <c r="F83" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G83" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H83" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I83" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -3677,24 +3677,24 @@
         <v>46388</v>
       </c>
       <c r="F84" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G84" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H84" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I84" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C85" t="s">
         <v>105</v>
@@ -3703,13 +3703,13 @@
         <v>46388</v>
       </c>
       <c r="F85" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G85" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H85" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I85" s="20">
         <v>0.4</v>
@@ -3720,7 +3720,7 @@
         <v>15</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C86" t="s">
         <v>120</v>
@@ -3729,10 +3729,10 @@
         <v>46388</v>
       </c>
       <c r="G86" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H86" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I86" s="20">
         <v>1</v>
@@ -3752,10 +3752,10 @@
         <v>46388</v>
       </c>
       <c r="G87" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H87" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I87" s="20">
         <v>1</v>
@@ -3775,10 +3775,10 @@
         <v>46388</v>
       </c>
       <c r="G88" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H88" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I88" s="20">
         <v>0.4</v>
@@ -3795,10 +3795,10 @@
         <v>46388</v>
       </c>
       <c r="G89" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H89" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I89" s="20">
         <v>0.4</v>
@@ -3809,16 +3809,16 @@
         <v>15</v>
       </c>
       <c r="B90" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E90" s="12">
         <v>46388</v>
       </c>
       <c r="G90" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H90" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I90" s="20">
         <v>1</v>
@@ -3835,10 +3835,10 @@
         <v>46388</v>
       </c>
       <c r="G91" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H91" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I91" s="20">
         <v>0.4</v>
@@ -3849,7 +3849,7 @@
         <v>15</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>82</v>
@@ -3858,16 +3858,16 @@
         <v>46388</v>
       </c>
       <c r="G92" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H92" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I92" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -3881,19 +3881,19 @@
         <v>46388</v>
       </c>
       <c r="F93" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G93" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I93" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -3907,13 +3907,13 @@
         <v>46388</v>
       </c>
       <c r="F94" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G94" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H94" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I94" s="20">
         <v>0.4</v>
@@ -3924,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C95" t="s">
         <v>125</v>
@@ -3936,7 +3936,7 @@
         <v>138</v>
       </c>
       <c r="H95" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I95" s="20">
         <v>1</v>
@@ -3959,7 +3959,7 @@
         <v>138</v>
       </c>
       <c r="H96" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I96" s="20">
         <v>0.7</v>
@@ -3982,7 +3982,7 @@
         <v>138</v>
       </c>
       <c r="H97" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I97" s="20">
         <v>0.4</v>
@@ -4005,7 +4005,7 @@
         <v>138</v>
       </c>
       <c r="H98" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I98" s="20">
         <v>0.4</v>
@@ -4028,7 +4028,7 @@
         <v>138</v>
       </c>
       <c r="H99" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I99" s="20">
         <v>0.4</v>
@@ -4051,7 +4051,7 @@
         <v>138</v>
       </c>
       <c r="H100" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I100" s="20">
         <v>0.7</v>
@@ -4062,7 +4062,7 @@
         <v>16</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C101" t="s">
         <v>101</v>
@@ -4074,7 +4074,7 @@
         <v>138</v>
       </c>
       <c r="H101" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I101" s="20">
         <v>0.4</v>
@@ -4097,7 +4097,7 @@
         <v>138</v>
       </c>
       <c r="H102" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I102" s="20">
         <v>0.4</v>
@@ -4108,7 +4108,7 @@
         <v>16</v>
       </c>
       <c r="B103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C103" t="s">
         <v>89</v>
@@ -4120,13 +4120,13 @@
         <v>138</v>
       </c>
       <c r="H103" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="I103" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+      <c r="I103" s="20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -4140,13 +4140,13 @@
         <v>46631</v>
       </c>
       <c r="F104" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G104" s="18" t="s">
         <v>138</v>
       </c>
       <c r="H104" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I104" s="20">
         <v>0.4</v>
@@ -4157,7 +4157,7 @@
         <v>128</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C105" t="s">
         <v>129</v>
@@ -4166,10 +4166,10 @@
         <v>46631</v>
       </c>
       <c r="G105" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H105" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I105" s="20">
         <v>0.4</v>
@@ -4189,10 +4189,10 @@
         <v>46631</v>
       </c>
       <c r="G106" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H106" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I106" s="20">
         <v>0.4</v>
@@ -4212,10 +4212,10 @@
         <v>46631</v>
       </c>
       <c r="G107" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H107" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I107" s="20">
         <v>0.4</v>
@@ -4226,7 +4226,7 @@
         <v>128</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C108" t="s">
         <v>101</v>
@@ -4235,10 +4235,10 @@
         <v>46631</v>
       </c>
       <c r="G108" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H108" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I108" s="20">
         <v>0.4</v>
@@ -4246,19 +4246,19 @@
     </row>
     <row r="109" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E109" s="12">
         <v>46296</v>
       </c>
       <c r="G109" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H109" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I109" s="20">
         <v>0.4</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="110" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>222</v>
@@ -4275,10 +4275,10 @@
         <v>46296</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H110" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I110" s="20">
         <v>0.4</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="111" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B111" t="s">
         <v>221</v>
@@ -4295,10 +4295,10 @@
         <v>46296</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H111" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I111" s="20">
         <v>1</v>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="112" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B112" t="s">
         <v>225</v>
@@ -4318,10 +4318,10 @@
         <v>46296</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H112" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I112" s="20">
         <v>0.7</v>
@@ -4329,7 +4329,7 @@
     </row>
     <row r="113" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B113" t="s">
         <v>230</v>
@@ -4338,10 +4338,10 @@
         <v>46569</v>
       </c>
       <c r="G113" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H113" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I113" s="20">
         <v>0.4</v>
@@ -4349,19 +4349,19 @@
     </row>
     <row r="114" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B114" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E114" s="12">
         <v>46569</v>
       </c>
       <c r="G114" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H114" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I114" s="20">
         <v>0.4</v>
@@ -4369,7 +4369,7 @@
     </row>
     <row r="115" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>231</v>
@@ -4378,21 +4378,21 @@
         <v>46569</v>
       </c>
       <c r="G115" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H115" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I115" s="20">
         <v>0.4</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C116" t="s">
         <v>100</v>
@@ -4401,10 +4401,10 @@
         <v>46569</v>
       </c>
       <c r="G116" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H116" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I116" s="20">
         <v>0.4</v>
@@ -4412,22 +4412,22 @@
     </row>
     <row r="117" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B117" t="s">
         <v>225</v>
       </c>
       <c r="C117" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E117" s="12">
         <v>46569</v>
       </c>
       <c r="G117" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H117" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I117" s="20">
         <v>0.4</v>
@@ -4435,19 +4435,19 @@
     </row>
     <row r="118" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E118" s="12">
         <v>46569</v>
       </c>
       <c r="G118" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H118" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I118" s="20">
         <v>0.4</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="119" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C119" t="s">
         <v>22</v>
@@ -4470,7 +4470,7 @@
         <v>190</v>
       </c>
       <c r="H119" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I119" s="20">
         <v>0.4</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="120" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>222</v>
@@ -4493,7 +4493,7 @@
         <v>190</v>
       </c>
       <c r="H120" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I120" s="20">
         <v>0.7</v>
@@ -4501,13 +4501,13 @@
     </row>
     <row r="121" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B121" t="s">
         <v>221</v>
       </c>
       <c r="C121" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E121" s="12">
         <v>46569</v>
@@ -4516,7 +4516,7 @@
         <v>190</v>
       </c>
       <c r="H121" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I121" s="20">
         <v>0.4</v>
@@ -4524,13 +4524,13 @@
     </row>
     <row r="122" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B122" t="s">
         <v>225</v>
       </c>
       <c r="C122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E122" s="12">
         <v>46569</v>
@@ -4540,7 +4540,7 @@
         <v>190</v>
       </c>
       <c r="H122" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I122" s="20">
         <v>0.4</v>
@@ -4548,19 +4548,19 @@
     </row>
     <row r="123" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E123" s="12">
         <v>46388</v>
       </c>
       <c r="G123" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I123" s="20">
         <v>0.4</v>
@@ -4568,7 +4568,7 @@
     </row>
     <row r="124" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>222</v>
@@ -4577,10 +4577,10 @@
         <v>46388</v>
       </c>
       <c r="G124" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I124" s="20">
         <v>0.4</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="125" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B125" t="s">
         <v>221</v>
@@ -4597,10 +4597,10 @@
         <v>46388</v>
       </c>
       <c r="G125" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H125" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I125" s="20">
         <v>1</v>
@@ -4608,7 +4608,7 @@
     </row>
     <row r="126" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>231</v>
@@ -4617,10 +4617,10 @@
         <v>46388</v>
       </c>
       <c r="G126" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H126" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I126" s="20">
         <v>0.4</v>
@@ -4628,10 +4628,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I126" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Group Report"/>
+        <filter val="RE"/>
+      </filters>
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -7181,7 +7182,7 @@
         <v>162</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>7</v>
@@ -7204,7 +7205,7 @@
         <v>162</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>7</v>
@@ -7227,7 +7228,7 @@
         <v>162</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>7</v>
@@ -7250,7 +7251,7 @@
         <v>162</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>7</v>
@@ -7273,7 +7274,7 @@
         <v>162</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>7</v>
@@ -8699,7 +8700,7 @@
         <v>162</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>7</v>
@@ -8722,7 +8723,7 @@
         <v>162</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>7</v>
@@ -8745,7 +8746,7 @@
         <v>162</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>7</v>
@@ -8768,7 +8769,7 @@
         <v>162</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>7</v>
@@ -8791,7 +8792,7 @@
         <v>162</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>7</v>
@@ -8820,7 +8821,7 @@
         <v>16</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E119" s="6">
         <v>46181</v>
@@ -8844,7 +8845,7 @@
         <v>16</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E120" s="6">
         <v>46182</v>
@@ -8868,7 +8869,7 @@
         <v>16</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E121" s="6">
         <v>46183</v>
@@ -8892,7 +8893,7 @@
         <v>16</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E122" s="6">
         <v>46184</v>
@@ -8916,7 +8917,7 @@
         <v>16</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E123" s="6">
         <v>46185</v>
@@ -9027,7 +9028,7 @@
     </row>
     <row r="128" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>22</v>
@@ -9036,7 +9037,7 @@
         <v>16</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E128" s="6">
         <v>46188</v>
@@ -9051,7 +9052,7 @@
     </row>
     <row r="129" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>22</v>
@@ -9075,7 +9076,7 @@
     </row>
     <row r="130" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>22</v>
@@ -9084,7 +9085,7 @@
         <v>181</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E130" s="6">
         <v>46190</v>
@@ -9099,16 +9100,16 @@
     </row>
     <row r="131" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E131" s="6">
         <v>46191</v>
@@ -9123,7 +9124,7 @@
     </row>
     <row r="132" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>22</v>
@@ -9132,7 +9133,7 @@
         <v>181</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E132" s="6">
         <v>46192</v>
@@ -9160,7 +9161,9 @@
   <cols>
     <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="30.33203125" customWidth="1"/>
-    <col min="4" max="16384" width="10.83203125" style="9"/>
+    <col min="4" max="9" width="10.83203125" style="9"/>
+    <col min="10" max="10" width="14" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" customFormat="1" x14ac:dyDescent="0.2">
@@ -9168,7 +9171,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D1" s="16" t="s">
         <v>221</v>
@@ -9180,7 +9183,7 @@
         <v>225</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H1" s="16" t="s">
         <v>228</v>
@@ -9210,7 +9213,7 @@
         <v>232</v>
       </c>
       <c r="Q1" s="16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
@@ -9218,7 +9221,7 @@
         <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>227</v>
@@ -9229,7 +9232,7 @@
         <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G3" s="9" t="s">
         <v>227</v>
@@ -9240,7 +9243,7 @@
         <v>195</v>
       </c>
       <c r="C4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>227</v>
@@ -9251,7 +9254,7 @@
         <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>227</v>
@@ -9265,7 +9268,7 @@
         <v>197</v>
       </c>
       <c r="C6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>227</v>
@@ -9279,7 +9282,7 @@
         <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>227</v>
@@ -9293,7 +9296,7 @@
         <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>227</v>
@@ -9304,7 +9307,7 @@
         <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>227</v>
@@ -9315,7 +9318,7 @@
         <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>227</v>
@@ -9332,7 +9335,7 @@
         <v>202</v>
       </c>
       <c r="C11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>227</v>
@@ -9349,7 +9352,7 @@
         <v>203</v>
       </c>
       <c r="C12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>227</v>
@@ -9363,7 +9366,7 @@
         <v>204</v>
       </c>
       <c r="C13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>227</v>
@@ -9377,7 +9380,7 @@
         <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>227</v>
@@ -9385,10 +9388,10 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" t="s">
         <v>248</v>
-      </c>
-      <c r="C15" t="s">
-        <v>249</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>227</v>
@@ -9402,7 +9405,7 @@
         <v>206</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>227</v>
@@ -9413,7 +9416,7 @@
         <v>207</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>227</v>
@@ -9421,10 +9424,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" t="s">
         <v>252</v>
-      </c>
-      <c r="C18" t="s">
-        <v>253</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>227</v>
@@ -9438,7 +9441,7 @@
         <v>208</v>
       </c>
       <c r="C19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>227</v>
@@ -9449,7 +9452,7 @@
         <v>209</v>
       </c>
       <c r="C20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>227</v>
@@ -9466,7 +9469,7 @@
         <v>210</v>
       </c>
       <c r="C21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>227</v>
@@ -9480,7 +9483,7 @@
         <v>211</v>
       </c>
       <c r="C22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>227</v>
@@ -9494,7 +9497,7 @@
         <v>212</v>
       </c>
       <c r="C23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>227</v>
@@ -9505,7 +9508,7 @@
         <v>213</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>227</v>
@@ -9516,7 +9519,7 @@
         <v>214</v>
       </c>
       <c r="C25" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>227</v>
@@ -9524,13 +9527,13 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>227</v>
@@ -9538,13 +9541,13 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>227</v>
@@ -9555,13 +9558,13 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>227</v>
@@ -9569,13 +9572,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B29" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C29" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>227</v>
@@ -9583,13 +9586,13 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B30" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C30" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>227</v>
@@ -9597,13 +9600,13 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>227</v>
@@ -9611,13 +9614,13 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>227</v>
@@ -9625,13 +9628,13 @@
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C33" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>227</v>
@@ -9639,13 +9642,13 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B34" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>227</v>
@@ -9653,13 +9656,13 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C35" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>227</v>
@@ -9667,13 +9670,13 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C36" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>227</v>
@@ -9681,13 +9684,13 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>227</v>
@@ -9695,13 +9698,13 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>227</v>
@@ -9709,13 +9712,13 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C39" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>227</v>
@@ -9723,13 +9726,13 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>227</v>
@@ -9737,13 +9740,13 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C41" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>227</v>
@@ -9751,13 +9754,13 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C42" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>227</v>
@@ -9765,13 +9768,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C43" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>227</v>
@@ -9782,7 +9785,7 @@
         <v>215</v>
       </c>
       <c r="C44" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>227</v>
@@ -9793,7 +9796,7 @@
         <v>216</v>
       </c>
       <c r="C45" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>227</v>
@@ -9804,7 +9807,7 @@
         <v>217</v>
       </c>
       <c r="C46" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>227</v>
@@ -9815,7 +9818,7 @@
         <v>218</v>
       </c>
       <c r="C47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G47" s="9" t="s">
         <v>227</v>
@@ -9826,7 +9829,7 @@
         <v>219</v>
       </c>
       <c r="C48" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K48" s="9" t="s">
         <v>227</v>
@@ -9843,7 +9846,7 @@
         <v>220</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>227</v>
@@ -9854,7 +9857,7 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L50" s="9" t="s">
         <v>227</v>
@@ -9862,10 +9865,10 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>285</v>
+      </c>
+      <c r="C51" t="s">
         <v>286</v>
-      </c>
-      <c r="C51" t="s">
-        <v>287</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>227</v>
@@ -9876,10 +9879,10 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C52" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>227</v>
@@ -9887,10 +9890,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>227</v>
@@ -9898,13 +9901,13 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B54" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C54" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>227</v>
@@ -9939,7 +9942,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
@@ -9949,7 +9952,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3962343E-3352-CA4C-9489-8FA7F994DED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877A70FF-5BF4-AD46-AF22-2716717AB5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Cookpit" sheetId="1" r:id="rId1"/>
@@ -1599,7 +1599,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1647,7 +1646,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1671,7 +1670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1695,7 +1694,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1719,7 +1718,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1743,7 +1742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1767,7 +1766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1791,7 +1790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1815,7 +1814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1840,7 +1839,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1867,7 +1866,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1894,7 +1893,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -1921,7 +1920,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1950,7 +1949,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1979,7 +1978,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -2003,7 +2002,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -2051,7 +2050,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -2075,7 +2074,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -2099,7 +2098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -2147,7 +2146,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -2171,7 +2170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -2195,7 +2194,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -2222,7 +2221,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -2246,7 +2245,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>8</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
@@ -2294,7 +2293,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -2318,7 +2317,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -2340,7 +2339,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>10</v>
       </c>
@@ -2364,7 +2363,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -2386,7 +2385,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -2410,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
@@ -2434,7 +2433,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -2482,7 +2481,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
@@ -2509,7 +2508,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
@@ -2536,7 +2535,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
@@ -2553,7 +2552,7 @@
       <c r="F38" s="21"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
@@ -2577,7 +2576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -2623,7 +2622,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
@@ -2647,7 +2646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
@@ -2671,7 +2670,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
@@ -2698,7 +2697,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -2722,7 +2721,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>12</v>
       </c>
@@ -2746,7 +2745,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
@@ -2768,7 +2767,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>12</v>
       </c>
@@ -2792,7 +2791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -2816,7 +2815,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>12</v>
       </c>
@@ -2840,7 +2839,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>12</v>
       </c>
@@ -2888,7 +2887,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>12</v>
       </c>
@@ -2910,7 +2909,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
@@ -2939,7 +2938,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -2963,7 +2962,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -3014,7 +3013,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -3041,7 +3040,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>13</v>
       </c>
@@ -3070,7 +3069,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>13</v>
       </c>
@@ -3094,7 +3093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>13</v>
       </c>
@@ -3118,7 +3117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>13</v>
       </c>
@@ -3142,7 +3141,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>13</v>
       </c>
@@ -3169,7 +3168,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>13</v>
       </c>
@@ -3196,7 +3195,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>13</v>
       </c>
@@ -3250,7 +3249,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>13</v>
       </c>
@@ -3279,7 +3278,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>13</v>
       </c>
@@ -3311,7 +3310,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>13</v>
       </c>
@@ -3333,7 +3332,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>13</v>
       </c>
@@ -3358,7 +3357,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -3381,7 +3380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -3404,7 +3403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -3421,7 +3420,7 @@
       <c r="H73" s="19"/>
       <c r="I73" s="20"/>
     </row>
-    <row r="74" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -3450,7 +3449,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -3473,7 +3472,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -3496,7 +3495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -3519,7 +3518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -3588,7 +3587,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -3611,7 +3610,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -3637,7 +3636,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -3663,7 +3662,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -3689,7 +3688,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>14</v>
       </c>
@@ -3715,7 +3714,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -3738,7 +3737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -3761,7 +3760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -3784,7 +3783,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -3804,7 +3803,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -3824,7 +3823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -3844,7 +3843,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -3867,7 +3866,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -3893,7 +3892,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -3919,7 +3918,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -3942,7 +3941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -3965,7 +3964,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -3988,7 +3987,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -4011,7 +4010,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -4034,7 +4033,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -4057,7 +4056,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -4080,7 +4079,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -4103,7 +4102,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -4126,7 +4125,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -4152,7 +4151,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>128</v>
       </c>
@@ -4175,7 +4174,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>128</v>
       </c>
@@ -4198,7 +4197,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>128</v>
       </c>
@@ -4221,7 +4220,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>128</v>
       </c>
@@ -4244,7 +4243,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>295</v>
       </c>
@@ -4264,7 +4263,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>295</v>
       </c>
@@ -4284,7 +4283,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>295</v>
       </c>
@@ -4304,7 +4303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>295</v>
       </c>
@@ -4327,7 +4326,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>295</v>
       </c>
@@ -4347,7 +4346,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>295</v>
       </c>
@@ -4367,7 +4366,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>295</v>
       </c>
@@ -4410,7 +4409,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>295</v>
       </c>
@@ -4433,7 +4432,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>295</v>
       </c>
@@ -4453,7 +4452,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>293</v>
       </c>
@@ -4476,7 +4475,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>293</v>
       </c>
@@ -4499,7 +4498,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>293</v>
       </c>
@@ -4522,7 +4521,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>293</v>
       </c>
@@ -4546,7 +4545,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>308</v>
       </c>
@@ -4566,7 +4565,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>308</v>
       </c>
@@ -4586,7 +4585,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>308</v>
       </c>
@@ -4606,7 +4605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>308</v>
       </c>
@@ -4627,14 +4626,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I126" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Group Report"/>
-        <filter val="RE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877A70FF-5BF4-AD46-AF22-2716717AB5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B311DF99-06AC-454B-803D-EB78778F356D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="354">
   <si>
     <t>Projeto</t>
   </si>
@@ -1100,7 +1100,10 @@
     <t>Vinicius Diniz Cabral</t>
   </si>
   <si>
-    <t>xx</t>
+    <t>Amauri José Falconi Pelisson</t>
+  </si>
+  <si>
+    <t>amauri.pelisson@numenit.com</t>
   </si>
 </sst>
 </file>
@@ -1599,13 +1602,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="1" max="1" width="64.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="66.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7" bestFit="1" customWidth="1"/>
@@ -1646,7 +1650,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1670,7 +1674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1694,7 +1698,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1718,7 +1722,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1739,10 +1743,10 @@
         <v>323</v>
       </c>
       <c r="I5" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1766,7 +1770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1787,10 +1791,10 @@
         <v>323</v>
       </c>
       <c r="I7" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1811,10 +1815,10 @@
         <v>323</v>
       </c>
       <c r="I8" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1839,7 +1843,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1866,7 +1870,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1893,7 +1897,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -1920,7 +1924,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1949,7 +1953,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1978,7 +1982,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -2002,7 +2006,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2026,7 +2030,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -2050,7 +2054,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -2074,7 +2078,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -2098,7 +2102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -2122,7 +2126,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -2146,7 +2150,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -2170,7 +2174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -2194,7 +2198,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -2221,7 +2225,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -2245,7 +2249,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>8</v>
       </c>
@@ -2269,7 +2273,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
@@ -2293,7 +2297,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -2317,7 +2321,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -2363,7 +2367,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -2385,7 +2389,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -2409,7 +2413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
@@ -2433,7 +2437,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -2457,7 +2461,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
@@ -2481,7 +2485,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
@@ -2508,7 +2512,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
@@ -2550,9 +2554,17 @@
         <v>46388</v>
       </c>
       <c r="F38" s="21"/>
-      <c r="I38" s="20"/>
-    </row>
-    <row r="39" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G38" t="s">
+        <v>138</v>
+      </c>
+      <c r="H38" t="s">
+        <v>321</v>
+      </c>
+      <c r="I38" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
@@ -2576,7 +2588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -2598,7 +2610,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -2622,7 +2634,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
@@ -2646,7 +2658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
@@ -2670,7 +2682,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
@@ -2697,7 +2709,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -2721,7 +2733,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>12</v>
       </c>
@@ -2745,7 +2757,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
@@ -2767,7 +2779,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>12</v>
       </c>
@@ -2815,7 +2827,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>12</v>
       </c>
@@ -2839,7 +2851,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>12</v>
       </c>
@@ -2863,7 +2875,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
@@ -2887,7 +2899,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>12</v>
       </c>
@@ -2909,7 +2921,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
@@ -2938,7 +2950,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -2962,7 +2974,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -2986,7 +2998,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -3013,7 +3025,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -3040,7 +3052,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>13</v>
       </c>
@@ -3069,7 +3081,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>13</v>
       </c>
@@ -3093,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>13</v>
       </c>
@@ -3117,7 +3129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>13</v>
       </c>
@@ -3141,7 +3153,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>13</v>
       </c>
@@ -3168,7 +3180,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>13</v>
       </c>
@@ -3195,7 +3207,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>13</v>
       </c>
@@ -3222,7 +3234,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>13</v>
       </c>
@@ -3249,7 +3261,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>13</v>
       </c>
@@ -3278,7 +3290,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>13</v>
       </c>
@@ -3307,10 +3319,10 @@
         <v>0.4</v>
       </c>
       <c r="J68">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>13</v>
       </c>
@@ -3332,7 +3344,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>13</v>
       </c>
@@ -3357,7 +3369,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -3380,7 +3392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -3403,7 +3415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -3416,11 +3428,17 @@
       <c r="E73" s="11">
         <v>46388</v>
       </c>
-      <c r="G73" s="18"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="20"/>
-    </row>
-    <row r="74" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G73" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="H73" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="I73" s="20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -3443,7 +3461,7 @@
         <v>323</v>
       </c>
       <c r="I74" s="20">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J74">
         <v>0.4</v>
@@ -3472,7 +3490,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -3495,7 +3513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -3518,7 +3536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -3541,7 +3559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>14</v>
       </c>
@@ -3564,7 +3582,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -3587,7 +3605,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -3610,7 +3628,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -3636,7 +3654,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -3662,7 +3680,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -3688,7 +3706,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>14</v>
       </c>
@@ -3714,7 +3732,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -3737,7 +3755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -3760,7 +3778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -3783,7 +3801,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -3803,7 +3821,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -3823,7 +3841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -3843,7 +3861,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -3866,7 +3884,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -3892,7 +3910,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -3918,7 +3936,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -3941,7 +3959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -3964,7 +3982,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -3987,7 +4005,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -4033,7 +4051,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -4056,7 +4074,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -4079,7 +4097,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -4102,7 +4120,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -4121,11 +4139,11 @@
       <c r="H103" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="I103" s="20" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I103" s="20">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -4151,7 +4169,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>128</v>
       </c>
@@ -4174,7 +4192,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>128</v>
       </c>
@@ -4197,7 +4215,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>128</v>
       </c>
@@ -4220,7 +4238,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>128</v>
       </c>
@@ -4243,7 +4261,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>295</v>
       </c>
@@ -4263,7 +4281,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>295</v>
       </c>
@@ -4283,7 +4301,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>295</v>
       </c>
@@ -4303,7 +4321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>295</v>
       </c>
@@ -4326,7 +4344,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>295</v>
       </c>
@@ -4346,7 +4364,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>295</v>
       </c>
@@ -4366,7 +4384,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>295</v>
       </c>
@@ -4386,7 +4404,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>295</v>
       </c>
@@ -4409,7 +4427,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>295</v>
       </c>
@@ -4432,7 +4450,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>295</v>
       </c>
@@ -4475,7 +4493,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>293</v>
       </c>
@@ -4498,7 +4516,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>293</v>
       </c>
@@ -4521,7 +4539,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>293</v>
       </c>
@@ -4545,7 +4563,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>308</v>
       </c>
@@ -4565,7 +4583,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>308</v>
       </c>
@@ -4585,7 +4603,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>308</v>
       </c>
@@ -4605,7 +4623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>308</v>
       </c>
@@ -4626,7 +4644,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I126" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Beatriz Chamon Reis Libardi &lt;beatriz.libardi@numenit.com&gt;"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9148,7 +9172,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19289A2C-A77A-0743-A158-A32EED5567A2}">
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.5" bestFit="1" customWidth="1"/>
@@ -9158,7 +9182,7 @@
     <col min="11" max="16384" width="10.83203125" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="16" t="s">
         <v>17</v>
       </c>
@@ -9207,8 +9231,11 @@
       <c r="Q1" s="16" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R1" s="16" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>193</v>
       </c>
@@ -9218,8 +9245,9 @@
       <c r="D2" s="9" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R2" s="13"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>194</v>
       </c>
@@ -9230,7 +9258,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>195</v>
       </c>
@@ -9241,7 +9269,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>196</v>
       </c>
@@ -9255,7 +9283,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>197</v>
       </c>
@@ -9269,7 +9297,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>198</v>
       </c>
@@ -9283,7 +9311,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>199</v>
       </c>
@@ -9294,7 +9322,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>200</v>
       </c>
@@ -9305,7 +9333,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>201</v>
       </c>
@@ -9322,7 +9350,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>202</v>
       </c>
@@ -9339,7 +9367,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>203</v>
       </c>
@@ -9353,7 +9381,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>204</v>
       </c>
@@ -9367,7 +9395,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>205</v>
       </c>
@@ -9378,7 +9406,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>247</v>
       </c>
@@ -9392,7 +9420,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>206</v>
       </c>
@@ -9902,6 +9930,20 @@
         <v>292</v>
       </c>
       <c r="D54" s="9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>352</v>
+      </c>
+      <c r="C55" t="s">
+        <v>353</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>227</v>
       </c>
     </row>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B311DF99-06AC-454B-803D-EB78778F356D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B07449-444D-5840-9380-B6F69F98A402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,9 +18,10 @@
     <sheet name="3-Atividades da Semana " sheetId="7" r:id="rId3"/>
     <sheet name="4 - Recursos" sheetId="9" r:id="rId4"/>
     <sheet name="5 - Vagas" sheetId="10" r:id="rId5"/>
+    <sheet name="Planilha3" sheetId="12" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$I$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-Cookpit'!$A$1:$K$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-Agenda Workshop'!$A$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4 - Recursos'!$A$1:$P$54</definedName>
   </definedNames>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="364">
   <si>
     <t>Projeto</t>
   </si>
@@ -1104,6 +1105,36 @@
   </si>
   <si>
     <t>amauri.pelisson@numenit.com</t>
+  </si>
+  <si>
+    <t>Inicio do projeto</t>
+  </si>
+  <si>
+    <t>AIRFIX - IMPLEMENTAÇÃO SAP CLOUD ERP</t>
+  </si>
+  <si>
+    <t>ADEMICON - IMPLANTAÇÃO S4HANA</t>
+  </si>
+  <si>
+    <t>SUPLEY - IMPLEMENTAÇÃO SAP CLOUD ERP PRIVATE</t>
+  </si>
+  <si>
+    <t>BRASAL - IMPLANTAÇÃO GROW</t>
+  </si>
+  <si>
+    <t>SOLINFTEC - IMPLANTAÇAO S4HANA</t>
+  </si>
+  <si>
+    <t>BRW - IMPLANTAÇÃO SAP S/4HANA (GROW)</t>
+  </si>
+  <si>
+    <t>ITAIPU - SAP CLOUD ERP - IMPLANTAÇÃO DE SOLUÇÕES SAP</t>
+  </si>
+  <si>
+    <t>TUTI EL ROSADO</t>
+  </si>
+  <si>
+    <t>PETMAX - Implantação SAP CLOUD ERP</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1299,6 +1330,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -1603,7 +1636,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="73.5" defaultRowHeight="17" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="64.5" bestFit="1" customWidth="1"/>
@@ -1618,7 +1651,7 @@
     <col min="10" max="10" width="17.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1649,8 +1682,11 @@
       <c r="J1" s="17" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K1" s="17" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1673,8 +1709,11 @@
       <c r="I2" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K2" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1697,8 +1736,11 @@
       <c r="I3" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K3" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1721,8 +1763,11 @@
       <c r="I4" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K4" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1745,8 +1790,11 @@
       <c r="I5" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K5" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1769,8 +1817,11 @@
       <c r="I6" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K6" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1793,8 +1844,11 @@
       <c r="I7" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K7" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1815,10 +1869,13 @@
         <v>323</v>
       </c>
       <c r="I8" s="20">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1842,8 +1899,11 @@
       <c r="I9" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K9" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1869,8 +1929,11 @@
       <c r="I10" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K10" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1896,8 +1959,11 @@
       <c r="I11" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K11" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -1923,8 +1989,11 @@
       <c r="I12" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K12" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1952,8 +2021,11 @@
       <c r="J13">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K13" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1981,8 +2053,11 @@
       <c r="J14">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K14" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -2005,8 +2080,11 @@
       <c r="I15" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K15" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -2029,8 +2107,11 @@
       <c r="I16" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K16" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -2053,8 +2134,11 @@
       <c r="I17" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K17" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -2077,8 +2161,11 @@
       <c r="I18" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K18" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -2101,8 +2188,11 @@
       <c r="I19" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K19" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -2125,8 +2215,11 @@
       <c r="I20" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K20" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -2149,8 +2242,11 @@
       <c r="I21" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K21" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -2173,8 +2269,11 @@
       <c r="I22" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K22" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -2197,8 +2296,11 @@
       <c r="I23" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K23" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -2224,8 +2326,11 @@
       <c r="I24" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K24" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -2248,8 +2353,11 @@
       <c r="I25" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K25" s="22">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>8</v>
       </c>
@@ -2272,8 +2380,11 @@
       <c r="I26" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K26" s="22">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
@@ -2296,8 +2407,11 @@
       <c r="I27" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K27" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -2320,8 +2434,11 @@
       <c r="I28" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K28" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -2342,8 +2459,11 @@
       <c r="I29" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K29" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>10</v>
       </c>
@@ -2366,8 +2486,11 @@
       <c r="I30" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K30" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -2388,8 +2511,11 @@
       <c r="I31" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K31" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -2412,8 +2538,11 @@
       <c r="I32" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K32" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
@@ -2436,8 +2565,11 @@
       <c r="I33" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K33" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -2460,8 +2592,11 @@
       <c r="I34" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K34" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
@@ -2484,8 +2619,11 @@
       <c r="I35" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K35" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
@@ -2511,8 +2649,11 @@
       <c r="I36" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K36" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
@@ -2538,8 +2679,11 @@
       <c r="I37" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K37" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
@@ -2563,8 +2707,11 @@
       <c r="I38" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K38" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
@@ -2587,8 +2734,11 @@
       <c r="I39" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K39" s="22">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -2609,8 +2759,11 @@
       <c r="I40" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K40" s="22">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -2633,8 +2786,11 @@
       <c r="I41" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K41" s="22">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
@@ -2657,8 +2813,11 @@
       <c r="I42" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K42" s="22">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
@@ -2681,8 +2840,11 @@
       <c r="I43" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K43" s="22">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
@@ -2708,8 +2870,11 @@
       <c r="I44" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K44" s="22">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -2732,8 +2897,11 @@
       <c r="I45" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K45" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>12</v>
       </c>
@@ -2756,8 +2924,11 @@
       <c r="I46" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K46" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
@@ -2778,8 +2949,11 @@
       <c r="I47" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K47" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>12</v>
       </c>
@@ -2802,8 +2976,11 @@
       <c r="I48" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K48" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -2826,8 +3003,11 @@
       <c r="I49" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K49" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>12</v>
       </c>
@@ -2850,8 +3030,11 @@
       <c r="I50" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K50" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>12</v>
       </c>
@@ -2874,8 +3057,11 @@
       <c r="I51" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K51" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
@@ -2898,8 +3084,11 @@
       <c r="I52" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K52" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>12</v>
       </c>
@@ -2920,8 +3109,11 @@
       <c r="I53" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K53" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
@@ -2949,8 +3141,11 @@
       <c r="J54">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K54" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -2973,8 +3168,11 @@
       <c r="I55" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K55" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -2997,8 +3195,11 @@
       <c r="I56" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K56" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -3024,8 +3225,11 @@
       <c r="I57" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K57" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -3051,8 +3255,11 @@
       <c r="I58" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K58" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>13</v>
       </c>
@@ -3081,7 +3288,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>13</v>
       </c>
@@ -3105,7 +3312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>13</v>
       </c>
@@ -3129,7 +3336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>13</v>
       </c>
@@ -3153,7 +3360,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>13</v>
       </c>
@@ -3180,7 +3387,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>13</v>
       </c>
@@ -3207,7 +3414,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>13</v>
       </c>
@@ -3234,7 +3441,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>13</v>
       </c>
@@ -3261,7 +3468,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>13</v>
       </c>
@@ -3290,7 +3497,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>13</v>
       </c>
@@ -3322,7 +3529,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>13</v>
       </c>
@@ -3344,7 +3551,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>13</v>
       </c>
@@ -3369,7 +3576,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -3391,8 +3598,11 @@
       <c r="I71" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K71" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -3414,8 +3624,11 @@
       <c r="I72" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K72" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -3438,7 +3651,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -3466,8 +3679,11 @@
       <c r="J74">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K74" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -3489,8 +3705,11 @@
       <c r="I75" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K75" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -3512,8 +3731,11 @@
       <c r="I76" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K76" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -3535,8 +3757,11 @@
       <c r="I77" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K77" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -3558,8 +3783,11 @@
       <c r="I78" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K78" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>14</v>
       </c>
@@ -3581,8 +3809,11 @@
       <c r="I79" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K79" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -3604,8 +3835,11 @@
       <c r="I80" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K80" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -3627,8 +3861,11 @@
       <c r="I81" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K81" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -3653,8 +3890,11 @@
       <c r="I82" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K82" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -3679,8 +3919,11 @@
       <c r="I83" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K83" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -3705,8 +3948,11 @@
       <c r="I84" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K84" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>14</v>
       </c>
@@ -3731,8 +3977,11 @@
       <c r="I85" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K85" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -3754,8 +4003,11 @@
       <c r="I86" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K86" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -3777,8 +4029,11 @@
       <c r="I87" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K87" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>15</v>
       </c>
@@ -3800,8 +4055,11 @@
       <c r="I88" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K88" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>15</v>
       </c>
@@ -3820,8 +4078,11 @@
       <c r="I89" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K89" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>15</v>
       </c>
@@ -3840,8 +4101,11 @@
       <c r="I90" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K90" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>15</v>
       </c>
@@ -3860,8 +4124,11 @@
       <c r="I91" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K91" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -3883,8 +4150,11 @@
       <c r="I92" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K92" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>15</v>
       </c>
@@ -3909,8 +4179,11 @@
       <c r="I93" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K93" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>15</v>
       </c>
@@ -3935,8 +4208,11 @@
       <c r="I94" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K94" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -3958,8 +4234,11 @@
       <c r="I95" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K95" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -3981,8 +4260,11 @@
       <c r="I96" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K96" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -4004,8 +4286,11 @@
       <c r="I97" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K97" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -4027,8 +4312,11 @@
       <c r="I98" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K98" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -4050,8 +4338,11 @@
       <c r="I99" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K99" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -4073,8 +4364,11 @@
       <c r="I100" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K100" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -4096,8 +4390,11 @@
       <c r="I101" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K101" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -4119,8 +4416,11 @@
       <c r="I102" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K102" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -4142,8 +4442,11 @@
       <c r="I103" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K103" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -4168,8 +4471,11 @@
       <c r="I104" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K104" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>128</v>
       </c>
@@ -4191,8 +4497,11 @@
       <c r="I105" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K105" s="23">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>128</v>
       </c>
@@ -4214,8 +4523,11 @@
       <c r="I106" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K106" s="23">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>128</v>
       </c>
@@ -4237,8 +4549,11 @@
       <c r="I107" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K107" s="23">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>128</v>
       </c>
@@ -4260,8 +4575,11 @@
       <c r="I108" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K108" s="23">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>295</v>
       </c>
@@ -4280,8 +4598,11 @@
       <c r="I109" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K109" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>295</v>
       </c>
@@ -4300,8 +4621,11 @@
       <c r="I110" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K110" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>295</v>
       </c>
@@ -4320,8 +4644,11 @@
       <c r="I111" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K111" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>295</v>
       </c>
@@ -4343,8 +4670,11 @@
       <c r="I112" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K112" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>295</v>
       </c>
@@ -4363,8 +4693,11 @@
       <c r="I113" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K113" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>295</v>
       </c>
@@ -4383,8 +4716,11 @@
       <c r="I114" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K114" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>295</v>
       </c>
@@ -4403,8 +4739,11 @@
       <c r="I115" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K115" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>295</v>
       </c>
@@ -4426,8 +4765,11 @@
       <c r="I116" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K116" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>295</v>
       </c>
@@ -4449,8 +4791,11 @@
       <c r="I117" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K117" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>295</v>
       </c>
@@ -4469,8 +4814,11 @@
       <c r="I118" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K118" s="23">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>293</v>
       </c>
@@ -4492,8 +4840,11 @@
       <c r="I119" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K119" s="22">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>293</v>
       </c>
@@ -4515,8 +4866,11 @@
       <c r="I120" s="20">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="121" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K120" s="22">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>293</v>
       </c>
@@ -4538,8 +4892,11 @@
       <c r="I121" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K121" s="22">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>293</v>
       </c>
@@ -4562,8 +4919,11 @@
       <c r="I122" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K122" s="22">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>308</v>
       </c>
@@ -4582,8 +4942,11 @@
       <c r="I123" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K123" s="23">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>308</v>
       </c>
@@ -4602,8 +4965,11 @@
       <c r="I124" s="20">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="125" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K124" s="22">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>308</v>
       </c>
@@ -4622,8 +4988,11 @@
       <c r="I125" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K125" s="22">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>308</v>
       </c>
@@ -4642,12 +5011,17 @@
       <c r="I126" s="20">
         <v>0.4</v>
       </c>
+      <c r="K126" s="22">
+        <v>46174</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I126" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
+  <autoFilter ref="A1:K126" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Beatriz Chamon Reis Libardi &lt;beatriz.libardi@numenit.com&gt;"/>
+        <filter val="4791 - TUTI EL ROSADO"/>
+        <filter val="4886 - PRINCIPIA COSMÉTICOS"/>
+        <filter val="5258 - PETMAX"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -9997,4 +10371,121 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705A791F-CD64-2F46-9CFD-C384032F6C15}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="47" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B1" s="22">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B2" s="22">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B3" s="22">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" s="22">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B5" s="22">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B6" s="22">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="22">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="22">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="22">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="22">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>361</v>
+      </c>
+      <c r="B11" s="22">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B12" s="22">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>363</v>
+      </c>
+      <c r="B13" s="22">
+        <v>46174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B07449-444D-5840-9380-B6F69F98A402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89FB63F-C193-4F49-97F3-62B8C195F546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>13</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>323</v>
       </c>
       <c r="I73" s="20">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3981,7 +3981,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>46140</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>16</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>16</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>16</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>16</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>16</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>16</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>16</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>16</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>16</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>46148</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>128</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>128</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>128</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>128</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>308</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>46193</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>308</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>308</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>308</v>
       </c>
@@ -5017,11 +5017,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K126" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
+    <filterColumn colId="2">
       <filters>
-        <filter val="4791 - TUTI EL ROSADO"/>
-        <filter val="4886 - PRINCIPIA COSMÉTICOS"/>
-        <filter val="5258 - PETMAX"/>
+        <filter val="Julio Cesar Alves Pacheco &lt;julio.pacheco@numenit.com&gt;"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/alocacao_controle_otimizado.xlsx
+++ b/alocacao_controle_otimizado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanna/Documents/Visao_Alocacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89FB63F-C193-4F49-97F3-62B8C195F546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3BDC44-DEC5-AE48-81E4-04D42CA57083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>13</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>13</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>46120</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" ht="17" hidden=